--- a/docs/301_鍵盤設計規格_方音符號輸入_台語注音二式編碼.xlsx
+++ b/docs/301_鍵盤設計規格_方音符號輸入_台語注音二式編碼.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08A9868-7343-4CE9-A940-A21D38A0D13C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE221F7B-6F12-4247-B621-549A8BB202EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="3" xr2:uid="{6D6F034E-466E-416C-B3CC-1F7937B8DE3D}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6D6F034E-466E-416C-B3CC-1F7937B8DE3D}"/>
   </bookViews>
   <sheets>
     <sheet name="台語注音二式【xlit解析】" sheetId="7" r:id="rId1"/>
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2220" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2220" uniqueCount="570">
   <si>
     <t>algebra:</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -2139,10 +2139,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>zi</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -2160,6 +2156,21 @@
   </si>
   <si>
     <t>./finals</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ø</t>
+  </si>
+  <si>
+    <t>Ø</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>=</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -2170,7 +2181,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="General;;"/>
   </numFmts>
-  <fonts count="119">
+  <fonts count="122">
     <font>
       <sz val="16"/>
       <color rgb="FF000000"/>
@@ -2964,6 +2975,29 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF7030A0"/>
+      <name val="Noto Sans TC Medium"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF7030A0"/>
+      <name val="Noto Sans TC Medium"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color rgb="FFFF0000"/>
+      <name val="KangXiZiDian.com 康熙字典體常用版"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -3428,7 +3462,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="279">
+  <cellXfs count="284">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4096,42 +4130,6 @@
     <xf numFmtId="0" fontId="108" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="101" fillId="29" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="29" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="29" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="30" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="30" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="30" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="30" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="30" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="30" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="30" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="30" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -4162,17 +4160,68 @@
     <xf numFmtId="176" fontId="116" fillId="9" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="21" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="118" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="118" fillId="9" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="21" fillId="9" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="118" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="100" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="118" fillId="9" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="100" fillId="30" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="30" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="30" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="30" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="30" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="30" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="30" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="30" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="29" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="29" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="29" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="121" fillId="9" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -12169,19 +12218,19 @@
       <c r="W3" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="X3" s="277" t="s">
+      <c r="X3" s="263" t="s">
         <v>542</v>
       </c>
-      <c r="Y3" s="278" t="s">
+      <c r="Y3" s="264" t="s">
         <v>40</v>
       </c>
       <c r="Z3" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="AA3" s="277" t="s">
+      <c r="AA3" s="263" t="s">
         <v>547</v>
       </c>
-      <c r="AB3" s="278"/>
+      <c r="AB3" s="264"/>
       <c r="AC3" s="52"/>
       <c r="AD3" s="49"/>
       <c r="AE3" s="53"/>
@@ -12232,39 +12281,39 @@
       <c r="G4" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="267" t="s">
+      <c r="H4" s="255" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="268"/>
-      <c r="J4" s="269" t="s">
+      <c r="I4" s="256"/>
+      <c r="J4" s="257" t="s">
         <v>48</v>
       </c>
-      <c r="K4" s="270" t="s">
+      <c r="K4" s="258" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="271"/>
-      <c r="M4" s="269" t="s">
+      <c r="L4" s="259"/>
+      <c r="M4" s="257" t="s">
         <v>50</v>
       </c>
-      <c r="N4" s="267" t="s">
+      <c r="N4" s="255" t="s">
         <v>51</v>
       </c>
-      <c r="O4" s="268"/>
-      <c r="P4" s="269" t="s">
+      <c r="O4" s="256"/>
+      <c r="P4" s="257" t="s">
         <v>52</v>
       </c>
-      <c r="Q4" s="270" t="s">
+      <c r="Q4" s="258" t="s">
         <v>53</v>
       </c>
-      <c r="R4" s="271"/>
-      <c r="S4" s="269" t="s">
+      <c r="R4" s="259"/>
+      <c r="S4" s="257" t="s">
         <v>54</v>
       </c>
-      <c r="T4" s="270" t="s">
+      <c r="T4" s="258" t="s">
         <v>55</v>
       </c>
-      <c r="U4" s="268"/>
-      <c r="V4" s="269" t="s">
+      <c r="U4" s="256"/>
+      <c r="V4" s="257" t="s">
         <v>557</v>
       </c>
       <c r="W4" s="66" t="s">
@@ -12488,7 +12537,7 @@
         <f xml:space="preserve"> ROW() - 4</f>
         <v>1</v>
       </c>
-      <c r="BO5" s="265" t="str" cm="1">
+      <c r="BO5" s="253" t="str" cm="1">
         <f t="array" ref="BO5:BR62" xml:space="preserve"> TRANSPOSE(D17:BI20)</f>
         <v>b</v>
       </c>
@@ -12631,7 +12680,7 @@
       </c>
       <c r="M6" s="38"/>
       <c r="N6" s="98" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="O6" s="97"/>
       <c r="P6" s="99"/>
@@ -12646,28 +12695,28 @@
       <c r="U6" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="V6" s="277" t="s">
+      <c r="V6" s="263" t="s">
         <v>543</v>
       </c>
-      <c r="W6" s="278" t="s">
+      <c r="W6" s="264" t="s">
         <v>87</v>
       </c>
       <c r="X6" s="48" t="s">
         <v>88</v>
       </c>
-      <c r="Y6" s="275" t="s">
+      <c r="Y6" s="265" t="s">
         <v>546</v>
       </c>
-      <c r="Z6" s="276" t="s">
+      <c r="Z6" s="266" t="s">
         <v>89</v>
       </c>
       <c r="AA6" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="AB6" s="275" t="s">
+      <c r="AB6" s="265" t="s">
         <v>275</v>
       </c>
-      <c r="AC6" s="276"/>
+      <c r="AC6" s="266"/>
       <c r="AD6" s="52"/>
       <c r="AE6" s="49"/>
       <c r="AF6" s="53"/>
@@ -12691,7 +12740,7 @@
         <f t="shared" ref="BN6:BN64" si="4" xml:space="preserve"> ROW() - 4</f>
         <v>2</v>
       </c>
-      <c r="BO6" s="265" t="str">
+      <c r="BO6" s="253" t="str">
         <v>p</v>
       </c>
       <c r="BP6" s="86" t="str">
@@ -12786,13 +12835,13 @@
         <v>2</v>
       </c>
       <c r="CZ6" s="93" t="str">
-        <v>L</v>
+        <v>ⁿ</v>
       </c>
       <c r="DA6" s="91" t="str">
         <v>L</v>
       </c>
       <c r="DB6" s="92" t="str">
-        <v>.</v>
+        <v>-</v>
       </c>
       <c r="DC6" s="77" t="str">
         <v>ㄥ</v>
@@ -12836,7 +12885,7 @@
       </c>
       <c r="M7" s="63"/>
       <c r="N7" s="105" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="O7" s="62" t="s">
         <v>99</v>
@@ -12880,16 +12929,16 @@
       <c r="AF7" s="107" t="s">
         <v>110</v>
       </c>
-      <c r="AG7" s="270"/>
-      <c r="AH7" s="271"/>
-      <c r="AI7" s="272" t="s">
+      <c r="AG7" s="258"/>
+      <c r="AH7" s="259"/>
+      <c r="AI7" s="260" t="s">
         <v>555</v>
       </c>
-      <c r="AJ7" s="270" t="s">
+      <c r="AJ7" s="258" t="s">
         <v>55</v>
       </c>
-      <c r="AK7" s="271"/>
-      <c r="AL7" s="272" t="s">
+      <c r="AK7" s="259"/>
+      <c r="AL7" s="260" t="s">
         <v>554</v>
       </c>
       <c r="AM7" s="69"/>
@@ -12906,7 +12955,7 @@
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="BO7" s="265" t="str">
+      <c r="BO7" s="253" t="str">
         <v>ph</v>
       </c>
       <c r="BP7" s="86" t="str">
@@ -13083,7 +13132,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="BO8" s="265" t="str">
+      <c r="BO8" s="253" t="str">
         <v>m</v>
       </c>
       <c r="BP8" s="86" t="str">
@@ -13211,28 +13260,28 @@
       <c r="V9" s="48" t="s">
         <v>122</v>
       </c>
-      <c r="W9" s="277" t="s">
+      <c r="W9" s="263" t="s">
         <v>544</v>
       </c>
-      <c r="X9" s="278" t="s">
+      <c r="X9" s="264" t="s">
         <v>123</v>
       </c>
       <c r="Y9" s="52" t="s">
         <v>124</v>
       </c>
-      <c r="Z9" s="275" t="s">
+      <c r="Z9" s="265" t="s">
         <v>259</v>
       </c>
-      <c r="AA9" s="276" t="s">
+      <c r="AA9" s="266" t="s">
         <v>125</v>
       </c>
       <c r="AB9" s="48" t="s">
         <v>126</v>
       </c>
-      <c r="AC9" s="275" t="s">
+      <c r="AC9" s="265" t="s">
         <v>127</v>
       </c>
-      <c r="AD9" s="276"/>
+      <c r="AD9" s="266"/>
       <c r="AE9" s="48"/>
       <c r="AF9" s="49"/>
       <c r="AG9" s="50"/>
@@ -13255,7 +13304,7 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="BO9" s="265" t="str">
+      <c r="BO9" s="253" t="str">
         <v>n</v>
       </c>
       <c r="BP9" s="86" t="str">
@@ -13389,7 +13438,7 @@
       </c>
       <c r="N10" s="63"/>
       <c r="O10" s="106" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="P10" s="104" t="s">
         <v>136</v>
@@ -13433,9 +13482,9 @@
       <c r="AG10" s="71" t="s">
         <v>147</v>
       </c>
-      <c r="AH10" s="270"/>
-      <c r="AI10" s="271"/>
-      <c r="AJ10" s="272" t="s">
+      <c r="AH10" s="258"/>
+      <c r="AI10" s="259"/>
+      <c r="AJ10" s="260" t="s">
         <v>556</v>
       </c>
       <c r="AK10" s="61"/>
@@ -13454,7 +13503,7 @@
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="BO10" s="265" t="str">
+      <c r="BO10" s="253" t="str">
         <v>t</v>
       </c>
       <c r="BP10" s="86" t="str">
@@ -13629,7 +13678,7 @@
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="BO11" s="265" t="str">
+      <c r="BO11" s="253" t="str">
         <v>th</v>
       </c>
       <c r="BP11" s="86" t="str">
@@ -13762,22 +13811,22 @@
       <c r="W12" s="48" t="s">
         <v>160</v>
       </c>
-      <c r="X12" s="277" t="s">
+      <c r="X12" s="263" t="s">
         <v>272</v>
       </c>
-      <c r="Y12" s="278" t="s">
+      <c r="Y12" s="264" t="s">
         <v>123</v>
       </c>
       <c r="Z12" s="48" t="s">
         <v>162</v>
       </c>
-      <c r="AA12" s="277" t="s">
+      <c r="AA12" s="263" t="s">
         <v>545</v>
       </c>
-      <c r="AB12" s="278" t="s">
+      <c r="AB12" s="264" t="s">
         <v>123</v>
       </c>
-      <c r="AC12" s="273"/>
+      <c r="AC12" s="261"/>
       <c r="AD12" s="110"/>
       <c r="AE12" s="111"/>
       <c r="AF12" s="112"/>
@@ -13803,7 +13852,7 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="BO12" s="265" t="str">
+      <c r="BO12" s="253" t="str">
         <v>l</v>
       </c>
       <c r="BP12" s="86" t="str">
@@ -13936,7 +13985,7 @@
       </c>
       <c r="O13" s="63"/>
       <c r="P13" s="106" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="Q13" s="104" t="s">
         <v>173</v>
@@ -13968,7 +14017,7 @@
       <c r="AB13" s="71" t="s">
         <v>180</v>
       </c>
-      <c r="AC13" s="274" t="s">
+      <c r="AC13" s="262" t="s">
         <v>558</v>
       </c>
       <c r="AD13" s="67"/>
@@ -14002,7 +14051,7 @@
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="BO13" s="265" t="str">
+      <c r="BO13" s="253" t="str">
         <v>g</v>
       </c>
       <c r="BP13" s="86" t="str">
@@ -14111,7 +14160,7 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="BO14" s="265" t="str">
+      <c r="BO14" s="253" t="str">
         <v>k</v>
       </c>
       <c r="BP14" s="86" t="str">
@@ -14280,7 +14329,7 @@
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="BO15" s="265" t="str">
+      <c r="BO15" s="253" t="str">
         <v>kh</v>
       </c>
       <c r="BP15" s="86" t="str">
@@ -14633,7 +14682,7 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="BO16" s="265" t="str">
+      <c r="BO16" s="253" t="str">
         <v>ng</v>
       </c>
       <c r="BP16" s="86" t="str">
@@ -14939,40 +14988,40 @@
         <v>auⁿ</v>
       </c>
       <c r="BA17" s="134">
+        <f>' 台語音標【xlit解析】'!BB3</f>
+        <v>1</v>
+      </c>
+      <c r="BB17" s="134">
+        <f>' 台語音標【xlit解析】'!BC3</f>
+        <v>7</v>
+      </c>
+      <c r="BC17" s="134">
+        <f>' 台語音標【xlit解析】'!BD3</f>
+        <v>3</v>
+      </c>
+      <c r="BD17" s="134">
+        <f>' 台語音標【xlit解析】'!BE3</f>
+        <v>2</v>
+      </c>
+      <c r="BE17" s="134">
+        <f>' 台語音標【xlit解析】'!BF3</f>
+        <v>5</v>
+      </c>
+      <c r="BF17" s="134">
+        <f>' 台語音標【xlit解析】'!BG3</f>
+        <v>8</v>
+      </c>
+      <c r="BG17" s="134">
+        <f>' 台語音標【xlit解析】'!BH3</f>
+        <v>4</v>
+      </c>
+      <c r="BH17" s="134">
+        <f>' 台語音標【xlit解析】'!BI3</f>
+        <v>0</v>
+      </c>
+      <c r="BI17" s="134" t="str">
         <f>' 台語音標【xlit解析】'!AZ3</f>
-        <v>1</v>
-      </c>
-      <c r="BB17" s="134">
-        <f>' 台語音標【xlit解析】'!BA3</f>
-        <v>7</v>
-      </c>
-      <c r="BC17" s="134">
-        <f>' 台語音標【xlit解析】'!BB3</f>
-        <v>3</v>
-      </c>
-      <c r="BD17" s="134">
-        <f>' 台語音標【xlit解析】'!BC3</f>
-        <v>2</v>
-      </c>
-      <c r="BE17" s="134">
-        <f>' 台語音標【xlit解析】'!BD3</f>
-        <v>5</v>
-      </c>
-      <c r="BF17" s="134">
-        <f>' 台語音標【xlit解析】'!BE3</f>
-        <v>8</v>
-      </c>
-      <c r="BG17" s="134">
-        <f>' 台語音標【xlit解析】'!BF3</f>
-        <v>4</v>
-      </c>
-      <c r="BH17" s="134">
-        <f>' 台語音標【xlit解析】'!BG3</f>
-        <v>0</v>
-      </c>
-      <c r="BI17" s="134" t="str">
-        <f>' 台語音標【xlit解析】'!BH3</f>
-        <v>L</v>
+        <v>ⁿ</v>
       </c>
       <c r="BJ17" s="134"/>
       <c r="BK17" s="134"/>
@@ -14980,7 +15029,7 @@
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="BO17" s="265" t="str">
+      <c r="BO17" s="253" t="str">
         <v>j</v>
       </c>
       <c r="BP17" s="86" t="str">
@@ -15285,39 +15334,39 @@
         <v>y</v>
       </c>
       <c r="BA18" s="124">
+        <f>' 台語音標【xlit解析】'!BB4</f>
+        <v>1</v>
+      </c>
+      <c r="BB18" s="124">
+        <f>' 台語音標【xlit解析】'!BC4</f>
+        <v>7</v>
+      </c>
+      <c r="BC18" s="124">
+        <f>' 台語音標【xlit解析】'!BD4</f>
+        <v>3</v>
+      </c>
+      <c r="BD18" s="124">
+        <f>' 台語音標【xlit解析】'!BE4</f>
+        <v>2</v>
+      </c>
+      <c r="BE18" s="124">
+        <f>' 台語音標【xlit解析】'!BF4</f>
+        <v>5</v>
+      </c>
+      <c r="BF18" s="124">
+        <f>' 台語音標【xlit解析】'!BG4</f>
+        <v>8</v>
+      </c>
+      <c r="BG18" s="124">
+        <f>' 台語音標【xlit解析】'!BH4</f>
+        <v>4</v>
+      </c>
+      <c r="BH18" s="124" t="str">
+        <f>' 台語音標【xlit解析】'!BI4</f>
+        <v>&amp;</v>
+      </c>
+      <c r="BI18" s="124" t="str">
         <f>' 台語音標【xlit解析】'!AZ4</f>
-        <v>1</v>
-      </c>
-      <c r="BB18" s="124">
-        <f>' 台語音標【xlit解析】'!BA4</f>
-        <v>7</v>
-      </c>
-      <c r="BC18" s="124">
-        <f>' 台語音標【xlit解析】'!BB4</f>
-        <v>3</v>
-      </c>
-      <c r="BD18" s="124">
-        <f>' 台語音標【xlit解析】'!BC4</f>
-        <v>2</v>
-      </c>
-      <c r="BE18" s="124">
-        <f>' 台語音標【xlit解析】'!BD4</f>
-        <v>5</v>
-      </c>
-      <c r="BF18" s="124">
-        <f>' 台語音標【xlit解析】'!BE4</f>
-        <v>8</v>
-      </c>
-      <c r="BG18" s="124">
-        <f>' 台語音標【xlit解析】'!BF4</f>
-        <v>4</v>
-      </c>
-      <c r="BH18" s="124" t="str">
-        <f>' 台語音標【xlit解析】'!BG4</f>
-        <v>&amp;</v>
-      </c>
-      <c r="BI18" s="124" t="str">
-        <f>' 台語音標【xlit解析】'!BH4</f>
         <v>L</v>
       </c>
       <c r="BJ18" s="124"/>
@@ -15326,7 +15375,7 @@
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="BO18" s="265" t="str">
+      <c r="BO18" s="253" t="str">
         <v>z(ts)</v>
       </c>
       <c r="BP18" s="86" t="str">
@@ -15631,40 +15680,40 @@
         <v>L</v>
       </c>
       <c r="BA19" s="128" t="str">
+        <f>' 台語音標【xlit解析】'!BB5</f>
+        <v>"</v>
+      </c>
+      <c r="BB19" s="128">
+        <f>' 台語音標【xlit解析】'!BC5</f>
+        <v>5</v>
+      </c>
+      <c r="BC19" s="128">
+        <f>' 台語音標【xlit解析】'!BD5</f>
+        <v>3</v>
+      </c>
+      <c r="BD19" s="128">
+        <f>' 台語音標【xlit解析】'!BE5</f>
+        <v>4</v>
+      </c>
+      <c r="BE19" s="128">
+        <f>' 台語音標【xlit解析】'!BF5</f>
+        <v>6</v>
+      </c>
+      <c r="BF19" s="128" t="str">
+        <f>' 台語音標【xlit解析】'!BG5</f>
+        <v>]</v>
+      </c>
+      <c r="BG19" s="128" t="str">
+        <f>' 台語音標【xlit解析】'!BH5</f>
+        <v>[</v>
+      </c>
+      <c r="BH19" s="128">
+        <f>' 台語音標【xlit解析】'!BI5</f>
+        <v>7</v>
+      </c>
+      <c r="BI19" s="128" t="str">
         <f>' 台語音標【xlit解析】'!AZ5</f>
-        <v>"</v>
-      </c>
-      <c r="BB19" s="128">
-        <f>' 台語音標【xlit解析】'!BA5</f>
-        <v>5</v>
-      </c>
-      <c r="BC19" s="128">
-        <f>' 台語音標【xlit解析】'!BB5</f>
-        <v>3</v>
-      </c>
-      <c r="BD19" s="128">
-        <f>' 台語音標【xlit解析】'!BC5</f>
-        <v>4</v>
-      </c>
-      <c r="BE19" s="128">
-        <f>' 台語音標【xlit解析】'!BD5</f>
-        <v>6</v>
-      </c>
-      <c r="BF19" s="128" t="str">
-        <f>' 台語音標【xlit解析】'!BE5</f>
-        <v>]</v>
-      </c>
-      <c r="BG19" s="128" t="str">
-        <f>' 台語音標【xlit解析】'!BF5</f>
-        <v>[</v>
-      </c>
-      <c r="BH19" s="128">
-        <f>' 台語音標【xlit解析】'!BG5</f>
-        <v>7</v>
-      </c>
-      <c r="BI19" s="128" t="str">
-        <f>' 台語音標【xlit解析】'!BH5</f>
-        <v>.</v>
+        <v>-</v>
       </c>
       <c r="BJ19" s="128"/>
       <c r="BK19" s="128"/>
@@ -15673,7 +15722,7 @@
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="BO19" s="265" t="str">
+      <c r="BO19" s="253" t="str">
         <v>c(tsh)</v>
       </c>
       <c r="BP19" s="86" t="str">
@@ -15978,39 +16027,39 @@
         <v>ㆯ</v>
       </c>
       <c r="BA20" s="131" t="str">
+        <f>' 台語音標【xlit解析】'!BB6</f>
+        <v>一</v>
+      </c>
+      <c r="BB20" s="131" t="str">
+        <f>' 台語音標【xlit解析】'!BC6</f>
+        <v>七</v>
+      </c>
+      <c r="BC20" s="131" t="str">
+        <f>' 台語音標【xlit解析】'!BD6</f>
+        <v>三</v>
+      </c>
+      <c r="BD20" s="131" t="str">
+        <f>' 台語音標【xlit解析】'!BE6</f>
+        <v>二</v>
+      </c>
+      <c r="BE20" s="131" t="str">
+        <f>' 台語音標【xlit解析】'!BF6</f>
+        <v>五</v>
+      </c>
+      <c r="BF20" s="131" t="str">
+        <f>' 台語音標【xlit解析】'!BG6</f>
+        <v>八</v>
+      </c>
+      <c r="BG20" s="131" t="str">
+        <f>' 台語音標【xlit解析】'!BH6</f>
+        <v>四</v>
+      </c>
+      <c r="BH20" s="131" t="str">
+        <f>' 台語音標【xlit解析】'!BI6</f>
+        <v>入</v>
+      </c>
+      <c r="BI20" s="131" t="str">
         <f>' 台語音標【xlit解析】'!AZ6</f>
-        <v>一</v>
-      </c>
-      <c r="BB20" s="131" t="str">
-        <f>' 台語音標【xlit解析】'!BA6</f>
-        <v>七</v>
-      </c>
-      <c r="BC20" s="131" t="str">
-        <f>' 台語音標【xlit解析】'!BB6</f>
-        <v>三</v>
-      </c>
-      <c r="BD20" s="131" t="str">
-        <f>' 台語音標【xlit解析】'!BC6</f>
-        <v>二</v>
-      </c>
-      <c r="BE20" s="131" t="str">
-        <f>' 台語音標【xlit解析】'!BD6</f>
-        <v>五</v>
-      </c>
-      <c r="BF20" s="131" t="str">
-        <f>' 台語音標【xlit解析】'!BE6</f>
-        <v>八</v>
-      </c>
-      <c r="BG20" s="131" t="str">
-        <f>' 台語音標【xlit解析】'!BF6</f>
-        <v>四</v>
-      </c>
-      <c r="BH20" s="131" t="str">
-        <f>' 台語音標【xlit解析】'!BG6</f>
-        <v>入</v>
-      </c>
-      <c r="BI20" s="131" t="str">
-        <f>' 台語音標【xlit解析】'!BH6</f>
         <v>ㄥ</v>
       </c>
       <c r="BJ20" s="131"/>
@@ -16020,7 +16069,7 @@
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="BO20" s="265" t="str">
+      <c r="BO20" s="253" t="str">
         <v>s</v>
       </c>
       <c r="BP20" s="86" t="str">
@@ -16116,7 +16165,7 @@
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="BO21" s="265" t="str">
+      <c r="BO21" s="253" t="str">
         <v>h</v>
       </c>
       <c r="BP21" s="86" t="str">
@@ -16369,7 +16418,7 @@
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="BO22" s="265" t="str">
+      <c r="BO22" s="253" t="str">
         <v>j(i)</v>
       </c>
       <c r="BP22" s="86" t="str">
@@ -16678,7 +16727,7 @@
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="BO23" s="265" t="str">
+      <c r="BO23" s="253" t="str">
         <v>z(i)</v>
       </c>
       <c r="BP23" s="86" t="str">
@@ -16994,7 +17043,7 @@
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="BO24" s="265" t="str">
+      <c r="BO24" s="253" t="str">
         <v>c(i)</v>
       </c>
       <c r="BP24" s="86" t="str">
@@ -17116,7 +17165,7 @@
         <f t="shared" si="4"/>
         <v>21</v>
       </c>
-      <c r="BO25" s="265" t="str">
+      <c r="BO25" s="253" t="str">
         <v>s(i)</v>
       </c>
       <c r="BP25" s="86" t="str">
@@ -17264,7 +17313,7 @@
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="BO26" s="265" t="str">
+      <c r="BO26" s="253" t="str">
         <v>a</v>
       </c>
       <c r="BP26" s="86" t="str">
@@ -17398,7 +17447,7 @@
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="BO27" s="265" t="str">
+      <c r="BO27" s="253" t="str">
         <v>i</v>
       </c>
       <c r="BP27" s="86" t="str">
@@ -17532,7 +17581,7 @@
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="BO28" s="265" t="str">
+      <c r="BO28" s="253" t="str">
         <v>ir</v>
       </c>
       <c r="BP28" s="86" t="str">
@@ -17659,7 +17708,7 @@
         <f t="shared" si="4"/>
         <v>25</v>
       </c>
-      <c r="BO29" s="265" t="str">
+      <c r="BO29" s="253" t="str">
         <v>u</v>
       </c>
       <c r="BP29" s="86" t="str">
@@ -17799,7 +17848,7 @@
         <f t="shared" si="4"/>
         <v>26</v>
       </c>
-      <c r="BO30" s="265" t="str">
+      <c r="BO30" s="253" t="str">
         <v>e</v>
       </c>
       <c r="BP30" s="86" t="str">
@@ -17931,7 +17980,7 @@
         <f t="shared" si="4"/>
         <v>27</v>
       </c>
-      <c r="BO31" s="265" t="str">
+      <c r="BO31" s="253" t="str">
         <v>oo</v>
       </c>
       <c r="BP31" s="86" t="str">
@@ -18036,7 +18085,7 @@
         <f t="shared" si="4"/>
         <v>28</v>
       </c>
-      <c r="BO32" s="265" t="str">
+      <c r="BO32" s="253" t="str">
         <v>o</v>
       </c>
       <c r="BP32" s="86" t="str">
@@ -18168,7 +18217,7 @@
         <f t="shared" si="4"/>
         <v>29</v>
       </c>
-      <c r="BO33" s="265" t="str">
+      <c r="BO33" s="253" t="str">
         <v>-m</v>
       </c>
       <c r="BP33" s="86" t="str">
@@ -18244,7 +18293,7 @@
       <c r="A34" s="147"/>
       <c r="B34" s="152" t="str">
         <f>_xlfn.CONCAT("  alphabet: """,D19:AZ19,BI19:BK19,BA19:BH19,"""")</f>
-        <v xml:space="preserve">  alphabet: "!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L."5346][7"</v>
+        <v xml:space="preserve">  alphabet: "!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L-"5346][7"</v>
       </c>
       <c r="C34" s="153"/>
       <c r="D34" s="153"/>
@@ -18306,7 +18355,7 @@
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="BO34" s="265" t="str">
+      <c r="BO34" s="253" t="str">
         <v>-n</v>
       </c>
       <c r="BP34" s="86" t="str">
@@ -18382,7 +18431,7 @@
       <c r="A35" s="61"/>
       <c r="B35" s="152" t="str">
         <f>_xlfn.CONCAT("  initials: """,D19:AZ19,BI19:BK19,"""")</f>
-        <v xml:space="preserve">  initials: "!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L."</v>
+        <v xml:space="preserve">  initials: "!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L-"</v>
       </c>
       <c r="C35" s="154"/>
       <c r="D35" s="155"/>
@@ -18450,7 +18499,7 @@
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="BO35" s="265" t="str">
+      <c r="BO35" s="253" t="str">
         <v>-ng</v>
       </c>
       <c r="BP35" s="86" t="str">
@@ -18593,7 +18642,7 @@
         <f t="shared" si="4"/>
         <v>32</v>
       </c>
-      <c r="BO36" s="265" t="str">
+      <c r="BO36" s="253" t="str">
         <v>-p</v>
       </c>
       <c r="BP36" s="86" t="str">
@@ -18691,7 +18740,7 @@
         <f t="shared" si="4"/>
         <v>33</v>
       </c>
-      <c r="BO37" s="265" t="str">
+      <c r="BO37" s="253" t="str">
         <v>-t</v>
       </c>
       <c r="BP37" s="86" t="str">
@@ -18793,7 +18842,7 @@
         <f t="shared" si="4"/>
         <v>34</v>
       </c>
-      <c r="BO38" s="265" t="str">
+      <c r="BO38" s="253" t="str">
         <v>-k</v>
       </c>
       <c r="BP38" s="86" t="str">
@@ -18933,7 +18982,7 @@
         <f t="shared" si="4"/>
         <v>35</v>
       </c>
-      <c r="BO39" s="265" t="str">
+      <c r="BO39" s="253" t="str">
         <v>-h</v>
       </c>
       <c r="BP39" s="86" t="str">
@@ -19077,7 +19126,7 @@
         <f t="shared" si="4"/>
         <v>36</v>
       </c>
-      <c r="BO40" s="265" t="str">
+      <c r="BO40" s="253" t="str">
         <v>ai</v>
       </c>
       <c r="BP40" s="86" t="str">
@@ -19241,7 +19290,7 @@
         <f t="shared" si="4"/>
         <v>37</v>
       </c>
-      <c r="BO41" s="265" t="str">
+      <c r="BO41" s="253" t="str">
         <v>au</v>
       </c>
       <c r="BP41" s="86" t="str">
@@ -19323,7 +19372,7 @@
       </c>
       <c r="E42" s="172" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(D19:BK19)</f>
-        <v>!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L"5346][7.</v>
+        <v>!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L"5346][7-</v>
       </c>
       <c r="F42" s="173"/>
       <c r="G42" s="173"/>
@@ -19401,7 +19450,7 @@
         <f t="shared" si="4"/>
         <v>38</v>
       </c>
-      <c r="BO42" s="265" t="str">
+      <c r="BO42" s="253" t="str">
         <v>am</v>
       </c>
       <c r="BP42" s="86" t="str">
@@ -19474,7 +19523,7 @@
       <c r="A43" s="135"/>
       <c r="B43" s="174" t="str">
         <f xml:space="preserve"> "    - xlit|" &amp; E41 &amp; "|" &amp; E42 &amp; "|"</f>
-        <v xml:space="preserve">    - xlit|bpPmntTlgkKŋjzcshJZCSaiwueOəMNGRFQVIUY@AWHdfqrvxy1732584&amp;L|!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L"5346][7.|</v>
+        <v xml:space="preserve">    - xlit|bpPmntTlgkKŋjzcshJZCSaiwueOəMNGRFQVIUY@AWHdfqrvxy1732584&amp;L|!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L"5346][7-|</v>
       </c>
       <c r="C43" s="175"/>
       <c r="D43" s="175"/>
@@ -19548,7 +19597,7 @@
         <f t="shared" si="4"/>
         <v>39</v>
       </c>
-      <c r="BO43" s="265" t="str">
+      <c r="BO43" s="253" t="str">
         <v>an</v>
       </c>
       <c r="BP43" s="86" t="str">
@@ -19633,7 +19682,7 @@
         <f t="shared" si="4"/>
         <v>40</v>
       </c>
-      <c r="BO44" s="265" t="str">
+      <c r="BO44" s="253" t="str">
         <v>ang</v>
       </c>
       <c r="BP44" s="86" t="str">
@@ -19708,7 +19757,7 @@
         <f t="shared" si="4"/>
         <v>41</v>
       </c>
-      <c r="BO45" s="265" t="str">
+      <c r="BO45" s="253" t="str">
         <v>om</v>
       </c>
       <c r="BP45" s="86" t="str">
@@ -19965,7 +20014,7 @@
         <f t="shared" si="4"/>
         <v>42</v>
       </c>
-      <c r="BO46" s="265" t="str">
+      <c r="BO46" s="253" t="str">
         <v>ong</v>
       </c>
       <c r="BP46" s="86" t="str">
@@ -20282,7 +20331,7 @@
         <f t="shared" si="4"/>
         <v>43</v>
       </c>
-      <c r="BO47" s="265" t="str">
+      <c r="BO47" s="253" t="str">
         <v>aⁿ</v>
       </c>
       <c r="BP47" s="86" t="str">
@@ -20581,7 +20630,7 @@
       </c>
       <c r="BG48" s="183" t="str">
         <f t="shared" si="19"/>
-        <v>.</v>
+        <v>-</v>
       </c>
       <c r="BH48" s="183" t="str">
         <f t="shared" si="19"/>
@@ -20598,7 +20647,7 @@
         <f t="shared" si="4"/>
         <v>44</v>
       </c>
-      <c r="BO48" s="265" t="str">
+      <c r="BO48" s="253" t="str">
         <v>iⁿ</v>
       </c>
       <c r="BP48" s="86" t="str">
@@ -20681,7 +20730,7 @@
         <f t="shared" si="4"/>
         <v>45</v>
       </c>
-      <c r="BO49" s="265" t="str">
+      <c r="BO49" s="253" t="str">
         <v>uⁿ</v>
       </c>
       <c r="BP49" s="86" t="str">
@@ -20817,7 +20866,7 @@
         <f t="shared" si="4"/>
         <v>46</v>
       </c>
-      <c r="BO50" s="265" t="str">
+      <c r="BO50" s="253" t="str">
         <v>eⁿ</v>
       </c>
       <c r="BP50" s="86" t="str">
@@ -20956,7 +21005,7 @@
         <f t="shared" si="4"/>
         <v>47</v>
       </c>
-      <c r="BO51" s="265" t="str">
+      <c r="BO51" s="253" t="str">
         <v>oⁿ</v>
       </c>
       <c r="BP51" s="86" t="str">
@@ -21094,7 +21143,7 @@
         <f t="shared" si="4"/>
         <v>48</v>
       </c>
-      <c r="BO52" s="265" t="str">
+      <c r="BO52" s="253" t="str">
         <v>aiⁿ</v>
       </c>
       <c r="BP52" s="86" t="str">
@@ -21174,7 +21223,7 @@
       </c>
       <c r="E53" s="188" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(D19:BK19)</f>
-        <v>!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L"5346][7.</v>
+        <v>!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L"5346][7-</v>
       </c>
       <c r="F53" s="188"/>
       <c r="G53" s="188"/>
@@ -21239,7 +21288,7 @@
         <f t="shared" si="4"/>
         <v>49</v>
       </c>
-      <c r="BO53" s="265" t="str">
+      <c r="BO53" s="253" t="str">
         <v>auⁿ</v>
       </c>
       <c r="BP53" s="86" t="str">
@@ -21384,7 +21433,7 @@
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="BO54" s="265">
+      <c r="BO54" s="253">
         <v>1</v>
       </c>
       <c r="BP54" s="86">
@@ -21455,7 +21504,7 @@
     <row r="55" spans="1:109" ht="45" customHeight="1">
       <c r="B55" s="174" t="str">
         <f xml:space="preserve"> "    - xlit|" &amp; E53 &amp; "|" &amp; E54 &amp; "|"</f>
-        <v xml:space="preserve">    - xlit|!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L"5346][7.|ㆠㄅㄆㄇㄋㄉㄊㄌㆣㄍㄎㄫㆡㄗㄘㄙㄏㆢㄐㄑㄒㄚㄧㆨㄨㆤㆦㄜㆬㄣㆭㆴㆵㆻㆷㄞㄠㆰㄢㄤㆱㆲㆩㆪㆫㆥㆧㆮㆯ一七三二五八四入ㄥ|</v>
+        <v xml:space="preserve">    - xlit|!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L"5346][7-|ㆠㄅㄆㄇㄋㄉㄊㄌㆣㄍㄎㄫㆡㄗㄘㄙㄏㆢㄐㄑㄒㄚㄧㆨㄨㆤㆦㄜㆬㄣㆭㆴㆵㆻㆷㄞㄠㆰㄢㄤㆱㆲㆩㆪㆫㆥㆧㆮㆯ一七三二五八四入ㄥ|</v>
       </c>
       <c r="C55" s="192"/>
       <c r="D55" s="192"/>
@@ -21523,7 +21572,7 @@
         <f t="shared" si="4"/>
         <v>51</v>
       </c>
-      <c r="BO55" s="265">
+      <c r="BO55" s="253">
         <v>7</v>
       </c>
       <c r="BP55" s="86">
@@ -21662,7 +21711,7 @@
         <f t="shared" si="4"/>
         <v>52</v>
       </c>
-      <c r="BO56" s="265">
+      <c r="BO56" s="253">
         <v>3</v>
       </c>
       <c r="BP56" s="86">
@@ -21738,7 +21787,7 @@
         <f t="shared" si="4"/>
         <v>53</v>
       </c>
-      <c r="BO57" s="265">
+      <c r="BO57" s="253">
         <v>2</v>
       </c>
       <c r="BP57" s="86">
@@ -21990,7 +22039,7 @@
         <f t="shared" si="4"/>
         <v>54</v>
       </c>
-      <c r="BO58" s="265">
+      <c r="BO58" s="253">
         <v>5</v>
       </c>
       <c r="BP58" s="86">
@@ -22285,7 +22334,7 @@
       </c>
       <c r="BG59" s="183" t="str">
         <f t="shared" si="20"/>
-        <v>.</v>
+        <v>-</v>
       </c>
       <c r="BH59" s="183" t="str">
         <f t="shared" si="20"/>
@@ -22302,7 +22351,7 @@
         <f t="shared" si="4"/>
         <v>55</v>
       </c>
-      <c r="BO59" s="265">
+      <c r="BO59" s="253">
         <v>8</v>
       </c>
       <c r="BP59" s="86">
@@ -22614,7 +22663,7 @@
         <f t="shared" si="4"/>
         <v>56</v>
       </c>
-      <c r="BO60" s="265">
+      <c r="BO60" s="253">
         <v>4</v>
       </c>
       <c r="BP60" s="86">
@@ -22746,7 +22795,7 @@
         <f t="shared" si="4"/>
         <v>57</v>
       </c>
-      <c r="BO61" s="265">
+      <c r="BO61" s="253">
         <v>0</v>
       </c>
       <c r="BP61" s="86" t="str">
@@ -22878,14 +22927,14 @@
         <f t="shared" si="4"/>
         <v>58</v>
       </c>
-      <c r="BO62" s="265" t="str">
-        <v>L</v>
+      <c r="BO62" s="253" t="str">
+        <v>ⁿ</v>
       </c>
       <c r="BP62" s="86" t="str">
         <v>L</v>
       </c>
       <c r="BQ62" s="76" t="str">
-        <v>.</v>
+        <v>-</v>
       </c>
       <c r="BR62" s="77" t="str">
         <v>ㄥ</v>
@@ -22899,7 +22948,7 @@
       </c>
       <c r="BV62" s="89" t="str">
         <f t="shared" si="16"/>
-        <v xml:space="preserve">    ".": { commit: "ㄥ" }  # /L/ ==&gt; L</v>
+        <v xml:space="preserve">    "-": { commit: "ㄥ" }  # /ⁿ/ ==&gt; L</v>
       </c>
       <c r="BX62" s="85">
         <f t="shared" si="6"/>
@@ -23012,7 +23061,7 @@
         <f t="shared" si="4"/>
         <v>59</v>
       </c>
-      <c r="BO63" s="265"/>
+      <c r="BO63" s="253"/>
       <c r="BP63" s="86"/>
       <c r="BQ63" s="76"/>
       <c r="BR63" s="77"/>
@@ -23132,7 +23181,7 @@
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="BO64" s="265"/>
+      <c r="BO64" s="253"/>
       <c r="BP64" s="86"/>
       <c r="BQ64" s="76"/>
       <c r="BR64" s="77"/>
@@ -26760,16 +26809,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="W9:X9"/>
     <mergeCell ref="AA12:AB12"/>
     <mergeCell ref="X12:Y12"/>
     <mergeCell ref="AB6:AC6"/>
     <mergeCell ref="AC9:AD9"/>
     <mergeCell ref="Z9:AA9"/>
     <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="W9:X9"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="B22:AA22">
@@ -27353,35 +27402,36 @@
         <f xml:space="preserve"> _xlfn.CONCAT("au", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+207F",4))))</f>
         <v>auⁿ</v>
       </c>
-      <c r="AZ3" s="209">
+      <c r="AZ3" s="279" t="str">
+        <f xml:space="preserve"> _xlfn.UNICHAR(HEX2DEC(RIGHT("U+207F",4)))</f>
+        <v>ⁿ</v>
+      </c>
+      <c r="BA3" s="234" t="s">
+        <v>567</v>
+      </c>
+      <c r="BB3" s="209">
         <v>1</v>
       </c>
-      <c r="BA3" s="209">
+      <c r="BC3" s="209">
         <v>7</v>
       </c>
-      <c r="BB3" s="209">
+      <c r="BD3" s="209">
         <v>3</v>
       </c>
-      <c r="BC3" s="209">
+      <c r="BE3" s="209">
         <v>2</v>
       </c>
-      <c r="BD3" s="209">
+      <c r="BF3" s="209">
         <v>5</v>
       </c>
-      <c r="BE3" s="209">
+      <c r="BG3" s="209">
         <v>8</v>
       </c>
-      <c r="BF3" s="209">
+      <c r="BH3" s="209">
         <v>4</v>
       </c>
-      <c r="BG3" s="209">
+      <c r="BI3" s="209">
         <v>0</v>
-      </c>
-      <c r="BH3" s="209" t="s">
-        <v>119</v>
-      </c>
-      <c r="BI3" s="209" t="s">
-        <v>222</v>
       </c>
       <c r="BJ3" s="209"/>
       <c r="BL3" s="238">
@@ -27596,35 +27646,35 @@
       <c r="AY4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AZ4" s="4">
+      <c r="AZ4" s="280" t="s">
+        <v>119</v>
+      </c>
+      <c r="BA4" s="280" t="s">
+        <v>567</v>
+      </c>
+      <c r="BB4" s="4">
         <v>1</v>
       </c>
-      <c r="BA4" s="4">
+      <c r="BC4" s="4">
         <v>7</v>
       </c>
-      <c r="BB4" s="4">
+      <c r="BD4" s="4">
         <v>3</v>
       </c>
-      <c r="BC4" s="4">
+      <c r="BE4" s="4">
         <v>2</v>
       </c>
-      <c r="BD4" s="4">
+      <c r="BF4" s="4">
         <v>5</v>
       </c>
-      <c r="BE4" s="4">
+      <c r="BG4" s="4">
         <v>8</v>
       </c>
-      <c r="BF4" s="4">
+      <c r="BH4" s="4">
         <v>4</v>
       </c>
-      <c r="BG4" s="6" t="s">
+      <c r="BI4" s="6" t="s">
         <v>535</v>
-      </c>
-      <c r="BH4" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="BI4" s="4" t="s">
-        <v>222</v>
       </c>
       <c r="BJ4" s="4"/>
       <c r="BL4" s="238">
@@ -27725,7 +27775,7 @@
       <c r="M5" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="N5" s="266" t="s">
+      <c r="N5" s="254" t="s">
         <v>550</v>
       </c>
       <c r="O5" s="5" t="s">
@@ -27839,35 +27889,35 @@
       <c r="AY5" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="AZ5" s="5" t="s">
+      <c r="AZ5" s="281" t="s">
+        <v>569</v>
+      </c>
+      <c r="BA5" s="281" t="s">
+        <v>568</v>
+      </c>
+      <c r="BB5" s="5" t="s">
         <v>560</v>
       </c>
-      <c r="BA5" s="5">
+      <c r="BC5" s="5">
         <v>5</v>
       </c>
-      <c r="BB5" s="5">
+      <c r="BD5" s="5">
         <v>3</v>
       </c>
-      <c r="BC5" s="5">
+      <c r="BE5" s="5">
         <v>4</v>
       </c>
-      <c r="BD5" s="5">
+      <c r="BF5" s="5">
         <v>6</v>
       </c>
-      <c r="BE5" s="5" t="s">
+      <c r="BG5" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="BF5" s="5" t="s">
+      <c r="BH5" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="BG5" s="5">
+      <c r="BI5" s="5">
         <v>7</v>
-      </c>
-      <c r="BH5" s="5" t="s">
-        <v>561</v>
-      </c>
-      <c r="BI5" s="5" t="s">
-        <v>222</v>
       </c>
       <c r="BJ5" s="5"/>
       <c r="BL5" s="238">
@@ -28082,35 +28132,35 @@
       <c r="AY6" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="AZ6" s="7" t="s">
+      <c r="AZ6" s="282" t="s">
+        <v>181</v>
+      </c>
+      <c r="BA6" s="282" t="s">
+        <v>566</v>
+      </c>
+      <c r="BB6" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="BA6" s="7" t="s">
+      <c r="BC6" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="BB6" s="7" t="s">
+      <c r="BD6" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="BC6" s="7" t="s">
+      <c r="BE6" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="BD6" s="7" t="s">
+      <c r="BF6" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="BE6" s="7" t="s">
+      <c r="BG6" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="BF6" s="7" t="s">
+      <c r="BH6" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="BG6" s="7" t="s">
+      <c r="BI6" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="BH6" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="BI6" s="7" t="s">
-        <v>222</v>
       </c>
       <c r="BJ6" s="7"/>
       <c r="BL6" s="238">
@@ -28426,8 +28476,8 @@
         <v>552</v>
       </c>
       <c r="C9" s="235" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("  alphabet: ","""", C5:AY5, AZ5:BH5, """")</f>
-        <v xml:space="preserve">  alphabet: "!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L"5346][7."</v>
+        <f xml:space="preserve"> _xlfn.CONCAT("  alphabet: ","""", C5:BA5, BB5:BI5, """")</f>
+        <v xml:space="preserve">  alphabet: "!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L-="5346][7"</v>
       </c>
       <c r="D9" s="234"/>
       <c r="E9" s="234"/>
@@ -28554,8 +28604,8 @@
         <v>553</v>
       </c>
       <c r="C10" s="1" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("  initials: ","""",C5:AY5, """")</f>
-        <v xml:space="preserve">  initials: "!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L"</v>
+        <f xml:space="preserve"> _xlfn.CONCAT("  initials: ","""", C5:BA5, """")</f>
+        <v xml:space="preserve">  initials: "!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L-="</v>
       </c>
       <c r="D10" s="234"/>
       <c r="E10" s="234"/>
@@ -28679,11 +28729,11 @@
     </row>
     <row r="11" spans="1:86">
       <c r="A11" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C11" s="1" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("  finals: ","""", AZ5:BH5, """")</f>
-        <v xml:space="preserve">  finals: ""5346][7."</v>
+        <f xml:space="preserve"> _xlfn.CONCAT("  finals: ","""", BB5:BI5, """")</f>
+        <v xml:space="preserve">  finals: ""5346][7"</v>
       </c>
       <c r="D11" s="234"/>
       <c r="E11" s="234"/>
@@ -28899,8 +28949,8 @@
     </row>
     <row r="14" spans="1:86" outlineLevel="1">
       <c r="B14" s="1" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xlit|", C4:BH4, "|", C5:BH5, "|")</f>
-        <v xml:space="preserve">    - xlit|bpPmntTlgkKŋjzcshJZCSaiwueOəMNGRFQVIUY@AWHdfqrvxy1732584&amp;L|!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L"5346][7.|</v>
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xlit|", C4:BI4, "|", C5:BI5, "|")</f>
+        <v xml:space="preserve">    - xlit|bpPmntTlgkKŋjzcshJZCSaiwueOəMNGRFQVIUY@AWHdfqrvxyLØ1732584&amp;|!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L-="5346][7|</v>
       </c>
       <c r="BL14" s="238">
         <v>13</v>
@@ -29058,7 +29108,7 @@
       </c>
       <c r="B17" s="1">
         <f xml:space="preserve"> SEARCH("|", $B$14, B16+1)</f>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="BL17" s="238">
         <v>16</v>
@@ -29112,7 +29162,7 @@
       </c>
       <c r="B18" s="1">
         <f xml:space="preserve"> SEARCH("|", $B$14, B17+1)</f>
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="BL18" s="238">
         <v>17</v>
@@ -29213,11 +29263,11 @@
       </c>
       <c r="B20" s="1">
         <f xml:space="preserve"> LEN(C20)</f>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C20" s="1" t="str">
         <f xml:space="preserve"> MID($B$14,B16+1, (B17-B16-1))</f>
-        <v>bpPmntTlgkKŋjzcshJZCSaiwueOəMNGRFQVIUY@AWHdfqrvxy1732584&amp;L</v>
+        <v>bpPmntTlgkKŋjzcshJZCSaiwueOəMNGRFQVIUY@AWHdfqrvxyLØ1732584&amp;</v>
       </c>
       <c r="BL20" s="238">
         <v>19</v>
@@ -29271,11 +29321,11 @@
       </c>
       <c r="B21" s="1">
         <f xml:space="preserve"> LEN(C21)</f>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C21" s="1" t="str">
         <f xml:space="preserve"> MID($B$14,B17+1, (B18-B17-1))</f>
-        <v>!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L"5346][7.</v>
+        <v>!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L-="5346][7</v>
       </c>
       <c r="BL21" s="238">
         <v>20</v>
@@ -29844,43 +29894,43 @@
       </c>
       <c r="AZ24" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>L</v>
       </c>
       <c r="BA24" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>Ø</v>
       </c>
       <c r="BB24" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BC24" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BD24" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BE24" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BF24" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BG24" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>&amp;</v>
+        <v>8</v>
       </c>
       <c r="BH24" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>L</v>
+        <v>4</v>
       </c>
       <c r="BI24" s="4" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>&amp;</v>
       </c>
       <c r="BJ24" s="4" t="str">
         <f t="shared" si="2"/>
@@ -30119,43 +30169,43 @@
       </c>
       <c r="AZ25" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>"</v>
+        <v>-</v>
       </c>
       <c r="BA25" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>=</v>
       </c>
       <c r="BB25" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>"</v>
       </c>
       <c r="BC25" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD25" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BE25" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>]</v>
+        <v>4</v>
       </c>
       <c r="BF25" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>[</v>
+        <v>6</v>
       </c>
       <c r="BG25" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>]</v>
       </c>
       <c r="BH25" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>.</v>
+        <v>[</v>
       </c>
       <c r="BI25" s="5" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="BJ25" s="5" t="str">
         <f t="shared" si="3"/>
@@ -30293,8 +30343,8 @@
     </row>
     <row r="29" spans="1:80" outlineLevel="1">
       <c r="B29" s="1" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xlit|", C5:BH5, "|", C6:BH6, "|")</f>
-        <v xml:space="preserve">    - xlit|!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L"5346][7.|ㆠㄅㄆㄇㄋㄉㄊㄌㆣㄍㄎㄫㆡㄗㄘㄙㄏㆢㄐㄑㄒㄚㄧㆨㄨㆤㆦㄜㆬㄣㆭㆴㆵㆻㆷㄞㄠㆰㄢㄤㆱㆲㆩㆪㆫㆥㆧㆮㆯ一七三二五八四入ㄥ|</v>
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xlit|", C5:BI5, "|", C6:BI6, "|")</f>
+        <v xml:space="preserve">    - xlit|!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L-="5346][7|ㆠㄅㄆㄇㄋㄉㄊㄌㆣㄍㄎㄫㆡㄗㄘㄙㄏㆢㄐㄑㄒㄚㄧㆨㄨㆤㆦㄜㆬㄣㆭㆴㆵㆻㆷㄞㄠㆰㄢㄤㆱㆲㆩㆪㆫㆥㆧㆮㆯㄥØ一七三二五八四入|</v>
       </c>
       <c r="BL29" s="238">
         <v>28</v>
@@ -30374,7 +30424,7 @@
       </c>
       <c r="B32" s="1">
         <f xml:space="preserve"> SEARCH("|", $B$29, B31+1)</f>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="BL32" s="238">
         <v>31</v>
@@ -30398,7 +30448,7 @@
       </c>
       <c r="B33" s="1">
         <f xml:space="preserve"> SEARCH("|", $B$29, B32+1)</f>
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="BL33" s="238">
         <v>32</v>
@@ -30439,11 +30489,11 @@
       </c>
       <c r="B35" s="1">
         <f xml:space="preserve"> LEN(C35)</f>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C35" s="1" t="str">
         <f xml:space="preserve"> MID($B$29,B31+1, (B32-B31-1))</f>
-        <v>!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L"5346][7.</v>
+        <v>!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L-="5346][7</v>
       </c>
       <c r="BL35" s="238">
         <v>34</v>
@@ -30467,11 +30517,11 @@
       </c>
       <c r="B36" s="1">
         <f xml:space="preserve"> LEN(C36)</f>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C36" s="1" t="str">
         <f xml:space="preserve"> MID($B$29,B32+1, (B33-B32-1))</f>
-        <v>ㆠㄅㄆㄇㄋㄉㄊㄌㆣㄍㄎㄫㆡㄗㄘㄙㄏㆢㄐㄑㄒㄚㄧㆨㄨㆤㆦㄜㆬㄣㆭㆴㆵㆻㆷㄞㄠㆰㄢㄤㆱㆲㆩㆪㆫㆥㆧㆮㆯ一七三二五八四入ㄥ</v>
+        <v>ㆠㄅㄆㄇㄋㄉㄊㄌㆣㄍㄎㄫㆡㄗㄘㄙㄏㆢㄐㄑㄒㄚㄧㆨㄨㆤㆦㄜㆬㄣㆭㆴㆵㆻㆷㄞㄠㆰㄢㄤㆱㆲㆩㆪㆫㆥㆧㆮㆯㄥØ一七三二五八四入</v>
       </c>
       <c r="BL36" s="238">
         <v>35</v>
@@ -30965,43 +31015,43 @@
       </c>
       <c r="AZ39" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>L</v>
       </c>
       <c r="BA39" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>Ø</v>
       </c>
       <c r="BB39" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BC39" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BD39" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BE39" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BF39" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BG39" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>&amp;</v>
+        <v>8</v>
       </c>
       <c r="BH39" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>L</v>
+        <v>4</v>
       </c>
       <c r="BI39" s="4" t="str">
         <f xml:space="preserve"> _xlfn.XLOOKUP(BI40, $C$25:$BJ$25,$C$24:$BJ$24, "")</f>
-        <v/>
+        <v>&amp;</v>
       </c>
       <c r="BJ39" s="4" t="str">
         <f xml:space="preserve"> _xlfn.XLOOKUP(BJ40, $C$25:$BJ$25,$C$24:$BJ$24, "")</f>
@@ -31225,43 +31275,43 @@
       </c>
       <c r="AZ40" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>"</v>
+        <v>-</v>
       </c>
       <c r="BA40" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>=</v>
       </c>
       <c r="BB40" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>"</v>
       </c>
       <c r="BC40" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD40" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BE40" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>]</v>
+        <v>4</v>
       </c>
       <c r="BF40" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>[</v>
+        <v>6</v>
       </c>
       <c r="BG40" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>]</v>
       </c>
       <c r="BH40" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>.</v>
+        <v>[</v>
       </c>
       <c r="BI40" s="5" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="BJ40" s="5" t="str">
         <f t="shared" si="6"/>
@@ -31485,43 +31535,43 @@
       </c>
       <c r="AZ41" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>一</v>
+        <v>ㄥ</v>
       </c>
       <c r="BA41" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>七</v>
+        <v>Ø</v>
       </c>
       <c r="BB41" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>三</v>
+        <v>一</v>
       </c>
       <c r="BC41" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>二</v>
+        <v>七</v>
       </c>
       <c r="BD41" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>五</v>
+        <v>三</v>
       </c>
       <c r="BE41" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>八</v>
+        <v>二</v>
       </c>
       <c r="BF41" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>四</v>
+        <v>五</v>
       </c>
       <c r="BG41" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>入</v>
+        <v>八</v>
       </c>
       <c r="BH41" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>ㄥ</v>
+        <v>四</v>
       </c>
       <c r="BI41" s="7" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>入</v>
       </c>
       <c r="BJ41" s="7" t="str">
         <f t="shared" si="7"/>
@@ -31700,34 +31750,34 @@
       <c r="BL51" s="238">
         <v>50</v>
       </c>
-      <c r="BM51" s="238">
-        <v>1</v>
-      </c>
-      <c r="BN51" s="239">
-        <v>1</v>
+      <c r="BM51" s="238" t="str">
+        <v>ⁿ</v>
+      </c>
+      <c r="BN51" s="239" t="str">
+        <v>L</v>
       </c>
       <c r="BO51" s="238" t="str">
-        <v>"</v>
+        <v>-</v>
       </c>
       <c r="BP51" s="238" t="str">
-        <v>一</v>
+        <v>ㄥ</v>
       </c>
     </row>
     <row r="52" spans="64:68">
       <c r="BL52" s="238">
         <v>51</v>
       </c>
-      <c r="BM52" s="238">
-        <v>7</v>
-      </c>
-      <c r="BN52" s="239">
-        <v>7</v>
-      </c>
-      <c r="BO52" s="238">
-        <v>5</v>
+      <c r="BM52" s="238" t="str">
+        <v>Ø</v>
+      </c>
+      <c r="BN52" s="239" t="str">
+        <v>Ø</v>
+      </c>
+      <c r="BO52" s="238" t="str">
+        <v>=</v>
       </c>
       <c r="BP52" s="238" t="str">
-        <v>七</v>
+        <v>Ø</v>
       </c>
     </row>
     <row r="53" spans="64:68">
@@ -31735,16 +31785,16 @@
         <v>52</v>
       </c>
       <c r="BM53" s="238">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BN53" s="239">
-        <v>3</v>
-      </c>
-      <c r="BO53" s="238">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="BO53" s="238" t="str">
+        <v>"</v>
       </c>
       <c r="BP53" s="238" t="str">
-        <v>三</v>
+        <v>一</v>
       </c>
     </row>
     <row r="54" spans="64:68">
@@ -31752,16 +31802,16 @@
         <v>53</v>
       </c>
       <c r="BM54" s="238">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BN54" s="238">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BO54" s="238">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BP54" s="238" t="str">
-        <v>二</v>
+        <v>七</v>
       </c>
     </row>
     <row r="55" spans="64:68">
@@ -31769,16 +31819,16 @@
         <v>54</v>
       </c>
       <c r="BM55" s="238">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BN55" s="238">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BO55" s="238">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BP55" s="238" t="str">
-        <v>五</v>
+        <v>三</v>
       </c>
     </row>
     <row r="56" spans="64:68">
@@ -31786,16 +31836,16 @@
         <v>55</v>
       </c>
       <c r="BM56" s="238">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BN56" s="238">
-        <v>8</v>
-      </c>
-      <c r="BO56" s="238" t="str">
-        <v>]</v>
+        <v>2</v>
+      </c>
+      <c r="BO56" s="238">
+        <v>4</v>
       </c>
       <c r="BP56" s="238" t="str">
-        <v>八</v>
+        <v>二</v>
       </c>
     </row>
     <row r="57" spans="64:68">
@@ -31803,16 +31853,16 @@
         <v>56</v>
       </c>
       <c r="BM57" s="238">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BN57" s="238">
-        <v>4</v>
-      </c>
-      <c r="BO57" s="238" t="str">
-        <v>[</v>
+        <v>5</v>
+      </c>
+      <c r="BO57" s="238">
+        <v>6</v>
       </c>
       <c r="BP57" s="238" t="str">
-        <v>四</v>
+        <v>五</v>
       </c>
     </row>
     <row r="58" spans="64:68">
@@ -31820,50 +31870,50 @@
         <v>57</v>
       </c>
       <c r="BM58" s="238">
-        <v>0</v>
-      </c>
-      <c r="BN58" s="238" t="str">
-        <v>&amp;</v>
-      </c>
-      <c r="BO58" s="238">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="BN58" s="238">
+        <v>8</v>
+      </c>
+      <c r="BO58" s="238" t="str">
+        <v>]</v>
       </c>
       <c r="BP58" s="238" t="str">
-        <v>入</v>
+        <v>八</v>
       </c>
     </row>
     <row r="59" spans="64:68">
       <c r="BL59" s="238">
         <v>58</v>
       </c>
-      <c r="BM59" s="238" t="str">
-        <v>L</v>
-      </c>
-      <c r="BN59" s="238" t="str">
-        <v>L</v>
+      <c r="BM59" s="238">
+        <v>4</v>
+      </c>
+      <c r="BN59" s="238">
+        <v>4</v>
       </c>
       <c r="BO59" s="238" t="str">
-        <v>.</v>
+        <v>[</v>
       </c>
       <c r="BP59" s="238" t="str">
-        <v>ㄥ</v>
+        <v>四</v>
       </c>
     </row>
     <row r="60" spans="64:68">
       <c r="BL60" s="238">
         <v>59</v>
       </c>
-      <c r="BM60" s="240" t="str">
-        <v/>
+      <c r="BM60" s="240">
+        <v>0</v>
       </c>
       <c r="BN60" s="240" t="str">
-        <v/>
-      </c>
-      <c r="BO60" s="240" t="str">
-        <v/>
+        <v>&amp;</v>
+      </c>
+      <c r="BO60" s="240">
+        <v>7</v>
       </c>
       <c r="BP60" s="240" t="str">
-        <v/>
+        <v>入</v>
       </c>
     </row>
     <row r="61" spans="64:68">
@@ -32230,39 +32280,39 @@
       <c r="G4" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="267" t="s">
+      <c r="H4" s="255" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="268"/>
-      <c r="J4" s="269" t="s">
+      <c r="I4" s="256"/>
+      <c r="J4" s="257" t="s">
         <v>48</v>
       </c>
-      <c r="K4" s="270" t="s">
+      <c r="K4" s="258" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="271"/>
-      <c r="M4" s="269" t="s">
+      <c r="L4" s="259"/>
+      <c r="M4" s="257" t="s">
         <v>50</v>
       </c>
-      <c r="N4" s="267" t="s">
+      <c r="N4" s="255" t="s">
         <v>51</v>
       </c>
-      <c r="O4" s="268"/>
-      <c r="P4" s="269" t="s">
+      <c r="O4" s="256"/>
+      <c r="P4" s="257" t="s">
         <v>52</v>
       </c>
-      <c r="Q4" s="270" t="s">
+      <c r="Q4" s="258" t="s">
         <v>53</v>
       </c>
-      <c r="R4" s="271"/>
-      <c r="S4" s="269" t="s">
+      <c r="R4" s="259"/>
+      <c r="S4" s="257" t="s">
         <v>54</v>
       </c>
-      <c r="T4" s="270" t="s">
+      <c r="T4" s="258" t="s">
         <v>62</v>
       </c>
-      <c r="U4" s="268"/>
-      <c r="V4" s="269" t="s">
+      <c r="U4" s="256"/>
+      <c r="V4" s="257" t="s">
         <v>63</v>
       </c>
       <c r="W4" s="66" t="s">
@@ -32288,14 +32338,16 @@
       <c r="AE4" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="AF4" s="274" t="s">
+      <c r="AF4" s="262" t="s">
         <v>558</v>
       </c>
       <c r="AG4" s="67"/>
       <c r="AH4" s="71" t="s">
         <v>559</v>
       </c>
-      <c r="AI4" s="72"/>
+      <c r="AI4" s="283" t="s">
+        <v>566</v>
+      </c>
       <c r="AJ4" s="70"/>
       <c r="AK4" s="73"/>
       <c r="AL4" s="61"/>
@@ -32486,7 +32538,7 @@
         <f xml:space="preserve"> ROW() - 4</f>
         <v>1</v>
       </c>
-      <c r="BO5" s="265" t="str" cm="1">
+      <c r="BO5" s="253" t="str" cm="1">
         <f t="array" ref="BO5:BR62" xml:space="preserve"> TRANSPOSE(D17:BI20)</f>
         <v>b</v>
       </c>
@@ -32685,7 +32737,7 @@
         <f t="shared" ref="BN6:BN64" si="4" xml:space="preserve"> ROW() - 4</f>
         <v>2</v>
       </c>
-      <c r="BO6" s="265" t="str">
+      <c r="BO6" s="253" t="str">
         <v>p</v>
       </c>
       <c r="BP6" s="86" t="str">
@@ -32780,13 +32832,13 @@
         <v>2</v>
       </c>
       <c r="CZ6" s="93" t="str">
-        <v>L</v>
+        <v>ⁿ</v>
       </c>
       <c r="DA6" s="91" t="str">
         <v>L</v>
       </c>
       <c r="DB6" s="92" t="str">
-        <v>.</v>
+        <v>-</v>
       </c>
       <c r="DC6" s="77" t="str">
         <v>ㄥ</v>
@@ -32874,16 +32926,16 @@
       <c r="AF7" s="107" t="s">
         <v>110</v>
       </c>
-      <c r="AG7" s="270"/>
-      <c r="AH7" s="271"/>
-      <c r="AI7" s="272" t="s">
+      <c r="AG7" s="258"/>
+      <c r="AH7" s="259"/>
+      <c r="AI7" s="260" t="s">
         <v>555</v>
       </c>
-      <c r="AJ7" s="270" t="s">
+      <c r="AJ7" s="258" t="s">
         <v>55</v>
       </c>
-      <c r="AK7" s="271"/>
-      <c r="AL7" s="272" t="s">
+      <c r="AK7" s="259"/>
+      <c r="AL7" s="260" t="s">
         <v>554</v>
       </c>
       <c r="AM7" s="69"/>
@@ -32900,7 +32952,7 @@
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="BO7" s="265" t="str">
+      <c r="BO7" s="253" t="str">
         <v>ph</v>
       </c>
       <c r="BP7" s="86" t="str">
@@ -33077,7 +33129,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="BO8" s="265" t="str">
+      <c r="BO8" s="253" t="str">
         <v>m</v>
       </c>
       <c r="BP8" s="86" t="str">
@@ -33247,7 +33299,7 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="BO9" s="265" t="str">
+      <c r="BO9" s="253" t="str">
         <v>n</v>
       </c>
       <c r="BP9" s="86" t="str">
@@ -33425,9 +33477,9 @@
       <c r="AG10" s="71" t="s">
         <v>147</v>
       </c>
-      <c r="AH10" s="270"/>
-      <c r="AI10" s="271"/>
-      <c r="AJ10" s="272" t="s">
+      <c r="AH10" s="258"/>
+      <c r="AI10" s="259"/>
+      <c r="AJ10" s="260" t="s">
         <v>556</v>
       </c>
       <c r="AK10" s="61"/>
@@ -33446,7 +33498,7 @@
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="BO10" s="265" t="str">
+      <c r="BO10" s="253" t="str">
         <v>t</v>
       </c>
       <c r="BP10" s="86" t="str">
@@ -33621,7 +33673,7 @@
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="BO11" s="265" t="str">
+      <c r="BO11" s="253" t="str">
         <v>th</v>
       </c>
       <c r="BP11" s="86" t="str">
@@ -33767,7 +33819,7 @@
       <c r="AB12" s="50" t="s">
         <v>163</v>
       </c>
-      <c r="AC12" s="273"/>
+      <c r="AC12" s="261"/>
       <c r="AD12" s="110"/>
       <c r="AE12" s="111"/>
       <c r="AF12" s="112"/>
@@ -33793,7 +33845,7 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="BO12" s="265" t="str">
+      <c r="BO12" s="253" t="str">
         <v>l</v>
       </c>
       <c r="BP12" s="86" t="str">
@@ -33958,7 +34010,7 @@
       <c r="AB13" s="71" t="s">
         <v>180</v>
       </c>
-      <c r="AC13" s="274"/>
+      <c r="AC13" s="262"/>
       <c r="AD13" s="67"/>
       <c r="AE13" s="71"/>
       <c r="AF13" s="69" t="s">
@@ -33988,7 +34040,7 @@
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="BO13" s="265" t="str">
+      <c r="BO13" s="253" t="str">
         <v>g</v>
       </c>
       <c r="BP13" s="86" t="str">
@@ -34097,7 +34149,7 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="BO14" s="265" t="str">
+      <c r="BO14" s="253" t="str">
         <v>k</v>
       </c>
       <c r="BP14" s="86" t="str">
@@ -34266,7 +34318,7 @@
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="BO15" s="265" t="str">
+      <c r="BO15" s="253" t="str">
         <v>kh</v>
       </c>
       <c r="BP15" s="86" t="str">
@@ -34619,7 +34671,7 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="BO16" s="265" t="str">
+      <c r="BO16" s="253" t="str">
         <v>ng</v>
       </c>
       <c r="BP16" s="86" t="str">
@@ -34925,40 +34977,40 @@
         <v>auⁿ</v>
       </c>
       <c r="BA17" s="134">
+        <f>' 台語音標【xlit解析】'!BB3</f>
+        <v>1</v>
+      </c>
+      <c r="BB17" s="134">
+        <f>' 台語音標【xlit解析】'!BC3</f>
+        <v>7</v>
+      </c>
+      <c r="BC17" s="134">
+        <f>' 台語音標【xlit解析】'!BD3</f>
+        <v>3</v>
+      </c>
+      <c r="BD17" s="134">
+        <f>' 台語音標【xlit解析】'!BE3</f>
+        <v>2</v>
+      </c>
+      <c r="BE17" s="134">
+        <f>' 台語音標【xlit解析】'!BF3</f>
+        <v>5</v>
+      </c>
+      <c r="BF17" s="134">
+        <f>' 台語音標【xlit解析】'!BG3</f>
+        <v>8</v>
+      </c>
+      <c r="BG17" s="134">
+        <f>' 台語音標【xlit解析】'!BH3</f>
+        <v>4</v>
+      </c>
+      <c r="BH17" s="134">
+        <f>' 台語音標【xlit解析】'!BI3</f>
+        <v>0</v>
+      </c>
+      <c r="BI17" s="134" t="str">
         <f>' 台語音標【xlit解析】'!AZ3</f>
-        <v>1</v>
-      </c>
-      <c r="BB17" s="134">
-        <f>' 台語音標【xlit解析】'!BA3</f>
-        <v>7</v>
-      </c>
-      <c r="BC17" s="134">
-        <f>' 台語音標【xlit解析】'!BB3</f>
-        <v>3</v>
-      </c>
-      <c r="BD17" s="134">
-        <f>' 台語音標【xlit解析】'!BC3</f>
-        <v>2</v>
-      </c>
-      <c r="BE17" s="134">
-        <f>' 台語音標【xlit解析】'!BD3</f>
-        <v>5</v>
-      </c>
-      <c r="BF17" s="134">
-        <f>' 台語音標【xlit解析】'!BE3</f>
-        <v>8</v>
-      </c>
-      <c r="BG17" s="134">
-        <f>' 台語音標【xlit解析】'!BF3</f>
-        <v>4</v>
-      </c>
-      <c r="BH17" s="134">
-        <f>' 台語音標【xlit解析】'!BG3</f>
-        <v>0</v>
-      </c>
-      <c r="BI17" s="134" t="str">
-        <f>' 台語音標【xlit解析】'!BH3</f>
-        <v>L</v>
+        <v>ⁿ</v>
       </c>
       <c r="BJ17" s="134"/>
       <c r="BK17" s="134"/>
@@ -34966,7 +35018,7 @@
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="BO17" s="265" t="str">
+      <c r="BO17" s="253" t="str">
         <v>j</v>
       </c>
       <c r="BP17" s="86" t="str">
@@ -35271,39 +35323,39 @@
         <v>y</v>
       </c>
       <c r="BA18" s="124">
+        <f>' 台語音標【xlit解析】'!BB4</f>
+        <v>1</v>
+      </c>
+      <c r="BB18" s="124">
+        <f>' 台語音標【xlit解析】'!BC4</f>
+        <v>7</v>
+      </c>
+      <c r="BC18" s="124">
+        <f>' 台語音標【xlit解析】'!BD4</f>
+        <v>3</v>
+      </c>
+      <c r="BD18" s="124">
+        <f>' 台語音標【xlit解析】'!BE4</f>
+        <v>2</v>
+      </c>
+      <c r="BE18" s="124">
+        <f>' 台語音標【xlit解析】'!BF4</f>
+        <v>5</v>
+      </c>
+      <c r="BF18" s="124">
+        <f>' 台語音標【xlit解析】'!BG4</f>
+        <v>8</v>
+      </c>
+      <c r="BG18" s="124">
+        <f>' 台語音標【xlit解析】'!BH4</f>
+        <v>4</v>
+      </c>
+      <c r="BH18" s="124" t="str">
+        <f>' 台語音標【xlit解析】'!BI4</f>
+        <v>&amp;</v>
+      </c>
+      <c r="BI18" s="124" t="str">
         <f>' 台語音標【xlit解析】'!AZ4</f>
-        <v>1</v>
-      </c>
-      <c r="BB18" s="124">
-        <f>' 台語音標【xlit解析】'!BA4</f>
-        <v>7</v>
-      </c>
-      <c r="BC18" s="124">
-        <f>' 台語音標【xlit解析】'!BB4</f>
-        <v>3</v>
-      </c>
-      <c r="BD18" s="124">
-        <f>' 台語音標【xlit解析】'!BC4</f>
-        <v>2</v>
-      </c>
-      <c r="BE18" s="124">
-        <f>' 台語音標【xlit解析】'!BD4</f>
-        <v>5</v>
-      </c>
-      <c r="BF18" s="124">
-        <f>' 台語音標【xlit解析】'!BE4</f>
-        <v>8</v>
-      </c>
-      <c r="BG18" s="124">
-        <f>' 台語音標【xlit解析】'!BF4</f>
-        <v>4</v>
-      </c>
-      <c r="BH18" s="124" t="str">
-        <f>' 台語音標【xlit解析】'!BG4</f>
-        <v>&amp;</v>
-      </c>
-      <c r="BI18" s="124" t="str">
-        <f>' 台語音標【xlit解析】'!BH4</f>
         <v>L</v>
       </c>
       <c r="BJ18" s="124"/>
@@ -35312,7 +35364,7 @@
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="BO18" s="265" t="str">
+      <c r="BO18" s="253" t="str">
         <v>z(ts)</v>
       </c>
       <c r="BP18" s="86" t="str">
@@ -35617,40 +35669,40 @@
         <v>L</v>
       </c>
       <c r="BA19" s="128" t="str">
+        <f>' 台語音標【xlit解析】'!BB5</f>
+        <v>"</v>
+      </c>
+      <c r="BB19" s="128">
+        <f>' 台語音標【xlit解析】'!BC5</f>
+        <v>5</v>
+      </c>
+      <c r="BC19" s="128">
+        <f>' 台語音標【xlit解析】'!BD5</f>
+        <v>3</v>
+      </c>
+      <c r="BD19" s="128">
+        <f>' 台語音標【xlit解析】'!BE5</f>
+        <v>4</v>
+      </c>
+      <c r="BE19" s="128">
+        <f>' 台語音標【xlit解析】'!BF5</f>
+        <v>6</v>
+      </c>
+      <c r="BF19" s="128" t="str">
+        <f>' 台語音標【xlit解析】'!BG5</f>
+        <v>]</v>
+      </c>
+      <c r="BG19" s="128" t="str">
+        <f>' 台語音標【xlit解析】'!BH5</f>
+        <v>[</v>
+      </c>
+      <c r="BH19" s="128">
+        <f>' 台語音標【xlit解析】'!BI5</f>
+        <v>7</v>
+      </c>
+      <c r="BI19" s="128" t="str">
         <f>' 台語音標【xlit解析】'!AZ5</f>
-        <v>"</v>
-      </c>
-      <c r="BB19" s="128">
-        <f>' 台語音標【xlit解析】'!BA5</f>
-        <v>5</v>
-      </c>
-      <c r="BC19" s="128">
-        <f>' 台語音標【xlit解析】'!BB5</f>
-        <v>3</v>
-      </c>
-      <c r="BD19" s="128">
-        <f>' 台語音標【xlit解析】'!BC5</f>
-        <v>4</v>
-      </c>
-      <c r="BE19" s="128">
-        <f>' 台語音標【xlit解析】'!BD5</f>
-        <v>6</v>
-      </c>
-      <c r="BF19" s="128" t="str">
-        <f>' 台語音標【xlit解析】'!BE5</f>
-        <v>]</v>
-      </c>
-      <c r="BG19" s="128" t="str">
-        <f>' 台語音標【xlit解析】'!BF5</f>
-        <v>[</v>
-      </c>
-      <c r="BH19" s="128">
-        <f>' 台語音標【xlit解析】'!BG5</f>
-        <v>7</v>
-      </c>
-      <c r="BI19" s="128" t="str">
-        <f>' 台語音標【xlit解析】'!BH5</f>
-        <v>.</v>
+        <v>-</v>
       </c>
       <c r="BJ19" s="128"/>
       <c r="BK19" s="128"/>
@@ -35659,7 +35711,7 @@
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="BO19" s="265" t="str">
+      <c r="BO19" s="253" t="str">
         <v>c(tsh)</v>
       </c>
       <c r="BP19" s="86" t="str">
@@ -35964,39 +36016,39 @@
         <v>ㆯ</v>
       </c>
       <c r="BA20" s="131" t="str">
+        <f>' 台語音標【xlit解析】'!BB6</f>
+        <v>一</v>
+      </c>
+      <c r="BB20" s="131" t="str">
+        <f>' 台語音標【xlit解析】'!BC6</f>
+        <v>七</v>
+      </c>
+      <c r="BC20" s="131" t="str">
+        <f>' 台語音標【xlit解析】'!BD6</f>
+        <v>三</v>
+      </c>
+      <c r="BD20" s="131" t="str">
+        <f>' 台語音標【xlit解析】'!BE6</f>
+        <v>二</v>
+      </c>
+      <c r="BE20" s="131" t="str">
+        <f>' 台語音標【xlit解析】'!BF6</f>
+        <v>五</v>
+      </c>
+      <c r="BF20" s="131" t="str">
+        <f>' 台語音標【xlit解析】'!BG6</f>
+        <v>八</v>
+      </c>
+      <c r="BG20" s="131" t="str">
+        <f>' 台語音標【xlit解析】'!BH6</f>
+        <v>四</v>
+      </c>
+      <c r="BH20" s="131" t="str">
+        <f>' 台語音標【xlit解析】'!BI6</f>
+        <v>入</v>
+      </c>
+      <c r="BI20" s="131" t="str">
         <f>' 台語音標【xlit解析】'!AZ6</f>
-        <v>一</v>
-      </c>
-      <c r="BB20" s="131" t="str">
-        <f>' 台語音標【xlit解析】'!BA6</f>
-        <v>七</v>
-      </c>
-      <c r="BC20" s="131" t="str">
-        <f>' 台語音標【xlit解析】'!BB6</f>
-        <v>三</v>
-      </c>
-      <c r="BD20" s="131" t="str">
-        <f>' 台語音標【xlit解析】'!BC6</f>
-        <v>二</v>
-      </c>
-      <c r="BE20" s="131" t="str">
-        <f>' 台語音標【xlit解析】'!BD6</f>
-        <v>五</v>
-      </c>
-      <c r="BF20" s="131" t="str">
-        <f>' 台語音標【xlit解析】'!BE6</f>
-        <v>八</v>
-      </c>
-      <c r="BG20" s="131" t="str">
-        <f>' 台語音標【xlit解析】'!BF6</f>
-        <v>四</v>
-      </c>
-      <c r="BH20" s="131" t="str">
-        <f>' 台語音標【xlit解析】'!BG6</f>
-        <v>入</v>
-      </c>
-      <c r="BI20" s="131" t="str">
-        <f>' 台語音標【xlit解析】'!BH6</f>
         <v>ㄥ</v>
       </c>
       <c r="BJ20" s="131"/>
@@ -36006,7 +36058,7 @@
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="BO20" s="265" t="str">
+      <c r="BO20" s="253" t="str">
         <v>s</v>
       </c>
       <c r="BP20" s="86" t="str">
@@ -36102,7 +36154,7 @@
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="BO21" s="265" t="str">
+      <c r="BO21" s="253" t="str">
         <v>h</v>
       </c>
       <c r="BP21" s="86" t="str">
@@ -36355,7 +36407,7 @@
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="BO22" s="265" t="str">
+      <c r="BO22" s="253" t="str">
         <v>j(i)</v>
       </c>
       <c r="BP22" s="86" t="str">
@@ -36664,7 +36716,7 @@
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="BO23" s="265" t="str">
+      <c r="BO23" s="253" t="str">
         <v>z(i)</v>
       </c>
       <c r="BP23" s="86" t="str">
@@ -36980,7 +37032,7 @@
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="BO24" s="265" t="str">
+      <c r="BO24" s="253" t="str">
         <v>c(i)</v>
       </c>
       <c r="BP24" s="86" t="str">
@@ -37102,7 +37154,7 @@
         <f t="shared" si="4"/>
         <v>21</v>
       </c>
-      <c r="BO25" s="265" t="str">
+      <c r="BO25" s="253" t="str">
         <v>s(i)</v>
       </c>
       <c r="BP25" s="86" t="str">
@@ -37250,7 +37302,7 @@
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="BO26" s="265" t="str">
+      <c r="BO26" s="253" t="str">
         <v>a</v>
       </c>
       <c r="BP26" s="86" t="str">
@@ -37384,7 +37436,7 @@
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="BO27" s="265" t="str">
+      <c r="BO27" s="253" t="str">
         <v>i</v>
       </c>
       <c r="BP27" s="86" t="str">
@@ -37518,7 +37570,7 @@
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="BO28" s="265" t="str">
+      <c r="BO28" s="253" t="str">
         <v>ir</v>
       </c>
       <c r="BP28" s="86" t="str">
@@ -37645,7 +37697,7 @@
         <f t="shared" si="4"/>
         <v>25</v>
       </c>
-      <c r="BO29" s="265" t="str">
+      <c r="BO29" s="253" t="str">
         <v>u</v>
       </c>
       <c r="BP29" s="86" t="str">
@@ -37785,7 +37837,7 @@
         <f t="shared" si="4"/>
         <v>26</v>
       </c>
-      <c r="BO30" s="265" t="str">
+      <c r="BO30" s="253" t="str">
         <v>e</v>
       </c>
       <c r="BP30" s="86" t="str">
@@ -37917,7 +37969,7 @@
         <f t="shared" si="4"/>
         <v>27</v>
       </c>
-      <c r="BO31" s="265" t="str">
+      <c r="BO31" s="253" t="str">
         <v>oo</v>
       </c>
       <c r="BP31" s="86" t="str">
@@ -38022,7 +38074,7 @@
         <f t="shared" si="4"/>
         <v>28</v>
       </c>
-      <c r="BO32" s="265" t="str">
+      <c r="BO32" s="253" t="str">
         <v>o</v>
       </c>
       <c r="BP32" s="86" t="str">
@@ -38154,7 +38206,7 @@
         <f t="shared" si="4"/>
         <v>29</v>
       </c>
-      <c r="BO33" s="265" t="str">
+      <c r="BO33" s="253" t="str">
         <v>-m</v>
       </c>
       <c r="BP33" s="86" t="str">
@@ -38230,7 +38282,7 @@
       <c r="A34" s="147"/>
       <c r="B34" s="152" t="str">
         <f>_xlfn.CONCAT("  alphabet: """,D19:AZ19,BI19:BK19,BA19:BH19,"""")</f>
-        <v xml:space="preserve">  alphabet: "!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L."5346][7"</v>
+        <v xml:space="preserve">  alphabet: "!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L-"5346][7"</v>
       </c>
       <c r="C34" s="153"/>
       <c r="D34" s="153"/>
@@ -38292,7 +38344,7 @@
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="BO34" s="265" t="str">
+      <c r="BO34" s="253" t="str">
         <v>-n</v>
       </c>
       <c r="BP34" s="86" t="str">
@@ -38368,7 +38420,7 @@
       <c r="A35" s="61"/>
       <c r="B35" s="152" t="str">
         <f>_xlfn.CONCAT("  initials: """,D19:AZ19,BI19:BK19,"""")</f>
-        <v xml:space="preserve">  initials: "!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L."</v>
+        <v xml:space="preserve">  initials: "!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L-"</v>
       </c>
       <c r="C35" s="154"/>
       <c r="D35" s="155"/>
@@ -38436,7 +38488,7 @@
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="BO35" s="265" t="str">
+      <c r="BO35" s="253" t="str">
         <v>-ng</v>
       </c>
       <c r="BP35" s="86" t="str">
@@ -38579,7 +38631,7 @@
         <f t="shared" si="4"/>
         <v>32</v>
       </c>
-      <c r="BO36" s="265" t="str">
+      <c r="BO36" s="253" t="str">
         <v>-p</v>
       </c>
       <c r="BP36" s="86" t="str">
@@ -38677,7 +38729,7 @@
         <f t="shared" si="4"/>
         <v>33</v>
       </c>
-      <c r="BO37" s="265" t="str">
+      <c r="BO37" s="253" t="str">
         <v>-t</v>
       </c>
       <c r="BP37" s="86" t="str">
@@ -38779,7 +38831,7 @@
         <f t="shared" si="4"/>
         <v>34</v>
       </c>
-      <c r="BO38" s="265" t="str">
+      <c r="BO38" s="253" t="str">
         <v>-k</v>
       </c>
       <c r="BP38" s="86" t="str">
@@ -38919,7 +38971,7 @@
         <f t="shared" si="4"/>
         <v>35</v>
       </c>
-      <c r="BO39" s="265" t="str">
+      <c r="BO39" s="253" t="str">
         <v>-h</v>
       </c>
       <c r="BP39" s="86" t="str">
@@ -39063,7 +39115,7 @@
         <f t="shared" si="4"/>
         <v>36</v>
       </c>
-      <c r="BO40" s="265" t="str">
+      <c r="BO40" s="253" t="str">
         <v>ai</v>
       </c>
       <c r="BP40" s="86" t="str">
@@ -39227,7 +39279,7 @@
         <f t="shared" si="4"/>
         <v>37</v>
       </c>
-      <c r="BO41" s="265" t="str">
+      <c r="BO41" s="253" t="str">
         <v>au</v>
       </c>
       <c r="BP41" s="86" t="str">
@@ -39309,7 +39361,7 @@
       </c>
       <c r="E42" s="172" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(D19:BK19)</f>
-        <v>!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L"5346][7.</v>
+        <v>!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L"5346][7-</v>
       </c>
       <c r="F42" s="173"/>
       <c r="G42" s="173"/>
@@ -39387,7 +39439,7 @@
         <f t="shared" si="4"/>
         <v>38</v>
       </c>
-      <c r="BO42" s="265" t="str">
+      <c r="BO42" s="253" t="str">
         <v>am</v>
       </c>
       <c r="BP42" s="86" t="str">
@@ -39460,7 +39512,7 @@
       <c r="A43" s="135"/>
       <c r="B43" s="174" t="str">
         <f xml:space="preserve"> "    - xlit|" &amp; E41 &amp; "|" &amp; E42 &amp; "|"</f>
-        <v xml:space="preserve">    - xlit|bpPmntTlgkKŋjzcshJZCSaiwueOəMNGRFQVIUY@AWHdfqrvxy1732584&amp;L|!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L"5346][7.|</v>
+        <v xml:space="preserve">    - xlit|bpPmntTlgkKŋjzcshJZCSaiwueOəMNGRFQVIUY@AWHdfqrvxy1732584&amp;L|!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L"5346][7-|</v>
       </c>
       <c r="C43" s="175"/>
       <c r="D43" s="175"/>
@@ -39534,7 +39586,7 @@
         <f t="shared" si="4"/>
         <v>39</v>
       </c>
-      <c r="BO43" s="265" t="str">
+      <c r="BO43" s="253" t="str">
         <v>an</v>
       </c>
       <c r="BP43" s="86" t="str">
@@ -39619,7 +39671,7 @@
         <f t="shared" si="4"/>
         <v>40</v>
       </c>
-      <c r="BO44" s="265" t="str">
+      <c r="BO44" s="253" t="str">
         <v>ang</v>
       </c>
       <c r="BP44" s="86" t="str">
@@ -39694,7 +39746,7 @@
         <f t="shared" si="4"/>
         <v>41</v>
       </c>
-      <c r="BO45" s="265" t="str">
+      <c r="BO45" s="253" t="str">
         <v>om</v>
       </c>
       <c r="BP45" s="86" t="str">
@@ -39951,7 +40003,7 @@
         <f t="shared" si="4"/>
         <v>42</v>
       </c>
-      <c r="BO46" s="265" t="str">
+      <c r="BO46" s="253" t="str">
         <v>ong</v>
       </c>
       <c r="BP46" s="86" t="str">
@@ -40268,7 +40320,7 @@
         <f t="shared" si="4"/>
         <v>43</v>
       </c>
-      <c r="BO47" s="265" t="str">
+      <c r="BO47" s="253" t="str">
         <v>aⁿ</v>
       </c>
       <c r="BP47" s="86" t="str">
@@ -40567,7 +40619,7 @@
       </c>
       <c r="BG48" s="183" t="str">
         <f t="shared" si="20"/>
-        <v>.</v>
+        <v>-</v>
       </c>
       <c r="BH48" s="183" t="str">
         <f t="shared" si="20"/>
@@ -40584,7 +40636,7 @@
         <f t="shared" si="4"/>
         <v>44</v>
       </c>
-      <c r="BO48" s="265" t="str">
+      <c r="BO48" s="253" t="str">
         <v>iⁿ</v>
       </c>
       <c r="BP48" s="86" t="str">
@@ -40667,7 +40719,7 @@
         <f t="shared" si="4"/>
         <v>45</v>
       </c>
-      <c r="BO49" s="265" t="str">
+      <c r="BO49" s="253" t="str">
         <v>uⁿ</v>
       </c>
       <c r="BP49" s="86" t="str">
@@ -40803,7 +40855,7 @@
         <f t="shared" si="4"/>
         <v>46</v>
       </c>
-      <c r="BO50" s="265" t="str">
+      <c r="BO50" s="253" t="str">
         <v>eⁿ</v>
       </c>
       <c r="BP50" s="86" t="str">
@@ -40942,7 +40994,7 @@
         <f t="shared" si="4"/>
         <v>47</v>
       </c>
-      <c r="BO51" s="265" t="str">
+      <c r="BO51" s="253" t="str">
         <v>oⁿ</v>
       </c>
       <c r="BP51" s="86" t="str">
@@ -41080,7 +41132,7 @@
         <f t="shared" si="4"/>
         <v>48</v>
       </c>
-      <c r="BO52" s="265" t="str">
+      <c r="BO52" s="253" t="str">
         <v>aiⁿ</v>
       </c>
       <c r="BP52" s="86" t="str">
@@ -41160,7 +41212,7 @@
       </c>
       <c r="E53" s="188" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(D19:BK19)</f>
-        <v>!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L"5346][7.</v>
+        <v>!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L"5346][7-</v>
       </c>
       <c r="F53" s="188"/>
       <c r="G53" s="188"/>
@@ -41225,7 +41277,7 @@
         <f t="shared" si="4"/>
         <v>49</v>
       </c>
-      <c r="BO53" s="265" t="str">
+      <c r="BO53" s="253" t="str">
         <v>auⁿ</v>
       </c>
       <c r="BP53" s="86" t="str">
@@ -41370,7 +41422,7 @@
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="BO54" s="265">
+      <c r="BO54" s="253">
         <v>1</v>
       </c>
       <c r="BP54" s="86">
@@ -41441,7 +41493,7 @@
     <row r="55" spans="1:109" ht="45" customHeight="1">
       <c r="B55" s="174" t="str">
         <f xml:space="preserve"> "    - xlit|" &amp; E53 &amp; "|" &amp; E54 &amp; "|"</f>
-        <v xml:space="preserve">    - xlit|!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L"5346][7.|ㆠㄅㄆㄇㄋㄉㄊㄌㆣㄍㄎㄫㆡㄗㄘㄙㄏㆢㄐㄑㄒㄚㄧㆨㄨㆤㆦㄜㆬㄣㆭㆴㆵㆻㆷㄞㄠㆰㄢㄤㆱㆲㆩㆪㆫㆥㆧㆮㆯ一七三二五八四入ㄥ|</v>
+        <v xml:space="preserve">    - xlit|!1qas2wxEedNYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L"5346][7-|ㆠㄅㄆㄇㄋㄉㄊㄌㆣㄍㄎㄫㆡㄗㄘㄙㄏㆢㄐㄑㄒㄚㄧㆨㄨㆤㆦㄜㆬㄣㆭㆴㆵㆻㆷㄞㄠㆰㄢㄤㆱㆲㆩㆪㆫㆥㆧㆮㆯ一七三二五八四入ㄥ|</v>
       </c>
       <c r="C55" s="192"/>
       <c r="D55" s="192"/>
@@ -41509,7 +41561,7 @@
         <f t="shared" si="4"/>
         <v>51</v>
       </c>
-      <c r="BO55" s="265">
+      <c r="BO55" s="253">
         <v>7</v>
       </c>
       <c r="BP55" s="86">
@@ -41648,7 +41700,7 @@
         <f t="shared" si="4"/>
         <v>52</v>
       </c>
-      <c r="BO56" s="265">
+      <c r="BO56" s="253">
         <v>3</v>
       </c>
       <c r="BP56" s="86">
@@ -41724,7 +41776,7 @@
         <f t="shared" si="4"/>
         <v>53</v>
       </c>
-      <c r="BO57" s="265">
+      <c r="BO57" s="253">
         <v>2</v>
       </c>
       <c r="BP57" s="86">
@@ -41976,7 +42028,7 @@
         <f t="shared" si="4"/>
         <v>54</v>
       </c>
-      <c r="BO58" s="265">
+      <c r="BO58" s="253">
         <v>5</v>
       </c>
       <c r="BP58" s="86">
@@ -42271,7 +42323,7 @@
       </c>
       <c r="BG59" s="183" t="str">
         <f t="shared" si="21"/>
-        <v>.</v>
+        <v>-</v>
       </c>
       <c r="BH59" s="183" t="str">
         <f t="shared" si="21"/>
@@ -42288,7 +42340,7 @@
         <f t="shared" si="4"/>
         <v>55</v>
       </c>
-      <c r="BO59" s="265">
+      <c r="BO59" s="253">
         <v>8</v>
       </c>
       <c r="BP59" s="86">
@@ -42600,7 +42652,7 @@
         <f t="shared" si="4"/>
         <v>56</v>
       </c>
-      <c r="BO60" s="265">
+      <c r="BO60" s="253">
         <v>4</v>
       </c>
       <c r="BP60" s="86">
@@ -42732,7 +42784,7 @@
         <f t="shared" si="4"/>
         <v>57</v>
       </c>
-      <c r="BO61" s="265">
+      <c r="BO61" s="253">
         <v>0</v>
       </c>
       <c r="BP61" s="86" t="str">
@@ -42864,14 +42916,14 @@
         <f t="shared" si="4"/>
         <v>58</v>
       </c>
-      <c r="BO62" s="265" t="str">
-        <v>L</v>
+      <c r="BO62" s="253" t="str">
+        <v>ⁿ</v>
       </c>
       <c r="BP62" s="86" t="str">
         <v>L</v>
       </c>
       <c r="BQ62" s="76" t="str">
-        <v>.</v>
+        <v>-</v>
       </c>
       <c r="BR62" s="77" t="str">
         <v>ㄥ</v>
@@ -42885,7 +42937,7 @@
       </c>
       <c r="BV62" s="89" t="str">
         <f t="shared" si="16"/>
-        <v xml:space="preserve">    ".": { commit: "ㄥ" }  # /L/ ==&gt; L</v>
+        <v xml:space="preserve">    "-": { commit: "ㄥ" }  # /ⁿ/ ==&gt; L</v>
       </c>
       <c r="BX62" s="85">
         <f t="shared" si="6"/>
@@ -42998,7 +43050,7 @@
         <f t="shared" si="4"/>
         <v>59</v>
       </c>
-      <c r="BO63" s="265"/>
+      <c r="BO63" s="253"/>
       <c r="BP63" s="86"/>
       <c r="BQ63" s="76"/>
       <c r="BR63" s="77"/>
@@ -43118,7 +43170,7 @@
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="BO64" s="265"/>
+      <c r="BO64" s="253"/>
       <c r="BP64" s="86"/>
       <c r="BQ64" s="76"/>
       <c r="BR64" s="77"/>
@@ -46784,25 +46836,25 @@
   <sheetData>
     <row r="1" spans="2:19" ht="21.75" thickBot="1"/>
     <row r="2" spans="2:19" ht="24" thickBot="1">
-      <c r="B2" s="256" t="s">
+      <c r="B2" s="267" t="s">
         <v>328</v>
       </c>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="269" t="s">
         <v>329</v>
       </c>
-      <c r="D2" s="259"/>
-      <c r="E2" s="262" t="s">
+      <c r="D2" s="270"/>
+      <c r="E2" s="273" t="s">
         <v>330</v>
       </c>
-      <c r="F2" s="263"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="262" t="s">
+      <c r="F2" s="274"/>
+      <c r="G2" s="275"/>
+      <c r="H2" s="273" t="s">
         <v>331</v>
       </c>
-      <c r="I2" s="263"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="263"/>
-      <c r="L2" s="264"/>
+      <c r="I2" s="274"/>
+      <c r="J2" s="274"/>
+      <c r="K2" s="274"/>
+      <c r="L2" s="275"/>
       <c r="O2" s="228" t="s">
         <v>480</v>
       </c>
@@ -46817,9 +46869,9 @@
       </c>
     </row>
     <row r="3" spans="2:19" ht="24" thickBot="1">
-      <c r="B3" s="257"/>
-      <c r="C3" s="260"/>
-      <c r="D3" s="261"/>
+      <c r="B3" s="268"/>
+      <c r="C3" s="271"/>
+      <c r="D3" s="272"/>
       <c r="E3" s="226" t="s">
         <v>332</v>
       </c>
@@ -46838,10 +46890,10 @@
       <c r="J3" s="226" t="s">
         <v>337</v>
       </c>
-      <c r="K3" s="262" t="s">
+      <c r="K3" s="273" t="s">
         <v>338</v>
       </c>
-      <c r="L3" s="264"/>
+      <c r="L3" s="275"/>
       <c r="O3" s="228" t="s">
         <v>274</v>
       </c>
@@ -47733,57 +47785,57 @@
       <c r="B27" s="226" t="s">
         <v>443</v>
       </c>
-      <c r="C27" s="253" t="s">
+      <c r="C27" s="276" t="s">
         <v>188</v>
       </c>
-      <c r="D27" s="254"/>
-      <c r="E27" s="253" t="s">
+      <c r="D27" s="277"/>
+      <c r="E27" s="276" t="s">
         <v>444</v>
       </c>
-      <c r="F27" s="255"/>
-      <c r="G27" s="255"/>
-      <c r="H27" s="255"/>
-      <c r="I27" s="255"/>
-      <c r="J27" s="254"/>
-      <c r="K27" s="253" t="s">
+      <c r="F27" s="278"/>
+      <c r="G27" s="278"/>
+      <c r="H27" s="278"/>
+      <c r="I27" s="278"/>
+      <c r="J27" s="277"/>
+      <c r="K27" s="276" t="s">
         <v>445</v>
       </c>
-      <c r="L27" s="254"/>
+      <c r="L27" s="277"/>
     </row>
     <row r="28" spans="2:20" ht="24" thickBot="1">
       <c r="B28" s="226" t="s">
         <v>446</v>
       </c>
-      <c r="C28" s="253" t="s">
+      <c r="C28" s="276" t="s">
         <v>447</v>
       </c>
-      <c r="D28" s="254"/>
-      <c r="E28" s="253" t="s">
+      <c r="D28" s="277"/>
+      <c r="E28" s="276" t="s">
         <v>444</v>
       </c>
-      <c r="F28" s="255"/>
-      <c r="G28" s="255"/>
-      <c r="H28" s="255"/>
-      <c r="I28" s="255"/>
-      <c r="J28" s="254"/>
-      <c r="K28" s="253" t="s">
+      <c r="F28" s="278"/>
+      <c r="G28" s="278"/>
+      <c r="H28" s="278"/>
+      <c r="I28" s="278"/>
+      <c r="J28" s="277"/>
+      <c r="K28" s="276" t="s">
         <v>448</v>
       </c>
-      <c r="L28" s="254"/>
+      <c r="L28" s="277"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:D3"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="K3:L3"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="E27:J27"/>
     <mergeCell ref="K27:L27"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:J28"/>
     <mergeCell ref="K28:L28"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:D3"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -47805,30 +47857,30 @@
   <sheetData>
     <row r="1" spans="2:20" ht="21.75" thickBot="1"/>
     <row r="2" spans="2:20" ht="24" thickBot="1">
-      <c r="B2" s="256" t="s">
+      <c r="B2" s="267" t="s">
         <v>328</v>
       </c>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="269" t="s">
         <v>329</v>
       </c>
-      <c r="D2" s="259"/>
-      <c r="E2" s="262" t="s">
+      <c r="D2" s="270"/>
+      <c r="E2" s="273" t="s">
         <v>330</v>
       </c>
-      <c r="F2" s="263"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="262" t="s">
+      <c r="F2" s="274"/>
+      <c r="G2" s="275"/>
+      <c r="H2" s="273" t="s">
         <v>331</v>
       </c>
-      <c r="I2" s="263"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="263"/>
-      <c r="L2" s="264"/>
+      <c r="I2" s="274"/>
+      <c r="J2" s="274"/>
+      <c r="K2" s="274"/>
+      <c r="L2" s="275"/>
     </row>
     <row r="3" spans="2:20" ht="24" thickBot="1">
-      <c r="B3" s="257"/>
-      <c r="C3" s="260"/>
-      <c r="D3" s="261"/>
+      <c r="B3" s="268"/>
+      <c r="C3" s="271"/>
+      <c r="D3" s="272"/>
       <c r="E3" s="226" t="s">
         <v>332</v>
       </c>
@@ -47847,10 +47899,10 @@
       <c r="J3" s="226" t="s">
         <v>337</v>
       </c>
-      <c r="K3" s="262" t="s">
+      <c r="K3" s="273" t="s">
         <v>338</v>
       </c>
-      <c r="L3" s="264"/>
+      <c r="L3" s="275"/>
       <c r="N3" s="232" t="s">
         <v>505</v>
       </c>
@@ -48883,43 +48935,43 @@
       <c r="B27" s="226" t="s">
         <v>443</v>
       </c>
-      <c r="C27" s="253" t="s">
+      <c r="C27" s="276" t="s">
         <v>188</v>
       </c>
-      <c r="D27" s="254"/>
-      <c r="E27" s="253" t="s">
+      <c r="D27" s="277"/>
+      <c r="E27" s="276" t="s">
         <v>444</v>
       </c>
-      <c r="F27" s="255"/>
-      <c r="G27" s="255"/>
-      <c r="H27" s="255"/>
-      <c r="I27" s="255"/>
-      <c r="J27" s="254"/>
-      <c r="K27" s="253" t="s">
+      <c r="F27" s="278"/>
+      <c r="G27" s="278"/>
+      <c r="H27" s="278"/>
+      <c r="I27" s="278"/>
+      <c r="J27" s="277"/>
+      <c r="K27" s="276" t="s">
         <v>445</v>
       </c>
-      <c r="L27" s="254"/>
+      <c r="L27" s="277"/>
     </row>
     <row r="28" spans="2:21" ht="24" thickBot="1">
       <c r="B28" s="226" t="s">
         <v>446</v>
       </c>
-      <c r="C28" s="253" t="s">
+      <c r="C28" s="276" t="s">
         <v>447</v>
       </c>
-      <c r="D28" s="254"/>
-      <c r="E28" s="253" t="s">
+      <c r="D28" s="277"/>
+      <c r="E28" s="276" t="s">
         <v>444</v>
       </c>
-      <c r="F28" s="255"/>
-      <c r="G28" s="255"/>
-      <c r="H28" s="255"/>
-      <c r="I28" s="255"/>
-      <c r="J28" s="254"/>
-      <c r="K28" s="253" t="s">
+      <c r="F28" s="278"/>
+      <c r="G28" s="278"/>
+      <c r="H28" s="278"/>
+      <c r="I28" s="278"/>
+      <c r="J28" s="277"/>
+      <c r="K28" s="276" t="s">
         <v>448</v>
       </c>
-      <c r="L28" s="254"/>
+      <c r="L28" s="277"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N4:T20">
@@ -48958,25 +49010,25 @@
   <sheetData>
     <row r="1" spans="2:18" ht="21.75" thickBot="1"/>
     <row r="2" spans="2:18" ht="24" thickBot="1">
-      <c r="B2" s="256" t="s">
+      <c r="B2" s="267" t="s">
         <v>328</v>
       </c>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="269" t="s">
         <v>329</v>
       </c>
-      <c r="D2" s="259"/>
-      <c r="E2" s="262" t="s">
+      <c r="D2" s="270"/>
+      <c r="E2" s="273" t="s">
         <v>330</v>
       </c>
-      <c r="F2" s="263"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="262" t="s">
+      <c r="F2" s="274"/>
+      <c r="G2" s="275"/>
+      <c r="H2" s="273" t="s">
         <v>331</v>
       </c>
-      <c r="I2" s="263"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="263"/>
-      <c r="L2" s="264"/>
+      <c r="I2" s="274"/>
+      <c r="J2" s="274"/>
+      <c r="K2" s="274"/>
+      <c r="L2" s="275"/>
       <c r="P2" s="228" t="str">
         <f xml:space="preserve"> "([48])"</f>
         <v>([48])</v>
@@ -48986,9 +49038,9 @@
       </c>
     </row>
     <row r="3" spans="2:18" ht="24" thickBot="1">
-      <c r="B3" s="257"/>
-      <c r="C3" s="260"/>
-      <c r="D3" s="261"/>
+      <c r="B3" s="268"/>
+      <c r="C3" s="271"/>
+      <c r="D3" s="272"/>
       <c r="E3" s="226" t="s">
         <v>332</v>
       </c>
@@ -49007,10 +49059,10 @@
       <c r="J3" s="226" t="s">
         <v>337</v>
       </c>
-      <c r="K3" s="262" t="s">
+      <c r="K3" s="273" t="s">
         <v>338</v>
       </c>
-      <c r="L3" s="264"/>
+      <c r="L3" s="275"/>
       <c r="N3" s="228" t="s">
         <v>450</v>
       </c>
@@ -49902,43 +49954,43 @@
       <c r="B27" s="226" t="s">
         <v>443</v>
       </c>
-      <c r="C27" s="253" t="s">
+      <c r="C27" s="276" t="s">
         <v>188</v>
       </c>
-      <c r="D27" s="254"/>
-      <c r="E27" s="253" t="s">
+      <c r="D27" s="277"/>
+      <c r="E27" s="276" t="s">
         <v>444</v>
       </c>
-      <c r="F27" s="255"/>
-      <c r="G27" s="255"/>
-      <c r="H27" s="255"/>
-      <c r="I27" s="255"/>
-      <c r="J27" s="254"/>
-      <c r="K27" s="253" t="s">
+      <c r="F27" s="278"/>
+      <c r="G27" s="278"/>
+      <c r="H27" s="278"/>
+      <c r="I27" s="278"/>
+      <c r="J27" s="277"/>
+      <c r="K27" s="276" t="s">
         <v>445</v>
       </c>
-      <c r="L27" s="254"/>
+      <c r="L27" s="277"/>
     </row>
     <row r="28" spans="2:19" ht="24" thickBot="1">
       <c r="B28" s="226" t="s">
         <v>446</v>
       </c>
-      <c r="C28" s="253" t="s">
+      <c r="C28" s="276" t="s">
         <v>447</v>
       </c>
-      <c r="D28" s="254"/>
-      <c r="E28" s="253" t="s">
+      <c r="D28" s="277"/>
+      <c r="E28" s="276" t="s">
         <v>444</v>
       </c>
-      <c r="F28" s="255"/>
-      <c r="G28" s="255"/>
-      <c r="H28" s="255"/>
-      <c r="I28" s="255"/>
-      <c r="J28" s="254"/>
-      <c r="K28" s="253" t="s">
+      <c r="F28" s="278"/>
+      <c r="G28" s="278"/>
+      <c r="H28" s="278"/>
+      <c r="I28" s="278"/>
+      <c r="J28" s="277"/>
+      <c r="K28" s="276" t="s">
         <v>448</v>
       </c>
-      <c r="L28" s="254"/>
+      <c r="L28" s="277"/>
     </row>
   </sheetData>
   <mergeCells count="11">

--- a/docs/301_鍵盤設計規格_方音符號輸入_台語注音二式編碼.xlsx
+++ b/docs/301_鍵盤設計規格_方音符號輸入_台語注音二式編碼.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E9C899-948C-4036-A62A-68B0C6C654BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23DA727F-83DE-41D5-9D1C-09419340D81E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{6D6F034E-466E-416C-B3CC-1F7937B8DE3D}"/>
+    <workbookView xWindow="54480" yWindow="-2985" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{6D6F034E-466E-416C-B3CC-1F7937B8DE3D}"/>
   </bookViews>
   <sheets>
     <sheet name="台語注音二式【xlit解析】" sheetId="7" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -4251,6 +4251,21 @@
     <xf numFmtId="176" fontId="121" fillId="9" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="122" fillId="15" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="118" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -4262,15 +4277,6 @@
     </xf>
     <xf numFmtId="176" fontId="21" fillId="9" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="29" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="29" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="29" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="100" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4299,20 +4305,14 @@
     <xf numFmtId="0" fontId="100" fillId="30" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="122" fillId="15" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    <xf numFmtId="0" fontId="101" fillId="29" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="101" fillId="29" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="101" fillId="29" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -9708,27 +9708,27 @@
         <v>1</v>
       </c>
       <c r="BC39" s="4" t="str">
-        <f>AZ18</f>
+        <f t="shared" ref="BC39:BH39" si="10">AZ18</f>
         <v>7</v>
       </c>
       <c r="BD39" s="4" t="str">
-        <f>BA18</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="BE39" s="4" t="str">
-        <f>BB18</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="BF39" s="4" t="str">
-        <f>BC18</f>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="BG39" s="4" t="str">
-        <f>BD18</f>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
       <c r="BH39" s="4" t="str">
-        <f>BE18</f>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="BI39" s="4"/>
@@ -9759,195 +9759,195 @@
         <v>!</v>
       </c>
       <c r="D40" s="247" t="str">
-        <f t="shared" ref="D40:AY40" si="10">D19</f>
+        <f t="shared" ref="D40:AY40" si="11">D19</f>
         <v>1</v>
       </c>
       <c r="E40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>q</v>
       </c>
       <c r="F40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>a</v>
       </c>
       <c r="G40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="H40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>w</v>
       </c>
       <c r="I40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>s</v>
       </c>
       <c r="J40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>x</v>
       </c>
       <c r="K40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>E</v>
       </c>
       <c r="L40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>e</v>
       </c>
       <c r="M40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>d</v>
       </c>
       <c r="N40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>G</v>
       </c>
       <c r="O40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Y</v>
       </c>
       <c r="P40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>y</v>
       </c>
       <c r="Q40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>h</v>
       </c>
       <c r="R40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>n</v>
       </c>
       <c r="S40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>R</v>
       </c>
       <c r="T40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>r</v>
       </c>
       <c r="U40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>f</v>
       </c>
       <c r="V40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>v</v>
       </c>
       <c r="W40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>c</v>
       </c>
       <c r="X40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>8</v>
       </c>
       <c r="Y40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>u</v>
       </c>
       <c r="Z40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>K</v>
       </c>
       <c r="AA40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>j</v>
       </c>
       <c r="AB40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>,</v>
       </c>
       <c r="AC40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>i</v>
       </c>
       <c r="AD40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>k</v>
       </c>
       <c r="AE40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
       <c r="AF40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>l</v>
       </c>
       <c r="AG40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>*</v>
       </c>
       <c r="AH40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>U</v>
       </c>
       <c r="AI40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>J</v>
       </c>
       <c r="AJ40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>&lt;</v>
       </c>
       <c r="AK40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>I</v>
       </c>
       <c r="AL40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>(</v>
       </c>
       <c r="AM40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>L</v>
       </c>
       <c r="AN40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>m</v>
       </c>
       <c r="AO40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>/</v>
       </c>
       <c r="AP40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>p</v>
       </c>
       <c r="AQ40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>M</v>
       </c>
       <c r="AR40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AS40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>;</v>
       </c>
       <c r="AT40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>O</v>
       </c>
       <c r="AU40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>o</v>
       </c>
       <c r="AV40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>b</v>
       </c>
       <c r="AW40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>t</v>
       </c>
       <c r="AX40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>g</v>
       </c>
       <c r="AY40" s="247" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>z</v>
       </c>
       <c r="AZ40" s="247" t="s">
@@ -10010,195 +10010,195 @@
         <v>ㆠ</v>
       </c>
       <c r="D41" s="242" t="str">
-        <f t="shared" ref="D41:AY41" si="11">D34</f>
+        <f t="shared" ref="D41:AY41" si="12">D34</f>
         <v>ㄅ</v>
       </c>
       <c r="E41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㄆ</v>
       </c>
       <c r="F41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㄇ</v>
       </c>
       <c r="G41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㄉ</v>
       </c>
       <c r="H41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㄊ</v>
       </c>
       <c r="I41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㄋ</v>
       </c>
       <c r="J41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㄌ</v>
       </c>
       <c r="K41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㆣ</v>
       </c>
       <c r="L41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㄍ</v>
       </c>
       <c r="M41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㄎ</v>
       </c>
       <c r="N41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㄫ</v>
       </c>
       <c r="O41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㆡ</v>
       </c>
       <c r="P41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㄗ</v>
       </c>
       <c r="Q41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㄘ</v>
       </c>
       <c r="R41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㄙ</v>
       </c>
       <c r="S41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㆢ</v>
       </c>
       <c r="T41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㄐ</v>
       </c>
       <c r="U41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㄑ</v>
       </c>
       <c r="V41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㄒ</v>
       </c>
       <c r="W41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㄏ</v>
       </c>
       <c r="X41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㄚ</v>
       </c>
       <c r="Y41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㄧ</v>
       </c>
       <c r="Z41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㆨ</v>
       </c>
       <c r="AA41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㄨ</v>
       </c>
       <c r="AB41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㆤ</v>
       </c>
       <c r="AC41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㆦ</v>
       </c>
       <c r="AD41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㄜ</v>
       </c>
       <c r="AE41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㄞ</v>
       </c>
       <c r="AF41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㄠ</v>
       </c>
       <c r="AG41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㆩ</v>
       </c>
       <c r="AH41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㆪ</v>
       </c>
       <c r="AI41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㆫ</v>
       </c>
       <c r="AJ41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㆥ</v>
       </c>
       <c r="AK41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㆧ</v>
       </c>
       <c r="AL41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㆮ</v>
       </c>
       <c r="AM41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㆯ</v>
       </c>
       <c r="AN41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㆬ</v>
       </c>
       <c r="AO41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㆭ</v>
       </c>
       <c r="AP41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㄣ</v>
       </c>
       <c r="AQ41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㆰ</v>
       </c>
       <c r="AR41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㄢ</v>
       </c>
       <c r="AS41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㄤ</v>
       </c>
       <c r="AT41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㆱ</v>
       </c>
       <c r="AU41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㆲ</v>
       </c>
       <c r="AV41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㆴ</v>
       </c>
       <c r="AW41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㆵ</v>
       </c>
       <c r="AX41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㆻ</v>
       </c>
       <c r="AY41" s="242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>ㆷ</v>
       </c>
       <c r="AZ41" s="242" t="str">
@@ -10214,27 +10214,27 @@
         <v>一</v>
       </c>
       <c r="BC41" s="242" t="str">
-        <f>AZ34</f>
+        <f t="shared" ref="BC41:BH41" si="13">AZ34</f>
         <v>˫</v>
       </c>
       <c r="BD41" s="242" t="str">
-        <f>BA34</f>
+        <f t="shared" si="13"/>
         <v>˪</v>
       </c>
       <c r="BE41" s="242" t="str">
-        <f>BB34</f>
+        <f t="shared" si="13"/>
         <v>ˋ</v>
       </c>
       <c r="BF41" s="242" t="str">
-        <f>BC34</f>
+        <f t="shared" si="13"/>
         <v>ˊ</v>
       </c>
       <c r="BG41" s="242" t="str">
-        <f>BD34</f>
+        <f t="shared" si="13"/>
         <v>八</v>
       </c>
       <c r="BH41" s="242" t="str">
-        <f>BE34</f>
+        <f t="shared" si="13"/>
         <v>四</v>
       </c>
       <c r="BI41" s="242"/>
@@ -12299,19 +12299,19 @@
       <c r="W3" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="X3" s="268" t="s">
+      <c r="X3" s="273" t="s">
         <v>542</v>
       </c>
-      <c r="Y3" s="269" t="s">
+      <c r="Y3" s="274" t="s">
         <v>40</v>
       </c>
       <c r="Z3" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="AA3" s="268" t="s">
+      <c r="AA3" s="273" t="s">
         <v>547</v>
       </c>
-      <c r="AB3" s="269"/>
+      <c r="AB3" s="274"/>
       <c r="AC3" s="52"/>
       <c r="AD3" s="49"/>
       <c r="AE3" s="53"/>
@@ -12776,28 +12776,28 @@
       <c r="U6" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="V6" s="268" t="s">
+      <c r="V6" s="273" t="s">
         <v>543</v>
       </c>
-      <c r="W6" s="269" t="s">
+      <c r="W6" s="274" t="s">
         <v>87</v>
       </c>
       <c r="X6" s="48" t="s">
         <v>88</v>
       </c>
-      <c r="Y6" s="270" t="s">
+      <c r="Y6" s="275" t="s">
         <v>546</v>
       </c>
-      <c r="Z6" s="271" t="s">
+      <c r="Z6" s="276" t="s">
         <v>89</v>
       </c>
       <c r="AA6" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="AB6" s="270" t="s">
+      <c r="AB6" s="275" t="s">
         <v>275</v>
       </c>
-      <c r="AC6" s="271"/>
+      <c r="AC6" s="276"/>
       <c r="AD6" s="52"/>
       <c r="AE6" s="49"/>
       <c r="AF6" s="53"/>
@@ -13341,28 +13341,28 @@
       <c r="V9" s="48" t="s">
         <v>122</v>
       </c>
-      <c r="W9" s="268" t="s">
+      <c r="W9" s="273" t="s">
         <v>544</v>
       </c>
-      <c r="X9" s="269" t="s">
+      <c r="X9" s="274" t="s">
         <v>123</v>
       </c>
       <c r="Y9" s="52" t="s">
         <v>124</v>
       </c>
-      <c r="Z9" s="270" t="s">
+      <c r="Z9" s="275" t="s">
         <v>259</v>
       </c>
-      <c r="AA9" s="271" t="s">
+      <c r="AA9" s="276" t="s">
         <v>125</v>
       </c>
       <c r="AB9" s="48" t="s">
         <v>126</v>
       </c>
-      <c r="AC9" s="270" t="s">
+      <c r="AC9" s="275" t="s">
         <v>127</v>
       </c>
-      <c r="AD9" s="271"/>
+      <c r="AD9" s="276"/>
       <c r="AE9" s="48"/>
       <c r="AF9" s="49"/>
       <c r="AG9" s="50"/>
@@ -13892,19 +13892,19 @@
       <c r="W12" s="48" t="s">
         <v>160</v>
       </c>
-      <c r="X12" s="268" t="s">
+      <c r="X12" s="273" t="s">
         <v>272</v>
       </c>
-      <c r="Y12" s="269" t="s">
+      <c r="Y12" s="274" t="s">
         <v>123</v>
       </c>
       <c r="Z12" s="48" t="s">
         <v>162</v>
       </c>
-      <c r="AA12" s="268" t="s">
+      <c r="AA12" s="273" t="s">
         <v>545</v>
       </c>
-      <c r="AB12" s="269" t="s">
+      <c r="AB12" s="274" t="s">
         <v>123</v>
       </c>
       <c r="AC12" s="261"/>
@@ -15902,16 +15902,16 @@
       <c r="BD20" s="131" t="s">
         <v>241</v>
       </c>
-      <c r="BE20" s="287" t="s">
+      <c r="BE20" s="271" t="s">
         <v>313</v>
       </c>
-      <c r="BF20" s="287" t="s">
+      <c r="BF20" s="271" t="s">
         <v>311</v>
       </c>
-      <c r="BG20" s="288" t="s">
+      <c r="BG20" s="272" t="s">
         <v>310</v>
       </c>
-      <c r="BH20" s="288" t="s">
+      <c r="BH20" s="272" t="s">
         <v>299</v>
       </c>
       <c r="BI20" s="131" t="s">
@@ -16368,214 +16368,214 @@
     <row r="23" spans="1:111" s="138" customFormat="1" ht="45" customHeight="1">
       <c r="A23" s="135"/>
       <c r="B23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(B22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(B22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" ref="B23:AA23" si="11" xml:space="preserve"> IF( ISNUMBER( FIND(B22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(B22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
         <v>22</v>
       </c>
       <c r="C23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(C22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(C22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="D23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(D22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(D22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>15</v>
       </c>
       <c r="E23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(E22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(E22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="F23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(F22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(F22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>26</v>
       </c>
       <c r="G23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(G22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(G22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>32</v>
       </c>
       <c r="H23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(H22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(H22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="I23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(I22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(I22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>21</v>
       </c>
       <c r="J23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(J22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(J22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>23</v>
       </c>
       <c r="K23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(K22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(K22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>18</v>
       </c>
       <c r="L23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(L22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(L22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>11</v>
       </c>
       <c r="M23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(M22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(M22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>8</v>
       </c>
       <c r="N23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(N22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(N22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="O23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(O22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(O22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
       <c r="P23" s="137" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(P22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(P22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>V</v>
       </c>
       <c r="Q23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(Q22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(Q22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="R23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(R22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(R22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>33</v>
       </c>
       <c r="S23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(S22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(S22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>34</v>
       </c>
       <c r="T23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(T22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(T22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>16</v>
       </c>
       <c r="U23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(U22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(U22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
       <c r="V23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(V22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(V22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>25</v>
       </c>
       <c r="W23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(W22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(W22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>35</v>
       </c>
       <c r="X23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(X22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(X22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>24</v>
       </c>
       <c r="Y23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(Y22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(Y22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>36</v>
       </c>
       <c r="Z23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(Z22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(Z22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>37</v>
       </c>
       <c r="AA23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AA22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AA22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>14</v>
       </c>
       <c r="AB23" s="135"/>
       <c r="AC23" s="135"/>
       <c r="AE23" s="135"/>
       <c r="AL23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AL22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AL22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" ref="AL23:BK23" si="12" xml:space="preserve"> IF( ISNUMBER( FIND(AL22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AL22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
         <v>22</v>
       </c>
       <c r="AM23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AM22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AM22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
       <c r="AN23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AN22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AN22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>15</v>
       </c>
       <c r="AO23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AO22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AO22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>5</v>
       </c>
       <c r="AP23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AP22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AP22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>26</v>
       </c>
       <c r="AQ23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AQ22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AQ22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>32</v>
       </c>
       <c r="AR23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AR22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AR22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="AS23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AS22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AS22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>21</v>
       </c>
       <c r="AT23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AT22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AT22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>23</v>
       </c>
       <c r="AU23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AU22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AU22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>18</v>
       </c>
       <c r="AV23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AV22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AV22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>11</v>
       </c>
       <c r="AW23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AW22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AW22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>8</v>
       </c>
       <c r="AX23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AX22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AX22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
       <c r="AY23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AY22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AY22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>7</v>
       </c>
       <c r="AZ23" s="137" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AZ22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AZ22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>V</v>
       </c>
       <c r="BA23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BA22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(BA22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>3</v>
       </c>
       <c r="BB23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BB22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(BB22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>33</v>
       </c>
       <c r="BC23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BC22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(BC22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>34</v>
       </c>
       <c r="BD23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BD22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(BD22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>16</v>
       </c>
       <c r="BE23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BE22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(BE22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>6</v>
       </c>
       <c r="BF23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BF22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(BF22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>25</v>
       </c>
       <c r="BG23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BG22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(BG22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>35</v>
       </c>
       <c r="BH23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BH22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(BH22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>24</v>
       </c>
       <c r="BI23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BI22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(BI22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>36</v>
       </c>
       <c r="BJ23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BJ22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(BJ22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>37</v>
       </c>
       <c r="BK23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BK22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(BK22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
       <c r="BL23" s="135"/>
@@ -16678,107 +16678,107 @@
     <row r="24" spans="1:111" s="135" customFormat="1" ht="45" customHeight="1">
       <c r="A24" s="61"/>
       <c r="B24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(B22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", B22)</f>
+        <f t="shared" ref="B24:AA24" si="13" xml:space="preserve"> IF( ISNUMBER( FIND(B22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", B22)</f>
         <v>X</v>
       </c>
       <c r="C24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(C22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", C22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="D24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(D22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", D22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="E24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(E22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", E22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="F24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(F22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", F22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="G24" s="140" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(G22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", G22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="H24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(H22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", H22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="I24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(I22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", I22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="J24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(J22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", J22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="K24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(K22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", K22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="L24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(L22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", L22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="M24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(M22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", M22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="N24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(N22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", N22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="O24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(O22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", O22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="P24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(P22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", P22)</f>
+        <f t="shared" si="13"/>
         <v>o</v>
       </c>
       <c r="Q24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(Q22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", Q22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="R24" s="140" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(R22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", R22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="S24" s="140" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(S22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", S22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="T24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(T22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", T22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="U24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(U22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", U22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="V24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(V22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", V22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="W24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(W22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", W22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="X24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(X22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", X22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="Y24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(Y22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", Y22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="Z24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(Z22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", Z22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="AA24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AA22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AA22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="AB24" s="141"/>
@@ -16792,107 +16792,107 @@
       <c r="AJ24" s="142"/>
       <c r="AK24" s="142"/>
       <c r="AL24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AL22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AL22)</f>
+        <f t="shared" ref="AL24:BK24" si="14" xml:space="preserve"> IF( ISNUMBER( FIND(AL22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AL22)</f>
         <v>X</v>
       </c>
       <c r="AM24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AM22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AM22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AN24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AN22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AN22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AO24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AO22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AO22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AP24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AP22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AP22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AQ24" s="140" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AQ22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AQ22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AR24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AR22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AR22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AS24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AS22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AS22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AT24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AT22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AT22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AU24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AU22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AU22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AV24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AV22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AV22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AW24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AW22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AW22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AX24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AX22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AX22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AY24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AY22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AY22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AZ24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AZ22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AZ22)</f>
+        <f t="shared" si="14"/>
         <v>o</v>
       </c>
       <c r="BA24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BA22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", BA22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="BB24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BB22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", BB22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="BC24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BC22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", BC22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="BD24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BD22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", BD22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="BE24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BE22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", BE22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="BF24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BF22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", BF22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="BG24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BG22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", BG22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="BH24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BH22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", BH22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="BI24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BI22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", BI22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="BJ24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BJ22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", BJ22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="BK24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BK22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", BK22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="BM24" s="10"/>
@@ -17231,7 +17231,7 @@
       <c r="CU26" s="94"/>
       <c r="CV26" s="95"/>
       <c r="CX26" s="96" t="str">
-        <f t="shared" ref="CX26:CX31" si="11" xml:space="preserve"> IFERROR( IF(LEN(CR26)=0, "", IF(EXACT(CR26,CQ26), "", "    - xform/^" &amp; CQ26 &amp; "/" &amp; CR26 &amp; "/  # " &amp; "【" &amp; CS26 &amp; "】 ==&gt; " &amp; CU26 &amp; "： " &amp; CT26 &amp; " [" &amp; CQ26 &amp; "]")), "")</f>
+        <f t="shared" ref="CX26:CX31" si="15" xml:space="preserve"> IFERROR( IF(LEN(CR26)=0, "", IF(EXACT(CR26,CQ26), "", "    - xform/^" &amp; CQ26 &amp; "/" &amp; CR26 &amp; "/  # " &amp; "【" &amp; CS26 &amp; "】 ==&gt; " &amp; CU26 &amp; "： " &amp; CT26 &amp; " [" &amp; CQ26 &amp; "]")), "")</f>
         <v/>
       </c>
       <c r="CY26" s="85">
@@ -17365,7 +17365,7 @@
       <c r="CU27" s="94"/>
       <c r="CV27" s="95"/>
       <c r="CX27" s="96" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="CY27" s="85">
@@ -17493,7 +17493,7 @@
       <c r="CU28" s="94"/>
       <c r="CV28" s="95"/>
       <c r="CX28" s="96" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="CY28" s="85">
@@ -17620,7 +17620,7 @@
       <c r="CU29" s="94"/>
       <c r="CV29" s="95"/>
       <c r="CX29" s="96" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="CY29" s="85">
@@ -17764,7 +17764,7 @@
       <c r="CV30" s="95"/>
       <c r="CW30" s="135"/>
       <c r="CX30" s="96" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="CY30" s="85">
@@ -17895,7 +17895,7 @@
       <c r="CV31" s="95"/>
       <c r="CW31" s="147"/>
       <c r="CX31" s="96" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="CY31" s="85">
@@ -18094,7 +18094,7 @@
         <v>2</v>
       </c>
       <c r="BV33" s="89" t="str">
-        <f t="shared" ref="BV33:BV62" si="12" xml:space="preserve"> "    """ &amp; BQ33 &amp; """: { commit: """ &amp; BR33 &amp; """ }" &amp; "  # " &amp; "/" &amp; BO33 &amp; "/ ==&gt; " &amp; BP33</f>
+        <f t="shared" ref="BV33:BV62" si="16" xml:space="preserve"> "    """ &amp; BQ33 &amp; """: { commit: """ &amp; BR33 &amp; """ }" &amp; "  # " &amp; "/" &amp; BO33 &amp; "/ ==&gt; " &amp; BP33</f>
         <v xml:space="preserve">    "9": { commit: "ㄞ" }  # /ai/ ==&gt; I</v>
       </c>
       <c r="BW33" s="90"/>
@@ -18131,7 +18131,7 @@
       <c r="CU33" s="94"/>
       <c r="CV33" s="95"/>
       <c r="CX33" s="17" t="str">
-        <f t="shared" ref="CX33:CX56" si="13" xml:space="preserve"> IF(CU33=0, "", "    - xform/^" &amp; CU33 &amp; "(?!\d)/" &amp; CQ33 &amp; "/  # " &amp; CR33 &amp; " [ " &amp; CU33 &amp; "]")</f>
+        <f t="shared" ref="CX33:CX56" si="17" xml:space="preserve"> IF(CU33=0, "", "    - xform/^" &amp; CU33 &amp; "(?!\d)/" &amp; CQ33 &amp; "/  # " &amp; CR33 &amp; " [ " &amp; CU33 &amp; "]")</f>
         <v/>
       </c>
       <c r="CY33" s="85">
@@ -18148,7 +18148,7 @@
     </row>
     <row r="34" spans="1:111" s="135" customFormat="1" ht="45" customHeight="1">
       <c r="A34" s="147"/>
-      <c r="B34" s="284" t="str">
+      <c r="B34" s="268" t="str">
         <f>_xlfn.CONCAT("  alphabet: """,D19:BC19, BD19:BJ19,"""")</f>
         <v xml:space="preserve">  alphabet: "!1qa2wsxEedGYyhnRrfvc8uKj,ik9l*UJ&lt;I(Lm/pM0;Oobtgz7-="5346]["</v>
       </c>
@@ -18232,7 +18232,7 @@
         <v>2</v>
       </c>
       <c r="BV34" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "l": { commit: "ㄠ" }  # /au/ ==&gt; U</v>
       </c>
       <c r="BW34" s="90"/>
@@ -18269,7 +18269,7 @@
       <c r="CU34" s="94"/>
       <c r="CV34" s="95"/>
       <c r="CX34" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY34" s="85">
@@ -18286,7 +18286,7 @@
     </row>
     <row r="35" spans="1:111" s="135" customFormat="1" ht="45" customHeight="1">
       <c r="A35" s="61"/>
-      <c r="B35" s="284" t="str">
+      <c r="B35" s="268" t="str">
         <f>_xlfn.CONCAT("  initials: """,D19:BC19, """")</f>
         <v xml:space="preserve">  initials: "!1qa2wsxEedGYyhnRrfvc8uKj,ik9l*UJ&lt;I(Lm/pM0;Oobtgz7-="</v>
       </c>
@@ -18376,7 +18376,7 @@
         <v>3</v>
       </c>
       <c r="BV35" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "*": { commit: "ㆩ" }  # /ann/ ==&gt; D</v>
       </c>
       <c r="BW35" s="90"/>
@@ -18413,7 +18413,7 @@
       <c r="CU35" s="94"/>
       <c r="CV35" s="95"/>
       <c r="CX35" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY35" s="85">
@@ -18429,7 +18429,7 @@
       <c r="DG35" s="17"/>
     </row>
     <row r="36" spans="1:111" s="135" customFormat="1" ht="45" customHeight="1">
-      <c r="B36" s="284" t="str">
+      <c r="B36" s="268" t="str">
         <f>_xlfn.CONCAT("  finals: """,BD19:BJ19,"""")</f>
         <v xml:space="preserve">  finals: ""5346]["</v>
       </c>
@@ -18519,7 +18519,7 @@
         <v>3</v>
       </c>
       <c r="BV36" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "U": { commit: "ㆪ" }  # /inn/ ==&gt; f</v>
       </c>
       <c r="BW36" s="90"/>
@@ -18556,7 +18556,7 @@
       <c r="CU36" s="94"/>
       <c r="CV36" s="95"/>
       <c r="CX36" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY36" s="85">
@@ -18617,7 +18617,7 @@
         <v>3</v>
       </c>
       <c r="BV37" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "J": { commit: "ㆫ" }  # /unn/ ==&gt; q</v>
       </c>
       <c r="BW37" s="90"/>
@@ -18654,7 +18654,7 @@
       <c r="CU37" s="94"/>
       <c r="CV37" s="95"/>
       <c r="CX37" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY37" s="85">
@@ -18719,7 +18719,7 @@
         <v>3</v>
       </c>
       <c r="BV38" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "&lt;": { commit: "ㆥ" }  # /enn/ ==&gt; r</v>
       </c>
       <c r="BW38" s="90"/>
@@ -18756,7 +18756,7 @@
       <c r="CU38" s="94"/>
       <c r="CV38" s="95"/>
       <c r="CX38" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY38" s="85">
@@ -18859,7 +18859,7 @@
         <v>3</v>
       </c>
       <c r="BV39" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "I": { commit: "ㆧ" }  # /onn/ ==&gt; v</v>
       </c>
       <c r="BW39" s="90"/>
@@ -18896,7 +18896,7 @@
       <c r="CU39" s="94"/>
       <c r="CV39" s="95"/>
       <c r="CX39" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY39" s="85">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="BU40" s="135"/>
       <c r="BV40" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "(": { commit: "ㆮ" }  # /ainn/ ==&gt; x</v>
       </c>
       <c r="BW40" s="90"/>
@@ -19042,7 +19042,7 @@
       <c r="CV40" s="95"/>
       <c r="CW40" s="135"/>
       <c r="CX40" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY40" s="85">
@@ -19168,7 +19168,7 @@
       </c>
       <c r="BU41" s="135"/>
       <c r="BV41" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "L": { commit: "ㆯ" }  # /aunn/ ==&gt; y</v>
       </c>
       <c r="BW41" s="90"/>
@@ -19203,7 +19203,7 @@
       <c r="CU41" s="94"/>
       <c r="CV41" s="95"/>
       <c r="CX41" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY41" s="85">
@@ -19327,7 +19327,7 @@
         <v>2</v>
       </c>
       <c r="BV42" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "m": { commit: "ㆬ" }  # /-m/ ==&gt; M</v>
       </c>
       <c r="BW42" s="90"/>
@@ -19362,7 +19362,7 @@
       <c r="CU42" s="94"/>
       <c r="CV42" s="95"/>
       <c r="CX42" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY42" s="85">
@@ -19378,13 +19378,13 @@
     </row>
     <row r="43" spans="1:111" ht="45" customHeight="1">
       <c r="A43" s="135"/>
-      <c r="B43" s="286" t="str">
+      <c r="B43" s="270" t="str">
         <f xml:space="preserve"> "    - xlit|" &amp; E41 &amp; "|" &amp; E42 &amp; "|"</f>
         <v xml:space="preserve">    - xlit|BbpmdtnlĞgkŋZzcsJjCShaiwueOəIUDfqrvxyMGNY@AWHRFQV&amp;LØ1732584|!1qa2wsxEedGYyhnRrfvc8uKj,ik9l*UJ&lt;I(Lm/pM0;Oobtgz7-="5346][|</v>
       </c>
       <c r="C43" s="175"/>
       <c r="D43" s="175"/>
-      <c r="E43" s="285"/>
+      <c r="E43" s="269"/>
       <c r="F43" s="175"/>
       <c r="G43" s="175"/>
       <c r="H43" s="175"/>
@@ -19474,7 +19474,7 @@
         <v>3</v>
       </c>
       <c r="BV43" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "/": { commit: "ㆭ" }  # /-ng/ ==&gt; G</v>
       </c>
       <c r="BW43" s="90"/>
@@ -19509,7 +19509,7 @@
       <c r="CU43" s="94"/>
       <c r="CV43" s="95"/>
       <c r="CX43" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY43" s="85">
@@ -19559,7 +19559,7 @@
         <v>2</v>
       </c>
       <c r="BV44" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "p": { commit: "ㄣ" }  # /-n/ ==&gt; N</v>
       </c>
       <c r="BW44" s="90"/>
@@ -19594,7 +19594,7 @@
       <c r="CU44" s="94"/>
       <c r="CV44" s="95"/>
       <c r="CX44" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY44" s="85">
@@ -19634,7 +19634,7 @@
         <v>2</v>
       </c>
       <c r="BV45" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "M": { commit: "ㆰ" }  # /am/ ==&gt; Y</v>
       </c>
       <c r="BW45" s="90"/>
@@ -19669,7 +19669,7 @@
       <c r="CU45" s="94"/>
       <c r="CV45" s="95"/>
       <c r="CX45" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY45" s="85">
@@ -19891,7 +19891,7 @@
         <v>2</v>
       </c>
       <c r="BV46" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "0": { commit: "ㄢ" }  # /an/ ==&gt; @</v>
       </c>
       <c r="BW46" s="90"/>
@@ -19926,7 +19926,7 @@
       <c r="CU46" s="94"/>
       <c r="CV46" s="95"/>
       <c r="CX46" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY46" s="85">
@@ -19946,239 +19946,239 @@
         <v>B</v>
       </c>
       <c r="C47" s="182" t="str">
-        <f t="shared" ref="C47:BI47" si="14" xml:space="preserve"> MID($E$41, C$46, 1)</f>
+        <f t="shared" ref="C47:BI47" si="18" xml:space="preserve"> MID($E$41, C$46, 1)</f>
         <v>b</v>
       </c>
       <c r="D47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>p</v>
       </c>
       <c r="E47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>m</v>
       </c>
       <c r="F47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>d</v>
       </c>
       <c r="G47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>t</v>
       </c>
       <c r="H47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>n</v>
       </c>
       <c r="I47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>l</v>
       </c>
       <c r="J47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Ğ</v>
       </c>
       <c r="K47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>g</v>
       </c>
       <c r="L47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>k</v>
       </c>
       <c r="M47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>ŋ</v>
       </c>
       <c r="N47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Z</v>
       </c>
       <c r="O47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>z</v>
       </c>
       <c r="P47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>c</v>
       </c>
       <c r="Q47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>s</v>
       </c>
       <c r="R47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>J</v>
       </c>
       <c r="S47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>j</v>
       </c>
       <c r="T47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>C</v>
       </c>
       <c r="U47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>S</v>
       </c>
       <c r="V47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>h</v>
       </c>
       <c r="W47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>a</v>
       </c>
       <c r="X47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>i</v>
       </c>
       <c r="Y47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>w</v>
       </c>
       <c r="Z47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>u</v>
       </c>
       <c r="AA47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>e</v>
       </c>
       <c r="AB47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>O</v>
       </c>
       <c r="AC47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>ə</v>
       </c>
       <c r="AD47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>I</v>
       </c>
       <c r="AE47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>U</v>
       </c>
       <c r="AF47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>D</v>
       </c>
       <c r="AG47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>f</v>
       </c>
       <c r="AH47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>q</v>
       </c>
       <c r="AI47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>r</v>
       </c>
       <c r="AJ47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>v</v>
       </c>
       <c r="AK47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>x</v>
       </c>
       <c r="AL47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>y</v>
       </c>
       <c r="AM47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>M</v>
       </c>
       <c r="AN47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>G</v>
       </c>
       <c r="AO47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>N</v>
       </c>
       <c r="AP47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Y</v>
       </c>
       <c r="AQ47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>@</v>
       </c>
       <c r="AR47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>A</v>
       </c>
       <c r="AS47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>W</v>
       </c>
       <c r="AT47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>H</v>
       </c>
       <c r="AU47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>R</v>
       </c>
       <c r="AV47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>F</v>
       </c>
       <c r="AW47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Q</v>
       </c>
       <c r="AX47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>V</v>
       </c>
       <c r="AY47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>&amp;</v>
       </c>
       <c r="AZ47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>L</v>
       </c>
       <c r="BA47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Ø</v>
       </c>
       <c r="BB47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="BC47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>7</v>
       </c>
       <c r="BD47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>3</v>
       </c>
       <c r="BE47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="BF47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>5</v>
       </c>
       <c r="BG47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>8</v>
       </c>
       <c r="BH47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>4</v>
       </c>
       <c r="BI47" s="182" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BJ47" s="163"/>
@@ -20208,7 +20208,7 @@
         <v>3</v>
       </c>
       <c r="BV47" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    ";": { commit: "ㄤ" }  # /ang/ ==&gt; A</v>
       </c>
       <c r="BX47" s="85">
@@ -20242,7 +20242,7 @@
       <c r="CU47" s="94"/>
       <c r="CV47" s="95"/>
       <c r="CX47" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY47" s="85">
@@ -20262,239 +20262,239 @@
         <v>!</v>
       </c>
       <c r="C48" s="183" t="str">
-        <f t="shared" ref="C48:BI48" si="15" xml:space="preserve"> MID($E$42, C$46, 1)</f>
+        <f t="shared" ref="C48:BI48" si="19" xml:space="preserve"> MID($E$42, C$46, 1)</f>
         <v>1</v>
       </c>
       <c r="D48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>q</v>
       </c>
       <c r="E48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>a</v>
       </c>
       <c r="F48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>2</v>
       </c>
       <c r="G48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>w</v>
       </c>
       <c r="H48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>s</v>
       </c>
       <c r="I48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>x</v>
       </c>
       <c r="J48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>E</v>
       </c>
       <c r="K48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>e</v>
       </c>
       <c r="L48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>d</v>
       </c>
       <c r="M48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>G</v>
       </c>
       <c r="N48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>Y</v>
       </c>
       <c r="O48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>y</v>
       </c>
       <c r="P48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>h</v>
       </c>
       <c r="Q48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>n</v>
       </c>
       <c r="R48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>R</v>
       </c>
       <c r="S48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>r</v>
       </c>
       <c r="T48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>f</v>
       </c>
       <c r="U48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>v</v>
       </c>
       <c r="V48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>c</v>
       </c>
       <c r="W48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>8</v>
       </c>
       <c r="X48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>u</v>
       </c>
       <c r="Y48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>K</v>
       </c>
       <c r="Z48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>j</v>
       </c>
       <c r="AA48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>,</v>
       </c>
       <c r="AB48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>i</v>
       </c>
       <c r="AC48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>k</v>
       </c>
       <c r="AD48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>9</v>
       </c>
       <c r="AE48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>l</v>
       </c>
       <c r="AF48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>*</v>
       </c>
       <c r="AG48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>U</v>
       </c>
       <c r="AH48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>J</v>
       </c>
       <c r="AI48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>&lt;</v>
       </c>
       <c r="AJ48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>I</v>
       </c>
       <c r="AK48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>(</v>
       </c>
       <c r="AL48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>L</v>
       </c>
       <c r="AM48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>m</v>
       </c>
       <c r="AN48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>/</v>
       </c>
       <c r="AO48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>p</v>
       </c>
       <c r="AP48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>M</v>
       </c>
       <c r="AQ48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AR48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>;</v>
       </c>
       <c r="AS48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>O</v>
       </c>
       <c r="AT48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>o</v>
       </c>
       <c r="AU48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>b</v>
       </c>
       <c r="AV48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>t</v>
       </c>
       <c r="AW48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>g</v>
       </c>
       <c r="AX48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>z</v>
       </c>
       <c r="AY48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>7</v>
       </c>
       <c r="AZ48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>-</v>
       </c>
       <c r="BA48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>=</v>
       </c>
       <c r="BB48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>"</v>
       </c>
       <c r="BC48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="BD48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>3</v>
       </c>
       <c r="BE48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>4</v>
       </c>
       <c r="BF48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>6</v>
       </c>
       <c r="BG48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>]</v>
       </c>
       <c r="BH48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>[</v>
       </c>
       <c r="BI48" s="183" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="BJ48" s="163"/>
@@ -20524,7 +20524,7 @@
         <v>2</v>
       </c>
       <c r="BV48" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "O": { commit: "ㆱ" }  # /om/ ==&gt; W</v>
       </c>
       <c r="BX48" s="85">
@@ -20558,7 +20558,7 @@
       <c r="CU48" s="94"/>
       <c r="CV48" s="95"/>
       <c r="CX48" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY48" s="85">
@@ -20607,7 +20607,7 @@
         <v>3</v>
       </c>
       <c r="BV49" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "o": { commit: "ㆲ" }  # /ong/ ==&gt; H</v>
       </c>
       <c r="BX49" s="85">
@@ -20641,7 +20641,7 @@
       <c r="CU49" s="94"/>
       <c r="CV49" s="95"/>
       <c r="CX49" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY49" s="85">
@@ -20743,7 +20743,7 @@
         <v>2</v>
       </c>
       <c r="BV50" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "b": { commit: "ㆴ" }  # /-p/ ==&gt; R</v>
       </c>
       <c r="BX50" s="85">
@@ -20777,7 +20777,7 @@
       <c r="CU50" s="94"/>
       <c r="CV50" s="95"/>
       <c r="CX50" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY50" s="85">
@@ -20882,7 +20882,7 @@
         <v>2</v>
       </c>
       <c r="BV51" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "t": { commit: "ㆵ" }  # /-t/ ==&gt; F</v>
       </c>
       <c r="BX51" s="85">
@@ -20916,7 +20916,7 @@
       <c r="CU51" s="94"/>
       <c r="CV51" s="95"/>
       <c r="CX51" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY51" s="85">
@@ -21020,7 +21020,7 @@
         <v>2</v>
       </c>
       <c r="BV52" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "g": { commit: "ㆻ" }  # /-k/ ==&gt; Q</v>
       </c>
       <c r="BX52" s="85">
@@ -21054,7 +21054,7 @@
       <c r="CU52" s="94"/>
       <c r="CV52" s="95"/>
       <c r="CX52" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY52" s="85">
@@ -21165,7 +21165,7 @@
         <v>2</v>
       </c>
       <c r="BV53" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "z": { commit: "ㆷ" }  # /-h/ ==&gt; V</v>
       </c>
       <c r="BX53" s="85">
@@ -21199,7 +21199,7 @@
       <c r="CU53" s="94"/>
       <c r="CV53" s="95"/>
       <c r="CX53" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY53" s="85">
@@ -21310,7 +21310,7 @@
         <v>4</v>
       </c>
       <c r="BV54" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "7": { commit: "入" }  # /[48]/ ==&gt; &amp;</v>
       </c>
       <c r="BX54" s="85">
@@ -21344,7 +21344,7 @@
       <c r="CU54" s="94"/>
       <c r="CV54" s="95"/>
       <c r="CX54" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY54" s="85">
@@ -21359,7 +21359,7 @@
       <c r="DE54" s="95"/>
     </row>
     <row r="55" spans="1:109" ht="45" customHeight="1">
-      <c r="B55" s="286" t="str">
+      <c r="B55" s="270" t="str">
         <f xml:space="preserve"> "    - xlit|" &amp; E53 &amp; "|" &amp; E54 &amp; "|"</f>
         <v xml:space="preserve">    - xlit|!1qa2wsxEedGYyhnRrfvc8uKj,ik9l*UJ&lt;I(Lm/pM0;Oobtgz7-="5346][|ㆠㄅㄆㄇㄉㄊㄋㄌㆣㄍㄎㄫㆡㄗㄘㄙㆢㄐㄑㄒㄏㄚㄧㆨㄨㆤㆦㄜㄞㄠㆩㆪㆫㆥㆧㆮㆯㆬㆭㄣㆰㄢㄤㆱㆲㆴㆵㆻㆷ入ㄥØ一七三二五八四|</v>
       </c>
@@ -21449,7 +21449,7 @@
         <v>1</v>
       </c>
       <c r="BV55" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "-": { commit: "ㄥ" }  # /ñ/ ==&gt; L</v>
       </c>
       <c r="BX55" s="85">
@@ -21483,7 +21483,7 @@
       <c r="CU55" s="94"/>
       <c r="CV55" s="95"/>
       <c r="CX55" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY55" s="85">
@@ -21588,7 +21588,7 @@
         <v>1</v>
       </c>
       <c r="BV56" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "=": { commit: "Ø" }  # /Ø/ ==&gt; Ø</v>
       </c>
       <c r="BX56" s="85">
@@ -21622,7 +21622,7 @@
       <c r="CU56" s="94"/>
       <c r="CV56" s="95"/>
       <c r="CX56" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY56" s="85">
@@ -21664,7 +21664,7 @@
         <v>1</v>
       </c>
       <c r="BV57" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    """: { commit: "一" }  # /1/ ==&gt; 1</v>
       </c>
       <c r="BX57" s="85">
@@ -21916,7 +21916,7 @@
         <v>1</v>
       </c>
       <c r="BV58" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "5": { commit: "七" }  # /7/ ==&gt; 7</v>
       </c>
       <c r="BX58" s="85">
@@ -21966,239 +21966,239 @@
         <v>!</v>
       </c>
       <c r="C59" s="183" t="str">
-        <f t="shared" ref="C59:BI59" si="16" xml:space="preserve"> MID($E$53, C$46, 1)</f>
+        <f t="shared" ref="C59:BI59" si="20" xml:space="preserve"> MID($E$53, C$46, 1)</f>
         <v>1</v>
       </c>
       <c r="D59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>q</v>
       </c>
       <c r="E59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>a</v>
       </c>
       <c r="F59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2</v>
       </c>
       <c r="G59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>w</v>
       </c>
       <c r="H59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>s</v>
       </c>
       <c r="I59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>x</v>
       </c>
       <c r="J59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>E</v>
       </c>
       <c r="K59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>e</v>
       </c>
       <c r="L59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>d</v>
       </c>
       <c r="M59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>G</v>
       </c>
       <c r="N59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>Y</v>
       </c>
       <c r="O59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>y</v>
       </c>
       <c r="P59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>h</v>
       </c>
       <c r="Q59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>n</v>
       </c>
       <c r="R59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>R</v>
       </c>
       <c r="S59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>r</v>
       </c>
       <c r="T59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>f</v>
       </c>
       <c r="U59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>v</v>
       </c>
       <c r="V59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>c</v>
       </c>
       <c r="W59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>8</v>
       </c>
       <c r="X59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>u</v>
       </c>
       <c r="Y59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>K</v>
       </c>
       <c r="Z59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>j</v>
       </c>
       <c r="AA59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>,</v>
       </c>
       <c r="AB59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>i</v>
       </c>
       <c r="AC59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>k</v>
       </c>
       <c r="AD59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>9</v>
       </c>
       <c r="AE59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>l</v>
       </c>
       <c r="AF59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>*</v>
       </c>
       <c r="AG59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>U</v>
       </c>
       <c r="AH59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>J</v>
       </c>
       <c r="AI59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>&lt;</v>
       </c>
       <c r="AJ59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>I</v>
       </c>
       <c r="AK59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>(</v>
       </c>
       <c r="AL59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>L</v>
       </c>
       <c r="AM59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>m</v>
       </c>
       <c r="AN59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>/</v>
       </c>
       <c r="AO59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>p</v>
       </c>
       <c r="AP59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>M</v>
       </c>
       <c r="AQ59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AR59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>;</v>
       </c>
       <c r="AS59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>O</v>
       </c>
       <c r="AT59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>o</v>
       </c>
       <c r="AU59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>b</v>
       </c>
       <c r="AV59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>t</v>
       </c>
       <c r="AW59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>g</v>
       </c>
       <c r="AX59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>z</v>
       </c>
       <c r="AY59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>7</v>
       </c>
       <c r="AZ59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-</v>
       </c>
       <c r="BA59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>=</v>
       </c>
       <c r="BB59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>"</v>
       </c>
       <c r="BC59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>5</v>
       </c>
       <c r="BD59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>3</v>
       </c>
       <c r="BE59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>4</v>
       </c>
       <c r="BF59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>6</v>
       </c>
       <c r="BG59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>]</v>
       </c>
       <c r="BH59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>[</v>
       </c>
       <c r="BI59" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="BJ59" s="163"/>
@@ -22228,7 +22228,7 @@
         <v>1</v>
       </c>
       <c r="BV59" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "3": { commit: "三" }  # /3/ ==&gt; 3</v>
       </c>
       <c r="BX59" s="85">
@@ -22278,239 +22278,239 @@
         <v>ㆠ</v>
       </c>
       <c r="C60" s="194" t="str">
-        <f t="shared" ref="C60:BI60" si="17" xml:space="preserve"> MID($E$54, C$46, 1)</f>
+        <f t="shared" ref="C60:BI60" si="21" xml:space="preserve"> MID($E$54, C$46, 1)</f>
         <v>ㄅ</v>
       </c>
       <c r="D60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄆ</v>
       </c>
       <c r="E60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄇ</v>
       </c>
       <c r="F60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄉ</v>
       </c>
       <c r="G60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄊ</v>
       </c>
       <c r="H60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄋ</v>
       </c>
       <c r="I60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄌ</v>
       </c>
       <c r="J60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㆣ</v>
       </c>
       <c r="K60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄍ</v>
       </c>
       <c r="L60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄎ</v>
       </c>
       <c r="M60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄫ</v>
       </c>
       <c r="N60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㆡ</v>
       </c>
       <c r="O60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄗ</v>
       </c>
       <c r="P60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄘ</v>
       </c>
       <c r="Q60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄙ</v>
       </c>
       <c r="R60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㆢ</v>
       </c>
       <c r="S60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄐ</v>
       </c>
       <c r="T60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄑ</v>
       </c>
       <c r="U60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄒ</v>
       </c>
       <c r="V60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄏ</v>
       </c>
       <c r="W60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄚ</v>
       </c>
       <c r="X60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄧ</v>
       </c>
       <c r="Y60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㆨ</v>
       </c>
       <c r="Z60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄨ</v>
       </c>
       <c r="AA60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㆤ</v>
       </c>
       <c r="AB60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㆦ</v>
       </c>
       <c r="AC60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄜ</v>
       </c>
       <c r="AD60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄞ</v>
       </c>
       <c r="AE60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄠ</v>
       </c>
       <c r="AF60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㆩ</v>
       </c>
       <c r="AG60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㆪ</v>
       </c>
       <c r="AH60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㆫ</v>
       </c>
       <c r="AI60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㆥ</v>
       </c>
       <c r="AJ60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㆧ</v>
       </c>
       <c r="AK60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㆮ</v>
       </c>
       <c r="AL60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㆯ</v>
       </c>
       <c r="AM60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㆬ</v>
       </c>
       <c r="AN60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㆭ</v>
       </c>
       <c r="AO60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄣ</v>
       </c>
       <c r="AP60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㆰ</v>
       </c>
       <c r="AQ60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄢ</v>
       </c>
       <c r="AR60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄤ</v>
       </c>
       <c r="AS60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㆱ</v>
       </c>
       <c r="AT60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㆲ</v>
       </c>
       <c r="AU60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㆴ</v>
       </c>
       <c r="AV60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㆵ</v>
       </c>
       <c r="AW60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㆻ</v>
       </c>
       <c r="AX60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㆷ</v>
       </c>
       <c r="AY60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>入</v>
       </c>
       <c r="AZ60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>ㄥ</v>
       </c>
       <c r="BA60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>Ø</v>
       </c>
       <c r="BB60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>一</v>
       </c>
       <c r="BC60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>七</v>
       </c>
       <c r="BD60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>三</v>
       </c>
       <c r="BE60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>二</v>
       </c>
       <c r="BF60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>五</v>
       </c>
       <c r="BG60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>八</v>
       </c>
       <c r="BH60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>四</v>
       </c>
       <c r="BI60" s="194" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="BJ60" s="163"/>
@@ -22540,7 +22540,7 @@
         <v>1</v>
       </c>
       <c r="BV60" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "4": { commit: "二" }  # /2/ ==&gt; 2</v>
       </c>
       <c r="BX60" s="85">
@@ -22672,7 +22672,7 @@
         <v>1</v>
       </c>
       <c r="BV61" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "6": { commit: "五" }  # /5/ ==&gt; 5</v>
       </c>
       <c r="BX61" s="85">
@@ -22804,7 +22804,7 @@
         <v>1</v>
       </c>
       <c r="BV62" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "]": { commit: "八" }  # /8/ ==&gt; 8</v>
       </c>
       <c r="BX62" s="85">
@@ -23237,7 +23237,7 @@
       <c r="BL66" s="163"/>
     </row>
     <row r="67" spans="1:109">
-      <c r="B67" s="286" t="str">
+      <c r="B67" s="270" t="str">
         <f xml:space="preserve"> "- xlit|" &amp; E65 &amp; "|" &amp; E66 &amp; "|"</f>
         <v>- xlit|BbpmdtnlĞgkŋZzcsJjCShaiwueOəIUDfqrvxyMGNY@AWHRFQV&amp;LØ173|ㆠㄅㄆㄇㄉㄊㄋㄌㆣㄍㄎㄫㆡㄗㄘㄙㆢㄐㄑㄒㄏㄚㄧㆨㄨㆤㆦㄜㄞㄠㆩㆪㆫㆥㆧㆮㆯㆬㆭㄣㆰㄢㄤㆱㆲㆴㆵㆻㆷ入ㄥØ一七三|</v>
       </c>
@@ -36357,214 +36357,214 @@
     <row r="23" spans="1:111" s="138" customFormat="1" ht="45" customHeight="1">
       <c r="A23" s="135"/>
       <c r="B23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(B22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(B22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" ref="B23:AA23" si="11" xml:space="preserve"> IF( ISNUMBER( FIND(B22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(B22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
         <v>22</v>
       </c>
       <c r="C23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(C22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(C22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="D23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(D22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(D22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>15</v>
       </c>
       <c r="E23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(E22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(E22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>43</v>
       </c>
       <c r="F23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(F22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(F22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>26</v>
       </c>
       <c r="G23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(G22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(G22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>44</v>
       </c>
       <c r="H23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(H22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(H22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
       <c r="I23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(I22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(I22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>17</v>
       </c>
       <c r="J23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(J22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(J22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>23</v>
       </c>
       <c r="K23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(K22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(K22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>13</v>
       </c>
       <c r="L23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(L22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(L22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="M23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(M22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(M22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>8</v>
       </c>
       <c r="N23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(N22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(N22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="O23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(O22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(O22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="P23" s="137" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(P22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(P22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>V</v>
       </c>
       <c r="Q23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(Q22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(Q22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="R23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(R22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(R22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>45</v>
       </c>
       <c r="S23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(S22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(S22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>46</v>
       </c>
       <c r="T23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(T22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(T22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>16</v>
       </c>
       <c r="U23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(U22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(U22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
       <c r="V23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(V22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(V22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>25</v>
       </c>
       <c r="W23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(W22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(W22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>47</v>
       </c>
       <c r="X23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(X22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(X22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>24</v>
       </c>
       <c r="Y23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(Y22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(Y22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>48</v>
       </c>
       <c r="Z23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(Z22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(Z22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>49</v>
       </c>
       <c r="AA23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AA22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AA22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="11"/>
         <v>14</v>
       </c>
       <c r="AB23" s="135"/>
       <c r="AC23" s="135"/>
       <c r="AE23" s="135"/>
       <c r="AL23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AL22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AL22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" ref="AL23:BK23" si="12" xml:space="preserve"> IF( ISNUMBER( FIND(AL22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AL22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
         <v>22</v>
       </c>
       <c r="AM23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AM22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AM22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AN23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AN22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AN22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>15</v>
       </c>
       <c r="AO23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AO22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AO22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>43</v>
       </c>
       <c r="AP23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AP22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AP22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>26</v>
       </c>
       <c r="AQ23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AQ22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AQ22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>44</v>
       </c>
       <c r="AR23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AR22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AR22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>9</v>
       </c>
       <c r="AS23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AS22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AS22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>17</v>
       </c>
       <c r="AT23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AT22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AT22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>23</v>
       </c>
       <c r="AU23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AU22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AU22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>13</v>
       </c>
       <c r="AV23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AV22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AV22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="AW23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AW22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AW22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>8</v>
       </c>
       <c r="AX23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AX22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AX22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
       <c r="AY23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AY22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AY22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>5</v>
       </c>
       <c r="AZ23" s="137" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AZ22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(AZ22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>V</v>
       </c>
       <c r="BA23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BA22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(BA22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
       <c r="BB23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BB22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(BB22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>45</v>
       </c>
       <c r="BC23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BC22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(BC22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>46</v>
       </c>
       <c r="BD23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BD22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(BD22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>16</v>
       </c>
       <c r="BE23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BE22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(BE22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>6</v>
       </c>
       <c r="BF23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BF22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(BF22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>25</v>
       </c>
       <c r="BG23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BG22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(BG22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>47</v>
       </c>
       <c r="BH23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BH22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(BH22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>24</v>
       </c>
       <c r="BI23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BI22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(BI22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>48</v>
       </c>
       <c r="BJ23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BJ22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(BJ22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>49</v>
       </c>
       <c r="BK23" s="137">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BK22, _xlfn.CONCAT($D$18:$BK$18)) ),  FIND(BK22, _xlfn.CONCAT($D$18:$BK$18)), "V")</f>
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
       <c r="BL23" s="135"/>
@@ -36667,107 +36667,107 @@
     <row r="24" spans="1:111" s="135" customFormat="1" ht="45" customHeight="1">
       <c r="A24" s="61"/>
       <c r="B24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(B22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", B22)</f>
+        <f t="shared" ref="B24:AA24" si="13" xml:space="preserve"> IF( ISNUMBER( FIND(B22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", B22)</f>
         <v>X</v>
       </c>
       <c r="C24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(C22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", C22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="D24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(D22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", D22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="E24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(E22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", E22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="F24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(F22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", F22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="G24" s="140" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(G22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", G22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="H24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(H22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", H22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="I24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(I22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", I22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="J24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(J22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", J22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="K24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(K22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", K22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="L24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(L22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", L22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="M24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(M22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", M22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="N24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(N22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", N22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="O24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(O22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", O22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="P24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(P22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", P22)</f>
+        <f t="shared" si="13"/>
         <v>o</v>
       </c>
       <c r="Q24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(Q22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", Q22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="R24" s="140" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(R22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", R22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="S24" s="140" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(S22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", S22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="T24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(T22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", T22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="U24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(U22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", U22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="V24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(V22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", V22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="W24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(W22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", W22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="X24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(X22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", X22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="Y24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(Y22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", Y22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="Z24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(Z22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", Z22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="AA24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AA22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AA22)</f>
+        <f t="shared" si="13"/>
         <v>X</v>
       </c>
       <c r="AB24" s="141"/>
@@ -36781,107 +36781,107 @@
       <c r="AJ24" s="142"/>
       <c r="AK24" s="142"/>
       <c r="AL24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AL22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AL22)</f>
+        <f t="shared" ref="AL24:BK24" si="14" xml:space="preserve"> IF( ISNUMBER( FIND(AL22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AL22)</f>
         <v>X</v>
       </c>
       <c r="AM24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AM22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AM22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AN24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AN22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AN22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AO24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AO22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AO22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AP24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AP22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AP22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AQ24" s="140" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AQ22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AQ22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AR24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AR22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AR22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AS24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AS22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AS22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AT24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AT22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AT22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AU24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AU22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AU22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AV24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AV22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AV22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AW24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AW22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AW22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AX24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AX22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AX22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AY24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AY22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AY22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="AZ24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(AZ22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", AZ22)</f>
+        <f t="shared" si="14"/>
         <v>o</v>
       </c>
       <c r="BA24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BA22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", BA22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="BB24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BB22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", BB22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="BC24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BC22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", BC22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="BD24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BD22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", BD22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="BE24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BE22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", BE22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="BF24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BF22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", BF22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="BG24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BG22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", BG22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="BH24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BH22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", BH22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="BI24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BI22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", BI22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="BJ24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BJ22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", BJ22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="BK24" s="139" t="str">
-        <f xml:space="preserve"> IF( ISNUMBER( FIND(BK22, _xlfn.CONCAT($D$18:$BK$18)) ), "X", BK22)</f>
+        <f t="shared" si="14"/>
         <v>X</v>
       </c>
       <c r="BM24" s="10"/>
@@ -37220,7 +37220,7 @@
       <c r="CU26" s="94"/>
       <c r="CV26" s="95"/>
       <c r="CX26" s="96" t="str">
-        <f t="shared" ref="CX26:CX31" si="11" xml:space="preserve"> IFERROR( IF(LEN(CR26)=0, "", IF(EXACT(CR26,CQ26), "", "    - xform/^" &amp; CQ26 &amp; "/" &amp; CR26 &amp; "/  # " &amp; "【" &amp; CS26 &amp; "】 ==&gt; " &amp; CU26 &amp; "： " &amp; CT26 &amp; " [" &amp; CQ26 &amp; "]")), "")</f>
+        <f t="shared" ref="CX26:CX31" si="15" xml:space="preserve"> IFERROR( IF(LEN(CR26)=0, "", IF(EXACT(CR26,CQ26), "", "    - xform/^" &amp; CQ26 &amp; "/" &amp; CR26 &amp; "/  # " &amp; "【" &amp; CS26 &amp; "】 ==&gt; " &amp; CU26 &amp; "： " &amp; CT26 &amp; " [" &amp; CQ26 &amp; "]")), "")</f>
         <v/>
       </c>
       <c r="CY26" s="85">
@@ -37354,7 +37354,7 @@
       <c r="CU27" s="94"/>
       <c r="CV27" s="95"/>
       <c r="CX27" s="96" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="CY27" s="85">
@@ -37482,7 +37482,7 @@
       <c r="CU28" s="94"/>
       <c r="CV28" s="95"/>
       <c r="CX28" s="96" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="CY28" s="85">
@@ -37609,7 +37609,7 @@
       <c r="CU29" s="94"/>
       <c r="CV29" s="95"/>
       <c r="CX29" s="96" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="CY29" s="85">
@@ -37753,7 +37753,7 @@
       <c r="CV30" s="95"/>
       <c r="CW30" s="135"/>
       <c r="CX30" s="96" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="CY30" s="85">
@@ -37884,7 +37884,7 @@
       <c r="CV31" s="95"/>
       <c r="CW31" s="147"/>
       <c r="CX31" s="96" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="CY31" s="85">
@@ -38083,7 +38083,7 @@
         <v>2</v>
       </c>
       <c r="BV33" s="89" t="str">
-        <f t="shared" ref="BV33:BV62" si="12" xml:space="preserve"> "    """ &amp; BQ33 &amp; """: { commit: """ &amp; BR33 &amp; """ }" &amp; "  # " &amp; "/" &amp; BO33 &amp; "/ ==&gt; " &amp; BP33</f>
+        <f t="shared" ref="BV33:BV62" si="16" xml:space="preserve"> "    """ &amp; BQ33 &amp; """: { commit: """ &amp; BR33 &amp; """ }" &amp; "  # " &amp; "/" &amp; BO33 &amp; "/ ==&gt; " &amp; BP33</f>
         <v xml:space="preserve">    "m": { commit: "ㆬ" }  # /-m/ ==&gt; M</v>
       </c>
       <c r="BW33" s="90"/>
@@ -38120,7 +38120,7 @@
       <c r="CU33" s="94"/>
       <c r="CV33" s="95"/>
       <c r="CX33" s="17" t="str">
-        <f t="shared" ref="CX33:CX56" si="13" xml:space="preserve"> IF(CU33=0, "", "    - xform/^" &amp; CU33 &amp; "(?!\d)/" &amp; CQ33 &amp; "/  # " &amp; CR33 &amp; " [ " &amp; CU33 &amp; "]")</f>
+        <f t="shared" ref="CX33:CX56" si="17" xml:space="preserve"> IF(CU33=0, "", "    - xform/^" &amp; CU33 &amp; "(?!\d)/" &amp; CQ33 &amp; "/  # " &amp; CR33 &amp; " [ " &amp; CU33 &amp; "]")</f>
         <v/>
       </c>
       <c r="CY33" s="85">
@@ -38221,7 +38221,7 @@
         <v>2</v>
       </c>
       <c r="BV34" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "p": { commit: "ㄣ" }  # /-n/ ==&gt; N</v>
       </c>
       <c r="BW34" s="90"/>
@@ -38258,7 +38258,7 @@
       <c r="CU34" s="94"/>
       <c r="CV34" s="95"/>
       <c r="CX34" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY34" s="85">
@@ -38365,7 +38365,7 @@
         <v>3</v>
       </c>
       <c r="BV35" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "/": { commit: "ㆭ" }  # /-ng/ ==&gt; G</v>
       </c>
       <c r="BW35" s="90"/>
@@ -38402,7 +38402,7 @@
       <c r="CU35" s="94"/>
       <c r="CV35" s="95"/>
       <c r="CX35" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY35" s="85">
@@ -38508,7 +38508,7 @@
         <v>2</v>
       </c>
       <c r="BV36" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "b": { commit: "ㆴ" }  # /-p/ ==&gt; R</v>
       </c>
       <c r="BW36" s="90"/>
@@ -38545,7 +38545,7 @@
       <c r="CU36" s="94"/>
       <c r="CV36" s="95"/>
       <c r="CX36" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY36" s="85">
@@ -38602,11 +38602,11 @@
         <v>33</v>
       </c>
       <c r="BT37" s="88">
-        <f t="shared" ref="BT37:BT64" si="14" xml:space="preserve"> LEN(BO37)</f>
+        <f t="shared" ref="BT37:BT64" si="18" xml:space="preserve"> LEN(BO37)</f>
         <v>2</v>
       </c>
       <c r="BV37" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "t": { commit: "ㆵ" }  # /-t/ ==&gt; F</v>
       </c>
       <c r="BW37" s="90"/>
@@ -38643,7 +38643,7 @@
       <c r="CU37" s="94"/>
       <c r="CV37" s="95"/>
       <c r="CX37" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY37" s="85">
@@ -38704,11 +38704,11 @@
         <v>33</v>
       </c>
       <c r="BT38" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="BV38" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "g": { commit: "ㆻ" }  # /-k/ ==&gt; Q</v>
       </c>
       <c r="BW38" s="90"/>
@@ -38745,7 +38745,7 @@
       <c r="CU38" s="94"/>
       <c r="CV38" s="95"/>
       <c r="CX38" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY38" s="85">
@@ -38844,11 +38844,11 @@
         <v>33</v>
       </c>
       <c r="BT39" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="BV39" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "z": { commit: "ㆷ" }  # /-h/ ==&gt; V</v>
       </c>
       <c r="BW39" s="90"/>
@@ -38885,7 +38885,7 @@
       <c r="CU39" s="94"/>
       <c r="CV39" s="95"/>
       <c r="CX39" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY39" s="85">
@@ -38988,12 +38988,12 @@
         <v>283</v>
       </c>
       <c r="BT40" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="BU40" s="135"/>
       <c r="BV40" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "9": { commit: "ㄞ" }  # /ai/ ==&gt; I</v>
       </c>
       <c r="BW40" s="90"/>
@@ -39031,7 +39031,7 @@
       <c r="CV40" s="95"/>
       <c r="CW40" s="135"/>
       <c r="CX40" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY40" s="85">
@@ -39152,12 +39152,12 @@
         <v>283</v>
       </c>
       <c r="BT41" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="BU41" s="135"/>
       <c r="BV41" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "l": { commit: "ㄠ" }  # /au/ ==&gt; U</v>
       </c>
       <c r="BW41" s="90"/>
@@ -39192,7 +39192,7 @@
       <c r="CU41" s="94"/>
       <c r="CV41" s="95"/>
       <c r="CX41" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY41" s="85">
@@ -39312,11 +39312,11 @@
         <v>283</v>
       </c>
       <c r="BT42" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="BV42" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "M": { commit: "ㆰ" }  # /am/ ==&gt; Y</v>
       </c>
       <c r="BW42" s="90"/>
@@ -39351,7 +39351,7 @@
       <c r="CU42" s="94"/>
       <c r="CV42" s="95"/>
       <c r="CX42" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY42" s="85">
@@ -39459,11 +39459,11 @@
         <v>283</v>
       </c>
       <c r="BT43" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="BV43" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "0": { commit: "ㄢ" }  # /an/ ==&gt; @</v>
       </c>
       <c r="BW43" s="90"/>
@@ -39498,7 +39498,7 @@
       <c r="CU43" s="94"/>
       <c r="CV43" s="95"/>
       <c r="CX43" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY43" s="85">
@@ -39544,11 +39544,11 @@
         <v>283</v>
       </c>
       <c r="BT44" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>3</v>
       </c>
       <c r="BV44" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    ";": { commit: "ㄤ" }  # /ang/ ==&gt; A</v>
       </c>
       <c r="BW44" s="90"/>
@@ -39583,7 +39583,7 @@
       <c r="CU44" s="94"/>
       <c r="CV44" s="95"/>
       <c r="CX44" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY44" s="85">
@@ -39619,11 +39619,11 @@
         <v>283</v>
       </c>
       <c r="BT45" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="BV45" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "O": { commit: "ㆱ" }  # /om/ ==&gt; W</v>
       </c>
       <c r="BW45" s="90"/>
@@ -39658,7 +39658,7 @@
       <c r="CU45" s="94"/>
       <c r="CV45" s="95"/>
       <c r="CX45" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY45" s="85">
@@ -39876,11 +39876,11 @@
         <v>283</v>
       </c>
       <c r="BT46" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>3</v>
       </c>
       <c r="BV46" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "o": { commit: "ㆲ" }  # /ong/ ==&gt; H</v>
       </c>
       <c r="BW46" s="90"/>
@@ -39915,7 +39915,7 @@
       <c r="CU46" s="94"/>
       <c r="CV46" s="95"/>
       <c r="CX46" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY46" s="85">
@@ -39935,239 +39935,239 @@
         <v>b</v>
       </c>
       <c r="C47" s="182" t="str">
-        <f t="shared" ref="C47:BI47" si="15" xml:space="preserve"> MID($E$41, C$46, 1)</f>
+        <f t="shared" ref="C47:BI47" si="19" xml:space="preserve"> MID($E$41, C$46, 1)</f>
         <v>p</v>
       </c>
       <c r="D47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>P</v>
       </c>
       <c r="E47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>m</v>
       </c>
       <c r="F47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>n</v>
       </c>
       <c r="G47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>t</v>
       </c>
       <c r="H47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>T</v>
       </c>
       <c r="I47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>l</v>
       </c>
       <c r="J47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>g</v>
       </c>
       <c r="K47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>k</v>
       </c>
       <c r="L47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>K</v>
       </c>
       <c r="M47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>ŋ</v>
       </c>
       <c r="N47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>j</v>
       </c>
       <c r="O47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>z</v>
       </c>
       <c r="P47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>c</v>
       </c>
       <c r="Q47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>s</v>
       </c>
       <c r="R47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>h</v>
       </c>
       <c r="S47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>J</v>
       </c>
       <c r="T47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>Z</v>
       </c>
       <c r="U47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>C</v>
       </c>
       <c r="V47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>S</v>
       </c>
       <c r="W47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>a</v>
       </c>
       <c r="X47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>i</v>
       </c>
       <c r="Y47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>w</v>
       </c>
       <c r="Z47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>u</v>
       </c>
       <c r="AA47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>e</v>
       </c>
       <c r="AB47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>O</v>
       </c>
       <c r="AC47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>ə</v>
       </c>
       <c r="AD47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>M</v>
       </c>
       <c r="AE47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>N</v>
       </c>
       <c r="AF47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>G</v>
       </c>
       <c r="AG47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>R</v>
       </c>
       <c r="AH47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>F</v>
       </c>
       <c r="AI47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>Q</v>
       </c>
       <c r="AJ47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>V</v>
       </c>
       <c r="AK47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>I</v>
       </c>
       <c r="AL47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>U</v>
       </c>
       <c r="AM47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>Y</v>
       </c>
       <c r="AN47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>@</v>
       </c>
       <c r="AO47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>A</v>
       </c>
       <c r="AP47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>W</v>
       </c>
       <c r="AQ47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>H</v>
       </c>
       <c r="AR47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>d</v>
       </c>
       <c r="AS47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>f</v>
       </c>
       <c r="AT47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>q</v>
       </c>
       <c r="AU47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>r</v>
       </c>
       <c r="AV47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>v</v>
       </c>
       <c r="AW47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>x</v>
       </c>
       <c r="AX47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>y</v>
       </c>
       <c r="AY47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>&amp;</v>
       </c>
       <c r="AZ47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>L</v>
       </c>
       <c r="BA47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>Ø</v>
       </c>
       <c r="BB47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="BC47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>7</v>
       </c>
       <c r="BD47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>3</v>
       </c>
       <c r="BE47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>2</v>
       </c>
       <c r="BF47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="BG47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>8</v>
       </c>
       <c r="BH47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>4</v>
       </c>
       <c r="BI47" s="182" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="BJ47" s="163"/>
@@ -40193,11 +40193,11 @@
         <v>283</v>
       </c>
       <c r="BT47" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="BV47" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "*": { commit: "ㆩ" }  # /aⁿ/ ==&gt; d</v>
       </c>
       <c r="BX47" s="85">
@@ -40231,7 +40231,7 @@
       <c r="CU47" s="94"/>
       <c r="CV47" s="95"/>
       <c r="CX47" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY47" s="85">
@@ -40251,239 +40251,239 @@
         <v>!</v>
       </c>
       <c r="C48" s="183" t="str">
-        <f t="shared" ref="C48:BI48" si="16" xml:space="preserve"> MID($E$42, C$46, 1)</f>
+        <f t="shared" ref="C48:BI48" si="20" xml:space="preserve"> MID($E$42, C$46, 1)</f>
         <v>1</v>
       </c>
       <c r="D48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>q</v>
       </c>
       <c r="E48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>a</v>
       </c>
       <c r="F48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>s</v>
       </c>
       <c r="G48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2</v>
       </c>
       <c r="H48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>w</v>
       </c>
       <c r="I48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>x</v>
       </c>
       <c r="J48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>E</v>
       </c>
       <c r="K48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>e</v>
       </c>
       <c r="L48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>d</v>
       </c>
       <c r="M48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>N</v>
       </c>
       <c r="N48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>Y</v>
       </c>
       <c r="O48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>y</v>
       </c>
       <c r="P48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>h</v>
       </c>
       <c r="Q48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>n</v>
       </c>
       <c r="R48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>c</v>
       </c>
       <c r="S48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>R</v>
       </c>
       <c r="T48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>r</v>
       </c>
       <c r="U48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>f</v>
       </c>
       <c r="V48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>v</v>
       </c>
       <c r="W48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>8</v>
       </c>
       <c r="X48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>u</v>
       </c>
       <c r="Y48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>K</v>
       </c>
       <c r="Z48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>j</v>
       </c>
       <c r="AA48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>,</v>
       </c>
       <c r="AB48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>i</v>
       </c>
       <c r="AC48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>k</v>
       </c>
       <c r="AD48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>m</v>
       </c>
       <c r="AE48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>p</v>
       </c>
       <c r="AF48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>/</v>
       </c>
       <c r="AG48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>b</v>
       </c>
       <c r="AH48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>t</v>
       </c>
       <c r="AI48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>g</v>
       </c>
       <c r="AJ48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>z</v>
       </c>
       <c r="AK48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>9</v>
       </c>
       <c r="AL48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>l</v>
       </c>
       <c r="AM48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>M</v>
       </c>
       <c r="AN48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AO48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>;</v>
       </c>
       <c r="AP48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>O</v>
       </c>
       <c r="AQ48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>o</v>
       </c>
       <c r="AR48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>*</v>
       </c>
       <c r="AS48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>U</v>
       </c>
       <c r="AT48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>J</v>
       </c>
       <c r="AU48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>&lt;</v>
       </c>
       <c r="AV48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>I</v>
       </c>
       <c r="AW48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>(</v>
       </c>
       <c r="AX48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>L</v>
       </c>
       <c r="AY48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>7</v>
       </c>
       <c r="AZ48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-</v>
       </c>
       <c r="BA48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>=</v>
       </c>
       <c r="BB48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>"</v>
       </c>
       <c r="BC48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>5</v>
       </c>
       <c r="BD48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>3</v>
       </c>
       <c r="BE48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>4</v>
       </c>
       <c r="BF48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>6</v>
       </c>
       <c r="BG48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>]</v>
       </c>
       <c r="BH48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>[</v>
       </c>
       <c r="BI48" s="183" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="BJ48" s="163"/>
@@ -40509,11 +40509,11 @@
         <v>283</v>
       </c>
       <c r="BT48" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="BV48" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "U": { commit: "ㆪ" }  # /iⁿ/ ==&gt; f</v>
       </c>
       <c r="BX48" s="85">
@@ -40547,7 +40547,7 @@
       <c r="CU48" s="94"/>
       <c r="CV48" s="95"/>
       <c r="CX48" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY48" s="85">
@@ -40592,11 +40592,11 @@
         <v>283</v>
       </c>
       <c r="BT49" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="BV49" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "J": { commit: "ㆫ" }  # /uⁿ/ ==&gt; q</v>
       </c>
       <c r="BX49" s="85">
@@ -40630,7 +40630,7 @@
       <c r="CU49" s="94"/>
       <c r="CV49" s="95"/>
       <c r="CX49" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY49" s="85">
@@ -40728,11 +40728,11 @@
         <v>283</v>
       </c>
       <c r="BT50" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="BV50" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "&lt;": { commit: "ㆥ" }  # /eⁿ/ ==&gt; r</v>
       </c>
       <c r="BX50" s="85">
@@ -40766,7 +40766,7 @@
       <c r="CU50" s="94"/>
       <c r="CV50" s="95"/>
       <c r="CX50" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY50" s="85">
@@ -40867,11 +40867,11 @@
         <v>283</v>
       </c>
       <c r="BT51" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="BV51" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "I": { commit: "ㆧ" }  # /oⁿ/ ==&gt; v</v>
       </c>
       <c r="BX51" s="85">
@@ -40905,7 +40905,7 @@
       <c r="CU51" s="94"/>
       <c r="CV51" s="95"/>
       <c r="CX51" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY51" s="85">
@@ -41005,11 +41005,11 @@
         <v>283</v>
       </c>
       <c r="BT52" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>3</v>
       </c>
       <c r="BV52" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "(": { commit: "ㆮ" }  # /aiⁿ/ ==&gt; x</v>
       </c>
       <c r="BX52" s="85">
@@ -41043,7 +41043,7 @@
       <c r="CU52" s="94"/>
       <c r="CV52" s="95"/>
       <c r="CX52" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY52" s="85">
@@ -41150,11 +41150,11 @@
         <v>283</v>
       </c>
       <c r="BT53" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>3</v>
       </c>
       <c r="BV53" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "L": { commit: "ㆯ" }  # /auⁿ/ ==&gt; y</v>
       </c>
       <c r="BX53" s="85">
@@ -41188,7 +41188,7 @@
       <c r="CU53" s="94"/>
       <c r="CV53" s="95"/>
       <c r="CX53" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY53" s="85">
@@ -41295,11 +41295,11 @@
         <v>284</v>
       </c>
       <c r="BT54" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="BV54" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "7": { commit: "入" }  # /0/ ==&gt; &amp;</v>
       </c>
       <c r="BX54" s="85">
@@ -41333,7 +41333,7 @@
       <c r="CU54" s="94"/>
       <c r="CV54" s="95"/>
       <c r="CX54" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY54" s="85">
@@ -41434,11 +41434,11 @@
         <v>284</v>
       </c>
       <c r="BT55" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="BV55" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "-": { commit: "ㄥ" }  # /ⁿ/ ==&gt; L</v>
       </c>
       <c r="BX55" s="85">
@@ -41472,7 +41472,7 @@
       <c r="CU55" s="94"/>
       <c r="CV55" s="95"/>
       <c r="CX55" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY55" s="85">
@@ -41573,11 +41573,11 @@
         <v>284</v>
       </c>
       <c r="BT56" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="BV56" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "=": { commit: "Ø" }  # /Ø/ ==&gt; Ø</v>
       </c>
       <c r="BX56" s="85">
@@ -41611,7 +41611,7 @@
       <c r="CU56" s="94"/>
       <c r="CV56" s="95"/>
       <c r="CX56" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="CY56" s="85">
@@ -41649,11 +41649,11 @@
         <v>284</v>
       </c>
       <c r="BT57" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="BV57" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    """: { commit: "一" }  # /1/ ==&gt; 1</v>
       </c>
       <c r="BX57" s="85">
@@ -41901,11 +41901,11 @@
         <v>284</v>
       </c>
       <c r="BT58" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="BV58" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "5": { commit: "七" }  # /7/ ==&gt; 7</v>
       </c>
       <c r="BX58" s="85">
@@ -41955,239 +41955,239 @@
         <v>!</v>
       </c>
       <c r="C59" s="183" t="str">
-        <f t="shared" ref="C59:BI59" si="17" xml:space="preserve"> MID($E$53, C$46, 1)</f>
+        <f t="shared" ref="C59:BI59" si="21" xml:space="preserve"> MID($E$53, C$46, 1)</f>
         <v>1</v>
       </c>
       <c r="D59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>q</v>
       </c>
       <c r="E59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>a</v>
       </c>
       <c r="F59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>s</v>
       </c>
       <c r="G59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>2</v>
       </c>
       <c r="H59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>w</v>
       </c>
       <c r="I59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>x</v>
       </c>
       <c r="J59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>E</v>
       </c>
       <c r="K59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>e</v>
       </c>
       <c r="L59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>d</v>
       </c>
       <c r="M59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>N</v>
       </c>
       <c r="N59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>Y</v>
       </c>
       <c r="O59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>y</v>
       </c>
       <c r="P59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>h</v>
       </c>
       <c r="Q59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>n</v>
       </c>
       <c r="R59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>c</v>
       </c>
       <c r="S59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>R</v>
       </c>
       <c r="T59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>r</v>
       </c>
       <c r="U59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>f</v>
       </c>
       <c r="V59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>v</v>
       </c>
       <c r="W59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>8</v>
       </c>
       <c r="X59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>u</v>
       </c>
       <c r="Y59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>K</v>
       </c>
       <c r="Z59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>j</v>
       </c>
       <c r="AA59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>,</v>
       </c>
       <c r="AB59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>i</v>
       </c>
       <c r="AC59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>k</v>
       </c>
       <c r="AD59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>m</v>
       </c>
       <c r="AE59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>p</v>
       </c>
       <c r="AF59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>/</v>
       </c>
       <c r="AG59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>b</v>
       </c>
       <c r="AH59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>t</v>
       </c>
       <c r="AI59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>g</v>
       </c>
       <c r="AJ59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>z</v>
       </c>
       <c r="AK59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>9</v>
       </c>
       <c r="AL59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>l</v>
       </c>
       <c r="AM59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>M</v>
       </c>
       <c r="AN59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AO59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>;</v>
       </c>
       <c r="AP59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>O</v>
       </c>
       <c r="AQ59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>o</v>
       </c>
       <c r="AR59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>*</v>
       </c>
       <c r="AS59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>U</v>
       </c>
       <c r="AT59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>J</v>
       </c>
       <c r="AU59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>&lt;</v>
       </c>
       <c r="AV59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>I</v>
       </c>
       <c r="AW59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>(</v>
       </c>
       <c r="AX59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>L</v>
       </c>
       <c r="AY59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>7</v>
       </c>
       <c r="AZ59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>-</v>
       </c>
       <c r="BA59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>=</v>
       </c>
       <c r="BB59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>"</v>
       </c>
       <c r="BC59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="BD59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>3</v>
       </c>
       <c r="BE59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>4</v>
       </c>
       <c r="BF59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>6</v>
       </c>
       <c r="BG59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>]</v>
       </c>
       <c r="BH59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>[</v>
       </c>
       <c r="BI59" s="183" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="BJ59" s="163"/>
@@ -42213,11 +42213,11 @@
         <v>284</v>
       </c>
       <c r="BT59" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="BV59" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "3": { commit: "三" }  # /3/ ==&gt; 3</v>
       </c>
       <c r="BX59" s="85">
@@ -42267,239 +42267,239 @@
         <v>ㆠ</v>
       </c>
       <c r="C60" s="194" t="str">
-        <f t="shared" ref="C60:BI60" si="18" xml:space="preserve"> MID($E$54, C$46, 1)</f>
+        <f t="shared" ref="C60:BI60" si="22" xml:space="preserve"> MID($E$54, C$46, 1)</f>
         <v>ㄅ</v>
       </c>
       <c r="D60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄆ</v>
       </c>
       <c r="E60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄇ</v>
       </c>
       <c r="F60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄋ</v>
       </c>
       <c r="G60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄉ</v>
       </c>
       <c r="H60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄊ</v>
       </c>
       <c r="I60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄌ</v>
       </c>
       <c r="J60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㆣ</v>
       </c>
       <c r="K60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄍ</v>
       </c>
       <c r="L60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄎ</v>
       </c>
       <c r="M60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄫ</v>
       </c>
       <c r="N60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㆡ</v>
       </c>
       <c r="O60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄗ</v>
       </c>
       <c r="P60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄘ</v>
       </c>
       <c r="Q60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄙ</v>
       </c>
       <c r="R60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄏ</v>
       </c>
       <c r="S60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㆢ</v>
       </c>
       <c r="T60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄐ</v>
       </c>
       <c r="U60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄑ</v>
       </c>
       <c r="V60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄒ</v>
       </c>
       <c r="W60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄚ</v>
       </c>
       <c r="X60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄧ</v>
       </c>
       <c r="Y60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㆨ</v>
       </c>
       <c r="Z60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄨ</v>
       </c>
       <c r="AA60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㆤ</v>
       </c>
       <c r="AB60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㆦ</v>
       </c>
       <c r="AC60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄜ</v>
       </c>
       <c r="AD60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㆬ</v>
       </c>
       <c r="AE60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄣ</v>
       </c>
       <c r="AF60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㆭ</v>
       </c>
       <c r="AG60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㆴ</v>
       </c>
       <c r="AH60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㆵ</v>
       </c>
       <c r="AI60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㆻ</v>
       </c>
       <c r="AJ60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㆷ</v>
       </c>
       <c r="AK60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄞ</v>
       </c>
       <c r="AL60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄠ</v>
       </c>
       <c r="AM60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㆰ</v>
       </c>
       <c r="AN60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄢ</v>
       </c>
       <c r="AO60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄤ</v>
       </c>
       <c r="AP60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㆱ</v>
       </c>
       <c r="AQ60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㆲ</v>
       </c>
       <c r="AR60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㆩ</v>
       </c>
       <c r="AS60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㆪ</v>
       </c>
       <c r="AT60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㆫ</v>
       </c>
       <c r="AU60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㆥ</v>
       </c>
       <c r="AV60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㆧ</v>
       </c>
       <c r="AW60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㆮ</v>
       </c>
       <c r="AX60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㆯ</v>
       </c>
       <c r="AY60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>入</v>
       </c>
       <c r="AZ60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>ㄥ</v>
       </c>
       <c r="BA60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>Ø</v>
       </c>
       <c r="BB60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>一</v>
       </c>
       <c r="BC60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>七</v>
       </c>
       <c r="BD60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>三</v>
       </c>
       <c r="BE60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>二</v>
       </c>
       <c r="BF60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>五</v>
       </c>
       <c r="BG60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>八</v>
       </c>
       <c r="BH60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>四</v>
       </c>
       <c r="BI60" s="194" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BJ60" s="163"/>
@@ -42525,11 +42525,11 @@
         <v>284</v>
       </c>
       <c r="BT60" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="BV60" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "4": { commit: "二" }  # /2/ ==&gt; 2</v>
       </c>
       <c r="BX60" s="85">
@@ -42657,11 +42657,11 @@
         <v>36</v>
       </c>
       <c r="BT61" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="BV61" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "6": { commit: "五" }  # /5/ ==&gt; 5</v>
       </c>
       <c r="BX61" s="85">
@@ -42789,11 +42789,11 @@
         <v>36</v>
       </c>
       <c r="BT62" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="BV62" s="89" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">    "]": { commit: "八" }  # /8/ ==&gt; 8</v>
       </c>
       <c r="BX62" s="85">
@@ -42921,7 +42921,7 @@
       </c>
       <c r="BS63" s="87"/>
       <c r="BT63" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="BX63" s="85">
@@ -43041,7 +43041,7 @@
       <c r="BR64" s="77"/>
       <c r="BS64" s="87"/>
       <c r="BT64" s="88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BX64" s="85">
@@ -46701,25 +46701,25 @@
   <sheetData>
     <row r="1" spans="2:19" ht="21.75" thickBot="1"/>
     <row r="2" spans="2:19" ht="24" thickBot="1">
-      <c r="B2" s="275" t="s">
+      <c r="B2" s="277" t="s">
         <v>328</v>
       </c>
-      <c r="C2" s="277" t="s">
+      <c r="C2" s="279" t="s">
         <v>329</v>
       </c>
-      <c r="D2" s="278"/>
-      <c r="E2" s="281" t="s">
+      <c r="D2" s="280"/>
+      <c r="E2" s="283" t="s">
         <v>330</v>
       </c>
-      <c r="F2" s="282"/>
-      <c r="G2" s="283"/>
-      <c r="H2" s="281" t="s">
+      <c r="F2" s="284"/>
+      <c r="G2" s="285"/>
+      <c r="H2" s="283" t="s">
         <v>331</v>
       </c>
-      <c r="I2" s="282"/>
-      <c r="J2" s="282"/>
-      <c r="K2" s="282"/>
-      <c r="L2" s="283"/>
+      <c r="I2" s="284"/>
+      <c r="J2" s="284"/>
+      <c r="K2" s="284"/>
+      <c r="L2" s="285"/>
       <c r="O2" s="228" t="s">
         <v>480</v>
       </c>
@@ -46734,9 +46734,9 @@
       </c>
     </row>
     <row r="3" spans="2:19" ht="24" thickBot="1">
-      <c r="B3" s="276"/>
-      <c r="C3" s="279"/>
-      <c r="D3" s="280"/>
+      <c r="B3" s="278"/>
+      <c r="C3" s="281"/>
+      <c r="D3" s="282"/>
       <c r="E3" s="226" t="s">
         <v>332</v>
       </c>
@@ -46755,10 +46755,10 @@
       <c r="J3" s="226" t="s">
         <v>337</v>
       </c>
-      <c r="K3" s="281" t="s">
+      <c r="K3" s="283" t="s">
         <v>338</v>
       </c>
-      <c r="L3" s="283"/>
+      <c r="L3" s="285"/>
       <c r="O3" s="228" t="s">
         <v>274</v>
       </c>
@@ -47650,57 +47650,57 @@
       <c r="B27" s="226" t="s">
         <v>443</v>
       </c>
-      <c r="C27" s="272" t="s">
+      <c r="C27" s="286" t="s">
         <v>188</v>
       </c>
-      <c r="D27" s="273"/>
-      <c r="E27" s="272" t="s">
+      <c r="D27" s="287"/>
+      <c r="E27" s="286" t="s">
         <v>444</v>
       </c>
-      <c r="F27" s="274"/>
-      <c r="G27" s="274"/>
-      <c r="H27" s="274"/>
-      <c r="I27" s="274"/>
-      <c r="J27" s="273"/>
-      <c r="K27" s="272" t="s">
+      <c r="F27" s="288"/>
+      <c r="G27" s="288"/>
+      <c r="H27" s="288"/>
+      <c r="I27" s="288"/>
+      <c r="J27" s="287"/>
+      <c r="K27" s="286" t="s">
         <v>445</v>
       </c>
-      <c r="L27" s="273"/>
+      <c r="L27" s="287"/>
     </row>
     <row r="28" spans="2:20" ht="24" thickBot="1">
       <c r="B28" s="226" t="s">
         <v>446</v>
       </c>
-      <c r="C28" s="272" t="s">
+      <c r="C28" s="286" t="s">
         <v>447</v>
       </c>
-      <c r="D28" s="273"/>
-      <c r="E28" s="272" t="s">
+      <c r="D28" s="287"/>
+      <c r="E28" s="286" t="s">
         <v>444</v>
       </c>
-      <c r="F28" s="274"/>
-      <c r="G28" s="274"/>
-      <c r="H28" s="274"/>
-      <c r="I28" s="274"/>
-      <c r="J28" s="273"/>
-      <c r="K28" s="272" t="s">
+      <c r="F28" s="288"/>
+      <c r="G28" s="288"/>
+      <c r="H28" s="288"/>
+      <c r="I28" s="288"/>
+      <c r="J28" s="287"/>
+      <c r="K28" s="286" t="s">
         <v>448</v>
       </c>
-      <c r="L28" s="273"/>
+      <c r="L28" s="287"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:D3"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="K3:L3"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="E27:J27"/>
     <mergeCell ref="K27:L27"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:J28"/>
     <mergeCell ref="K28:L28"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:D3"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -47722,30 +47722,30 @@
   <sheetData>
     <row r="1" spans="2:20" ht="21.75" thickBot="1"/>
     <row r="2" spans="2:20" ht="24" thickBot="1">
-      <c r="B2" s="275" t="s">
+      <c r="B2" s="277" t="s">
         <v>328</v>
       </c>
-      <c r="C2" s="277" t="s">
+      <c r="C2" s="279" t="s">
         <v>329</v>
       </c>
-      <c r="D2" s="278"/>
-      <c r="E2" s="281" t="s">
+      <c r="D2" s="280"/>
+      <c r="E2" s="283" t="s">
         <v>330</v>
       </c>
-      <c r="F2" s="282"/>
-      <c r="G2" s="283"/>
-      <c r="H2" s="281" t="s">
+      <c r="F2" s="284"/>
+      <c r="G2" s="285"/>
+      <c r="H2" s="283" t="s">
         <v>331</v>
       </c>
-      <c r="I2" s="282"/>
-      <c r="J2" s="282"/>
-      <c r="K2" s="282"/>
-      <c r="L2" s="283"/>
+      <c r="I2" s="284"/>
+      <c r="J2" s="284"/>
+      <c r="K2" s="284"/>
+      <c r="L2" s="285"/>
     </row>
     <row r="3" spans="2:20" ht="24" thickBot="1">
-      <c r="B3" s="276"/>
-      <c r="C3" s="279"/>
-      <c r="D3" s="280"/>
+      <c r="B3" s="278"/>
+      <c r="C3" s="281"/>
+      <c r="D3" s="282"/>
       <c r="E3" s="226" t="s">
         <v>332</v>
       </c>
@@ -47764,10 +47764,10 @@
       <c r="J3" s="226" t="s">
         <v>337</v>
       </c>
-      <c r="K3" s="281" t="s">
+      <c r="K3" s="283" t="s">
         <v>338</v>
       </c>
-      <c r="L3" s="283"/>
+      <c r="L3" s="285"/>
       <c r="N3" s="232" t="s">
         <v>505</v>
       </c>
@@ -48800,43 +48800,43 @@
       <c r="B27" s="226" t="s">
         <v>443</v>
       </c>
-      <c r="C27" s="272" t="s">
+      <c r="C27" s="286" t="s">
         <v>188</v>
       </c>
-      <c r="D27" s="273"/>
-      <c r="E27" s="272" t="s">
+      <c r="D27" s="287"/>
+      <c r="E27" s="286" t="s">
         <v>444</v>
       </c>
-      <c r="F27" s="274"/>
-      <c r="G27" s="274"/>
-      <c r="H27" s="274"/>
-      <c r="I27" s="274"/>
-      <c r="J27" s="273"/>
-      <c r="K27" s="272" t="s">
+      <c r="F27" s="288"/>
+      <c r="G27" s="288"/>
+      <c r="H27" s="288"/>
+      <c r="I27" s="288"/>
+      <c r="J27" s="287"/>
+      <c r="K27" s="286" t="s">
         <v>445</v>
       </c>
-      <c r="L27" s="273"/>
+      <c r="L27" s="287"/>
     </row>
     <row r="28" spans="2:21" ht="24" thickBot="1">
       <c r="B28" s="226" t="s">
         <v>446</v>
       </c>
-      <c r="C28" s="272" t="s">
+      <c r="C28" s="286" t="s">
         <v>447</v>
       </c>
-      <c r="D28" s="273"/>
-      <c r="E28" s="272" t="s">
+      <c r="D28" s="287"/>
+      <c r="E28" s="286" t="s">
         <v>444</v>
       </c>
-      <c r="F28" s="274"/>
-      <c r="G28" s="274"/>
-      <c r="H28" s="274"/>
-      <c r="I28" s="274"/>
-      <c r="J28" s="273"/>
-      <c r="K28" s="272" t="s">
+      <c r="F28" s="288"/>
+      <c r="G28" s="288"/>
+      <c r="H28" s="288"/>
+      <c r="I28" s="288"/>
+      <c r="J28" s="287"/>
+      <c r="K28" s="286" t="s">
         <v>448</v>
       </c>
-      <c r="L28" s="273"/>
+      <c r="L28" s="287"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N4:T20">
@@ -48875,25 +48875,25 @@
   <sheetData>
     <row r="1" spans="2:18" ht="21.75" thickBot="1"/>
     <row r="2" spans="2:18" ht="24" thickBot="1">
-      <c r="B2" s="275" t="s">
+      <c r="B2" s="277" t="s">
         <v>328</v>
       </c>
-      <c r="C2" s="277" t="s">
+      <c r="C2" s="279" t="s">
         <v>329</v>
       </c>
-      <c r="D2" s="278"/>
-      <c r="E2" s="281" t="s">
+      <c r="D2" s="280"/>
+      <c r="E2" s="283" t="s">
         <v>330</v>
       </c>
-      <c r="F2" s="282"/>
-      <c r="G2" s="283"/>
-      <c r="H2" s="281" t="s">
+      <c r="F2" s="284"/>
+      <c r="G2" s="285"/>
+      <c r="H2" s="283" t="s">
         <v>331</v>
       </c>
-      <c r="I2" s="282"/>
-      <c r="J2" s="282"/>
-      <c r="K2" s="282"/>
-      <c r="L2" s="283"/>
+      <c r="I2" s="284"/>
+      <c r="J2" s="284"/>
+      <c r="K2" s="284"/>
+      <c r="L2" s="285"/>
       <c r="P2" s="228" t="str">
         <f xml:space="preserve"> "([48])"</f>
         <v>([48])</v>
@@ -48903,9 +48903,9 @@
       </c>
     </row>
     <row r="3" spans="2:18" ht="24" thickBot="1">
-      <c r="B3" s="276"/>
-      <c r="C3" s="279"/>
-      <c r="D3" s="280"/>
+      <c r="B3" s="278"/>
+      <c r="C3" s="281"/>
+      <c r="D3" s="282"/>
       <c r="E3" s="226" t="s">
         <v>332</v>
       </c>
@@ -48924,10 +48924,10 @@
       <c r="J3" s="226" t="s">
         <v>337</v>
       </c>
-      <c r="K3" s="281" t="s">
+      <c r="K3" s="283" t="s">
         <v>338</v>
       </c>
-      <c r="L3" s="283"/>
+      <c r="L3" s="285"/>
       <c r="N3" s="228" t="s">
         <v>450</v>
       </c>
@@ -49819,43 +49819,43 @@
       <c r="B27" s="226" t="s">
         <v>443</v>
       </c>
-      <c r="C27" s="272" t="s">
+      <c r="C27" s="286" t="s">
         <v>188</v>
       </c>
-      <c r="D27" s="273"/>
-      <c r="E27" s="272" t="s">
+      <c r="D27" s="287"/>
+      <c r="E27" s="286" t="s">
         <v>444</v>
       </c>
-      <c r="F27" s="274"/>
-      <c r="G27" s="274"/>
-      <c r="H27" s="274"/>
-      <c r="I27" s="274"/>
-      <c r="J27" s="273"/>
-      <c r="K27" s="272" t="s">
+      <c r="F27" s="288"/>
+      <c r="G27" s="288"/>
+      <c r="H27" s="288"/>
+      <c r="I27" s="288"/>
+      <c r="J27" s="287"/>
+      <c r="K27" s="286" t="s">
         <v>445</v>
       </c>
-      <c r="L27" s="273"/>
+      <c r="L27" s="287"/>
     </row>
     <row r="28" spans="2:19" ht="24" thickBot="1">
       <c r="B28" s="226" t="s">
         <v>446</v>
       </c>
-      <c r="C28" s="272" t="s">
+      <c r="C28" s="286" t="s">
         <v>447</v>
       </c>
-      <c r="D28" s="273"/>
-      <c r="E28" s="272" t="s">
+      <c r="D28" s="287"/>
+      <c r="E28" s="286" t="s">
         <v>444</v>
       </c>
-      <c r="F28" s="274"/>
-      <c r="G28" s="274"/>
-      <c r="H28" s="274"/>
-      <c r="I28" s="274"/>
-      <c r="J28" s="273"/>
-      <c r="K28" s="272" t="s">
+      <c r="F28" s="288"/>
+      <c r="G28" s="288"/>
+      <c r="H28" s="288"/>
+      <c r="I28" s="288"/>
+      <c r="J28" s="287"/>
+      <c r="K28" s="286" t="s">
         <v>448</v>
       </c>
-      <c r="L28" s="273"/>
+      <c r="L28" s="287"/>
     </row>
   </sheetData>
   <mergeCells count="11">

--- a/docs/301_鍵盤設計規格_方音符號輸入_台語注音二式編碼.xlsx
+++ b/docs/301_鍵盤設計規格_方音符號輸入_台語注音二式編碼.xlsx
@@ -1,54 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23DA727F-83DE-41D5-9D1C-09419340D81E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921C984D-9848-4087-B1C2-6E3F24BB4469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="54480" yWindow="-2985" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{6D6F034E-466E-416C-B3CC-1F7937B8DE3D}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6D6F034E-466E-416C-B3CC-1F7937B8DE3D}"/>
   </bookViews>
   <sheets>
-    <sheet name="台語注音二式【xlit解析】" sheetId="7" r:id="rId1"/>
-    <sheet name="台語注音二式【RIME設置】 " sheetId="8" r:id="rId2"/>
-    <sheet name=" 台語音標【xlit解析】" sheetId="1" r:id="rId3"/>
-    <sheet name="方音符號【RIME設置】" sheetId="2" r:id="rId4"/>
-    <sheet name="韻母列表" sheetId="4" r:id="rId5"/>
-    <sheet name="韻母列表 (陽聲韻轉換)" sheetId="5" r:id="rId6"/>
-    <sheet name="韻母列表 (3)" sheetId="6" r:id="rId7"/>
-    <sheet name="聲調符號" sheetId="3" r:id="rId8"/>
+    <sheet name="台語注音二式【xlit驗證】" sheetId="9" r:id="rId1"/>
+    <sheet name="台語注音二式【xlit解析】" sheetId="7" r:id="rId2"/>
+    <sheet name="台語注音二式【RIME設置】 " sheetId="8" r:id="rId3"/>
+    <sheet name=" 台語音標【xlit解析】" sheetId="1" r:id="rId4"/>
+    <sheet name="方音符號【RIME設置】" sheetId="2" r:id="rId5"/>
+    <sheet name="韻母列表" sheetId="4" r:id="rId6"/>
+    <sheet name="韻母列表 (陽聲韻轉換)" sheetId="5" r:id="rId7"/>
+    <sheet name="韻母列表 (3)" sheetId="6" r:id="rId8"/>
+    <sheet name="聲調符號" sheetId="3" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">方音符號【RIME設置】!$BR$4:$BT$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'台語注音二式【RIME設置】 '!$BR$4:$BT$59</definedName>
-    <definedName name="_xlnm.Criteria" localSheetId="3">方音符號【RIME設置】!$CQ$1:$CQ$2</definedName>
-    <definedName name="_xlnm.Criteria" localSheetId="1">'台語注音二式【RIME設置】 '!$CQ$1:$CQ$2</definedName>
-    <definedName name="_xlnm.Extract" localSheetId="3">方音符號【RIME設置】!$CR$4:$CV$4</definedName>
-    <definedName name="_xlnm.Extract" localSheetId="1">'台語注音二式【RIME設置】 '!$CR$4:$CV$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">方音符號【RIME設置】!$BR$4:$BT$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'台語注音二式【RIME設置】 '!$BR$4:$BT$59</definedName>
+    <definedName name="_xlnm.Criteria" localSheetId="4">方音符號【RIME設置】!$CQ$1:$CQ$2</definedName>
+    <definedName name="_xlnm.Criteria" localSheetId="2">'台語注音二式【RIME設置】 '!$CQ$1:$CQ$2</definedName>
+    <definedName name="_xlnm.Extract" localSheetId="4">方音符號【RIME設置】!$CR$4:$CV$4</definedName>
+    <definedName name="_xlnm.Extract" localSheetId="2">'台語注音二式【RIME設置】 '!$CR$4:$CV$4</definedName>
     <definedName name="十五音韻母">#REF!</definedName>
     <definedName name="十五音韻母對照表">#REF!</definedName>
-    <definedName name="方音符號" localSheetId="3">#REF!</definedName>
-    <definedName name="方音符號" localSheetId="1">#REF!</definedName>
+    <definedName name="方音符號" localSheetId="4">#REF!</definedName>
+    <definedName name="方音符號" localSheetId="2">#REF!</definedName>
     <definedName name="方音符號">#REF!</definedName>
     <definedName name="台羅韻母八音反切">#REF!</definedName>
     <definedName name="白話字韻母八音反切">#REF!</definedName>
-    <definedName name="字典編碼" localSheetId="3">#REF!</definedName>
-    <definedName name="字典編碼" localSheetId="1">#REF!</definedName>
+    <definedName name="字典編碼" localSheetId="4">#REF!</definedName>
+    <definedName name="字典編碼" localSheetId="2">#REF!</definedName>
     <definedName name="字典編碼">#REF!</definedName>
     <definedName name="注音符號">#REF!</definedName>
     <definedName name="注音編碼">#REF!</definedName>
-    <definedName name="拼音字母" localSheetId="3">#REF!</definedName>
-    <definedName name="拼音字母" localSheetId="1">#REF!</definedName>
+    <definedName name="拼音字母" localSheetId="4">#REF!</definedName>
+    <definedName name="拼音字母" localSheetId="2">#REF!</definedName>
     <definedName name="拼音字母">#REF!</definedName>
     <definedName name="閩拼韻母八音反切">#REF!</definedName>
     <definedName name="聲母碼">#REF!</definedName>
     <definedName name="聲母碼表">#REF!</definedName>
-    <definedName name="鍵盤位置" localSheetId="3">#REF!</definedName>
-    <definedName name="鍵盤位置" localSheetId="1">#REF!</definedName>
+    <definedName name="鍵盤位置" localSheetId="4">#REF!</definedName>
+    <definedName name="鍵盤位置" localSheetId="2">#REF!</definedName>
     <definedName name="鍵盤位置">#REF!</definedName>
     <definedName name="鍵盤按鍵">#REF!</definedName>
     <definedName name="韻母對照表">#REF!</definedName>
@@ -98,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2457" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2763" uniqueCount="590">
   <si>
     <t>algebra:</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -2222,6 +2223,20 @@
   <si>
     <t>=</t>
   </si>
+  <si>
+    <t>!1qa2wsxEedNcYyhnRrfv8uKj,ik9l*UJ&lt;I(Lm/pM0;Oobtgz=-"5346[].7</t>
+  </si>
+  <si>
+    <t>BbpmdtnlĞgkŋhZzcsJjCSaiwueOəIUDfqrvxyMGNY@AWHRFQVØL173254806</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!1qa2wsxEedNcYyhnRrfv8uKj,ik9l*UJ&lt;I(Lm/pM0;Oobtgz=-"5346[].7</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆠㄅㄆㄇㄉㄊㄋㄌㆣㄍㄎㄫㄏㆡㄗㄘㄙㆢㄐㄑㄒㄚㄧㆨㄨㆤㆦㄜㄞㄠㆩㆪㆫㆥㆧㆮㆯㆬㆭㄣㆰㄢㄤㆱㆲㆴㆵㆻㆷØㄥ一七三二五四八輕ʔ</t>
+  </si>
 </sst>
 </file>
 
@@ -2230,7 +2245,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="General;;"/>
   </numFmts>
-  <fonts count="126">
+  <fonts count="127">
     <font>
       <sz val="16"/>
       <color rgb="FF000000"/>
@@ -2299,7 +2314,6 @@
     <font>
       <sz val="20"/>
       <name val="宋体"/>
-      <charset val="136"/>
     </font>
     <font>
       <sz val="24"/>
@@ -2349,7 +2363,6 @@
       <sz val="20"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="136"/>
     </font>
     <font>
       <b/>
@@ -2369,7 +2382,6 @@
       <sz val="20"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="136"/>
     </font>
     <font>
       <b/>
@@ -2395,7 +2407,6 @@
     <font>
       <sz val="24"/>
       <name val="宋体"/>
-      <charset val="136"/>
     </font>
     <font>
       <sz val="26"/>
@@ -2431,7 +2442,6 @@
     <font>
       <sz val="18"/>
       <name val="宋体"/>
-      <charset val="136"/>
     </font>
     <font>
       <sz val="24"/>
@@ -2530,7 +2540,6 @@
       <sz val="18"/>
       <color rgb="FF0070C0"/>
       <name val="宋体"/>
-      <charset val="136"/>
     </font>
     <font>
       <sz val="18"/>
@@ -2702,7 +2711,6 @@
     <font>
       <sz val="22"/>
       <name val="宋体"/>
-      <charset val="136"/>
     </font>
     <font>
       <sz val="22"/>
@@ -3071,6 +3079,13 @@
       <sz val="24"/>
       <color theme="0"/>
       <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Sarasa Fixed CL"/>
       <family val="3"/>
       <charset val="136"/>
     </font>
@@ -3538,7 +3553,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="289">
+  <cellXfs count="291">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4278,6 +4293,15 @@
     <xf numFmtId="176" fontId="21" fillId="9" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="101" fillId="29" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="29" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="29" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="100" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4305,15 +4329,8 @@
     <xf numFmtId="0" fontId="100" fillId="30" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="101" fillId="29" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="29" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="29" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="126" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -4752,7 +4769,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55526294-CC81-4CA6-8F3B-4D8F28532425}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B04868BE-4141-4119-9A74-1597E64EFDB6}">
   <dimension ref="A1:CH76"/>
   <sheetFormatPr defaultRowHeight="25.5" outlineLevelRow="1"/>
   <cols>
@@ -5967,15 +5984,27 @@
       </c>
     </row>
     <row r="14" spans="1:86" outlineLevel="1">
-      <c r="C14" s="1" t="str">
-        <f xml:space="preserve"> MID(C9, B10+1,  B11-B10-1)</f>
-        <v>BbpmdtnlGgkŋZzcsJjCShaiwueOəIUdfqrvxyMGNY@AWHRFQV7325841L&amp;*</v>
-      </c>
+      <c r="C14" s="289" t="s">
+        <v>587</v>
+      </c>
+      <c r="D14" s="290"/>
+      <c r="E14" s="290"/>
+      <c r="F14" s="290"/>
+      <c r="G14" s="290"/>
+      <c r="H14" s="290"/>
+      <c r="I14" s="290"/>
+      <c r="J14" s="290"/>
+      <c r="K14" s="290"/>
+      <c r="L14" s="290"/>
+      <c r="M14" s="290"/>
+      <c r="N14" s="290"/>
+      <c r="O14" s="290"/>
+      <c r="P14" s="290"/>
       <c r="BL14" s="238" t="str">
         <v>ŋ</v>
       </c>
       <c r="BM14" s="238" t="str">
-        <v>G</v>
+        <v>N</v>
       </c>
       <c r="BN14" s="238" t="str">
         <v>ㄫ</v>
@@ -6014,18 +6043,30 @@
       </c>
     </row>
     <row r="15" spans="1:86" outlineLevel="1">
-      <c r="C15" s="1" t="str">
-        <f xml:space="preserve"> MID(C9, B11+1,  B12-B11-1)</f>
-        <v>!1qa2wsxEedGYyhnRrfvc8uKj,ik9l*UJ&lt;I(Lm/pM0;Oobtgz53467][N.-</v>
-      </c>
+      <c r="C15" s="289" t="s">
+        <v>586</v>
+      </c>
+      <c r="D15" s="290"/>
+      <c r="E15" s="290"/>
+      <c r="F15" s="290"/>
+      <c r="G15" s="290"/>
+      <c r="H15" s="290"/>
+      <c r="I15" s="290"/>
+      <c r="J15" s="290"/>
+      <c r="K15" s="290"/>
+      <c r="L15" s="290"/>
+      <c r="M15" s="290"/>
+      <c r="N15" s="290"/>
+      <c r="O15" s="290"/>
+      <c r="P15" s="290"/>
       <c r="BL15" s="238" t="str">
-        <v>Z</v>
+        <v>h</v>
       </c>
       <c r="BM15" s="238" t="str">
-        <v>Y</v>
+        <v>c</v>
       </c>
       <c r="BN15" s="238" t="str">
-        <v>ㆡ</v>
+        <v>ㄏ</v>
       </c>
       <c r="BO15" s="238"/>
       <c r="BP15" s="238"/>
@@ -6062,13 +6103,13 @@
     </row>
     <row r="16" spans="1:86" outlineLevel="1">
       <c r="BL16" s="238" t="str">
-        <v>z</v>
+        <v>Z</v>
       </c>
       <c r="BM16" s="238" t="str">
-        <v>y</v>
+        <v>Y</v>
       </c>
       <c r="BN16" s="239" t="str">
-        <v>ㄗ</v>
+        <v>ㆡ</v>
       </c>
       <c r="BO16" s="238"/>
       <c r="BP16" s="238"/>
@@ -6345,13 +6386,13 @@
         <v>60</v>
       </c>
       <c r="BL17" s="238" t="str">
-        <v>c</v>
+        <v>z</v>
       </c>
       <c r="BM17" s="238" t="str">
-        <v>h</v>
+        <v>y</v>
       </c>
       <c r="BN17" s="239" t="str">
-        <v>ㄘ</v>
+        <v>ㄗ</v>
       </c>
       <c r="BO17" s="238"/>
       <c r="BP17" s="238"/>
@@ -6425,7 +6466,7 @@
       </c>
       <c r="K18" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>G</v>
+        <v>Ğ</v>
       </c>
       <c r="L18" s="4" t="str">
         <f t="shared" si="3"/>
@@ -6441,39 +6482,39 @@
       </c>
       <c r="O18" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>Z</v>
+        <v>h</v>
       </c>
       <c r="P18" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>z</v>
+        <v>Z</v>
       </c>
       <c r="Q18" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>c</v>
+        <v>z</v>
       </c>
       <c r="R18" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>s</v>
+        <v>c</v>
       </c>
       <c r="S18" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>J</v>
+        <v>s</v>
       </c>
       <c r="T18" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>j</v>
+        <v>J</v>
       </c>
       <c r="U18" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>C</v>
+        <v>j</v>
       </c>
       <c r="V18" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>S</v>
+        <v>C</v>
       </c>
       <c r="W18" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>h</v>
+        <v>S</v>
       </c>
       <c r="X18" s="4" t="str">
         <f t="shared" si="3"/>
@@ -6513,7 +6554,7 @@
       </c>
       <c r="AG18" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>d</v>
+        <v>D</v>
       </c>
       <c r="AH18" s="4" t="str">
         <f t="shared" si="3"/>
@@ -6589,57 +6630,57 @@
       </c>
       <c r="AZ18" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>Ø</v>
       </c>
       <c r="BA18" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>L</v>
       </c>
       <c r="BB18" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC18" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD18" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BE18" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BF18" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BG18" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>L</v>
+        <v>4</v>
       </c>
       <c r="BH18" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>&amp;</v>
+        <v>8</v>
       </c>
       <c r="BI18" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>*</v>
+        <v>0</v>
       </c>
       <c r="BJ18" s="4" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>6</v>
       </c>
       <c r="BK18" s="1"/>
       <c r="BL18" s="238" t="str">
-        <v>s</v>
+        <v>c</v>
       </c>
       <c r="BM18" s="238" t="str">
-        <v>n</v>
+        <v>h</v>
       </c>
       <c r="BN18" s="239" t="str">
-        <v>ㄙ</v>
+        <v>ㄘ</v>
       </c>
       <c r="BO18" s="238"/>
       <c r="BP18" s="238"/>
@@ -6725,43 +6766,43 @@
       </c>
       <c r="N19" s="247" t="str">
         <f t="shared" si="4"/>
-        <v>G</v>
+        <v>N</v>
       </c>
       <c r="O19" s="247" t="str">
         <f t="shared" si="4"/>
-        <v>Y</v>
+        <v>c</v>
       </c>
       <c r="P19" s="247" t="str">
         <f t="shared" si="4"/>
-        <v>y</v>
+        <v>Y</v>
       </c>
       <c r="Q19" s="247" t="str">
         <f t="shared" si="4"/>
-        <v>h</v>
+        <v>y</v>
       </c>
       <c r="R19" s="247" t="str">
         <f t="shared" si="4"/>
-        <v>n</v>
+        <v>h</v>
       </c>
       <c r="S19" s="247" t="str">
         <f t="shared" si="4"/>
-        <v>R</v>
+        <v>n</v>
       </c>
       <c r="T19" s="247" t="str">
         <f t="shared" si="4"/>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="U19" s="247" t="str">
         <f t="shared" si="4"/>
-        <v>f</v>
+        <v>r</v>
       </c>
       <c r="V19" s="247" t="str">
         <f t="shared" si="4"/>
-        <v>v</v>
+        <v>f</v>
       </c>
       <c r="W19" s="247" t="str">
         <f t="shared" si="4"/>
-        <v>c</v>
+        <v>v</v>
       </c>
       <c r="X19" s="247" t="str">
         <f t="shared" si="4"/>
@@ -6877,57 +6918,57 @@
       </c>
       <c r="AZ19" s="247" t="str">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>=</v>
       </c>
       <c r="BA19" s="247" t="str">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>-</v>
       </c>
       <c r="BB19" s="247" t="str">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>"</v>
       </c>
       <c r="BC19" s="247" t="str">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD19" s="247" t="str">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BE19" s="247" t="str">
         <f t="shared" si="4"/>
-        <v>]</v>
+        <v>4</v>
       </c>
       <c r="BF19" s="247" t="str">
         <f t="shared" si="4"/>
-        <v>[</v>
+        <v>6</v>
       </c>
       <c r="BG19" s="247" t="str">
         <f t="shared" si="4"/>
-        <v>N</v>
+        <v>[</v>
       </c>
       <c r="BH19" s="247" t="str">
         <f t="shared" si="4"/>
-        <v>.</v>
+        <v>]</v>
       </c>
       <c r="BI19" s="247" t="str">
         <f t="shared" si="4"/>
-        <v>-</v>
+        <v>.</v>
       </c>
       <c r="BJ19" s="247" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="BK19" s="1"/>
       <c r="BL19" s="238" t="str">
-        <v>J</v>
+        <v>s</v>
       </c>
       <c r="BM19" s="238" t="str">
-        <v>R</v>
+        <v>n</v>
       </c>
       <c r="BN19" s="239" t="str">
-        <v>ㆢ</v>
+        <v>ㄙ</v>
       </c>
       <c r="BO19" s="238"/>
       <c r="BP19" s="238"/>
@@ -7027,13 +7068,13 @@
       <c r="BJ20" s="1"/>
       <c r="BK20" s="1"/>
       <c r="BL20" s="238" t="str">
-        <v>j</v>
+        <v>J</v>
       </c>
       <c r="BM20" s="238" t="str">
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="BN20" s="239" t="str">
-        <v>ㄐ</v>
+        <v>ㆢ</v>
       </c>
       <c r="BO20" s="238"/>
       <c r="BP20" s="238"/>
@@ -7133,13 +7174,13 @@
       <c r="BJ21" s="1"/>
       <c r="BK21" s="1"/>
       <c r="BL21" s="238" t="str">
-        <v>C</v>
+        <v>j</v>
       </c>
       <c r="BM21" s="238" t="str">
-        <v>f</v>
+        <v>r</v>
       </c>
       <c r="BN21" s="239" t="str">
-        <v>ㄑ</v>
+        <v>ㄐ</v>
       </c>
       <c r="BO21" s="238"/>
       <c r="BP21" s="238"/>
@@ -7239,13 +7280,13 @@
       <c r="BJ22" s="1"/>
       <c r="BK22" s="1"/>
       <c r="BL22" s="238" t="str">
-        <v>S</v>
+        <v>C</v>
       </c>
       <c r="BM22" s="238" t="str">
-        <v>v</v>
+        <v>f</v>
       </c>
       <c r="BN22" s="239" t="str">
-        <v>ㄒ</v>
+        <v>ㄑ</v>
       </c>
       <c r="BO22" s="238"/>
       <c r="BP22" s="238"/>
@@ -7347,13 +7388,13 @@
       <c r="BJ23" s="1"/>
       <c r="BK23" s="1"/>
       <c r="BL23" s="238" t="str">
-        <v>h</v>
+        <v>S</v>
       </c>
       <c r="BM23" s="238" t="str">
-        <v>c</v>
+        <v>v</v>
       </c>
       <c r="BN23" s="239" t="str">
-        <v>ㄏ</v>
+        <v>ㄒ</v>
       </c>
       <c r="BO23" s="238"/>
       <c r="BP23" s="238"/>
@@ -7864,31 +7905,30 @@
     <row r="29" spans="1:80" s="237" customFormat="1" outlineLevel="1">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
-      <c r="C29" s="1" t="str">
-        <f xml:space="preserve"> MID(C24, B25+1,  B26-B25-1)</f>
-        <v>!1qa2wsxEedGYyhnRrfvc8uKj,ik9l*UJ&lt;I(Lm/pM0;Oobtgz53467][N.-</v>
-      </c>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="1"/>
-      <c r="S29" s="1"/>
-      <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
-      <c r="W29" s="1"/>
-      <c r="X29" s="1"/>
+      <c r="C29" s="289" t="s">
+        <v>588</v>
+      </c>
+      <c r="D29" s="289"/>
+      <c r="E29" s="289"/>
+      <c r="F29" s="289"/>
+      <c r="G29" s="289"/>
+      <c r="H29" s="289"/>
+      <c r="I29" s="289"/>
+      <c r="J29" s="289"/>
+      <c r="K29" s="289"/>
+      <c r="L29" s="289"/>
+      <c r="M29" s="289"/>
+      <c r="N29" s="289"/>
+      <c r="O29" s="289"/>
+      <c r="P29" s="289"/>
+      <c r="Q29" s="289"/>
+      <c r="R29" s="289"/>
+      <c r="S29" s="289"/>
+      <c r="T29" s="289"/>
+      <c r="U29" s="289"/>
+      <c r="V29" s="289"/>
+      <c r="W29" s="289"/>
+      <c r="X29" s="289"/>
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
@@ -7958,31 +7998,30 @@
     <row r="30" spans="1:80" s="237" customFormat="1" outlineLevel="1">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
-      <c r="C30" s="1" t="str">
-        <f xml:space="preserve"> MID(C24, B26+1,  B27-B26-1)</f>
-        <v>ㆠㄅㄆㄇㄉㄊㄋㄌㆣㄍㄎㄫㆡㄗㄘㄙㆢㄐㄑㄒㄏㄚㄧㆨㄨㆤㆦㄜㄞㄠㆩㆪㆫㆥㆧㆮㆯㆬㆭㄣㆰㄢㄤㆱㆲㆴㆵㆻㆷ˫˪ˋˊ八四一ㄥ入ñ</v>
-      </c>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="1"/>
-      <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
-      <c r="W30" s="1"/>
-      <c r="X30" s="1"/>
+      <c r="C30" s="289" t="s">
+        <v>589</v>
+      </c>
+      <c r="D30" s="289"/>
+      <c r="E30" s="289"/>
+      <c r="F30" s="289"/>
+      <c r="G30" s="289"/>
+      <c r="H30" s="289"/>
+      <c r="I30" s="289"/>
+      <c r="J30" s="289"/>
+      <c r="K30" s="289"/>
+      <c r="L30" s="289"/>
+      <c r="M30" s="289"/>
+      <c r="N30" s="289"/>
+      <c r="O30" s="289"/>
+      <c r="P30" s="289"/>
+      <c r="Q30" s="289"/>
+      <c r="R30" s="289"/>
+      <c r="S30" s="289"/>
+      <c r="T30" s="289"/>
+      <c r="U30" s="289"/>
+      <c r="V30" s="289"/>
+      <c r="W30" s="289"/>
+      <c r="X30" s="289"/>
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
       <c r="AA30" s="1"/>
@@ -8432,43 +8471,43 @@
       </c>
       <c r="N33" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>G</v>
+        <v>N</v>
       </c>
       <c r="O33" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>Y</v>
+        <v>c</v>
       </c>
       <c r="P33" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>y</v>
+        <v>Y</v>
       </c>
       <c r="Q33" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>h</v>
+        <v>y</v>
       </c>
       <c r="R33" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>n</v>
+        <v>h</v>
       </c>
       <c r="S33" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>R</v>
+        <v>n</v>
       </c>
       <c r="T33" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="U33" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>f</v>
+        <v>r</v>
       </c>
       <c r="V33" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>v</v>
+        <v>f</v>
       </c>
       <c r="W33" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>c</v>
+        <v>v</v>
       </c>
       <c r="X33" s="4" t="str">
         <f t="shared" si="6"/>
@@ -8584,47 +8623,47 @@
       </c>
       <c r="AZ33" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>=</v>
       </c>
       <c r="BA33" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>-</v>
       </c>
       <c r="BB33" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>"</v>
       </c>
       <c r="BC33" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD33" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BE33" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>]</v>
+        <v>4</v>
       </c>
       <c r="BF33" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>[</v>
+        <v>6</v>
       </c>
       <c r="BG33" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>N</v>
+        <v>[</v>
       </c>
       <c r="BH33" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>.</v>
+        <v>]</v>
       </c>
       <c r="BI33" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>.</v>
       </c>
       <c r="BJ33" s="4" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="BK33" s="1"/>
       <c r="BL33" s="238" t="str">
@@ -8694,39 +8733,39 @@
       </c>
       <c r="O34" s="242" t="str">
         <f t="shared" si="7"/>
-        <v>ㆡ</v>
+        <v>ㄏ</v>
       </c>
       <c r="P34" s="242" t="str">
         <f t="shared" si="7"/>
-        <v>ㄗ</v>
+        <v>ㆡ</v>
       </c>
       <c r="Q34" s="242" t="str">
         <f t="shared" si="7"/>
-        <v>ㄘ</v>
+        <v>ㄗ</v>
       </c>
       <c r="R34" s="242" t="str">
         <f t="shared" si="7"/>
-        <v>ㄙ</v>
+        <v>ㄘ</v>
       </c>
       <c r="S34" s="242" t="str">
         <f t="shared" si="7"/>
-        <v>ㆢ</v>
+        <v>ㄙ</v>
       </c>
       <c r="T34" s="242" t="str">
         <f t="shared" si="7"/>
-        <v>ㄐ</v>
+        <v>ㆢ</v>
       </c>
       <c r="U34" s="242" t="str">
         <f t="shared" si="7"/>
-        <v>ㄑ</v>
+        <v>ㄐ</v>
       </c>
       <c r="V34" s="242" t="str">
         <f t="shared" si="7"/>
-        <v>ㄒ</v>
+        <v>ㄑ</v>
       </c>
       <c r="W34" s="242" t="str">
         <f t="shared" si="7"/>
-        <v>ㄏ</v>
+        <v>ㄒ</v>
       </c>
       <c r="X34" s="242" t="str">
         <f t="shared" si="7"/>
@@ -8842,47 +8881,47 @@
       </c>
       <c r="AZ34" s="242" t="str">
         <f t="shared" si="7"/>
-        <v>˫</v>
+        <v>Ø</v>
       </c>
       <c r="BA34" s="242" t="str">
         <f t="shared" si="7"/>
-        <v>˪</v>
+        <v>ㄥ</v>
       </c>
       <c r="BB34" s="242" t="str">
         <f t="shared" si="7"/>
-        <v>ˋ</v>
+        <v>一</v>
       </c>
       <c r="BC34" s="242" t="str">
         <f t="shared" si="7"/>
-        <v>ˊ</v>
+        <v>七</v>
       </c>
       <c r="BD34" s="242" t="str">
         <f t="shared" si="7"/>
-        <v>八</v>
+        <v>三</v>
       </c>
       <c r="BE34" s="242" t="str">
         <f t="shared" si="7"/>
-        <v>四</v>
+        <v>二</v>
       </c>
       <c r="BF34" s="242" t="str">
         <f t="shared" si="7"/>
-        <v>一</v>
+        <v>五</v>
       </c>
       <c r="BG34" s="242" t="str">
         <f t="shared" si="7"/>
-        <v>ㄥ</v>
+        <v>四</v>
       </c>
       <c r="BH34" s="242" t="str">
         <f t="shared" si="7"/>
-        <v>入</v>
+        <v>八</v>
       </c>
       <c r="BI34" s="242" t="str">
         <f t="shared" si="7"/>
-        <v>ñ</v>
+        <v>輕</v>
       </c>
       <c r="BJ34" s="242" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>ʔ</v>
       </c>
       <c r="BK34" s="1"/>
       <c r="BL34" s="238" t="str">
@@ -9506,7 +9545,7 @@
         <v>B</v>
       </c>
       <c r="D39" s="4" t="str">
-        <f t="shared" ref="D39:AY39" si="9">D18</f>
+        <f t="shared" ref="D39:AY40" si="9">D18</f>
         <v>b</v>
       </c>
       <c r="E39" s="4" t="str">
@@ -9550,39 +9589,39 @@
       </c>
       <c r="O39" s="4" t="str">
         <f t="shared" si="9"/>
-        <v>Z</v>
+        <v>h</v>
       </c>
       <c r="P39" s="4" t="str">
         <f t="shared" si="9"/>
-        <v>z</v>
+        <v>Z</v>
       </c>
       <c r="Q39" s="4" t="str">
         <f t="shared" si="9"/>
-        <v>c</v>
+        <v>z</v>
       </c>
       <c r="R39" s="4" t="str">
         <f t="shared" si="9"/>
-        <v>s</v>
+        <v>c</v>
       </c>
       <c r="S39" s="4" t="str">
         <f t="shared" si="9"/>
-        <v>J</v>
+        <v>s</v>
       </c>
       <c r="T39" s="4" t="str">
         <f t="shared" si="9"/>
-        <v>j</v>
+        <v>J</v>
       </c>
       <c r="U39" s="4" t="str">
         <f t="shared" si="9"/>
-        <v>C</v>
+        <v>j</v>
       </c>
       <c r="V39" s="4" t="str">
         <f t="shared" si="9"/>
-        <v>S</v>
+        <v>C</v>
       </c>
       <c r="W39" s="4" t="str">
         <f t="shared" si="9"/>
-        <v>h</v>
+        <v>S</v>
       </c>
       <c r="X39" s="4" t="str">
         <f t="shared" si="9"/>
@@ -9697,44 +9736,44 @@
       </c>
       <c r="AZ39" s="4" t="str">
         <f>BG18</f>
-        <v>L</v>
+        <v>4</v>
       </c>
       <c r="BA39" s="4" t="str">
         <f>BH18</f>
-        <v>&amp;</v>
+        <v>8</v>
       </c>
       <c r="BB39" s="4" t="str">
         <f>BF18</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BC39" s="4" t="str">
         <f t="shared" ref="BC39:BH39" si="10">AZ18</f>
-        <v>7</v>
+        <v>Ø</v>
       </c>
       <c r="BD39" s="4" t="str">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>L</v>
       </c>
       <c r="BE39" s="4" t="str">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BF39" s="4" t="str">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BG39" s="4" t="str">
         <f t="shared" si="10"/>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BH39" s="4" t="str">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BI39" s="4"/>
       <c r="BJ39" s="4" t="str">
         <f>BJ18</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="BK39" s="1"/>
       <c r="BL39" s="238" t="str">
@@ -9759,195 +9798,195 @@
         <v>!</v>
       </c>
       <c r="D40" s="247" t="str">
-        <f t="shared" ref="D40:AY40" si="11">D19</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="E40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>q</v>
       </c>
       <c r="F40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>a</v>
       </c>
       <c r="G40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="H40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>w</v>
       </c>
       <c r="I40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>s</v>
       </c>
       <c r="J40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>x</v>
       </c>
       <c r="K40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>E</v>
       </c>
       <c r="L40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>e</v>
       </c>
       <c r="M40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>d</v>
       </c>
       <c r="N40" s="247" t="str">
-        <f t="shared" si="11"/>
-        <v>G</v>
+        <f t="shared" si="9"/>
+        <v>N</v>
       </c>
       <c r="O40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
+        <v>c</v>
+      </c>
+      <c r="P40" s="247" t="str">
+        <f t="shared" si="9"/>
         <v>Y</v>
       </c>
-      <c r="P40" s="247" t="str">
-        <f t="shared" si="11"/>
+      <c r="Q40" s="247" t="str">
+        <f t="shared" si="9"/>
         <v>y</v>
       </c>
-      <c r="Q40" s="247" t="str">
-        <f t="shared" si="11"/>
+      <c r="R40" s="247" t="str">
+        <f t="shared" si="9"/>
         <v>h</v>
       </c>
-      <c r="R40" s="247" t="str">
-        <f t="shared" si="11"/>
+      <c r="S40" s="247" t="str">
+        <f t="shared" si="9"/>
         <v>n</v>
       </c>
-      <c r="S40" s="247" t="str">
-        <f t="shared" si="11"/>
+      <c r="T40" s="247" t="str">
+        <f t="shared" si="9"/>
         <v>R</v>
       </c>
-      <c r="T40" s="247" t="str">
-        <f t="shared" si="11"/>
+      <c r="U40" s="247" t="str">
+        <f t="shared" si="9"/>
         <v>r</v>
       </c>
-      <c r="U40" s="247" t="str">
-        <f t="shared" si="11"/>
+      <c r="V40" s="247" t="str">
+        <f t="shared" si="9"/>
         <v>f</v>
       </c>
-      <c r="V40" s="247" t="str">
-        <f t="shared" si="11"/>
+      <c r="W40" s="247" t="str">
+        <f t="shared" si="9"/>
         <v>v</v>
       </c>
-      <c r="W40" s="247" t="str">
-        <f t="shared" si="11"/>
-        <v>c</v>
-      </c>
       <c r="X40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
       <c r="Y40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>u</v>
       </c>
       <c r="Z40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>K</v>
       </c>
       <c r="AA40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>j</v>
       </c>
       <c r="AB40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>,</v>
       </c>
       <c r="AC40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>i</v>
       </c>
       <c r="AD40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>k</v>
       </c>
       <c r="AE40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
       <c r="AF40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>l</v>
       </c>
       <c r="AG40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>*</v>
       </c>
       <c r="AH40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>U</v>
       </c>
       <c r="AI40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>J</v>
       </c>
       <c r="AJ40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>&lt;</v>
       </c>
       <c r="AK40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>I</v>
       </c>
       <c r="AL40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>(</v>
       </c>
       <c r="AM40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>L</v>
       </c>
       <c r="AN40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>m</v>
       </c>
       <c r="AO40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>/</v>
       </c>
       <c r="AP40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>p</v>
       </c>
       <c r="AQ40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>M</v>
       </c>
       <c r="AR40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AS40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>;</v>
       </c>
       <c r="AT40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>O</v>
       </c>
       <c r="AU40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>o</v>
       </c>
       <c r="AV40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>b</v>
       </c>
       <c r="AW40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>t</v>
       </c>
       <c r="AX40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>g</v>
       </c>
       <c r="AY40" s="247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>z</v>
       </c>
       <c r="AZ40" s="247" t="s">
@@ -9955,26 +9994,26 @@
       </c>
       <c r="BA40" s="247" t="str">
         <f>BH19</f>
-        <v>.</v>
+        <v>]</v>
       </c>
       <c r="BB40" s="247" t="s">
         <v>560</v>
       </c>
       <c r="BC40" s="247" t="str">
         <f>AZ19</f>
-        <v>5</v>
+        <v>=</v>
       </c>
       <c r="BD40" s="247" t="str">
         <f>BA19</f>
-        <v>3</v>
+        <v>-</v>
       </c>
       <c r="BE40" s="247" t="str">
         <f>BB19</f>
-        <v>4</v>
+        <v>"</v>
       </c>
       <c r="BF40" s="247" t="str">
         <f>BC19</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BG40" s="247" t="s">
         <v>293</v>
@@ -9985,7 +10024,7 @@
       <c r="BI40" s="247"/>
       <c r="BJ40" s="247" t="str">
         <f>BJ19</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="BK40" s="1"/>
       <c r="BL40" s="238" t="str">
@@ -10010,237 +10049,237 @@
         <v>ㆠ</v>
       </c>
       <c r="D41" s="242" t="str">
-        <f t="shared" ref="D41:AY41" si="12">D34</f>
+        <f t="shared" ref="D41:AY41" si="11">D34</f>
         <v>ㄅ</v>
       </c>
       <c r="E41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㄆ</v>
       </c>
       <c r="F41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㄇ</v>
       </c>
       <c r="G41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㄉ</v>
       </c>
       <c r="H41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㄊ</v>
       </c>
       <c r="I41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㄋ</v>
       </c>
       <c r="J41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㄌ</v>
       </c>
       <c r="K41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㆣ</v>
       </c>
       <c r="L41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㄍ</v>
       </c>
       <c r="M41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㄎ</v>
       </c>
       <c r="N41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㄫ</v>
       </c>
       <c r="O41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
+        <v>ㄏ</v>
+      </c>
+      <c r="P41" s="242" t="str">
+        <f t="shared" si="11"/>
         <v>ㆡ</v>
       </c>
-      <c r="P41" s="242" t="str">
-        <f t="shared" si="12"/>
+      <c r="Q41" s="242" t="str">
+        <f t="shared" si="11"/>
         <v>ㄗ</v>
       </c>
-      <c r="Q41" s="242" t="str">
-        <f t="shared" si="12"/>
+      <c r="R41" s="242" t="str">
+        <f t="shared" si="11"/>
         <v>ㄘ</v>
       </c>
-      <c r="R41" s="242" t="str">
-        <f t="shared" si="12"/>
+      <c r="S41" s="242" t="str">
+        <f t="shared" si="11"/>
         <v>ㄙ</v>
       </c>
-      <c r="S41" s="242" t="str">
-        <f t="shared" si="12"/>
+      <c r="T41" s="242" t="str">
+        <f t="shared" si="11"/>
         <v>ㆢ</v>
       </c>
-      <c r="T41" s="242" t="str">
-        <f t="shared" si="12"/>
+      <c r="U41" s="242" t="str">
+        <f t="shared" si="11"/>
         <v>ㄐ</v>
       </c>
-      <c r="U41" s="242" t="str">
-        <f t="shared" si="12"/>
+      <c r="V41" s="242" t="str">
+        <f t="shared" si="11"/>
         <v>ㄑ</v>
       </c>
-      <c r="V41" s="242" t="str">
-        <f t="shared" si="12"/>
+      <c r="W41" s="242" t="str">
+        <f t="shared" si="11"/>
         <v>ㄒ</v>
       </c>
-      <c r="W41" s="242" t="str">
-        <f t="shared" si="12"/>
-        <v>ㄏ</v>
-      </c>
       <c r="X41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㄚ</v>
       </c>
       <c r="Y41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㄧ</v>
       </c>
       <c r="Z41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㆨ</v>
       </c>
       <c r="AA41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㄨ</v>
       </c>
       <c r="AB41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㆤ</v>
       </c>
       <c r="AC41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㆦ</v>
       </c>
       <c r="AD41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㄜ</v>
       </c>
       <c r="AE41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㄞ</v>
       </c>
       <c r="AF41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㄠ</v>
       </c>
       <c r="AG41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㆩ</v>
       </c>
       <c r="AH41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㆪ</v>
       </c>
       <c r="AI41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㆫ</v>
       </c>
       <c r="AJ41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㆥ</v>
       </c>
       <c r="AK41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㆧ</v>
       </c>
       <c r="AL41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㆮ</v>
       </c>
       <c r="AM41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㆯ</v>
       </c>
       <c r="AN41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㆬ</v>
       </c>
       <c r="AO41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㆭ</v>
       </c>
       <c r="AP41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㄣ</v>
       </c>
       <c r="AQ41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㆰ</v>
       </c>
       <c r="AR41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㄢ</v>
       </c>
       <c r="AS41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㄤ</v>
       </c>
       <c r="AT41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㆱ</v>
       </c>
       <c r="AU41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㆲ</v>
       </c>
       <c r="AV41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㆴ</v>
       </c>
       <c r="AW41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㆵ</v>
       </c>
       <c r="AX41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㆻ</v>
       </c>
       <c r="AY41" s="242" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>ㆷ</v>
       </c>
       <c r="AZ41" s="242" t="str">
         <f>BG34</f>
-        <v>ㄥ</v>
+        <v>四</v>
       </c>
       <c r="BA41" s="242" t="str">
         <f>BH34</f>
-        <v>入</v>
+        <v>八</v>
       </c>
       <c r="BB41" s="242" t="str">
         <f>BF34</f>
+        <v>五</v>
+      </c>
+      <c r="BC41" s="242" t="str">
+        <f t="shared" ref="BC41:BH41" si="12">AZ34</f>
+        <v>Ø</v>
+      </c>
+      <c r="BD41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄥ</v>
+      </c>
+      <c r="BE41" s="242" t="str">
+        <f t="shared" si="12"/>
         <v>一</v>
       </c>
-      <c r="BC41" s="242" t="str">
-        <f t="shared" ref="BC41:BH41" si="13">AZ34</f>
-        <v>˫</v>
-      </c>
-      <c r="BD41" s="242" t="str">
-        <f t="shared" si="13"/>
-        <v>˪</v>
-      </c>
-      <c r="BE41" s="242" t="str">
-        <f t="shared" si="13"/>
-        <v>ˋ</v>
-      </c>
       <c r="BF41" s="242" t="str">
-        <f t="shared" si="13"/>
-        <v>ˊ</v>
+        <f t="shared" si="12"/>
+        <v>七</v>
       </c>
       <c r="BG41" s="242" t="str">
-        <f t="shared" si="13"/>
-        <v>八</v>
+        <f t="shared" si="12"/>
+        <v>三</v>
       </c>
       <c r="BH41" s="242" t="str">
-        <f t="shared" si="13"/>
-        <v>四</v>
+        <f t="shared" si="12"/>
+        <v>二</v>
       </c>
       <c r="BI41" s="242"/>
       <c r="BJ41" s="242" t="str">
         <f>BJ34</f>
-        <v/>
+        <v>ʔ</v>
       </c>
       <c r="BK41" s="1"/>
       <c r="BL41" s="238" t="str">
@@ -11080,13 +11119,13 @@
       <c r="BJ52" s="1"/>
       <c r="BK52" s="1"/>
       <c r="BL52" s="238" t="str">
-        <v>L</v>
+        <v>4</v>
       </c>
       <c r="BM52" s="238" t="str">
         <v>-</v>
       </c>
       <c r="BN52" s="239" t="str">
-        <v>ㄥ</v>
+        <v>四</v>
       </c>
       <c r="BO52" s="238"/>
       <c r="BP52" s="238"/>
@@ -11156,81 +11195,81 @@
       <c r="BJ53" s="1"/>
       <c r="BK53" s="1"/>
       <c r="BL53" s="238" t="str">
-        <v>&amp;</v>
+        <v>8</v>
       </c>
       <c r="BM53" s="238" t="str">
-        <v>.</v>
+        <v>]</v>
       </c>
       <c r="BN53" s="239" t="str">
-        <v>入</v>
+        <v>八</v>
       </c>
       <c r="BO53" s="238"/>
       <c r="BP53" s="238"/>
     </row>
     <row r="54" spans="1:68">
       <c r="BL54" s="237" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BM54" s="237" t="str">
         <v>"</v>
       </c>
       <c r="BN54" s="237" t="str">
-        <v>一</v>
+        <v>五</v>
       </c>
     </row>
     <row r="55" spans="1:68">
       <c r="BL55" s="237" t="str">
-        <v>7</v>
+        <v>Ø</v>
       </c>
       <c r="BM55" s="237" t="str">
-        <v>5</v>
+        <v>=</v>
       </c>
       <c r="BN55" s="237" t="str">
-        <v>˫</v>
+        <v>Ø</v>
       </c>
     </row>
     <row r="56" spans="1:68">
       <c r="BL56" s="237" t="str">
-        <v>3</v>
+        <v>L</v>
       </c>
       <c r="BM56" s="237" t="str">
-        <v>3</v>
+        <v>-</v>
       </c>
       <c r="BN56" s="237" t="str">
-        <v>˪</v>
+        <v>ㄥ</v>
       </c>
     </row>
     <row r="57" spans="1:68">
       <c r="BL57" s="237" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM57" s="237" t="str">
-        <v>4</v>
+        <v>"</v>
       </c>
       <c r="BN57" s="237" t="str">
-        <v>ˋ</v>
+        <v>一</v>
       </c>
     </row>
     <row r="58" spans="1:68">
       <c r="BL58" s="237" t="str">
+        <v>7</v>
+      </c>
+      <c r="BM58" s="237" t="str">
         <v>5</v>
       </c>
-      <c r="BM58" s="237" t="str">
-        <v>6</v>
-      </c>
       <c r="BN58" s="237" t="str">
-        <v>ˊ</v>
+        <v>七</v>
       </c>
     </row>
     <row r="59" spans="1:68">
       <c r="BL59" s="237" t="str">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BM59" s="237" t="str">
         <v>]</v>
       </c>
       <c r="BN59" s="237" t="str">
-        <v>八</v>
+        <v>三</v>
       </c>
     </row>
     <row r="60" spans="1:68" s="237" customFormat="1">
@@ -11298,13 +11337,13 @@
       <c r="BJ60" s="1"/>
       <c r="BK60" s="1"/>
       <c r="BL60" s="238" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BM60" s="238" t="str">
         <v>[</v>
       </c>
       <c r="BN60" s="238" t="str">
-        <v>四</v>
+        <v>二</v>
       </c>
       <c r="BO60" s="238"/>
       <c r="BP60" s="238"/>
@@ -11450,13 +11489,13 @@
       <c r="BJ62" s="1"/>
       <c r="BK62" s="1"/>
       <c r="BL62" s="238" t="str">
-        <v/>
+        <v>6</v>
       </c>
       <c r="BM62" s="238" t="str">
-        <v/>
+        <v>7</v>
       </c>
       <c r="BN62" s="238" t="str">
-        <v/>
+        <v>ʔ</v>
       </c>
       <c r="BO62" s="238"/>
       <c r="BP62" s="238"/>
@@ -12028,6 +12067,7282 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55526294-CC81-4CA6-8F3B-4D8F28532425}">
+  <dimension ref="A1:CH76"/>
+  <sheetFormatPr defaultRowHeight="25.5" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="10" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6" style="1" customWidth="1"/>
+    <col min="3" max="62" width="5.3984375" style="1" customWidth="1"/>
+    <col min="63" max="63" width="8.796875" style="1"/>
+    <col min="64" max="64" width="8.796875" style="237"/>
+    <col min="65" max="68" width="10.3984375" style="237" customWidth="1"/>
+    <col min="69" max="69" width="8.796875" style="237"/>
+    <col min="70" max="70" width="6.5" style="237" bestFit="1" customWidth="1"/>
+    <col min="71" max="72" width="11.19921875" style="237" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="6.5" style="237" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="11.19921875" style="237" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="8.796875" style="237"/>
+    <col min="76" max="76" width="6.5" style="237" bestFit="1" customWidth="1"/>
+    <col min="77" max="78" width="11.19921875" style="237" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="6.5" style="237" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="11.19921875" style="237" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="8.796875" style="237"/>
+    <col min="82" max="82" width="6.5" style="237" bestFit="1" customWidth="1"/>
+    <col min="83" max="84" width="11.19921875" style="237" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="6.5" style="237" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="11.19921875" style="237" bestFit="1" customWidth="1"/>
+    <col min="87" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:86">
+      <c r="A1" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="2" spans="1:86">
+      <c r="BL2" s="236" t="s">
+        <v>286</v>
+      </c>
+      <c r="BM2" s="236" t="e" cm="1">
+        <f t="array" ref="BM2">TRANSPOSE(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BN2" s="236"/>
+      <c r="BO2" s="236"/>
+      <c r="BP2" s="236"/>
+      <c r="BR2" s="236" t="s">
+        <v>184</v>
+      </c>
+      <c r="BS2" s="236" t="s">
+        <v>531</v>
+      </c>
+      <c r="BT2" s="236" t="s">
+        <v>201</v>
+      </c>
+      <c r="BU2" s="236" t="s">
+        <v>509</v>
+      </c>
+      <c r="BV2" s="236" t="s">
+        <v>208</v>
+      </c>
+      <c r="BX2" s="236" t="s">
+        <v>184</v>
+      </c>
+      <c r="BY2" s="236" t="s">
+        <v>531</v>
+      </c>
+      <c r="BZ2" s="236" t="s">
+        <v>201</v>
+      </c>
+      <c r="CA2" s="236" t="s">
+        <v>509</v>
+      </c>
+      <c r="CB2" s="236" t="s">
+        <v>208</v>
+      </c>
+      <c r="CD2" s="236" t="s">
+        <v>184</v>
+      </c>
+      <c r="CE2" s="236" t="s">
+        <v>531</v>
+      </c>
+      <c r="CF2" s="236" t="s">
+        <v>201</v>
+      </c>
+      <c r="CG2" s="236" t="s">
+        <v>509</v>
+      </c>
+      <c r="CH2" s="236" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="3" spans="1:86">
+      <c r="A3" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="C3" s="1" t="str">
+        <f xml:space="preserve"> "!1qas2wxEedGYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L:5346][7N"</f>
+        <v>!1qas2wxEedGYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L:5346][7N</v>
+      </c>
+      <c r="BL3" s="238" t="str" cm="1">
+        <f t="array" ref="BL3:BN62" xml:space="preserve"> TRANSPOSE(C39:BJ41)</f>
+        <v>B</v>
+      </c>
+      <c r="BM3" s="238" t="str">
+        <v>!</v>
+      </c>
+      <c r="BN3" s="238" t="str">
+        <v>ㆠ</v>
+      </c>
+      <c r="BO3" s="238"/>
+      <c r="BP3" s="238"/>
+      <c r="BR3" s="238">
+        <v>1</v>
+      </c>
+      <c r="BS3" s="238" t="s">
+        <v>38</v>
+      </c>
+      <c r="BT3" s="238" t="s">
+        <v>38</v>
+      </c>
+      <c r="BU3" s="238" t="s">
+        <v>223</v>
+      </c>
+      <c r="BV3" s="238" t="s">
+        <v>37</v>
+      </c>
+      <c r="BX3" s="238">
+        <v>1</v>
+      </c>
+      <c r="BY3" s="238" t="s">
+        <v>57</v>
+      </c>
+      <c r="BZ3" s="238" t="s">
+        <v>57</v>
+      </c>
+      <c r="CA3" s="238" t="s">
+        <v>219</v>
+      </c>
+      <c r="CB3" s="238" t="s">
+        <v>234</v>
+      </c>
+      <c r="CD3" s="238">
+        <v>1</v>
+      </c>
+      <c r="CE3" s="7">
+        <v>1</v>
+      </c>
+      <c r="CF3" s="7">
+        <v>1</v>
+      </c>
+      <c r="CG3" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="CH3" s="7" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="4" spans="1:86">
+      <c r="BL4" s="238" t="str">
+        <v>b</v>
+      </c>
+      <c r="BM4" s="238" t="str">
+        <v>1</v>
+      </c>
+      <c r="BN4" s="238" t="str">
+        <v>ㄅ</v>
+      </c>
+      <c r="BO4" s="238"/>
+      <c r="BP4" s="238"/>
+      <c r="BR4" s="238">
+        <v>2</v>
+      </c>
+      <c r="BS4" s="238" t="s">
+        <v>45</v>
+      </c>
+      <c r="BT4" s="238" t="s">
+        <v>45</v>
+      </c>
+      <c r="BU4" s="238" t="s">
+        <v>221</v>
+      </c>
+      <c r="BV4" s="238" t="s">
+        <v>44</v>
+      </c>
+      <c r="BX4" s="238">
+        <v>2</v>
+      </c>
+      <c r="BY4" s="238" t="s">
+        <v>104</v>
+      </c>
+      <c r="BZ4" s="238" t="s">
+        <v>104</v>
+      </c>
+      <c r="CA4" s="238" t="s">
+        <v>141</v>
+      </c>
+      <c r="CB4" s="238" t="s">
+        <v>103</v>
+      </c>
+      <c r="CD4" s="238">
+        <v>2</v>
+      </c>
+      <c r="CE4" s="7">
+        <v>7</v>
+      </c>
+      <c r="CF4" s="7">
+        <v>7</v>
+      </c>
+      <c r="CG4" s="7">
+        <v>5</v>
+      </c>
+      <c r="CH4" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="5" spans="1:86">
+      <c r="C5" s="3">
+        <f xml:space="preserve"> COLUMN() -2</f>
+        <v>1</v>
+      </c>
+      <c r="D5" s="3">
+        <f t="shared" ref="D5:BJ5" si="0" xml:space="preserve"> COLUMN() -2</f>
+        <v>2</v>
+      </c>
+      <c r="E5" s="3">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F5" s="3">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="H5" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="J5" s="3">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="K5" s="3">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="L5" s="3">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M5" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="N5" s="3">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="O5" s="3">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="P5" s="3">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="Q5" s="3">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="R5" s="3">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="S5" s="3">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="T5" s="3">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="U5" s="3">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="V5" s="3">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="W5" s="3">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="X5" s="3">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="Z5" s="3">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AA5" s="3">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AB5" s="3">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AC5" s="3">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="AD5" s="3">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="AE5" s="3">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="AF5" s="3">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="AG5" s="3">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="AH5" s="3">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="AI5" s="3">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="AJ5" s="3">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="AK5" s="3">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="AL5" s="3">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="AM5" s="3">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="AN5" s="3">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="AO5" s="3">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="AP5" s="3">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="AQ5" s="3">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="AR5" s="3">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="AS5" s="3">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="AT5" s="3">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="AU5" s="3">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="AV5" s="3">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="AW5" s="3">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="AX5" s="3">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="AY5" s="3">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="AZ5" s="3">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="BA5" s="3">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="BB5" s="3">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="BC5" s="3">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="BD5" s="3">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="BE5" s="3">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="BF5" s="3">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="BG5" s="3">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="BH5" s="3">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="BI5" s="3">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="BJ5" s="3">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="BL5" s="238" t="str">
+        <v>p</v>
+      </c>
+      <c r="BM5" s="238" t="str">
+        <v>q</v>
+      </c>
+      <c r="BN5" s="239" t="str">
+        <v>ㄆ</v>
+      </c>
+      <c r="BO5" s="238"/>
+      <c r="BP5" s="238"/>
+      <c r="BR5" s="238">
+        <v>3</v>
+      </c>
+      <c r="BS5" s="238" t="s">
+        <v>93</v>
+      </c>
+      <c r="BT5" s="238" t="s">
+        <v>76</v>
+      </c>
+      <c r="BU5" s="238" t="s">
+        <v>191</v>
+      </c>
+      <c r="BV5" s="238" t="s">
+        <v>92</v>
+      </c>
+      <c r="BX5" s="238">
+        <v>3</v>
+      </c>
+      <c r="BY5" s="238" t="s">
+        <v>125</v>
+      </c>
+      <c r="BZ5" s="238" t="s">
+        <v>195</v>
+      </c>
+      <c r="CA5" s="238" t="s">
+        <v>118</v>
+      </c>
+      <c r="CB5" s="238" t="s">
+        <v>124</v>
+      </c>
+      <c r="CD5" s="238">
+        <v>3</v>
+      </c>
+      <c r="CE5" s="7">
+        <v>3</v>
+      </c>
+      <c r="CF5" s="7">
+        <v>3</v>
+      </c>
+      <c r="CG5" s="7">
+        <v>3</v>
+      </c>
+      <c r="CH5" s="7" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="6" spans="1:86">
+      <c r="C6" s="241" t="str">
+        <f xml:space="preserve"> MID($C$3, C5, 1)</f>
+        <v>!</v>
+      </c>
+      <c r="D6" s="241" t="str">
+        <f t="shared" ref="D6:BJ6" si="1" xml:space="preserve"> MID($C$3, D5, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="E6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>q</v>
+      </c>
+      <c r="F6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>a</v>
+      </c>
+      <c r="G6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>s</v>
+      </c>
+      <c r="H6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="I6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>w</v>
+      </c>
+      <c r="J6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>x</v>
+      </c>
+      <c r="K6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>E</v>
+      </c>
+      <c r="L6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>e</v>
+      </c>
+      <c r="M6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>d</v>
+      </c>
+      <c r="N6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>G</v>
+      </c>
+      <c r="O6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>Y</v>
+      </c>
+      <c r="P6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>y</v>
+      </c>
+      <c r="Q6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>h</v>
+      </c>
+      <c r="R6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>n</v>
+      </c>
+      <c r="S6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>c</v>
+      </c>
+      <c r="T6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>R</v>
+      </c>
+      <c r="U6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>r</v>
+      </c>
+      <c r="V6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>f</v>
+      </c>
+      <c r="W6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>v</v>
+      </c>
+      <c r="X6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="Y6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>u</v>
+      </c>
+      <c r="Z6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>K</v>
+      </c>
+      <c r="AA6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>j</v>
+      </c>
+      <c r="AB6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>,</v>
+      </c>
+      <c r="AC6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>i</v>
+      </c>
+      <c r="AD6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>k</v>
+      </c>
+      <c r="AE6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>m</v>
+      </c>
+      <c r="AF6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>p</v>
+      </c>
+      <c r="AG6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>/</v>
+      </c>
+      <c r="AH6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>b</v>
+      </c>
+      <c r="AI6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>t</v>
+      </c>
+      <c r="AJ6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>g</v>
+      </c>
+      <c r="AK6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>z</v>
+      </c>
+      <c r="AL6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="AM6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>l</v>
+      </c>
+      <c r="AN6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>M</v>
+      </c>
+      <c r="AO6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>;</v>
+      </c>
+      <c r="AQ6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>O</v>
+      </c>
+      <c r="AR6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>o</v>
+      </c>
+      <c r="AS6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>*</v>
+      </c>
+      <c r="AT6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>U</v>
+      </c>
+      <c r="AU6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>J</v>
+      </c>
+      <c r="AV6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;</v>
+      </c>
+      <c r="AW6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>I</v>
+      </c>
+      <c r="AX6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>(</v>
+      </c>
+      <c r="AY6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>L</v>
+      </c>
+      <c r="AZ6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>:</v>
+      </c>
+      <c r="BA6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="BB6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="BC6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="BD6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="BE6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>]</v>
+      </c>
+      <c r="BF6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>[</v>
+      </c>
+      <c r="BG6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="BH6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v>N</v>
+      </c>
+      <c r="BI6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="BJ6" s="241" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="BL6" s="238" t="str">
+        <v>m</v>
+      </c>
+      <c r="BM6" s="238" t="str">
+        <v>a</v>
+      </c>
+      <c r="BN6" s="238" t="str">
+        <v>ㄇ</v>
+      </c>
+      <c r="BO6" s="238"/>
+      <c r="BP6" s="238"/>
+      <c r="BR6" s="238">
+        <v>4</v>
+      </c>
+      <c r="BS6" s="238" t="s">
+        <v>188</v>
+      </c>
+      <c r="BT6" s="238" t="s">
+        <v>188</v>
+      </c>
+      <c r="BU6" s="238" t="s">
+        <v>57</v>
+      </c>
+      <c r="BV6" s="238" t="s">
+        <v>128</v>
+      </c>
+      <c r="BX6" s="238">
+        <v>4</v>
+      </c>
+      <c r="BY6" s="238" t="s">
+        <v>141</v>
+      </c>
+      <c r="BZ6" s="238" t="s">
+        <v>141</v>
+      </c>
+      <c r="CA6" s="238" t="s">
+        <v>187</v>
+      </c>
+      <c r="CB6" s="238" t="s">
+        <v>140</v>
+      </c>
+      <c r="CD6" s="238">
+        <v>4</v>
+      </c>
+      <c r="CE6" s="7">
+        <v>2</v>
+      </c>
+      <c r="CF6" s="7">
+        <v>2</v>
+      </c>
+      <c r="CG6" s="7">
+        <v>4</v>
+      </c>
+      <c r="CH6" s="7" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="7" spans="1:86">
+      <c r="BL7" s="238" t="str">
+        <v>d</v>
+      </c>
+      <c r="BM7" s="238" t="str">
+        <v>2</v>
+      </c>
+      <c r="BN7" s="238" t="str">
+        <v>ㄉ</v>
+      </c>
+      <c r="BO7" s="238"/>
+      <c r="BP7" s="238"/>
+      <c r="BR7" s="238">
+        <v>5</v>
+      </c>
+      <c r="BS7" s="238" t="s">
+        <v>189</v>
+      </c>
+      <c r="BT7" s="238" t="s">
+        <v>189</v>
+      </c>
+      <c r="BU7" s="238" t="s">
+        <v>176</v>
+      </c>
+      <c r="BV7" s="238" t="s">
+        <v>130</v>
+      </c>
+      <c r="BX7" s="238">
+        <v>5</v>
+      </c>
+      <c r="BY7" s="238" t="s">
+        <v>180</v>
+      </c>
+      <c r="BZ7" s="238" t="s">
+        <v>180</v>
+      </c>
+      <c r="CA7" s="238" t="s">
+        <v>224</v>
+      </c>
+      <c r="CB7" s="238" t="s">
+        <v>179</v>
+      </c>
+      <c r="CD7" s="238">
+        <v>5</v>
+      </c>
+      <c r="CE7" s="7">
+        <v>5</v>
+      </c>
+      <c r="CF7" s="7">
+        <v>5</v>
+      </c>
+      <c r="CG7" s="7">
+        <v>6</v>
+      </c>
+      <c r="CH7" s="7" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="8" spans="1:86">
+      <c r="A8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BL8" s="238" t="str">
+        <v>t</v>
+      </c>
+      <c r="BM8" s="238" t="str">
+        <v>w</v>
+      </c>
+      <c r="BN8" s="238" t="str">
+        <v>ㄊ</v>
+      </c>
+      <c r="BO8" s="238"/>
+      <c r="BP8" s="238"/>
+      <c r="BR8" s="238">
+        <v>6</v>
+      </c>
+      <c r="BS8" s="238" t="s">
+        <v>193</v>
+      </c>
+      <c r="BT8" s="238" t="s">
+        <v>193</v>
+      </c>
+      <c r="BU8" s="238" t="s">
+        <v>220</v>
+      </c>
+      <c r="BV8" s="238" t="s">
+        <v>46</v>
+      </c>
+      <c r="BX8" s="238">
+        <v>6</v>
+      </c>
+      <c r="BY8" s="238" t="s">
+        <v>106</v>
+      </c>
+      <c r="BZ8" s="238" t="s">
+        <v>75</v>
+      </c>
+      <c r="CA8" s="238" t="s">
+        <v>104</v>
+      </c>
+      <c r="CB8" s="238" t="s">
+        <v>105</v>
+      </c>
+      <c r="CD8" s="238">
+        <v>6</v>
+      </c>
+      <c r="CE8" s="7">
+        <v>8</v>
+      </c>
+      <c r="CF8" s="7">
+        <v>8</v>
+      </c>
+      <c r="CG8" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="CH8" s="7" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:86">
+      <c r="C9" s="1" t="str">
+        <f xml:space="preserve"> "- xlit|BbpmdtnlGgkŋZzcsJjCShaiwueOəIUdfqrvxyMGNY@AWHRFQV7325841L&amp;*|!1qa2wsxEedGYyhnRrfvc8uKj,ik9l*UJ&lt;I(Lm/pM0;Oobtgz53467][N.-|"</f>
+        <v>- xlit|BbpmdtnlGgkŋZzcsJjCShaiwueOəIUdfqrvxyMGNY@AWHRFQV7325841L&amp;*|!1qa2wsxEedGYyhnRrfvc8uKj,ik9l*UJ&lt;I(Lm/pM0;Oobtgz53467][N.-|</v>
+      </c>
+      <c r="BL9" s="238" t="str">
+        <v>n</v>
+      </c>
+      <c r="BM9" s="238" t="str">
+        <v>s</v>
+      </c>
+      <c r="BN9" s="238" t="str">
+        <v>ㄋ</v>
+      </c>
+      <c r="BO9" s="238"/>
+      <c r="BP9" s="238"/>
+      <c r="BR9" s="238">
+        <v>7</v>
+      </c>
+      <c r="BS9" s="238" t="s">
+        <v>510</v>
+      </c>
+      <c r="BT9" s="238" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU9" s="238" t="s">
+        <v>195</v>
+      </c>
+      <c r="BV9" s="238" t="s">
+        <v>94</v>
+      </c>
+      <c r="BX9" s="238">
+        <v>7</v>
+      </c>
+      <c r="BY9" s="238" t="s">
+        <v>190</v>
+      </c>
+      <c r="BZ9" s="238" t="s">
+        <v>10</v>
+      </c>
+      <c r="CA9" s="238" t="s">
+        <v>133</v>
+      </c>
+      <c r="CB9" s="238" t="s">
+        <v>142</v>
+      </c>
+      <c r="CD9" s="238">
+        <v>7</v>
+      </c>
+      <c r="CE9" s="7">
+        <v>4</v>
+      </c>
+      <c r="CF9" s="7">
+        <v>4</v>
+      </c>
+      <c r="CG9" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="CH9" s="7" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:86">
+      <c r="A10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="1">
+        <f xml:space="preserve"> SEARCH("|", C9)</f>
+        <v>7</v>
+      </c>
+      <c r="BL10" s="238" t="str">
+        <v>l</v>
+      </c>
+      <c r="BM10" s="238" t="str">
+        <v>x</v>
+      </c>
+      <c r="BN10" s="238" t="str">
+        <v>ㄌ</v>
+      </c>
+      <c r="BO10" s="238"/>
+      <c r="BP10" s="238"/>
+      <c r="BR10" s="238">
+        <v>8</v>
+      </c>
+      <c r="BS10" s="238" t="s">
+        <v>168</v>
+      </c>
+      <c r="BT10" s="238" t="s">
+        <v>168</v>
+      </c>
+      <c r="BU10" s="238" t="s">
+        <v>196</v>
+      </c>
+      <c r="BV10" s="238" t="s">
+        <v>167</v>
+      </c>
+      <c r="BX10" s="238">
+        <v>8</v>
+      </c>
+      <c r="BY10" s="238" t="s">
+        <v>178</v>
+      </c>
+      <c r="BZ10" s="238" t="s">
+        <v>154</v>
+      </c>
+      <c r="CA10" s="238" t="s">
+        <v>188</v>
+      </c>
+      <c r="CB10" s="238" t="s">
+        <v>177</v>
+      </c>
+      <c r="CD10" s="238">
+        <v>8</v>
+      </c>
+      <c r="CE10" s="7">
+        <v>0</v>
+      </c>
+      <c r="CF10" s="7">
+        <v>0</v>
+      </c>
+      <c r="CG10" s="7">
+        <v>7</v>
+      </c>
+      <c r="CH10" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:86">
+      <c r="A11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="1">
+        <f xml:space="preserve"> SEARCH("|", C9, B10+1)</f>
+        <v>67</v>
+      </c>
+      <c r="BL11" s="238" t="str">
+        <v>Ğ</v>
+      </c>
+      <c r="BM11" s="238" t="str">
+        <v>E</v>
+      </c>
+      <c r="BN11" s="238" t="str">
+        <v>ㆣ</v>
+      </c>
+      <c r="BO11" s="238"/>
+      <c r="BP11" s="238"/>
+      <c r="BR11" s="238">
+        <v>9</v>
+      </c>
+      <c r="BS11" s="238" t="s">
+        <v>80</v>
+      </c>
+      <c r="BT11" s="238" t="s">
+        <v>97</v>
+      </c>
+      <c r="BU11" s="238" t="s">
+        <v>69</v>
+      </c>
+      <c r="BV11" s="238" t="s">
+        <v>80</v>
+      </c>
+      <c r="BX11" s="238">
+        <v>9</v>
+      </c>
+      <c r="BY11" s="238" t="s">
+        <v>518</v>
+      </c>
+      <c r="BZ11" s="238" t="s">
+        <v>153</v>
+      </c>
+      <c r="CA11" s="238" t="s">
+        <v>45</v>
+      </c>
+      <c r="CB11" s="238" t="s">
+        <v>109</v>
+      </c>
+      <c r="CD11" s="238">
+        <v>9</v>
+      </c>
+      <c r="CE11" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="CF11" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="CG11" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="CH11" s="7" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="12" spans="1:86">
+      <c r="A12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="1">
+        <f xml:space="preserve"> SEARCH("|",C9, B11+1)</f>
+        <v>127</v>
+      </c>
+      <c r="BL12" s="238" t="str">
+        <v>g</v>
+      </c>
+      <c r="BM12" s="238" t="str">
+        <v>e</v>
+      </c>
+      <c r="BN12" s="239" t="str">
+        <v>ㄍ</v>
+      </c>
+      <c r="BO12" s="238"/>
+      <c r="BP12" s="238"/>
+      <c r="BR12" s="238">
+        <v>10</v>
+      </c>
+      <c r="BS12" s="238" t="s">
+        <v>133</v>
+      </c>
+      <c r="BT12" s="238" t="s">
+        <v>133</v>
+      </c>
+      <c r="BU12" s="238" t="s">
+        <v>180</v>
+      </c>
+      <c r="BV12" s="238" t="s">
+        <v>96</v>
+      </c>
+      <c r="BX12" s="238">
+        <v>10</v>
+      </c>
+      <c r="BY12" s="238" t="s">
+        <v>183</v>
+      </c>
+      <c r="BZ12" s="238" t="s">
+        <v>115</v>
+      </c>
+      <c r="CA12" s="238" t="s">
+        <v>225</v>
+      </c>
+      <c r="CB12" s="238" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="13" spans="1:86" outlineLevel="1">
+      <c r="BL13" s="238" t="str">
+        <v>k</v>
+      </c>
+      <c r="BM13" s="238" t="str">
+        <v>d</v>
+      </c>
+      <c r="BN13" s="238" t="str">
+        <v>ㄎ</v>
+      </c>
+      <c r="BO13" s="238"/>
+      <c r="BP13" s="238"/>
+      <c r="BR13" s="238">
+        <v>11</v>
+      </c>
+      <c r="BS13" s="238" t="s">
+        <v>511</v>
+      </c>
+      <c r="BT13" s="238" t="s">
+        <v>118</v>
+      </c>
+      <c r="BU13" s="238" t="s">
+        <v>185</v>
+      </c>
+      <c r="BV13" s="238" t="s">
+        <v>132</v>
+      </c>
+      <c r="BX13" s="238">
+        <v>11</v>
+      </c>
+      <c r="BY13" s="238" t="s">
+        <v>519</v>
+      </c>
+      <c r="BZ13" s="238" t="s">
+        <v>70</v>
+      </c>
+      <c r="CA13" s="238" t="s">
+        <v>38</v>
+      </c>
+      <c r="CB13" s="238" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="14" spans="1:86" outlineLevel="1">
+      <c r="C14" s="1" t="str">
+        <f xml:space="preserve"> MID(C9, B10+1,  B11-B10-1)</f>
+        <v>BbpmdtnlGgkŋZzcsJjCShaiwueOəIUdfqrvxyMGNY@AWHRFQV7325841L&amp;*</v>
+      </c>
+      <c r="BL14" s="238" t="str">
+        <v>ŋ</v>
+      </c>
+      <c r="BM14" s="238" t="str">
+        <v>G</v>
+      </c>
+      <c r="BN14" s="238" t="str">
+        <v>ㄫ</v>
+      </c>
+      <c r="BO14" s="238"/>
+      <c r="BP14" s="238"/>
+      <c r="BR14" s="238">
+        <v>12</v>
+      </c>
+      <c r="BS14" s="238" t="s">
+        <v>447</v>
+      </c>
+      <c r="BT14" s="238" t="s">
+        <v>217</v>
+      </c>
+      <c r="BU14" s="238" t="s">
+        <v>115</v>
+      </c>
+      <c r="BV14" s="238" t="s">
+        <v>158</v>
+      </c>
+      <c r="BX14" s="238">
+        <v>12</v>
+      </c>
+      <c r="BY14" s="238" t="s">
+        <v>520</v>
+      </c>
+      <c r="BZ14" s="238" t="s">
+        <v>114</v>
+      </c>
+      <c r="CA14" s="238" t="s">
+        <v>193</v>
+      </c>
+      <c r="CB14" s="238" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:86" outlineLevel="1">
+      <c r="C15" s="1" t="str">
+        <f xml:space="preserve"> MID(C9, B11+1,  B12-B11-1)</f>
+        <v>!1qa2wsxEedGYyhnRrfvc8uKj,ik9l*UJ&lt;I(Lm/pM0;Oobtgz53467][N.-</v>
+      </c>
+      <c r="BL15" s="238" t="str">
+        <v>Z</v>
+      </c>
+      <c r="BM15" s="238" t="str">
+        <v>Y</v>
+      </c>
+      <c r="BN15" s="238" t="str">
+        <v>ㆡ</v>
+      </c>
+      <c r="BO15" s="238"/>
+      <c r="BP15" s="238"/>
+      <c r="BR15" s="238">
+        <v>13</v>
+      </c>
+      <c r="BS15" s="238" t="s">
+        <v>187</v>
+      </c>
+      <c r="BT15" s="238" t="s">
+        <v>187</v>
+      </c>
+      <c r="BU15" s="238" t="s">
+        <v>72</v>
+      </c>
+      <c r="BV15" s="238" t="s">
+        <v>84</v>
+      </c>
+      <c r="BX15" s="238">
+        <v>13</v>
+      </c>
+      <c r="BY15" s="238" t="s">
+        <v>521</v>
+      </c>
+      <c r="BZ15" s="238" t="s">
+        <v>67</v>
+      </c>
+      <c r="CA15" s="238" t="s">
+        <v>97</v>
+      </c>
+      <c r="CB15" s="238" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:86" outlineLevel="1">
+      <c r="BL16" s="238" t="str">
+        <v>z</v>
+      </c>
+      <c r="BM16" s="238" t="str">
+        <v>y</v>
+      </c>
+      <c r="BN16" s="239" t="str">
+        <v>ㄗ</v>
+      </c>
+      <c r="BO16" s="238"/>
+      <c r="BP16" s="238"/>
+      <c r="BR16" s="238">
+        <v>14</v>
+      </c>
+      <c r="BS16" s="238" t="s">
+        <v>512</v>
+      </c>
+      <c r="BT16" s="238" t="s">
+        <v>102</v>
+      </c>
+      <c r="BU16" s="238" t="s">
+        <v>197</v>
+      </c>
+      <c r="BV16" s="238" t="s">
+        <v>101</v>
+      </c>
+      <c r="BX16" s="238">
+        <v>14</v>
+      </c>
+      <c r="BY16" s="238" t="s">
+        <v>522</v>
+      </c>
+      <c r="BZ16" s="238" t="s">
+        <v>151</v>
+      </c>
+      <c r="CA16" s="238" t="s">
+        <v>102</v>
+      </c>
+      <c r="CB16" s="238" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80" outlineLevel="1">
+      <c r="C17" s="3">
+        <f xml:space="preserve"> COLUMN() -2</f>
+        <v>1</v>
+      </c>
+      <c r="D17" s="3">
+        <f t="shared" ref="D17:BJ17" si="2" xml:space="preserve"> COLUMN() -2</f>
+        <v>2</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="F17" s="3">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="G17" s="3">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="H17" s="3">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="I17" s="3">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="J17" s="3">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="K17" s="3">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="L17" s="3">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M17" s="3">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="N17" s="3">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="O17" s="3">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="P17" s="3">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="Q17" s="3">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="R17" s="3">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="S17" s="3">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="T17" s="3">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="U17" s="3">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="V17" s="3">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="W17" s="3">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="X17" s="3">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="Z17" s="3">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="AA17" s="3">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="AB17" s="3">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="AC17" s="3">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="AD17" s="3">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="AE17" s="3">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="AF17" s="3">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="AG17" s="3">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+      <c r="AH17" s="3">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="AI17" s="3">
+        <f t="shared" si="2"/>
+        <v>33</v>
+      </c>
+      <c r="AJ17" s="3">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+      <c r="AK17" s="3">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+      <c r="AL17" s="3">
+        <f t="shared" si="2"/>
+        <v>36</v>
+      </c>
+      <c r="AM17" s="3">
+        <f t="shared" si="2"/>
+        <v>37</v>
+      </c>
+      <c r="AN17" s="3">
+        <f t="shared" si="2"/>
+        <v>38</v>
+      </c>
+      <c r="AO17" s="3">
+        <f t="shared" si="2"/>
+        <v>39</v>
+      </c>
+      <c r="AP17" s="3">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+      <c r="AQ17" s="3">
+        <f t="shared" si="2"/>
+        <v>41</v>
+      </c>
+      <c r="AR17" s="3">
+        <f t="shared" si="2"/>
+        <v>42</v>
+      </c>
+      <c r="AS17" s="3">
+        <f t="shared" si="2"/>
+        <v>43</v>
+      </c>
+      <c r="AT17" s="3">
+        <f t="shared" si="2"/>
+        <v>44</v>
+      </c>
+      <c r="AU17" s="3">
+        <f t="shared" si="2"/>
+        <v>45</v>
+      </c>
+      <c r="AV17" s="3">
+        <f t="shared" si="2"/>
+        <v>46</v>
+      </c>
+      <c r="AW17" s="3">
+        <f t="shared" si="2"/>
+        <v>47</v>
+      </c>
+      <c r="AX17" s="3">
+        <f t="shared" si="2"/>
+        <v>48</v>
+      </c>
+      <c r="AY17" s="3">
+        <f t="shared" si="2"/>
+        <v>49</v>
+      </c>
+      <c r="AZ17" s="3">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="BA17" s="3">
+        <f t="shared" si="2"/>
+        <v>51</v>
+      </c>
+      <c r="BB17" s="3">
+        <f t="shared" si="2"/>
+        <v>52</v>
+      </c>
+      <c r="BC17" s="3">
+        <f t="shared" si="2"/>
+        <v>53</v>
+      </c>
+      <c r="BD17" s="3">
+        <f t="shared" si="2"/>
+        <v>54</v>
+      </c>
+      <c r="BE17" s="3">
+        <f t="shared" si="2"/>
+        <v>55</v>
+      </c>
+      <c r="BF17" s="3">
+        <f t="shared" si="2"/>
+        <v>56</v>
+      </c>
+      <c r="BG17" s="3">
+        <f t="shared" si="2"/>
+        <v>57</v>
+      </c>
+      <c r="BH17" s="3">
+        <f t="shared" si="2"/>
+        <v>58</v>
+      </c>
+      <c r="BI17" s="3">
+        <f t="shared" si="2"/>
+        <v>59</v>
+      </c>
+      <c r="BJ17" s="3">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="BL17" s="238" t="str">
+        <v>c</v>
+      </c>
+      <c r="BM17" s="238" t="str">
+        <v>h</v>
+      </c>
+      <c r="BN17" s="239" t="str">
+        <v>ㄘ</v>
+      </c>
+      <c r="BO17" s="238"/>
+      <c r="BP17" s="238"/>
+      <c r="BR17" s="238">
+        <v>15</v>
+      </c>
+      <c r="BS17" s="238" t="s">
+        <v>513</v>
+      </c>
+      <c r="BT17" s="238" t="s">
+        <v>139</v>
+      </c>
+      <c r="BU17" s="238" t="s">
+        <v>170</v>
+      </c>
+      <c r="BV17" s="238" t="s">
+        <v>138</v>
+      </c>
+      <c r="BX17" s="238">
+        <v>15</v>
+      </c>
+      <c r="BY17" s="238" t="s">
+        <v>59</v>
+      </c>
+      <c r="BZ17" s="238" t="s">
+        <v>74</v>
+      </c>
+      <c r="CA17" s="238" t="s">
+        <v>226</v>
+      </c>
+      <c r="CB17" s="238" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80" s="237" customFormat="1" outlineLevel="1">
+      <c r="A18" s="244" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="4" t="str">
+        <f xml:space="preserve"> MID( $C$14,C$17,1)</f>
+        <v>B</v>
+      </c>
+      <c r="D18" s="4" t="str">
+        <f t="shared" ref="D18:BJ18" si="3" xml:space="preserve"> MID( $C$14,D$17,1)</f>
+        <v>b</v>
+      </c>
+      <c r="E18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>p</v>
+      </c>
+      <c r="F18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>m</v>
+      </c>
+      <c r="G18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>d</v>
+      </c>
+      <c r="H18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>t</v>
+      </c>
+      <c r="I18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>n</v>
+      </c>
+      <c r="J18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>l</v>
+      </c>
+      <c r="K18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>G</v>
+      </c>
+      <c r="L18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>g</v>
+      </c>
+      <c r="M18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>k</v>
+      </c>
+      <c r="N18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>ŋ</v>
+      </c>
+      <c r="O18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>Z</v>
+      </c>
+      <c r="P18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>z</v>
+      </c>
+      <c r="Q18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>c</v>
+      </c>
+      <c r="R18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>s</v>
+      </c>
+      <c r="S18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>J</v>
+      </c>
+      <c r="T18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>j</v>
+      </c>
+      <c r="U18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>C</v>
+      </c>
+      <c r="V18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>S</v>
+      </c>
+      <c r="W18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>h</v>
+      </c>
+      <c r="X18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>a</v>
+      </c>
+      <c r="Y18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>i</v>
+      </c>
+      <c r="Z18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>w</v>
+      </c>
+      <c r="AA18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>u</v>
+      </c>
+      <c r="AB18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>e</v>
+      </c>
+      <c r="AC18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>O</v>
+      </c>
+      <c r="AD18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>ə</v>
+      </c>
+      <c r="AE18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>I</v>
+      </c>
+      <c r="AF18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>U</v>
+      </c>
+      <c r="AG18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>d</v>
+      </c>
+      <c r="AH18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>f</v>
+      </c>
+      <c r="AI18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>q</v>
+      </c>
+      <c r="AJ18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>r</v>
+      </c>
+      <c r="AK18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>v</v>
+      </c>
+      <c r="AL18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>x</v>
+      </c>
+      <c r="AM18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>y</v>
+      </c>
+      <c r="AN18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>M</v>
+      </c>
+      <c r="AO18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>G</v>
+      </c>
+      <c r="AP18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>N</v>
+      </c>
+      <c r="AQ18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>Y</v>
+      </c>
+      <c r="AR18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>@</v>
+      </c>
+      <c r="AS18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>A</v>
+      </c>
+      <c r="AT18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>W</v>
+      </c>
+      <c r="AU18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>H</v>
+      </c>
+      <c r="AV18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>R</v>
+      </c>
+      <c r="AW18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>F</v>
+      </c>
+      <c r="AX18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>Q</v>
+      </c>
+      <c r="AY18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>V</v>
+      </c>
+      <c r="AZ18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="BA18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="BB18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="BC18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="BD18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="BE18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="BF18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="BG18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>L</v>
+      </c>
+      <c r="BH18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>&amp;</v>
+      </c>
+      <c r="BI18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>*</v>
+      </c>
+      <c r="BJ18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="BK18" s="1"/>
+      <c r="BL18" s="238" t="str">
+        <v>s</v>
+      </c>
+      <c r="BM18" s="238" t="str">
+        <v>n</v>
+      </c>
+      <c r="BN18" s="239" t="str">
+        <v>ㄙ</v>
+      </c>
+      <c r="BO18" s="238"/>
+      <c r="BP18" s="238"/>
+      <c r="BR18" s="238">
+        <v>16</v>
+      </c>
+      <c r="BS18" s="238" t="s">
+        <v>176</v>
+      </c>
+      <c r="BT18" s="238" t="s">
+        <v>176</v>
+      </c>
+      <c r="BU18" s="238" t="s">
+        <v>189</v>
+      </c>
+      <c r="BV18" s="238" t="s">
+        <v>175</v>
+      </c>
+      <c r="BX18" s="238">
+        <v>16</v>
+      </c>
+      <c r="BY18" s="238" t="s">
+        <v>145</v>
+      </c>
+      <c r="BZ18" s="238" t="s">
+        <v>73</v>
+      </c>
+      <c r="CA18" s="238" t="s">
+        <v>168</v>
+      </c>
+      <c r="CB18" s="238" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80" s="237" customFormat="1" outlineLevel="1">
+      <c r="A19" s="245" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="246"/>
+      <c r="C19" s="247" t="str">
+        <f xml:space="preserve"> MID($C$15,C$17,1)</f>
+        <v>!</v>
+      </c>
+      <c r="D19" s="247" t="str">
+        <f t="shared" ref="D19:BJ19" si="4" xml:space="preserve"> MID($C$15,D$17,1)</f>
+        <v>1</v>
+      </c>
+      <c r="E19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>q</v>
+      </c>
+      <c r="F19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>a</v>
+      </c>
+      <c r="G19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="H19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>w</v>
+      </c>
+      <c r="I19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>s</v>
+      </c>
+      <c r="J19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>x</v>
+      </c>
+      <c r="K19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>E</v>
+      </c>
+      <c r="L19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>e</v>
+      </c>
+      <c r="M19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>d</v>
+      </c>
+      <c r="N19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>G</v>
+      </c>
+      <c r="O19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>Y</v>
+      </c>
+      <c r="P19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>y</v>
+      </c>
+      <c r="Q19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>h</v>
+      </c>
+      <c r="R19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>n</v>
+      </c>
+      <c r="S19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>R</v>
+      </c>
+      <c r="T19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>r</v>
+      </c>
+      <c r="U19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>f</v>
+      </c>
+      <c r="V19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>v</v>
+      </c>
+      <c r="W19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>c</v>
+      </c>
+      <c r="X19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="Y19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>u</v>
+      </c>
+      <c r="Z19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>K</v>
+      </c>
+      <c r="AA19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>j</v>
+      </c>
+      <c r="AB19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>,</v>
+      </c>
+      <c r="AC19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>i</v>
+      </c>
+      <c r="AD19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>k</v>
+      </c>
+      <c r="AE19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="AF19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>l</v>
+      </c>
+      <c r="AG19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>*</v>
+      </c>
+      <c r="AH19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>U</v>
+      </c>
+      <c r="AI19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>J</v>
+      </c>
+      <c r="AJ19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>&lt;</v>
+      </c>
+      <c r="AK19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>I</v>
+      </c>
+      <c r="AL19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>(</v>
+      </c>
+      <c r="AM19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>L</v>
+      </c>
+      <c r="AN19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>m</v>
+      </c>
+      <c r="AO19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>/</v>
+      </c>
+      <c r="AP19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>p</v>
+      </c>
+      <c r="AQ19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>M</v>
+      </c>
+      <c r="AR19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AS19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>;</v>
+      </c>
+      <c r="AT19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>O</v>
+      </c>
+      <c r="AU19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>o</v>
+      </c>
+      <c r="AV19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>b</v>
+      </c>
+      <c r="AW19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>t</v>
+      </c>
+      <c r="AX19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>g</v>
+      </c>
+      <c r="AY19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>z</v>
+      </c>
+      <c r="AZ19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="BA19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="BB19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="BC19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="BD19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="BE19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>]</v>
+      </c>
+      <c r="BF19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>[</v>
+      </c>
+      <c r="BG19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>N</v>
+      </c>
+      <c r="BH19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>.</v>
+      </c>
+      <c r="BI19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v>-</v>
+      </c>
+      <c r="BJ19" s="247" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="BK19" s="1"/>
+      <c r="BL19" s="238" t="str">
+        <v>J</v>
+      </c>
+      <c r="BM19" s="238" t="str">
+        <v>R</v>
+      </c>
+      <c r="BN19" s="239" t="str">
+        <v>ㆢ</v>
+      </c>
+      <c r="BO19" s="238"/>
+      <c r="BP19" s="238"/>
+      <c r="BR19" s="238">
+        <v>17</v>
+      </c>
+      <c r="BS19" s="238" t="s">
+        <v>170</v>
+      </c>
+      <c r="BT19" s="238" t="s">
+        <v>170</v>
+      </c>
+      <c r="BU19" s="238" t="s">
+        <v>139</v>
+      </c>
+      <c r="BV19" s="238" t="s">
+        <v>169</v>
+      </c>
+      <c r="BX19" s="238">
+        <v>17</v>
+      </c>
+      <c r="BY19" s="238" t="s">
+        <v>161</v>
+      </c>
+      <c r="BZ19" s="238" t="s">
+        <v>72</v>
+      </c>
+      <c r="CA19" s="238" t="s">
+        <v>154</v>
+      </c>
+      <c r="CB19" s="238" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80" s="237" customFormat="1" outlineLevel="1">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1"/>
+      <c r="W20" s="1"/>
+      <c r="X20" s="1"/>
+      <c r="Y20" s="1"/>
+      <c r="Z20" s="1"/>
+      <c r="AA20" s="1"/>
+      <c r="AB20" s="1"/>
+      <c r="AC20" s="1"/>
+      <c r="AD20" s="1"/>
+      <c r="AE20" s="1"/>
+      <c r="AF20" s="1"/>
+      <c r="AG20" s="1"/>
+      <c r="AH20" s="1"/>
+      <c r="AI20" s="1"/>
+      <c r="AJ20" s="1"/>
+      <c r="AK20" s="1"/>
+      <c r="AL20" s="1"/>
+      <c r="AM20" s="1"/>
+      <c r="AN20" s="1"/>
+      <c r="AO20" s="1"/>
+      <c r="AP20" s="1"/>
+      <c r="AQ20" s="1"/>
+      <c r="AR20" s="1"/>
+      <c r="AS20" s="1"/>
+      <c r="AT20" s="1"/>
+      <c r="AU20" s="1"/>
+      <c r="AV20" s="1"/>
+      <c r="AW20" s="1"/>
+      <c r="AX20" s="1"/>
+      <c r="AY20" s="1"/>
+      <c r="AZ20" s="1"/>
+      <c r="BA20" s="1"/>
+      <c r="BB20" s="1"/>
+      <c r="BC20" s="1"/>
+      <c r="BD20" s="1"/>
+      <c r="BE20" s="1"/>
+      <c r="BF20" s="1"/>
+      <c r="BG20" s="1"/>
+      <c r="BH20" s="1"/>
+      <c r="BI20" s="1"/>
+      <c r="BJ20" s="1"/>
+      <c r="BK20" s="1"/>
+      <c r="BL20" s="238" t="str">
+        <v>j</v>
+      </c>
+      <c r="BM20" s="238" t="str">
+        <v>r</v>
+      </c>
+      <c r="BN20" s="239" t="str">
+        <v>ㄐ</v>
+      </c>
+      <c r="BO20" s="238"/>
+      <c r="BP20" s="238"/>
+      <c r="BR20" s="238">
+        <v>18</v>
+      </c>
+      <c r="BS20" s="238" t="s">
+        <v>514</v>
+      </c>
+      <c r="BT20" s="238" t="s">
+        <v>117</v>
+      </c>
+      <c r="BU20" s="238" t="s">
+        <v>70</v>
+      </c>
+      <c r="BV20" s="238" t="s">
+        <v>82</v>
+      </c>
+      <c r="BX20" s="238">
+        <v>18</v>
+      </c>
+      <c r="BY20" s="238" t="s">
+        <v>61</v>
+      </c>
+      <c r="BZ20" s="238" t="s">
+        <v>218</v>
+      </c>
+      <c r="CA20" s="238" t="s">
+        <v>227</v>
+      </c>
+      <c r="CB20" s="238" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80" s="237" customFormat="1">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="1"/>
+      <c r="W21" s="1"/>
+      <c r="X21" s="1"/>
+      <c r="Y21" s="1"/>
+      <c r="Z21" s="1"/>
+      <c r="AA21" s="1"/>
+      <c r="AB21" s="1"/>
+      <c r="AC21" s="1"/>
+      <c r="AD21" s="1"/>
+      <c r="AE21" s="1"/>
+      <c r="AF21" s="1"/>
+      <c r="AG21" s="1"/>
+      <c r="AH21" s="1"/>
+      <c r="AI21" s="1"/>
+      <c r="AJ21" s="1"/>
+      <c r="AK21" s="1"/>
+      <c r="AL21" s="1"/>
+      <c r="AM21" s="1"/>
+      <c r="AN21" s="1"/>
+      <c r="AO21" s="1"/>
+      <c r="AP21" s="1"/>
+      <c r="AQ21" s="1"/>
+      <c r="AR21" s="1"/>
+      <c r="AS21" s="1"/>
+      <c r="AT21" s="1"/>
+      <c r="AU21" s="1"/>
+      <c r="AV21" s="1"/>
+      <c r="AW21" s="1"/>
+      <c r="AX21" s="1"/>
+      <c r="AY21" s="1"/>
+      <c r="AZ21" s="1"/>
+      <c r="BA21" s="1"/>
+      <c r="BB21" s="1"/>
+      <c r="BC21" s="1"/>
+      <c r="BD21" s="1"/>
+      <c r="BE21" s="1"/>
+      <c r="BF21" s="1"/>
+      <c r="BG21" s="1"/>
+      <c r="BH21" s="1"/>
+      <c r="BI21" s="1"/>
+      <c r="BJ21" s="1"/>
+      <c r="BK21" s="1"/>
+      <c r="BL21" s="238" t="str">
+        <v>C</v>
+      </c>
+      <c r="BM21" s="238" t="str">
+        <v>f</v>
+      </c>
+      <c r="BN21" s="239" t="str">
+        <v>ㄑ</v>
+      </c>
+      <c r="BO21" s="238"/>
+      <c r="BP21" s="238"/>
+      <c r="BR21" s="238">
+        <v>19</v>
+      </c>
+      <c r="BS21" s="238" t="s">
+        <v>515</v>
+      </c>
+      <c r="BT21" s="238" t="s">
+        <v>148</v>
+      </c>
+      <c r="BU21" s="238" t="s">
+        <v>192</v>
+      </c>
+      <c r="BV21" s="238" t="s">
+        <v>98</v>
+      </c>
+      <c r="BX21" s="238">
+        <v>19</v>
+      </c>
+      <c r="BY21" s="238" t="s">
+        <v>147</v>
+      </c>
+      <c r="BZ21" s="238" t="s">
+        <v>111</v>
+      </c>
+      <c r="CA21" s="238" t="s">
+        <v>228</v>
+      </c>
+      <c r="CB21" s="238" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80" s="237" customFormat="1">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1"/>
+      <c r="W22" s="1"/>
+      <c r="X22" s="1"/>
+      <c r="Y22" s="1"/>
+      <c r="Z22" s="1"/>
+      <c r="AA22" s="1"/>
+      <c r="AB22" s="1"/>
+      <c r="AC22" s="1"/>
+      <c r="AD22" s="1"/>
+      <c r="AE22" s="1"/>
+      <c r="AF22" s="1"/>
+      <c r="AG22" s="1"/>
+      <c r="AH22" s="1"/>
+      <c r="AI22" s="1"/>
+      <c r="AJ22" s="1"/>
+      <c r="AK22" s="1"/>
+      <c r="AL22" s="1"/>
+      <c r="AM22" s="1"/>
+      <c r="AN22" s="1"/>
+      <c r="AO22" s="1"/>
+      <c r="AP22" s="1"/>
+      <c r="AQ22" s="1"/>
+      <c r="AR22" s="1"/>
+      <c r="AS22" s="1"/>
+      <c r="AT22" s="1"/>
+      <c r="AU22" s="1"/>
+      <c r="AV22" s="1"/>
+      <c r="AW22" s="1"/>
+      <c r="AX22" s="1"/>
+      <c r="AY22" s="1"/>
+      <c r="AZ22" s="1"/>
+      <c r="BA22" s="1"/>
+      <c r="BB22" s="1"/>
+      <c r="BC22" s="1"/>
+      <c r="BD22" s="1"/>
+      <c r="BE22" s="1"/>
+      <c r="BF22" s="1"/>
+      <c r="BG22" s="1"/>
+      <c r="BH22" s="1"/>
+      <c r="BI22" s="1"/>
+      <c r="BJ22" s="1"/>
+      <c r="BK22" s="1"/>
+      <c r="BL22" s="238" t="str">
+        <v>S</v>
+      </c>
+      <c r="BM22" s="238" t="str">
+        <v>v</v>
+      </c>
+      <c r="BN22" s="239" t="str">
+        <v>ㄒ</v>
+      </c>
+      <c r="BO22" s="238"/>
+      <c r="BP22" s="238"/>
+      <c r="BR22" s="238">
+        <v>20</v>
+      </c>
+      <c r="BS22" s="238" t="s">
+        <v>516</v>
+      </c>
+      <c r="BT22" s="238" t="s">
+        <v>150</v>
+      </c>
+      <c r="BU22" s="238" t="s">
+        <v>186</v>
+      </c>
+      <c r="BV22" s="238" t="s">
+        <v>134</v>
+      </c>
+      <c r="BX22" s="238">
+        <v>20</v>
+      </c>
+      <c r="BY22" s="238" t="s">
+        <v>91</v>
+      </c>
+      <c r="BZ22" s="238" t="s">
+        <v>68</v>
+      </c>
+      <c r="CA22" s="238" t="s">
+        <v>75</v>
+      </c>
+      <c r="CB22" s="238" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80" s="237" customFormat="1">
+      <c r="A23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+      <c r="V23" s="1"/>
+      <c r="W23" s="1"/>
+      <c r="X23" s="1"/>
+      <c r="Y23" s="1"/>
+      <c r="Z23" s="1"/>
+      <c r="AA23" s="1"/>
+      <c r="AB23" s="1"/>
+      <c r="AC23" s="1"/>
+      <c r="AD23" s="1"/>
+      <c r="AE23" s="1"/>
+      <c r="AF23" s="1"/>
+      <c r="AG23" s="1"/>
+      <c r="AH23" s="1"/>
+      <c r="AI23" s="1"/>
+      <c r="AJ23" s="1"/>
+      <c r="AK23" s="1"/>
+      <c r="AL23" s="1"/>
+      <c r="AM23" s="1"/>
+      <c r="AN23" s="1"/>
+      <c r="AO23" s="1"/>
+      <c r="AP23" s="1"/>
+      <c r="AQ23" s="1"/>
+      <c r="AR23" s="1"/>
+      <c r="AS23" s="1"/>
+      <c r="AT23" s="1"/>
+      <c r="AU23" s="1"/>
+      <c r="AV23" s="1"/>
+      <c r="AW23" s="1"/>
+      <c r="AX23" s="1"/>
+      <c r="AY23" s="1"/>
+      <c r="AZ23" s="1"/>
+      <c r="BA23" s="1"/>
+      <c r="BB23" s="1"/>
+      <c r="BC23" s="1"/>
+      <c r="BD23" s="1"/>
+      <c r="BE23" s="1"/>
+      <c r="BF23" s="1"/>
+      <c r="BG23" s="1"/>
+      <c r="BH23" s="1"/>
+      <c r="BI23" s="1"/>
+      <c r="BJ23" s="1"/>
+      <c r="BK23" s="1"/>
+      <c r="BL23" s="238" t="str">
+        <v>h</v>
+      </c>
+      <c r="BM23" s="238" t="str">
+        <v>c</v>
+      </c>
+      <c r="BN23" s="239" t="str">
+        <v>ㄏ</v>
+      </c>
+      <c r="BO23" s="238"/>
+      <c r="BP23" s="238"/>
+      <c r="BR23" s="238">
+        <v>21</v>
+      </c>
+      <c r="BS23" s="238" t="s">
+        <v>517</v>
+      </c>
+      <c r="BT23" s="238" t="s">
+        <v>112</v>
+      </c>
+      <c r="BU23" s="238" t="s">
+        <v>194</v>
+      </c>
+      <c r="BV23" s="238" t="s">
+        <v>171</v>
+      </c>
+      <c r="BX23" s="238">
+        <v>21</v>
+      </c>
+      <c r="BY23" s="238" t="s">
+        <v>108</v>
+      </c>
+      <c r="BZ23" s="238" t="s">
+        <v>116</v>
+      </c>
+      <c r="CA23" s="238" t="s">
+        <v>190</v>
+      </c>
+      <c r="CB23" s="238" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80" s="237" customFormat="1">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1" t="str">
+        <f xml:space="preserve"> "- xlit|!1qa2wsxEedGYyhnRrfvc8uKj,ik9l*UJ&lt;I(Lm/pM0;Oobtgz53467][N.-|ㆠㄅㄆㄇㄉㄊㄋㄌㆣㄍㄎㄫㆡㄗㄘㄙㆢㄐㄑㄒㄏㄚㄧㆨㄨㆤㆦㄜㄞㄠㆩㆪㆫㆥㆧㆮㆯㆬㆭㄣㆰㄢㄤㆱㆲㆴㆵㆻㆷ˫˪ˋˊ八四一ㄥ入ñ|"</f>
+        <v>- xlit|!1qa2wsxEedGYyhnRrfvc8uKj,ik9l*UJ&lt;I(Lm/pM0;Oobtgz53467][N.-|ㆠㄅㄆㄇㄉㄊㄋㄌㆣㄍㄎㄫㆡㄗㄘㄙㆢㄐㄑㄒㄏㄚㄧㆨㄨㆤㆦㄜㄞㄠㆩㆪㆫㆥㆧㆮㆯㆬㆭㄣㆰㄢㄤㆱㆲㆴㆵㆻㆷ˫˪ˋˊ八四一ㄥ入ñ|</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1"/>
+      <c r="W24" s="1"/>
+      <c r="X24" s="1"/>
+      <c r="Y24" s="1"/>
+      <c r="Z24" s="1"/>
+      <c r="AA24" s="1"/>
+      <c r="AB24" s="1"/>
+      <c r="AC24" s="1"/>
+      <c r="AD24" s="1"/>
+      <c r="AE24" s="1"/>
+      <c r="AF24" s="1"/>
+      <c r="AG24" s="1"/>
+      <c r="AH24" s="1"/>
+      <c r="AI24" s="1"/>
+      <c r="AJ24" s="1"/>
+      <c r="AK24" s="1"/>
+      <c r="AL24" s="1"/>
+      <c r="AM24" s="1"/>
+      <c r="AN24" s="1"/>
+      <c r="AO24" s="1"/>
+      <c r="AP24" s="1"/>
+      <c r="AQ24" s="1"/>
+      <c r="AR24" s="1"/>
+      <c r="AS24" s="1"/>
+      <c r="AT24" s="1"/>
+      <c r="AU24" s="1"/>
+      <c r="AV24" s="1"/>
+      <c r="AW24" s="1"/>
+      <c r="AX24" s="1"/>
+      <c r="AY24" s="1"/>
+      <c r="AZ24" s="1"/>
+      <c r="BA24" s="1"/>
+      <c r="BB24" s="1"/>
+      <c r="BC24" s="1"/>
+      <c r="BD24" s="1"/>
+      <c r="BE24" s="1"/>
+      <c r="BF24" s="1"/>
+      <c r="BG24" s="1"/>
+      <c r="BH24" s="1"/>
+      <c r="BI24" s="1"/>
+      <c r="BJ24" s="1"/>
+      <c r="BK24" s="1"/>
+      <c r="BL24" s="238" t="str">
+        <v>a</v>
+      </c>
+      <c r="BM24" s="238" t="str">
+        <v>8</v>
+      </c>
+      <c r="BN24" s="239" t="str">
+        <v>ㄚ</v>
+      </c>
+      <c r="BO24" s="238"/>
+      <c r="BP24" s="238"/>
+      <c r="BX24" s="238">
+        <v>22</v>
+      </c>
+      <c r="BY24" s="238" t="s">
+        <v>523</v>
+      </c>
+      <c r="BZ24" s="238" t="s">
+        <v>185</v>
+      </c>
+      <c r="CA24" s="238" t="s">
+        <v>229</v>
+      </c>
+      <c r="CB24" s="238" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80" s="237" customFormat="1">
+      <c r="A25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" s="1">
+        <f xml:space="preserve"> SEARCH("|", C24)</f>
+        <v>7</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="1"/>
+      <c r="X25" s="1"/>
+      <c r="Y25" s="1"/>
+      <c r="Z25" s="1"/>
+      <c r="AA25" s="1"/>
+      <c r="AB25" s="1"/>
+      <c r="AC25" s="1"/>
+      <c r="AD25" s="1"/>
+      <c r="AE25" s="1"/>
+      <c r="AF25" s="1"/>
+      <c r="AG25" s="1"/>
+      <c r="AH25" s="1"/>
+      <c r="AI25" s="1"/>
+      <c r="AJ25" s="1"/>
+      <c r="AK25" s="1"/>
+      <c r="AL25" s="1"/>
+      <c r="AM25" s="1"/>
+      <c r="AN25" s="1"/>
+      <c r="AO25" s="1"/>
+      <c r="AP25" s="1"/>
+      <c r="AQ25" s="1"/>
+      <c r="AR25" s="1"/>
+      <c r="AS25" s="1"/>
+      <c r="AT25" s="1"/>
+      <c r="AU25" s="1"/>
+      <c r="AV25" s="1"/>
+      <c r="AW25" s="1"/>
+      <c r="AX25" s="1"/>
+      <c r="AY25" s="1"/>
+      <c r="AZ25" s="1"/>
+      <c r="BA25" s="1"/>
+      <c r="BB25" s="1"/>
+      <c r="BC25" s="1"/>
+      <c r="BD25" s="1"/>
+      <c r="BE25" s="1"/>
+      <c r="BF25" s="1"/>
+      <c r="BG25" s="1"/>
+      <c r="BH25" s="1"/>
+      <c r="BI25" s="1"/>
+      <c r="BJ25" s="1"/>
+      <c r="BK25" s="1"/>
+      <c r="BL25" s="238" t="str">
+        <v>i</v>
+      </c>
+      <c r="BM25" s="238" t="str">
+        <v>u</v>
+      </c>
+      <c r="BN25" s="239" t="str">
+        <v>ㄧ</v>
+      </c>
+      <c r="BO25" s="238"/>
+      <c r="BP25" s="238"/>
+      <c r="BX25" s="238">
+        <v>23</v>
+      </c>
+      <c r="BY25" s="238" t="s">
+        <v>524</v>
+      </c>
+      <c r="BZ25" s="238" t="s">
+        <v>186</v>
+      </c>
+      <c r="CA25" s="238" t="s">
+        <v>73</v>
+      </c>
+      <c r="CB25" s="238" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80" s="237" customFormat="1">
+      <c r="A26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B26" s="1">
+        <f xml:space="preserve"> SEARCH("|", C24, B25+1)</f>
+        <v>67</v>
+      </c>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
+      <c r="X26" s="1"/>
+      <c r="Y26" s="1"/>
+      <c r="Z26" s="1"/>
+      <c r="AA26" s="1"/>
+      <c r="AB26" s="1"/>
+      <c r="AC26" s="1"/>
+      <c r="AD26" s="1"/>
+      <c r="AE26" s="1"/>
+      <c r="AF26" s="1"/>
+      <c r="AG26" s="1"/>
+      <c r="AH26" s="1"/>
+      <c r="AI26" s="1"/>
+      <c r="AJ26" s="1"/>
+      <c r="AK26" s="1"/>
+      <c r="AL26" s="1"/>
+      <c r="AM26" s="1"/>
+      <c r="AN26" s="1"/>
+      <c r="AO26" s="1"/>
+      <c r="AP26" s="1"/>
+      <c r="AQ26" s="1"/>
+      <c r="AR26" s="1"/>
+      <c r="AS26" s="1"/>
+      <c r="AT26" s="1"/>
+      <c r="AU26" s="1"/>
+      <c r="AV26" s="1"/>
+      <c r="AW26" s="1"/>
+      <c r="AX26" s="1"/>
+      <c r="AY26" s="1"/>
+      <c r="AZ26" s="1"/>
+      <c r="BA26" s="1"/>
+      <c r="BB26" s="1"/>
+      <c r="BC26" s="1"/>
+      <c r="BD26" s="1"/>
+      <c r="BE26" s="1"/>
+      <c r="BF26" s="1"/>
+      <c r="BG26" s="1"/>
+      <c r="BH26" s="1"/>
+      <c r="BI26" s="1"/>
+      <c r="BJ26" s="1"/>
+      <c r="BK26" s="1"/>
+      <c r="BL26" s="238" t="str">
+        <v>w</v>
+      </c>
+      <c r="BM26" s="238" t="str">
+        <v>K</v>
+      </c>
+      <c r="BN26" s="239" t="str">
+        <v>ㆨ</v>
+      </c>
+      <c r="BO26" s="238"/>
+      <c r="BP26" s="238"/>
+      <c r="BX26" s="238">
+        <v>24</v>
+      </c>
+      <c r="BY26" s="238" t="s">
+        <v>525</v>
+      </c>
+      <c r="BZ26" s="238" t="s">
+        <v>191</v>
+      </c>
+      <c r="CA26" s="238" t="s">
+        <v>117</v>
+      </c>
+      <c r="CB26" s="238" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80" s="237" customFormat="1">
+      <c r="A27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="1">
+        <f xml:space="preserve"> SEARCH("|",C24, B26+1)</f>
+        <v>127</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="1"/>
+      <c r="W27" s="1"/>
+      <c r="X27" s="1"/>
+      <c r="Y27" s="1"/>
+      <c r="Z27" s="1"/>
+      <c r="AA27" s="1"/>
+      <c r="AB27" s="1"/>
+      <c r="AC27" s="1"/>
+      <c r="AD27" s="1"/>
+      <c r="AE27" s="1"/>
+      <c r="AF27" s="1"/>
+      <c r="AG27" s="1"/>
+      <c r="AH27" s="1"/>
+      <c r="AI27" s="1"/>
+      <c r="AJ27" s="1"/>
+      <c r="AK27" s="1"/>
+      <c r="AL27" s="1"/>
+      <c r="AM27" s="1"/>
+      <c r="AN27" s="1"/>
+      <c r="AO27" s="1"/>
+      <c r="AP27" s="1"/>
+      <c r="AQ27" s="1"/>
+      <c r="AR27" s="1"/>
+      <c r="AS27" s="1"/>
+      <c r="AT27" s="1"/>
+      <c r="AU27" s="1"/>
+      <c r="AV27" s="1"/>
+      <c r="AW27" s="1"/>
+      <c r="AX27" s="1"/>
+      <c r="AY27" s="1"/>
+      <c r="AZ27" s="1"/>
+      <c r="BA27" s="1"/>
+      <c r="BB27" s="1"/>
+      <c r="BC27" s="1"/>
+      <c r="BD27" s="1"/>
+      <c r="BE27" s="1"/>
+      <c r="BF27" s="1"/>
+      <c r="BG27" s="1"/>
+      <c r="BH27" s="1"/>
+      <c r="BI27" s="1"/>
+      <c r="BJ27" s="1"/>
+      <c r="BK27" s="1"/>
+      <c r="BL27" s="238" t="str">
+        <v>u</v>
+      </c>
+      <c r="BM27" s="238" t="str">
+        <v>j</v>
+      </c>
+      <c r="BN27" s="238" t="str">
+        <v>ㄨ</v>
+      </c>
+      <c r="BO27" s="238"/>
+      <c r="BP27" s="238"/>
+      <c r="BX27" s="238">
+        <v>25</v>
+      </c>
+      <c r="BY27" s="238" t="s">
+        <v>526</v>
+      </c>
+      <c r="BZ27" s="238" t="s">
+        <v>192</v>
+      </c>
+      <c r="CA27" s="238" t="s">
+        <v>230</v>
+      </c>
+      <c r="CB27" s="238" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80" s="237" customFormat="1" outlineLevel="1">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="1"/>
+      <c r="Z28" s="1"/>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="1"/>
+      <c r="AC28" s="1"/>
+      <c r="AD28" s="1"/>
+      <c r="AE28" s="1"/>
+      <c r="AF28" s="1"/>
+      <c r="AG28" s="1"/>
+      <c r="AH28" s="1"/>
+      <c r="AI28" s="1"/>
+      <c r="AJ28" s="1"/>
+      <c r="AK28" s="1"/>
+      <c r="AL28" s="1"/>
+      <c r="AM28" s="1"/>
+      <c r="AN28" s="1"/>
+      <c r="AO28" s="1"/>
+      <c r="AP28" s="1"/>
+      <c r="AQ28" s="1"/>
+      <c r="AR28" s="1"/>
+      <c r="AS28" s="1"/>
+      <c r="AT28" s="1"/>
+      <c r="AU28" s="1"/>
+      <c r="AV28" s="1"/>
+      <c r="AW28" s="1"/>
+      <c r="AX28" s="1"/>
+      <c r="AY28" s="1"/>
+      <c r="AZ28" s="1"/>
+      <c r="BA28" s="1"/>
+      <c r="BB28" s="1"/>
+      <c r="BC28" s="1"/>
+      <c r="BD28" s="1"/>
+      <c r="BE28" s="1"/>
+      <c r="BF28" s="1"/>
+      <c r="BG28" s="1"/>
+      <c r="BH28" s="1"/>
+      <c r="BI28" s="1"/>
+      <c r="BJ28" s="1"/>
+      <c r="BK28" s="1"/>
+      <c r="BL28" s="238" t="str">
+        <v>e</v>
+      </c>
+      <c r="BM28" s="238" t="str">
+        <v>,</v>
+      </c>
+      <c r="BN28" s="238" t="str">
+        <v>ㆤ</v>
+      </c>
+      <c r="BO28" s="238"/>
+      <c r="BP28" s="238"/>
+      <c r="BX28" s="238">
+        <v>26</v>
+      </c>
+      <c r="BY28" s="238" t="s">
+        <v>527</v>
+      </c>
+      <c r="BZ28" s="238" t="s">
+        <v>194</v>
+      </c>
+      <c r="CA28" s="238" t="s">
+        <v>74</v>
+      </c>
+      <c r="CB28" s="238" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:80" s="237" customFormat="1" outlineLevel="1">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1" t="str">
+        <f xml:space="preserve"> MID(C24, B25+1,  B26-B25-1)</f>
+        <v>!1qa2wsxEedGYyhnRrfvc8uKj,ik9l*UJ&lt;I(Lm/pM0;Oobtgz53467][N.-</v>
+      </c>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="1"/>
+      <c r="W29" s="1"/>
+      <c r="X29" s="1"/>
+      <c r="Y29" s="1"/>
+      <c r="Z29" s="1"/>
+      <c r="AA29" s="1"/>
+      <c r="AB29" s="1"/>
+      <c r="AC29" s="1"/>
+      <c r="AD29" s="1"/>
+      <c r="AE29" s="1"/>
+      <c r="AF29" s="1"/>
+      <c r="AG29" s="1"/>
+      <c r="AH29" s="1"/>
+      <c r="AI29" s="1"/>
+      <c r="AJ29" s="1"/>
+      <c r="AK29" s="1"/>
+      <c r="AL29" s="1"/>
+      <c r="AM29" s="1"/>
+      <c r="AN29" s="1"/>
+      <c r="AO29" s="1"/>
+      <c r="AP29" s="1"/>
+      <c r="AQ29" s="1"/>
+      <c r="AR29" s="1"/>
+      <c r="AS29" s="1"/>
+      <c r="AT29" s="1"/>
+      <c r="AU29" s="1"/>
+      <c r="AV29" s="1"/>
+      <c r="AW29" s="1"/>
+      <c r="AX29" s="1"/>
+      <c r="AY29" s="1"/>
+      <c r="AZ29" s="1"/>
+      <c r="BA29" s="1"/>
+      <c r="BB29" s="1"/>
+      <c r="BC29" s="1"/>
+      <c r="BD29" s="1"/>
+      <c r="BE29" s="1"/>
+      <c r="BF29" s="1"/>
+      <c r="BG29" s="1"/>
+      <c r="BH29" s="1"/>
+      <c r="BI29" s="1"/>
+      <c r="BJ29" s="1"/>
+      <c r="BK29" s="1"/>
+      <c r="BL29" s="238" t="str">
+        <v>O</v>
+      </c>
+      <c r="BM29" s="238" t="str">
+        <v>i</v>
+      </c>
+      <c r="BN29" s="238" t="str">
+        <v>ㆦ</v>
+      </c>
+      <c r="BO29" s="238"/>
+      <c r="BP29" s="238"/>
+      <c r="BX29" s="238">
+        <v>27</v>
+      </c>
+      <c r="BY29" s="238" t="s">
+        <v>528</v>
+      </c>
+      <c r="BZ29" s="238" t="s">
+        <v>196</v>
+      </c>
+      <c r="CA29" s="238" t="s">
+        <v>231</v>
+      </c>
+      <c r="CB29" s="238" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:80" s="237" customFormat="1" outlineLevel="1">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1" t="str">
+        <f xml:space="preserve"> MID(C24, B26+1,  B27-B26-1)</f>
+        <v>ㆠㄅㄆㄇㄉㄊㄋㄌㆣㄍㄎㄫㆡㄗㄘㄙㆢㄐㄑㄒㄏㄚㄧㆨㄨㆤㆦㄜㄞㄠㆩㆪㆫㆥㆧㆮㆯㆬㆭㄣㆰㄢㄤㆱㆲㆴㆵㆻㆷ˫˪ˋˊ八四一ㄥ入ñ</v>
+      </c>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
+      <c r="U30" s="1"/>
+      <c r="V30" s="1"/>
+      <c r="W30" s="1"/>
+      <c r="X30" s="1"/>
+      <c r="Y30" s="1"/>
+      <c r="Z30" s="1"/>
+      <c r="AA30" s="1"/>
+      <c r="AB30" s="1"/>
+      <c r="AC30" s="1"/>
+      <c r="AD30" s="1"/>
+      <c r="AE30" s="1"/>
+      <c r="AF30" s="1"/>
+      <c r="AG30" s="1"/>
+      <c r="AH30" s="1"/>
+      <c r="AI30" s="1"/>
+      <c r="AJ30" s="1"/>
+      <c r="AK30" s="1"/>
+      <c r="AL30" s="1"/>
+      <c r="AM30" s="1"/>
+      <c r="AN30" s="1"/>
+      <c r="AO30" s="1"/>
+      <c r="AP30" s="1"/>
+      <c r="AQ30" s="1"/>
+      <c r="AR30" s="1"/>
+      <c r="AS30" s="1"/>
+      <c r="AT30" s="1"/>
+      <c r="AU30" s="1"/>
+      <c r="AV30" s="1"/>
+      <c r="AW30" s="1"/>
+      <c r="AX30" s="1"/>
+      <c r="AY30" s="1"/>
+      <c r="AZ30" s="1"/>
+      <c r="BA30" s="1"/>
+      <c r="BB30" s="1"/>
+      <c r="BC30" s="1"/>
+      <c r="BD30" s="1"/>
+      <c r="BE30" s="1"/>
+      <c r="BF30" s="1"/>
+      <c r="BG30" s="1"/>
+      <c r="BH30" s="1"/>
+      <c r="BI30" s="1"/>
+      <c r="BJ30" s="1"/>
+      <c r="BK30" s="1"/>
+      <c r="BL30" s="238" t="str">
+        <v>ə</v>
+      </c>
+      <c r="BM30" s="238" t="str">
+        <v>k</v>
+      </c>
+      <c r="BN30" s="238" t="str">
+        <v>ㄜ</v>
+      </c>
+      <c r="BO30" s="238"/>
+      <c r="BP30" s="238"/>
+      <c r="BX30" s="238">
+        <v>28</v>
+      </c>
+      <c r="BY30" s="238" t="s">
+        <v>529</v>
+      </c>
+      <c r="BZ30" s="238" t="s">
+        <v>197</v>
+      </c>
+      <c r="CA30" s="238" t="s">
+        <v>119</v>
+      </c>
+      <c r="CB30" s="238" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="31" spans="1:80" s="237" customFormat="1" outlineLevel="1">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
+      <c r="W31" s="1"/>
+      <c r="X31" s="1"/>
+      <c r="Y31" s="1"/>
+      <c r="Z31" s="1"/>
+      <c r="AA31" s="1"/>
+      <c r="AB31" s="1"/>
+      <c r="AC31" s="1"/>
+      <c r="AD31" s="1"/>
+      <c r="AE31" s="1"/>
+      <c r="AF31" s="1"/>
+      <c r="AG31" s="1"/>
+      <c r="AH31" s="1"/>
+      <c r="AI31" s="1"/>
+      <c r="AJ31" s="1"/>
+      <c r="AK31" s="1"/>
+      <c r="AL31" s="1"/>
+      <c r="AM31" s="1"/>
+      <c r="AN31" s="1"/>
+      <c r="AO31" s="1"/>
+      <c r="AP31" s="1"/>
+      <c r="AQ31" s="1"/>
+      <c r="AR31" s="1"/>
+      <c r="AS31" s="1"/>
+      <c r="AT31" s="1"/>
+      <c r="AU31" s="1"/>
+      <c r="AV31" s="1"/>
+      <c r="AW31" s="1"/>
+      <c r="AX31" s="1"/>
+      <c r="AY31" s="1"/>
+      <c r="AZ31" s="1"/>
+      <c r="BA31" s="1"/>
+      <c r="BB31" s="1"/>
+      <c r="BC31" s="1"/>
+      <c r="BD31" s="1"/>
+      <c r="BE31" s="1"/>
+      <c r="BF31" s="1"/>
+      <c r="BG31" s="1"/>
+      <c r="BH31" s="1"/>
+      <c r="BI31" s="1"/>
+      <c r="BJ31" s="1"/>
+      <c r="BK31" s="1"/>
+      <c r="BL31" s="238" t="str">
+        <v>I</v>
+      </c>
+      <c r="BM31" s="238" t="str">
+        <v>9</v>
+      </c>
+      <c r="BN31" s="238" t="str">
+        <v>ㄞ</v>
+      </c>
+      <c r="BO31" s="238"/>
+      <c r="BP31" s="238"/>
+    </row>
+    <row r="32" spans="1:80" s="237" customFormat="1" outlineLevel="1">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="3">
+        <f xml:space="preserve"> COLUMN() -2</f>
+        <v>1</v>
+      </c>
+      <c r="D32" s="3">
+        <f t="shared" ref="D32:BJ32" si="5" xml:space="preserve"> COLUMN() -2</f>
+        <v>2</v>
+      </c>
+      <c r="E32" s="3">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="G32" s="3">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="H32" s="3">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="I32" s="3">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="J32" s="3">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="L32" s="3">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="M32" s="3">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="N32" s="3">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="O32" s="3">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="P32" s="3">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="Q32" s="3">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="R32" s="3">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="S32" s="3">
+        <f t="shared" si="5"/>
+        <v>17</v>
+      </c>
+      <c r="T32" s="3">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="U32" s="3">
+        <f t="shared" si="5"/>
+        <v>19</v>
+      </c>
+      <c r="V32" s="3">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="W32" s="3">
+        <f t="shared" si="5"/>
+        <v>21</v>
+      </c>
+      <c r="X32" s="3">
+        <f t="shared" si="5"/>
+        <v>22</v>
+      </c>
+      <c r="Y32" s="3">
+        <f t="shared" si="5"/>
+        <v>23</v>
+      </c>
+      <c r="Z32" s="3">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="AA32" s="3">
+        <f t="shared" si="5"/>
+        <v>25</v>
+      </c>
+      <c r="AB32" s="3">
+        <f t="shared" si="5"/>
+        <v>26</v>
+      </c>
+      <c r="AC32" s="3">
+        <f t="shared" si="5"/>
+        <v>27</v>
+      </c>
+      <c r="AD32" s="3">
+        <f t="shared" si="5"/>
+        <v>28</v>
+      </c>
+      <c r="AE32" s="3">
+        <f t="shared" si="5"/>
+        <v>29</v>
+      </c>
+      <c r="AF32" s="3">
+        <f t="shared" si="5"/>
+        <v>30</v>
+      </c>
+      <c r="AG32" s="3">
+        <f t="shared" si="5"/>
+        <v>31</v>
+      </c>
+      <c r="AH32" s="3">
+        <f t="shared" si="5"/>
+        <v>32</v>
+      </c>
+      <c r="AI32" s="3">
+        <f t="shared" si="5"/>
+        <v>33</v>
+      </c>
+      <c r="AJ32" s="3">
+        <f t="shared" si="5"/>
+        <v>34</v>
+      </c>
+      <c r="AK32" s="3">
+        <f t="shared" si="5"/>
+        <v>35</v>
+      </c>
+      <c r="AL32" s="3">
+        <f t="shared" si="5"/>
+        <v>36</v>
+      </c>
+      <c r="AM32" s="3">
+        <f t="shared" si="5"/>
+        <v>37</v>
+      </c>
+      <c r="AN32" s="3">
+        <f t="shared" si="5"/>
+        <v>38</v>
+      </c>
+      <c r="AO32" s="3">
+        <f t="shared" si="5"/>
+        <v>39</v>
+      </c>
+      <c r="AP32" s="3">
+        <f t="shared" si="5"/>
+        <v>40</v>
+      </c>
+      <c r="AQ32" s="3">
+        <f t="shared" si="5"/>
+        <v>41</v>
+      </c>
+      <c r="AR32" s="3">
+        <f t="shared" si="5"/>
+        <v>42</v>
+      </c>
+      <c r="AS32" s="3">
+        <f t="shared" si="5"/>
+        <v>43</v>
+      </c>
+      <c r="AT32" s="3">
+        <f t="shared" si="5"/>
+        <v>44</v>
+      </c>
+      <c r="AU32" s="3">
+        <f t="shared" si="5"/>
+        <v>45</v>
+      </c>
+      <c r="AV32" s="3">
+        <f t="shared" si="5"/>
+        <v>46</v>
+      </c>
+      <c r="AW32" s="3">
+        <f t="shared" si="5"/>
+        <v>47</v>
+      </c>
+      <c r="AX32" s="3">
+        <f t="shared" si="5"/>
+        <v>48</v>
+      </c>
+      <c r="AY32" s="3">
+        <f t="shared" si="5"/>
+        <v>49</v>
+      </c>
+      <c r="AZ32" s="3">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="BA32" s="3">
+        <f t="shared" si="5"/>
+        <v>51</v>
+      </c>
+      <c r="BB32" s="3">
+        <f t="shared" si="5"/>
+        <v>52</v>
+      </c>
+      <c r="BC32" s="3">
+        <f t="shared" si="5"/>
+        <v>53</v>
+      </c>
+      <c r="BD32" s="3">
+        <f t="shared" si="5"/>
+        <v>54</v>
+      </c>
+      <c r="BE32" s="3">
+        <f t="shared" si="5"/>
+        <v>55</v>
+      </c>
+      <c r="BF32" s="3">
+        <f t="shared" si="5"/>
+        <v>56</v>
+      </c>
+      <c r="BG32" s="3">
+        <f t="shared" si="5"/>
+        <v>57</v>
+      </c>
+      <c r="BH32" s="3">
+        <f t="shared" si="5"/>
+        <v>58</v>
+      </c>
+      <c r="BI32" s="3">
+        <f t="shared" si="5"/>
+        <v>59</v>
+      </c>
+      <c r="BJ32" s="3">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="BK32" s="1"/>
+      <c r="BL32" s="238" t="str">
+        <v>U</v>
+      </c>
+      <c r="BM32" s="238" t="str">
+        <v>l</v>
+      </c>
+      <c r="BN32" s="238" t="str">
+        <v>ㄠ</v>
+      </c>
+      <c r="BO32" s="238"/>
+      <c r="BP32" s="238"/>
+    </row>
+    <row r="33" spans="1:68" s="237" customFormat="1" outlineLevel="1">
+      <c r="A33" s="244" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="C33" s="4" t="str">
+        <f xml:space="preserve"> MID($C$29,C$32,1)</f>
+        <v>!</v>
+      </c>
+      <c r="D33" s="4" t="str">
+        <f t="shared" ref="D33:BJ33" si="6" xml:space="preserve"> MID($C$29,D$32,1)</f>
+        <v>1</v>
+      </c>
+      <c r="E33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>q</v>
+      </c>
+      <c r="F33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>a</v>
+      </c>
+      <c r="G33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>w</v>
+      </c>
+      <c r="I33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>s</v>
+      </c>
+      <c r="J33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>x</v>
+      </c>
+      <c r="K33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>E</v>
+      </c>
+      <c r="L33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>e</v>
+      </c>
+      <c r="M33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>d</v>
+      </c>
+      <c r="N33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>G</v>
+      </c>
+      <c r="O33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>Y</v>
+      </c>
+      <c r="P33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>y</v>
+      </c>
+      <c r="Q33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>h</v>
+      </c>
+      <c r="R33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>n</v>
+      </c>
+      <c r="S33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>R</v>
+      </c>
+      <c r="T33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>r</v>
+      </c>
+      <c r="U33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>f</v>
+      </c>
+      <c r="V33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>v</v>
+      </c>
+      <c r="W33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>c</v>
+      </c>
+      <c r="X33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="Y33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>u</v>
+      </c>
+      <c r="Z33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>K</v>
+      </c>
+      <c r="AA33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>j</v>
+      </c>
+      <c r="AB33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>,</v>
+      </c>
+      <c r="AC33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>i</v>
+      </c>
+      <c r="AD33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>k</v>
+      </c>
+      <c r="AE33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="AF33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>l</v>
+      </c>
+      <c r="AG33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>*</v>
+      </c>
+      <c r="AH33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>U</v>
+      </c>
+      <c r="AI33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>J</v>
+      </c>
+      <c r="AJ33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;</v>
+      </c>
+      <c r="AK33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>I</v>
+      </c>
+      <c r="AL33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>(</v>
+      </c>
+      <c r="AM33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>L</v>
+      </c>
+      <c r="AN33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>m</v>
+      </c>
+      <c r="AO33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>/</v>
+      </c>
+      <c r="AP33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>p</v>
+      </c>
+      <c r="AQ33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>M</v>
+      </c>
+      <c r="AR33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AS33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>;</v>
+      </c>
+      <c r="AT33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>O</v>
+      </c>
+      <c r="AU33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>o</v>
+      </c>
+      <c r="AV33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>b</v>
+      </c>
+      <c r="AW33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>t</v>
+      </c>
+      <c r="AX33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>g</v>
+      </c>
+      <c r="AY33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>z</v>
+      </c>
+      <c r="AZ33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="BA33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="BB33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="BC33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="BD33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="BE33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>]</v>
+      </c>
+      <c r="BF33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>[</v>
+      </c>
+      <c r="BG33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>N</v>
+      </c>
+      <c r="BH33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>.</v>
+      </c>
+      <c r="BI33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>-</v>
+      </c>
+      <c r="BJ33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="BK33" s="1"/>
+      <c r="BL33" s="238" t="str">
+        <v>D</v>
+      </c>
+      <c r="BM33" s="238" t="str">
+        <v>*</v>
+      </c>
+      <c r="BN33" s="238" t="str">
+        <v>ㆩ</v>
+      </c>
+      <c r="BO33" s="238"/>
+      <c r="BP33" s="238"/>
+    </row>
+    <row r="34" spans="1:68" s="237" customFormat="1" outlineLevel="1">
+      <c r="A34" s="243" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="242" t="str">
+        <f xml:space="preserve"> MID($C$30,C$32,1)</f>
+        <v>ㆠ</v>
+      </c>
+      <c r="D34" s="242" t="str">
+        <f t="shared" ref="D34:BJ34" si="7" xml:space="preserve"> MID($C$30,D$32,1)</f>
+        <v>ㄅ</v>
+      </c>
+      <c r="E34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄆ</v>
+      </c>
+      <c r="F34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄇ</v>
+      </c>
+      <c r="G34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄉ</v>
+      </c>
+      <c r="H34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄊ</v>
+      </c>
+      <c r="I34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄋ</v>
+      </c>
+      <c r="J34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄌ</v>
+      </c>
+      <c r="K34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆣ</v>
+      </c>
+      <c r="L34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄍ</v>
+      </c>
+      <c r="M34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄎ</v>
+      </c>
+      <c r="N34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄫ</v>
+      </c>
+      <c r="O34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆡ</v>
+      </c>
+      <c r="P34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄗ</v>
+      </c>
+      <c r="Q34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄘ</v>
+      </c>
+      <c r="R34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄙ</v>
+      </c>
+      <c r="S34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆢ</v>
+      </c>
+      <c r="T34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄐ</v>
+      </c>
+      <c r="U34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄑ</v>
+      </c>
+      <c r="V34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄒ</v>
+      </c>
+      <c r="W34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄏ</v>
+      </c>
+      <c r="X34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄚ</v>
+      </c>
+      <c r="Y34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧ</v>
+      </c>
+      <c r="Z34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆨ</v>
+      </c>
+      <c r="AA34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄨ</v>
+      </c>
+      <c r="AB34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆤ</v>
+      </c>
+      <c r="AC34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆦ</v>
+      </c>
+      <c r="AD34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄜ</v>
+      </c>
+      <c r="AE34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄞ</v>
+      </c>
+      <c r="AF34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄠ</v>
+      </c>
+      <c r="AG34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆩ</v>
+      </c>
+      <c r="AH34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆪ</v>
+      </c>
+      <c r="AI34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆫ</v>
+      </c>
+      <c r="AJ34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆥ</v>
+      </c>
+      <c r="AK34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆧ</v>
+      </c>
+      <c r="AL34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆮ</v>
+      </c>
+      <c r="AM34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆯ</v>
+      </c>
+      <c r="AN34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆬ</v>
+      </c>
+      <c r="AO34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆭ</v>
+      </c>
+      <c r="AP34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄣ</v>
+      </c>
+      <c r="AQ34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆰ</v>
+      </c>
+      <c r="AR34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄢ</v>
+      </c>
+      <c r="AS34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄤ</v>
+      </c>
+      <c r="AT34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆱ</v>
+      </c>
+      <c r="AU34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆲ</v>
+      </c>
+      <c r="AV34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆴ</v>
+      </c>
+      <c r="AW34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆵ</v>
+      </c>
+      <c r="AX34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆻ</v>
+      </c>
+      <c r="AY34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆷ</v>
+      </c>
+      <c r="AZ34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>˫</v>
+      </c>
+      <c r="BA34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>˪</v>
+      </c>
+      <c r="BB34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ˋ</v>
+      </c>
+      <c r="BC34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ˊ</v>
+      </c>
+      <c r="BD34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>八</v>
+      </c>
+      <c r="BE34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>四</v>
+      </c>
+      <c r="BF34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>一</v>
+      </c>
+      <c r="BG34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄥ</v>
+      </c>
+      <c r="BH34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>入</v>
+      </c>
+      <c r="BI34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v>ñ</v>
+      </c>
+      <c r="BJ34" s="242" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="BK34" s="1"/>
+      <c r="BL34" s="238" t="str">
+        <v>f</v>
+      </c>
+      <c r="BM34" s="238" t="str">
+        <v>U</v>
+      </c>
+      <c r="BN34" s="238" t="str">
+        <v>ㆪ</v>
+      </c>
+      <c r="BO34" s="238"/>
+      <c r="BP34" s="238"/>
+    </row>
+    <row r="35" spans="1:68" s="237" customFormat="1" outlineLevel="1">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
+      <c r="U35" s="1"/>
+      <c r="V35" s="1"/>
+      <c r="W35" s="1"/>
+      <c r="X35" s="1"/>
+      <c r="Y35" s="1"/>
+      <c r="Z35" s="1"/>
+      <c r="AA35" s="1"/>
+      <c r="AB35" s="1"/>
+      <c r="AC35" s="1"/>
+      <c r="AD35" s="1"/>
+      <c r="AE35" s="1"/>
+      <c r="AF35" s="1"/>
+      <c r="AG35" s="1"/>
+      <c r="AH35" s="1"/>
+      <c r="AI35" s="1"/>
+      <c r="AJ35" s="1"/>
+      <c r="AK35" s="1"/>
+      <c r="AL35" s="1"/>
+      <c r="AM35" s="1"/>
+      <c r="AN35" s="1"/>
+      <c r="AO35" s="1"/>
+      <c r="AP35" s="1"/>
+      <c r="AQ35" s="1"/>
+      <c r="AR35" s="1"/>
+      <c r="AS35" s="1"/>
+      <c r="AT35" s="1"/>
+      <c r="AU35" s="1"/>
+      <c r="AV35" s="1"/>
+      <c r="AW35" s="1"/>
+      <c r="AX35" s="1"/>
+      <c r="AY35" s="1"/>
+      <c r="AZ35" s="1"/>
+      <c r="BA35" s="1"/>
+      <c r="BB35" s="1"/>
+      <c r="BC35" s="1"/>
+      <c r="BD35" s="1"/>
+      <c r="BE35" s="1"/>
+      <c r="BF35" s="1"/>
+      <c r="BG35" s="1"/>
+      <c r="BH35" s="1"/>
+      <c r="BI35" s="1"/>
+      <c r="BJ35" s="1"/>
+      <c r="BK35" s="1"/>
+      <c r="BL35" s="238" t="str">
+        <v>q</v>
+      </c>
+      <c r="BM35" s="238" t="str">
+        <v>J</v>
+      </c>
+      <c r="BN35" s="238" t="str">
+        <v>ㆫ</v>
+      </c>
+      <c r="BO35" s="238"/>
+      <c r="BP35" s="238"/>
+    </row>
+    <row r="36" spans="1:68" s="237" customFormat="1">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+      <c r="V36" s="1"/>
+      <c r="W36" s="1"/>
+      <c r="X36" s="1"/>
+      <c r="Y36" s="1"/>
+      <c r="Z36" s="1"/>
+      <c r="AA36" s="1"/>
+      <c r="AB36" s="1"/>
+      <c r="AC36" s="1"/>
+      <c r="AD36" s="1"/>
+      <c r="AE36" s="1"/>
+      <c r="AF36" s="1"/>
+      <c r="AG36" s="1"/>
+      <c r="AH36" s="1"/>
+      <c r="AI36" s="1"/>
+      <c r="AJ36" s="1"/>
+      <c r="AK36" s="1"/>
+      <c r="AL36" s="1"/>
+      <c r="AM36" s="1"/>
+      <c r="AN36" s="1"/>
+      <c r="AO36" s="1"/>
+      <c r="AP36" s="1"/>
+      <c r="AQ36" s="1"/>
+      <c r="AR36" s="1"/>
+      <c r="AS36" s="1"/>
+      <c r="AT36" s="1"/>
+      <c r="AU36" s="1"/>
+      <c r="AV36" s="1"/>
+      <c r="AW36" s="1"/>
+      <c r="AX36" s="1"/>
+      <c r="AY36" s="1"/>
+      <c r="AZ36" s="1"/>
+      <c r="BA36" s="1"/>
+      <c r="BB36" s="1"/>
+      <c r="BC36" s="1"/>
+      <c r="BD36" s="1"/>
+      <c r="BE36" s="1"/>
+      <c r="BF36" s="1"/>
+      <c r="BG36" s="1"/>
+      <c r="BH36" s="1"/>
+      <c r="BI36" s="1"/>
+      <c r="BJ36" s="1"/>
+      <c r="BK36" s="1"/>
+      <c r="BL36" s="238" t="str">
+        <v>r</v>
+      </c>
+      <c r="BM36" s="238" t="str">
+        <v>&lt;</v>
+      </c>
+      <c r="BN36" s="238" t="str">
+        <v>ㆥ</v>
+      </c>
+      <c r="BO36" s="238"/>
+      <c r="BP36" s="238"/>
+    </row>
+    <row r="37" spans="1:68" s="234" customFormat="1">
+      <c r="C37" s="251">
+        <f xml:space="preserve"> COLUMN() -2</f>
+        <v>1</v>
+      </c>
+      <c r="D37" s="251">
+        <f t="shared" ref="D37:BJ37" si="8" xml:space="preserve"> COLUMN() -2</f>
+        <v>2</v>
+      </c>
+      <c r="E37" s="251">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="F37" s="251">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="G37" s="251">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="H37" s="251">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+      <c r="I37" s="251">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+      <c r="J37" s="251">
+        <f t="shared" si="8"/>
+        <v>8</v>
+      </c>
+      <c r="K37" s="251">
+        <f t="shared" si="8"/>
+        <v>9</v>
+      </c>
+      <c r="L37" s="251">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="M37" s="251">
+        <f t="shared" si="8"/>
+        <v>11</v>
+      </c>
+      <c r="N37" s="251">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="O37" s="251">
+        <f t="shared" si="8"/>
+        <v>13</v>
+      </c>
+      <c r="P37" s="251">
+        <f t="shared" si="8"/>
+        <v>14</v>
+      </c>
+      <c r="Q37" s="251">
+        <f t="shared" si="8"/>
+        <v>15</v>
+      </c>
+      <c r="R37" s="251">
+        <f t="shared" si="8"/>
+        <v>16</v>
+      </c>
+      <c r="S37" s="251">
+        <f t="shared" si="8"/>
+        <v>17</v>
+      </c>
+      <c r="T37" s="251">
+        <f t="shared" si="8"/>
+        <v>18</v>
+      </c>
+      <c r="U37" s="251">
+        <f t="shared" si="8"/>
+        <v>19</v>
+      </c>
+      <c r="V37" s="251">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="W37" s="251">
+        <f t="shared" si="8"/>
+        <v>21</v>
+      </c>
+      <c r="X37" s="251">
+        <f t="shared" si="8"/>
+        <v>22</v>
+      </c>
+      <c r="Y37" s="251">
+        <f t="shared" si="8"/>
+        <v>23</v>
+      </c>
+      <c r="Z37" s="251">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="AA37" s="251">
+        <f t="shared" si="8"/>
+        <v>25</v>
+      </c>
+      <c r="AB37" s="251">
+        <f t="shared" si="8"/>
+        <v>26</v>
+      </c>
+      <c r="AC37" s="251">
+        <f t="shared" si="8"/>
+        <v>27</v>
+      </c>
+      <c r="AD37" s="251">
+        <f t="shared" si="8"/>
+        <v>28</v>
+      </c>
+      <c r="AE37" s="251">
+        <f t="shared" si="8"/>
+        <v>29</v>
+      </c>
+      <c r="AF37" s="251">
+        <f t="shared" si="8"/>
+        <v>30</v>
+      </c>
+      <c r="AG37" s="251">
+        <f t="shared" si="8"/>
+        <v>31</v>
+      </c>
+      <c r="AH37" s="251">
+        <f t="shared" si="8"/>
+        <v>32</v>
+      </c>
+      <c r="AI37" s="251">
+        <f t="shared" si="8"/>
+        <v>33</v>
+      </c>
+      <c r="AJ37" s="251">
+        <f t="shared" si="8"/>
+        <v>34</v>
+      </c>
+      <c r="AK37" s="251">
+        <f t="shared" si="8"/>
+        <v>35</v>
+      </c>
+      <c r="AL37" s="251">
+        <f t="shared" si="8"/>
+        <v>36</v>
+      </c>
+      <c r="AM37" s="251">
+        <f t="shared" si="8"/>
+        <v>37</v>
+      </c>
+      <c r="AN37" s="251">
+        <f t="shared" si="8"/>
+        <v>38</v>
+      </c>
+      <c r="AO37" s="251">
+        <f t="shared" si="8"/>
+        <v>39</v>
+      </c>
+      <c r="AP37" s="251">
+        <f t="shared" si="8"/>
+        <v>40</v>
+      </c>
+      <c r="AQ37" s="251">
+        <f t="shared" si="8"/>
+        <v>41</v>
+      </c>
+      <c r="AR37" s="251">
+        <f t="shared" si="8"/>
+        <v>42</v>
+      </c>
+      <c r="AS37" s="251">
+        <f t="shared" si="8"/>
+        <v>43</v>
+      </c>
+      <c r="AT37" s="251">
+        <f t="shared" si="8"/>
+        <v>44</v>
+      </c>
+      <c r="AU37" s="251">
+        <f t="shared" si="8"/>
+        <v>45</v>
+      </c>
+      <c r="AV37" s="251">
+        <f t="shared" si="8"/>
+        <v>46</v>
+      </c>
+      <c r="AW37" s="251">
+        <f t="shared" si="8"/>
+        <v>47</v>
+      </c>
+      <c r="AX37" s="251">
+        <f t="shared" si="8"/>
+        <v>48</v>
+      </c>
+      <c r="AY37" s="251">
+        <f t="shared" si="8"/>
+        <v>49</v>
+      </c>
+      <c r="AZ37" s="251">
+        <f t="shared" si="8"/>
+        <v>50</v>
+      </c>
+      <c r="BA37" s="251">
+        <f t="shared" si="8"/>
+        <v>51</v>
+      </c>
+      <c r="BB37" s="251">
+        <f t="shared" si="8"/>
+        <v>52</v>
+      </c>
+      <c r="BC37" s="251">
+        <f t="shared" si="8"/>
+        <v>53</v>
+      </c>
+      <c r="BD37" s="251">
+        <f t="shared" si="8"/>
+        <v>54</v>
+      </c>
+      <c r="BE37" s="251">
+        <f t="shared" si="8"/>
+        <v>55</v>
+      </c>
+      <c r="BF37" s="251">
+        <f t="shared" si="8"/>
+        <v>56</v>
+      </c>
+      <c r="BG37" s="251">
+        <f t="shared" si="8"/>
+        <v>57</v>
+      </c>
+      <c r="BH37" s="251">
+        <f t="shared" si="8"/>
+        <v>58</v>
+      </c>
+      <c r="BI37" s="251">
+        <f t="shared" si="8"/>
+        <v>59</v>
+      </c>
+      <c r="BJ37" s="251">
+        <f t="shared" si="8"/>
+        <v>60</v>
+      </c>
+      <c r="BL37" s="7" t="str">
+        <v>v</v>
+      </c>
+      <c r="BM37" s="7" t="str">
+        <v>I</v>
+      </c>
+      <c r="BN37" s="7" t="str">
+        <v>ㆧ</v>
+      </c>
+      <c r="BO37" s="7"/>
+      <c r="BP37" s="7"/>
+    </row>
+    <row r="38" spans="1:68" s="237" customFormat="1">
+      <c r="A38" s="248" t="s">
+        <v>573</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="249" t="s">
+        <v>243</v>
+      </c>
+      <c r="D38" s="249" t="s">
+        <v>242</v>
+      </c>
+      <c r="E38" s="249" t="s">
+        <v>244</v>
+      </c>
+      <c r="F38" s="249" t="s">
+        <v>245</v>
+      </c>
+      <c r="G38" s="249" t="s">
+        <v>246</v>
+      </c>
+      <c r="H38" s="249" t="s">
+        <v>95</v>
+      </c>
+      <c r="I38" s="249" t="s">
+        <v>247</v>
+      </c>
+      <c r="J38" s="249" t="s">
+        <v>248</v>
+      </c>
+      <c r="K38" s="249" t="s">
+        <v>530</v>
+      </c>
+      <c r="L38" s="249" t="s">
+        <v>279</v>
+      </c>
+      <c r="M38" s="249" t="s">
+        <v>280</v>
+      </c>
+      <c r="N38" s="249" t="s">
+        <v>249</v>
+      </c>
+      <c r="O38" s="249" t="s">
+        <v>250</v>
+      </c>
+      <c r="P38" s="249" t="s">
+        <v>538</v>
+      </c>
+      <c r="Q38" s="249" t="s">
+        <v>539</v>
+      </c>
+      <c r="R38" s="249" t="s">
+        <v>251</v>
+      </c>
+      <c r="S38" s="249" t="s">
+        <v>253</v>
+      </c>
+      <c r="T38" s="249" t="s">
+        <v>540</v>
+      </c>
+      <c r="U38" s="249" t="s">
+        <v>541</v>
+      </c>
+      <c r="V38" s="249" t="s">
+        <v>256</v>
+      </c>
+      <c r="W38" s="249" t="s">
+        <v>252</v>
+      </c>
+      <c r="X38" s="249" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y38" s="249" t="s">
+        <v>258</v>
+      </c>
+      <c r="Z38" s="249" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA38" s="249" t="s">
+        <v>260</v>
+      </c>
+      <c r="AB38" s="249" t="s">
+        <v>261</v>
+      </c>
+      <c r="AC38" s="249" t="s">
+        <v>262</v>
+      </c>
+      <c r="AD38" s="249" t="s">
+        <v>263</v>
+      </c>
+      <c r="AE38" s="250" t="s">
+        <v>270</v>
+      </c>
+      <c r="AF38" s="250" t="s">
+        <v>271</v>
+      </c>
+      <c r="AG38" s="250" t="s">
+        <v>542</v>
+      </c>
+      <c r="AH38" s="250" t="s">
+        <v>543</v>
+      </c>
+      <c r="AI38" s="250" t="s">
+        <v>544</v>
+      </c>
+      <c r="AJ38" s="250" t="s">
+        <v>545</v>
+      </c>
+      <c r="AK38" s="250" t="s">
+        <v>546</v>
+      </c>
+      <c r="AL38" s="249" t="s">
+        <v>547</v>
+      </c>
+      <c r="AM38" s="249" t="s">
+        <v>548</v>
+      </c>
+      <c r="AN38" s="250" t="s">
+        <v>264</v>
+      </c>
+      <c r="AO38" s="250" t="s">
+        <v>265</v>
+      </c>
+      <c r="AP38" s="250" t="s">
+        <v>110</v>
+      </c>
+      <c r="AQ38" s="249" t="s">
+        <v>272</v>
+      </c>
+      <c r="AR38" s="249" t="s">
+        <v>273</v>
+      </c>
+      <c r="AS38" s="249" t="s">
+        <v>274</v>
+      </c>
+      <c r="AT38" s="249" t="s">
+        <v>275</v>
+      </c>
+      <c r="AU38" s="249" t="s">
+        <v>276</v>
+      </c>
+      <c r="AV38" s="250" t="s">
+        <v>266</v>
+      </c>
+      <c r="AW38" s="250" t="s">
+        <v>267</v>
+      </c>
+      <c r="AX38" s="250" t="s">
+        <v>268</v>
+      </c>
+      <c r="AY38" s="250" t="s">
+        <v>269</v>
+      </c>
+      <c r="AZ38" s="249" t="s">
+        <v>570</v>
+      </c>
+      <c r="BA38" s="249" t="s">
+        <v>482</v>
+      </c>
+      <c r="BB38" s="249">
+        <v>1</v>
+      </c>
+      <c r="BC38" s="249">
+        <v>7</v>
+      </c>
+      <c r="BD38" s="249">
+        <v>3</v>
+      </c>
+      <c r="BE38" s="249">
+        <v>2</v>
+      </c>
+      <c r="BF38" s="249">
+        <v>5</v>
+      </c>
+      <c r="BG38" s="249">
+        <v>8</v>
+      </c>
+      <c r="BH38" s="249">
+        <v>4</v>
+      </c>
+      <c r="BI38" s="249"/>
+      <c r="BJ38" s="249"/>
+      <c r="BK38" s="1"/>
+      <c r="BL38" s="238" t="str">
+        <v>x</v>
+      </c>
+      <c r="BM38" s="238" t="str">
+        <v>(</v>
+      </c>
+      <c r="BN38" s="238" t="str">
+        <v>ㆮ</v>
+      </c>
+      <c r="BO38" s="238"/>
+      <c r="BP38" s="238"/>
+    </row>
+    <row r="39" spans="1:68" s="237" customFormat="1">
+      <c r="A39" s="244" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="4" t="str">
+        <f>C18</f>
+        <v>B</v>
+      </c>
+      <c r="D39" s="4" t="str">
+        <f t="shared" ref="D39:AY39" si="9">D18</f>
+        <v>b</v>
+      </c>
+      <c r="E39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>p</v>
+      </c>
+      <c r="F39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>m</v>
+      </c>
+      <c r="G39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>d</v>
+      </c>
+      <c r="H39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>t</v>
+      </c>
+      <c r="I39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>n</v>
+      </c>
+      <c r="J39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>l</v>
+      </c>
+      <c r="K39" s="252" t="s">
+        <v>549</v>
+      </c>
+      <c r="L39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>g</v>
+      </c>
+      <c r="M39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>k</v>
+      </c>
+      <c r="N39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>ŋ</v>
+      </c>
+      <c r="O39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>Z</v>
+      </c>
+      <c r="P39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>z</v>
+      </c>
+      <c r="Q39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>c</v>
+      </c>
+      <c r="R39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>s</v>
+      </c>
+      <c r="S39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>J</v>
+      </c>
+      <c r="T39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>j</v>
+      </c>
+      <c r="U39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>C</v>
+      </c>
+      <c r="V39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>S</v>
+      </c>
+      <c r="W39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>h</v>
+      </c>
+      <c r="X39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>a</v>
+      </c>
+      <c r="Y39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>i</v>
+      </c>
+      <c r="Z39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>w</v>
+      </c>
+      <c r="AA39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>u</v>
+      </c>
+      <c r="AB39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>e</v>
+      </c>
+      <c r="AC39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>O</v>
+      </c>
+      <c r="AD39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>ə</v>
+      </c>
+      <c r="AE39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>I</v>
+      </c>
+      <c r="AF39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>U</v>
+      </c>
+      <c r="AG39" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="AH39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>f</v>
+      </c>
+      <c r="AI39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>q</v>
+      </c>
+      <c r="AJ39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>r</v>
+      </c>
+      <c r="AK39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>v</v>
+      </c>
+      <c r="AL39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>x</v>
+      </c>
+      <c r="AM39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>y</v>
+      </c>
+      <c r="AN39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>M</v>
+      </c>
+      <c r="AO39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>G</v>
+      </c>
+      <c r="AP39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>N</v>
+      </c>
+      <c r="AQ39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="AR39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>@</v>
+      </c>
+      <c r="AS39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>A</v>
+      </c>
+      <c r="AT39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>W</v>
+      </c>
+      <c r="AU39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>H</v>
+      </c>
+      <c r="AV39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>R</v>
+      </c>
+      <c r="AW39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>F</v>
+      </c>
+      <c r="AX39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>Q</v>
+      </c>
+      <c r="AY39" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v>V</v>
+      </c>
+      <c r="AZ39" s="4" t="str">
+        <f>BG18</f>
+        <v>L</v>
+      </c>
+      <c r="BA39" s="4" t="str">
+        <f>BH18</f>
+        <v>&amp;</v>
+      </c>
+      <c r="BB39" s="4" t="str">
+        <f>BF18</f>
+        <v>1</v>
+      </c>
+      <c r="BC39" s="4" t="str">
+        <f t="shared" ref="BC39:BH39" si="10">AZ18</f>
+        <v>7</v>
+      </c>
+      <c r="BD39" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="BE39" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="BF39" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>5</v>
+      </c>
+      <c r="BG39" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>8</v>
+      </c>
+      <c r="BH39" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="BI39" s="4"/>
+      <c r="BJ39" s="4" t="str">
+        <f>BJ18</f>
+        <v/>
+      </c>
+      <c r="BK39" s="1"/>
+      <c r="BL39" s="238" t="str">
+        <v>y</v>
+      </c>
+      <c r="BM39" s="238" t="str">
+        <v>L</v>
+      </c>
+      <c r="BN39" s="238" t="str">
+        <v>ㆯ</v>
+      </c>
+      <c r="BO39" s="238"/>
+      <c r="BP39" s="238"/>
+    </row>
+    <row r="40" spans="1:68" s="237" customFormat="1">
+      <c r="A40" s="245" t="s">
+        <v>64</v>
+      </c>
+      <c r="B40" s="246"/>
+      <c r="C40" s="247" t="str">
+        <f>C19</f>
+        <v>!</v>
+      </c>
+      <c r="D40" s="247" t="str">
+        <f t="shared" ref="D40:AY40" si="11">D19</f>
+        <v>1</v>
+      </c>
+      <c r="E40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>q</v>
+      </c>
+      <c r="F40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>a</v>
+      </c>
+      <c r="G40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="H40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>w</v>
+      </c>
+      <c r="I40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>s</v>
+      </c>
+      <c r="J40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>x</v>
+      </c>
+      <c r="K40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>E</v>
+      </c>
+      <c r="L40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>e</v>
+      </c>
+      <c r="M40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>d</v>
+      </c>
+      <c r="N40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>G</v>
+      </c>
+      <c r="O40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>Y</v>
+      </c>
+      <c r="P40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>y</v>
+      </c>
+      <c r="Q40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>h</v>
+      </c>
+      <c r="R40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>n</v>
+      </c>
+      <c r="S40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>R</v>
+      </c>
+      <c r="T40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>r</v>
+      </c>
+      <c r="U40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>f</v>
+      </c>
+      <c r="V40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>v</v>
+      </c>
+      <c r="W40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>c</v>
+      </c>
+      <c r="X40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>8</v>
+      </c>
+      <c r="Y40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>u</v>
+      </c>
+      <c r="Z40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>K</v>
+      </c>
+      <c r="AA40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>j</v>
+      </c>
+      <c r="AB40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>,</v>
+      </c>
+      <c r="AC40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>i</v>
+      </c>
+      <c r="AD40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>k</v>
+      </c>
+      <c r="AE40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>9</v>
+      </c>
+      <c r="AF40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>l</v>
+      </c>
+      <c r="AG40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>*</v>
+      </c>
+      <c r="AH40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>U</v>
+      </c>
+      <c r="AI40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>J</v>
+      </c>
+      <c r="AJ40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>&lt;</v>
+      </c>
+      <c r="AK40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>I</v>
+      </c>
+      <c r="AL40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>(</v>
+      </c>
+      <c r="AM40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>L</v>
+      </c>
+      <c r="AN40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>m</v>
+      </c>
+      <c r="AO40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>/</v>
+      </c>
+      <c r="AP40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>p</v>
+      </c>
+      <c r="AQ40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>M</v>
+      </c>
+      <c r="AR40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AS40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>;</v>
+      </c>
+      <c r="AT40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>O</v>
+      </c>
+      <c r="AU40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>o</v>
+      </c>
+      <c r="AV40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>b</v>
+      </c>
+      <c r="AW40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>t</v>
+      </c>
+      <c r="AX40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>g</v>
+      </c>
+      <c r="AY40" s="247" t="str">
+        <f t="shared" si="11"/>
+        <v>z</v>
+      </c>
+      <c r="AZ40" s="247" t="s">
+        <v>569</v>
+      </c>
+      <c r="BA40" s="247" t="str">
+        <f>BH19</f>
+        <v>.</v>
+      </c>
+      <c r="BB40" s="247" t="s">
+        <v>560</v>
+      </c>
+      <c r="BC40" s="247" t="str">
+        <f>AZ19</f>
+        <v>5</v>
+      </c>
+      <c r="BD40" s="247" t="str">
+        <f>BA19</f>
+        <v>3</v>
+      </c>
+      <c r="BE40" s="247" t="str">
+        <f>BB19</f>
+        <v>4</v>
+      </c>
+      <c r="BF40" s="247" t="str">
+        <f>BC19</f>
+        <v>6</v>
+      </c>
+      <c r="BG40" s="247" t="s">
+        <v>293</v>
+      </c>
+      <c r="BH40" s="247" t="s">
+        <v>314</v>
+      </c>
+      <c r="BI40" s="247"/>
+      <c r="BJ40" s="247" t="str">
+        <f>BJ19</f>
+        <v/>
+      </c>
+      <c r="BK40" s="1"/>
+      <c r="BL40" s="238" t="str">
+        <v>M</v>
+      </c>
+      <c r="BM40" s="238" t="str">
+        <v>m</v>
+      </c>
+      <c r="BN40" s="238" t="str">
+        <v>ㆬ</v>
+      </c>
+      <c r="BO40" s="238"/>
+      <c r="BP40" s="238"/>
+    </row>
+    <row r="41" spans="1:68" s="237" customFormat="1">
+      <c r="A41" s="243" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" s="1"/>
+      <c r="C41" s="242" t="str">
+        <f>C34</f>
+        <v>ㆠ</v>
+      </c>
+      <c r="D41" s="242" t="str">
+        <f t="shared" ref="D41:AY41" si="12">D34</f>
+        <v>ㄅ</v>
+      </c>
+      <c r="E41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄆ</v>
+      </c>
+      <c r="F41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄇ</v>
+      </c>
+      <c r="G41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄉ</v>
+      </c>
+      <c r="H41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄊ</v>
+      </c>
+      <c r="I41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄋ</v>
+      </c>
+      <c r="J41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄌ</v>
+      </c>
+      <c r="K41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㆣ</v>
+      </c>
+      <c r="L41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄍ</v>
+      </c>
+      <c r="M41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄎ</v>
+      </c>
+      <c r="N41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄫ</v>
+      </c>
+      <c r="O41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㆡ</v>
+      </c>
+      <c r="P41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄗ</v>
+      </c>
+      <c r="Q41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄘ</v>
+      </c>
+      <c r="R41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄙ</v>
+      </c>
+      <c r="S41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㆢ</v>
+      </c>
+      <c r="T41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄐ</v>
+      </c>
+      <c r="U41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄑ</v>
+      </c>
+      <c r="V41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄒ</v>
+      </c>
+      <c r="W41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄏ</v>
+      </c>
+      <c r="X41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄚ</v>
+      </c>
+      <c r="Y41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄧ</v>
+      </c>
+      <c r="Z41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㆨ</v>
+      </c>
+      <c r="AA41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄨ</v>
+      </c>
+      <c r="AB41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㆤ</v>
+      </c>
+      <c r="AC41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㆦ</v>
+      </c>
+      <c r="AD41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄜ</v>
+      </c>
+      <c r="AE41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄞ</v>
+      </c>
+      <c r="AF41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄠ</v>
+      </c>
+      <c r="AG41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㆩ</v>
+      </c>
+      <c r="AH41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㆪ</v>
+      </c>
+      <c r="AI41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㆫ</v>
+      </c>
+      <c r="AJ41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㆥ</v>
+      </c>
+      <c r="AK41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㆧ</v>
+      </c>
+      <c r="AL41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㆮ</v>
+      </c>
+      <c r="AM41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㆯ</v>
+      </c>
+      <c r="AN41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㆬ</v>
+      </c>
+      <c r="AO41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㆭ</v>
+      </c>
+      <c r="AP41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄣ</v>
+      </c>
+      <c r="AQ41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㆰ</v>
+      </c>
+      <c r="AR41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄢ</v>
+      </c>
+      <c r="AS41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㄤ</v>
+      </c>
+      <c r="AT41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㆱ</v>
+      </c>
+      <c r="AU41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㆲ</v>
+      </c>
+      <c r="AV41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㆴ</v>
+      </c>
+      <c r="AW41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㆵ</v>
+      </c>
+      <c r="AX41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㆻ</v>
+      </c>
+      <c r="AY41" s="242" t="str">
+        <f t="shared" si="12"/>
+        <v>ㆷ</v>
+      </c>
+      <c r="AZ41" s="242" t="str">
+        <f>BG34</f>
+        <v>ㄥ</v>
+      </c>
+      <c r="BA41" s="242" t="str">
+        <f>BH34</f>
+        <v>入</v>
+      </c>
+      <c r="BB41" s="242" t="str">
+        <f>BF34</f>
+        <v>一</v>
+      </c>
+      <c r="BC41" s="242" t="str">
+        <f t="shared" ref="BC41:BH41" si="13">AZ34</f>
+        <v>˫</v>
+      </c>
+      <c r="BD41" s="242" t="str">
+        <f t="shared" si="13"/>
+        <v>˪</v>
+      </c>
+      <c r="BE41" s="242" t="str">
+        <f t="shared" si="13"/>
+        <v>ˋ</v>
+      </c>
+      <c r="BF41" s="242" t="str">
+        <f t="shared" si="13"/>
+        <v>ˊ</v>
+      </c>
+      <c r="BG41" s="242" t="str">
+        <f t="shared" si="13"/>
+        <v>八</v>
+      </c>
+      <c r="BH41" s="242" t="str">
+        <f t="shared" si="13"/>
+        <v>四</v>
+      </c>
+      <c r="BI41" s="242"/>
+      <c r="BJ41" s="242" t="str">
+        <f>BJ34</f>
+        <v/>
+      </c>
+      <c r="BK41" s="1"/>
+      <c r="BL41" s="238" t="str">
+        <v>G</v>
+      </c>
+      <c r="BM41" s="238" t="str">
+        <v>/</v>
+      </c>
+      <c r="BN41" s="239" t="str">
+        <v>ㆭ</v>
+      </c>
+      <c r="BO41" s="238"/>
+      <c r="BP41" s="238"/>
+    </row>
+    <row r="42" spans="1:68" s="237" customFormat="1">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="1"/>
+      <c r="Q42" s="1"/>
+      <c r="R42" s="1"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="1"/>
+      <c r="U42" s="1"/>
+      <c r="V42" s="1"/>
+      <c r="W42" s="1"/>
+      <c r="X42" s="1"/>
+      <c r="Y42" s="1"/>
+      <c r="Z42" s="1"/>
+      <c r="AA42" s="1"/>
+      <c r="AB42" s="1"/>
+      <c r="AC42" s="1"/>
+      <c r="AD42" s="1"/>
+      <c r="AE42" s="1"/>
+      <c r="AF42" s="1"/>
+      <c r="AG42" s="1"/>
+      <c r="AH42" s="1"/>
+      <c r="AI42" s="1"/>
+      <c r="AJ42" s="1"/>
+      <c r="AK42" s="1"/>
+      <c r="AL42" s="1"/>
+      <c r="AM42" s="1"/>
+      <c r="AN42" s="1"/>
+      <c r="AO42" s="1"/>
+      <c r="AP42" s="1"/>
+      <c r="AQ42" s="1"/>
+      <c r="AR42" s="1"/>
+      <c r="AS42" s="1"/>
+      <c r="AT42" s="1"/>
+      <c r="AU42" s="1"/>
+      <c r="AV42" s="1"/>
+      <c r="AW42" s="1"/>
+      <c r="AX42" s="1"/>
+      <c r="AY42" s="1"/>
+      <c r="AZ42" s="1"/>
+      <c r="BA42" s="1"/>
+      <c r="BB42" s="1"/>
+      <c r="BC42" s="1"/>
+      <c r="BD42" s="1"/>
+      <c r="BE42" s="1"/>
+      <c r="BF42" s="1"/>
+      <c r="BG42" s="1"/>
+      <c r="BH42" s="1"/>
+      <c r="BI42" s="1"/>
+      <c r="BJ42" s="1"/>
+      <c r="BK42" s="1"/>
+      <c r="BL42" s="238" t="str">
+        <v>N</v>
+      </c>
+      <c r="BM42" s="238" t="str">
+        <v>p</v>
+      </c>
+      <c r="BN42" s="239" t="str">
+        <v>ㄣ</v>
+      </c>
+      <c r="BO42" s="238"/>
+      <c r="BP42" s="238"/>
+    </row>
+    <row r="43" spans="1:68" s="237" customFormat="1">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
+      <c r="Q43" s="1"/>
+      <c r="R43" s="1"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="1"/>
+      <c r="U43" s="1"/>
+      <c r="V43" s="1"/>
+      <c r="W43" s="1"/>
+      <c r="X43" s="1"/>
+      <c r="Y43" s="1"/>
+      <c r="Z43" s="1"/>
+      <c r="AA43" s="1"/>
+      <c r="AB43" s="1"/>
+      <c r="AC43" s="1"/>
+      <c r="AD43" s="1"/>
+      <c r="AE43" s="1"/>
+      <c r="AF43" s="1"/>
+      <c r="AG43" s="1"/>
+      <c r="AH43" s="1"/>
+      <c r="AI43" s="1"/>
+      <c r="AJ43" s="1"/>
+      <c r="AK43" s="1"/>
+      <c r="AL43" s="1"/>
+      <c r="AM43" s="1"/>
+      <c r="AN43" s="1"/>
+      <c r="AO43" s="1"/>
+      <c r="AP43" s="1"/>
+      <c r="AQ43" s="1"/>
+      <c r="AR43" s="1"/>
+      <c r="AS43" s="1"/>
+      <c r="AT43" s="1"/>
+      <c r="AU43" s="1"/>
+      <c r="AV43" s="1"/>
+      <c r="AW43" s="1"/>
+      <c r="AX43" s="1"/>
+      <c r="AY43" s="1"/>
+      <c r="AZ43" s="1"/>
+      <c r="BA43" s="1"/>
+      <c r="BB43" s="1"/>
+      <c r="BC43" s="1"/>
+      <c r="BD43" s="1"/>
+      <c r="BE43" s="1"/>
+      <c r="BF43" s="1"/>
+      <c r="BG43" s="1"/>
+      <c r="BH43" s="1"/>
+      <c r="BI43" s="1"/>
+      <c r="BJ43" s="1"/>
+      <c r="BK43" s="1"/>
+      <c r="BL43" s="238" t="str">
+        <v>Y</v>
+      </c>
+      <c r="BM43" s="238" t="str">
+        <v>M</v>
+      </c>
+      <c r="BN43" s="239" t="str">
+        <v>ㆰ</v>
+      </c>
+      <c r="BO43" s="238"/>
+      <c r="BP43" s="238"/>
+    </row>
+    <row r="44" spans="1:68" s="237" customFormat="1">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+      <c r="Q44" s="1"/>
+      <c r="R44" s="1"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="1"/>
+      <c r="U44" s="1"/>
+      <c r="V44" s="1"/>
+      <c r="W44" s="1"/>
+      <c r="X44" s="1"/>
+      <c r="Y44" s="1"/>
+      <c r="Z44" s="1"/>
+      <c r="AA44" s="1"/>
+      <c r="AB44" s="1"/>
+      <c r="AC44" s="1"/>
+      <c r="AD44" s="1"/>
+      <c r="AE44" s="1"/>
+      <c r="AF44" s="1"/>
+      <c r="AG44" s="1"/>
+      <c r="AH44" s="1"/>
+      <c r="AI44" s="1"/>
+      <c r="AJ44" s="1"/>
+      <c r="AK44" s="1"/>
+      <c r="AL44" s="1"/>
+      <c r="AM44" s="1"/>
+      <c r="AN44" s="1"/>
+      <c r="AO44" s="1"/>
+      <c r="AP44" s="1"/>
+      <c r="AQ44" s="1"/>
+      <c r="AR44" s="1"/>
+      <c r="AS44" s="1"/>
+      <c r="AT44" s="1"/>
+      <c r="AU44" s="1"/>
+      <c r="AV44" s="1"/>
+      <c r="AW44" s="1"/>
+      <c r="AX44" s="1"/>
+      <c r="AY44" s="1"/>
+      <c r="AZ44" s="1"/>
+      <c r="BA44" s="1"/>
+      <c r="BB44" s="1"/>
+      <c r="BC44" s="1"/>
+      <c r="BD44" s="1"/>
+      <c r="BE44" s="1"/>
+      <c r="BF44" s="1"/>
+      <c r="BG44" s="1"/>
+      <c r="BH44" s="1"/>
+      <c r="BI44" s="1"/>
+      <c r="BJ44" s="1"/>
+      <c r="BK44" s="1"/>
+      <c r="BL44" s="238" t="str">
+        <v>@</v>
+      </c>
+      <c r="BM44" s="238" t="str">
+        <v>0</v>
+      </c>
+      <c r="BN44" s="239" t="str">
+        <v>ㄢ</v>
+      </c>
+      <c r="BO44" s="238"/>
+      <c r="BP44" s="238"/>
+    </row>
+    <row r="45" spans="1:68" s="237" customFormat="1">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+      <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="1"/>
+      <c r="U45" s="1"/>
+      <c r="V45" s="1"/>
+      <c r="W45" s="1"/>
+      <c r="X45" s="1"/>
+      <c r="Y45" s="1"/>
+      <c r="Z45" s="1"/>
+      <c r="AA45" s="1"/>
+      <c r="AB45" s="1"/>
+      <c r="AC45" s="1"/>
+      <c r="AD45" s="1"/>
+      <c r="AE45" s="1"/>
+      <c r="AF45" s="1"/>
+      <c r="AG45" s="1"/>
+      <c r="AH45" s="1"/>
+      <c r="AI45" s="1"/>
+      <c r="AJ45" s="1"/>
+      <c r="AK45" s="1"/>
+      <c r="AL45" s="1"/>
+      <c r="AM45" s="1"/>
+      <c r="AN45" s="1"/>
+      <c r="AO45" s="1"/>
+      <c r="AP45" s="1"/>
+      <c r="AQ45" s="1"/>
+      <c r="AR45" s="1"/>
+      <c r="AS45" s="1"/>
+      <c r="AT45" s="1"/>
+      <c r="AU45" s="1"/>
+      <c r="AV45" s="1"/>
+      <c r="AW45" s="1"/>
+      <c r="AX45" s="1"/>
+      <c r="AY45" s="1"/>
+      <c r="AZ45" s="1"/>
+      <c r="BA45" s="1"/>
+      <c r="BB45" s="1"/>
+      <c r="BC45" s="1"/>
+      <c r="BD45" s="1"/>
+      <c r="BE45" s="1"/>
+      <c r="BF45" s="1"/>
+      <c r="BG45" s="1"/>
+      <c r="BH45" s="1"/>
+      <c r="BI45" s="1"/>
+      <c r="BJ45" s="1"/>
+      <c r="BK45" s="1"/>
+      <c r="BL45" s="238" t="str">
+        <v>A</v>
+      </c>
+      <c r="BM45" s="238" t="str">
+        <v>;</v>
+      </c>
+      <c r="BN45" s="239" t="str">
+        <v>ㄤ</v>
+      </c>
+      <c r="BO45" s="238"/>
+      <c r="BP45" s="238"/>
+    </row>
+    <row r="46" spans="1:68" s="237" customFormat="1">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="O46" s="1"/>
+      <c r="P46" s="1"/>
+      <c r="Q46" s="1"/>
+      <c r="R46" s="1"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="1"/>
+      <c r="U46" s="1"/>
+      <c r="V46" s="1"/>
+      <c r="W46" s="1"/>
+      <c r="X46" s="1"/>
+      <c r="Y46" s="1"/>
+      <c r="Z46" s="1"/>
+      <c r="AA46" s="1"/>
+      <c r="AB46" s="1"/>
+      <c r="AC46" s="1"/>
+      <c r="AD46" s="1"/>
+      <c r="AE46" s="1"/>
+      <c r="AF46" s="1"/>
+      <c r="AG46" s="1"/>
+      <c r="AH46" s="1"/>
+      <c r="AI46" s="1"/>
+      <c r="AJ46" s="1"/>
+      <c r="AK46" s="1"/>
+      <c r="AL46" s="1"/>
+      <c r="AM46" s="1"/>
+      <c r="AN46" s="1"/>
+      <c r="AO46" s="1"/>
+      <c r="AP46" s="1"/>
+      <c r="AQ46" s="1"/>
+      <c r="AR46" s="1"/>
+      <c r="AS46" s="1"/>
+      <c r="AT46" s="1"/>
+      <c r="AU46" s="1"/>
+      <c r="AV46" s="1"/>
+      <c r="AW46" s="1"/>
+      <c r="AX46" s="1"/>
+      <c r="AY46" s="1"/>
+      <c r="AZ46" s="1"/>
+      <c r="BA46" s="1"/>
+      <c r="BB46" s="1"/>
+      <c r="BC46" s="1"/>
+      <c r="BD46" s="1"/>
+      <c r="BE46" s="1"/>
+      <c r="BF46" s="1"/>
+      <c r="BG46" s="1"/>
+      <c r="BH46" s="1"/>
+      <c r="BI46" s="1"/>
+      <c r="BJ46" s="1"/>
+      <c r="BK46" s="1"/>
+      <c r="BL46" s="238" t="str">
+        <v>W</v>
+      </c>
+      <c r="BM46" s="238" t="str">
+        <v>O</v>
+      </c>
+      <c r="BN46" s="239" t="str">
+        <v>ㆱ</v>
+      </c>
+      <c r="BO46" s="238"/>
+      <c r="BP46" s="238"/>
+    </row>
+    <row r="47" spans="1:68" s="237" customFormat="1">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="1"/>
+      <c r="Q47" s="1"/>
+      <c r="R47" s="1"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="1"/>
+      <c r="U47" s="1"/>
+      <c r="V47" s="1"/>
+      <c r="W47" s="1"/>
+      <c r="X47" s="1"/>
+      <c r="Y47" s="1"/>
+      <c r="Z47" s="1"/>
+      <c r="AA47" s="1"/>
+      <c r="AB47" s="1"/>
+      <c r="AC47" s="1"/>
+      <c r="AD47" s="1"/>
+      <c r="AE47" s="1"/>
+      <c r="AF47" s="1"/>
+      <c r="AG47" s="1"/>
+      <c r="AH47" s="1"/>
+      <c r="AI47" s="1"/>
+      <c r="AJ47" s="1"/>
+      <c r="AK47" s="1"/>
+      <c r="AL47" s="1"/>
+      <c r="AM47" s="1"/>
+      <c r="AN47" s="1"/>
+      <c r="AO47" s="1"/>
+      <c r="AP47" s="1"/>
+      <c r="AQ47" s="1"/>
+      <c r="AR47" s="1"/>
+      <c r="AS47" s="1"/>
+      <c r="AT47" s="1"/>
+      <c r="AU47" s="1"/>
+      <c r="AV47" s="1"/>
+      <c r="AW47" s="1"/>
+      <c r="AX47" s="1"/>
+      <c r="AY47" s="1"/>
+      <c r="AZ47" s="1"/>
+      <c r="BA47" s="1"/>
+      <c r="BB47" s="1"/>
+      <c r="BC47" s="1"/>
+      <c r="BD47" s="1"/>
+      <c r="BE47" s="1"/>
+      <c r="BF47" s="1"/>
+      <c r="BG47" s="1"/>
+      <c r="BH47" s="1"/>
+      <c r="BI47" s="1"/>
+      <c r="BJ47" s="1"/>
+      <c r="BK47" s="1"/>
+      <c r="BL47" s="238" t="str">
+        <v>H</v>
+      </c>
+      <c r="BM47" s="238" t="str">
+        <v>o</v>
+      </c>
+      <c r="BN47" s="239" t="str">
+        <v>ㆲ</v>
+      </c>
+      <c r="BO47" s="238"/>
+      <c r="BP47" s="238"/>
+    </row>
+    <row r="48" spans="1:68" s="237" customFormat="1">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="1"/>
+      <c r="Q48" s="1"/>
+      <c r="R48" s="1"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="1"/>
+      <c r="U48" s="1"/>
+      <c r="V48" s="1"/>
+      <c r="W48" s="1"/>
+      <c r="X48" s="1"/>
+      <c r="Y48" s="1"/>
+      <c r="Z48" s="1"/>
+      <c r="AA48" s="1"/>
+      <c r="AB48" s="1"/>
+      <c r="AC48" s="1"/>
+      <c r="AD48" s="1"/>
+      <c r="AE48" s="1"/>
+      <c r="AF48" s="1"/>
+      <c r="AG48" s="1"/>
+      <c r="AH48" s="1"/>
+      <c r="AI48" s="1"/>
+      <c r="AJ48" s="1"/>
+      <c r="AK48" s="1"/>
+      <c r="AL48" s="1"/>
+      <c r="AM48" s="1"/>
+      <c r="AN48" s="1"/>
+      <c r="AO48" s="1"/>
+      <c r="AP48" s="1"/>
+      <c r="AQ48" s="1"/>
+      <c r="AR48" s="1"/>
+      <c r="AS48" s="1"/>
+      <c r="AT48" s="1"/>
+      <c r="AU48" s="1"/>
+      <c r="AV48" s="1"/>
+      <c r="AW48" s="1"/>
+      <c r="AX48" s="1"/>
+      <c r="AY48" s="1"/>
+      <c r="AZ48" s="1"/>
+      <c r="BA48" s="1"/>
+      <c r="BB48" s="1"/>
+      <c r="BC48" s="1"/>
+      <c r="BD48" s="1"/>
+      <c r="BE48" s="1"/>
+      <c r="BF48" s="1"/>
+      <c r="BG48" s="1"/>
+      <c r="BH48" s="1"/>
+      <c r="BI48" s="1"/>
+      <c r="BJ48" s="1"/>
+      <c r="BK48" s="1"/>
+      <c r="BL48" s="238" t="str">
+        <v>R</v>
+      </c>
+      <c r="BM48" s="238" t="str">
+        <v>b</v>
+      </c>
+      <c r="BN48" s="239" t="str">
+        <v>ㆴ</v>
+      </c>
+      <c r="BO48" s="238"/>
+      <c r="BP48" s="238"/>
+    </row>
+    <row r="49" spans="1:68" s="237" customFormat="1">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="O49" s="1"/>
+      <c r="P49" s="1"/>
+      <c r="Q49" s="1"/>
+      <c r="R49" s="1"/>
+      <c r="S49" s="1"/>
+      <c r="T49" s="1"/>
+      <c r="U49" s="1"/>
+      <c r="V49" s="1"/>
+      <c r="W49" s="1"/>
+      <c r="X49" s="1"/>
+      <c r="Y49" s="1"/>
+      <c r="Z49" s="1"/>
+      <c r="AA49" s="1"/>
+      <c r="AB49" s="1"/>
+      <c r="AC49" s="1"/>
+      <c r="AD49" s="1"/>
+      <c r="AE49" s="1"/>
+      <c r="AF49" s="1"/>
+      <c r="AG49" s="1"/>
+      <c r="AH49" s="1"/>
+      <c r="AI49" s="1"/>
+      <c r="AJ49" s="1"/>
+      <c r="AK49" s="1"/>
+      <c r="AL49" s="1"/>
+      <c r="AM49" s="1"/>
+      <c r="AN49" s="1"/>
+      <c r="AO49" s="1"/>
+      <c r="AP49" s="1"/>
+      <c r="AQ49" s="1"/>
+      <c r="AR49" s="1"/>
+      <c r="AS49" s="1"/>
+      <c r="AT49" s="1"/>
+      <c r="AU49" s="1"/>
+      <c r="AV49" s="1"/>
+      <c r="AW49" s="1"/>
+      <c r="AX49" s="1"/>
+      <c r="AY49" s="1"/>
+      <c r="AZ49" s="1"/>
+      <c r="BA49" s="1"/>
+      <c r="BB49" s="1"/>
+      <c r="BC49" s="1"/>
+      <c r="BD49" s="1"/>
+      <c r="BE49" s="1"/>
+      <c r="BF49" s="1"/>
+      <c r="BG49" s="1"/>
+      <c r="BH49" s="1"/>
+      <c r="BI49" s="1"/>
+      <c r="BJ49" s="1"/>
+      <c r="BK49" s="1"/>
+      <c r="BL49" s="238" t="str">
+        <v>F</v>
+      </c>
+      <c r="BM49" s="238" t="str">
+        <v>t</v>
+      </c>
+      <c r="BN49" s="239" t="str">
+        <v>ㆵ</v>
+      </c>
+      <c r="BO49" s="238"/>
+      <c r="BP49" s="238"/>
+    </row>
+    <row r="50" spans="1:68" s="237" customFormat="1">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
+      <c r="Q50" s="1"/>
+      <c r="R50" s="1"/>
+      <c r="S50" s="1"/>
+      <c r="T50" s="1"/>
+      <c r="U50" s="1"/>
+      <c r="V50" s="1"/>
+      <c r="W50" s="1"/>
+      <c r="X50" s="1"/>
+      <c r="Y50" s="1"/>
+      <c r="Z50" s="1"/>
+      <c r="AA50" s="1"/>
+      <c r="AB50" s="1"/>
+      <c r="AC50" s="1"/>
+      <c r="AD50" s="1"/>
+      <c r="AE50" s="1"/>
+      <c r="AF50" s="1"/>
+      <c r="AG50" s="1"/>
+      <c r="AH50" s="1"/>
+      <c r="AI50" s="1"/>
+      <c r="AJ50" s="1"/>
+      <c r="AK50" s="1"/>
+      <c r="AL50" s="1"/>
+      <c r="AM50" s="1"/>
+      <c r="AN50" s="1"/>
+      <c r="AO50" s="1"/>
+      <c r="AP50" s="1"/>
+      <c r="AQ50" s="1"/>
+      <c r="AR50" s="1"/>
+      <c r="AS50" s="1"/>
+      <c r="AT50" s="1"/>
+      <c r="AU50" s="1"/>
+      <c r="AV50" s="1"/>
+      <c r="AW50" s="1"/>
+      <c r="AX50" s="1"/>
+      <c r="AY50" s="1"/>
+      <c r="AZ50" s="1"/>
+      <c r="BA50" s="1"/>
+      <c r="BB50" s="1"/>
+      <c r="BC50" s="1"/>
+      <c r="BD50" s="1"/>
+      <c r="BE50" s="1"/>
+      <c r="BF50" s="1"/>
+      <c r="BG50" s="1"/>
+      <c r="BH50" s="1"/>
+      <c r="BI50" s="1"/>
+      <c r="BJ50" s="1"/>
+      <c r="BK50" s="1"/>
+      <c r="BL50" s="238" t="str">
+        <v>Q</v>
+      </c>
+      <c r="BM50" s="238" t="str">
+        <v>g</v>
+      </c>
+      <c r="BN50" s="239" t="str">
+        <v>ㆻ</v>
+      </c>
+      <c r="BO50" s="238"/>
+      <c r="BP50" s="238"/>
+    </row>
+    <row r="51" spans="1:68" s="237" customFormat="1">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1"/>
+      <c r="U51" s="1"/>
+      <c r="V51" s="1"/>
+      <c r="W51" s="1"/>
+      <c r="X51" s="1"/>
+      <c r="Y51" s="1"/>
+      <c r="Z51" s="1"/>
+      <c r="AA51" s="1"/>
+      <c r="AB51" s="1"/>
+      <c r="AC51" s="1"/>
+      <c r="AD51" s="1"/>
+      <c r="AE51" s="1"/>
+      <c r="AF51" s="1"/>
+      <c r="AG51" s="1"/>
+      <c r="AH51" s="1"/>
+      <c r="AI51" s="1"/>
+      <c r="AJ51" s="1"/>
+      <c r="AK51" s="1"/>
+      <c r="AL51" s="1"/>
+      <c r="AM51" s="1"/>
+      <c r="AN51" s="1"/>
+      <c r="AO51" s="1"/>
+      <c r="AP51" s="1"/>
+      <c r="AQ51" s="1"/>
+      <c r="AR51" s="1"/>
+      <c r="AS51" s="1"/>
+      <c r="AT51" s="1"/>
+      <c r="AU51" s="1"/>
+      <c r="AV51" s="1"/>
+      <c r="AW51" s="1"/>
+      <c r="AX51" s="1"/>
+      <c r="AY51" s="1"/>
+      <c r="AZ51" s="1"/>
+      <c r="BA51" s="1"/>
+      <c r="BB51" s="1"/>
+      <c r="BC51" s="1"/>
+      <c r="BD51" s="1"/>
+      <c r="BE51" s="1"/>
+      <c r="BF51" s="1"/>
+      <c r="BG51" s="1"/>
+      <c r="BH51" s="1"/>
+      <c r="BI51" s="1"/>
+      <c r="BJ51" s="1"/>
+      <c r="BK51" s="1"/>
+      <c r="BL51" s="238" t="str">
+        <v>V</v>
+      </c>
+      <c r="BM51" s="238" t="str">
+        <v>z</v>
+      </c>
+      <c r="BN51" s="239" t="str">
+        <v>ㆷ</v>
+      </c>
+      <c r="BO51" s="238"/>
+      <c r="BP51" s="238"/>
+    </row>
+    <row r="52" spans="1:68" s="237" customFormat="1">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
+      <c r="O52" s="1"/>
+      <c r="P52" s="1"/>
+      <c r="Q52" s="1"/>
+      <c r="R52" s="1"/>
+      <c r="S52" s="1"/>
+      <c r="T52" s="1"/>
+      <c r="U52" s="1"/>
+      <c r="V52" s="1"/>
+      <c r="W52" s="1"/>
+      <c r="X52" s="1"/>
+      <c r="Y52" s="1"/>
+      <c r="Z52" s="1"/>
+      <c r="AA52" s="1"/>
+      <c r="AB52" s="1"/>
+      <c r="AC52" s="1"/>
+      <c r="AD52" s="1"/>
+      <c r="AE52" s="1"/>
+      <c r="AF52" s="1"/>
+      <c r="AG52" s="1"/>
+      <c r="AH52" s="1"/>
+      <c r="AI52" s="1"/>
+      <c r="AJ52" s="1"/>
+      <c r="AK52" s="1"/>
+      <c r="AL52" s="1"/>
+      <c r="AM52" s="1"/>
+      <c r="AN52" s="1"/>
+      <c r="AO52" s="1"/>
+      <c r="AP52" s="1"/>
+      <c r="AQ52" s="1"/>
+      <c r="AR52" s="1"/>
+      <c r="AS52" s="1"/>
+      <c r="AT52" s="1"/>
+      <c r="AU52" s="1"/>
+      <c r="AV52" s="1"/>
+      <c r="AW52" s="1"/>
+      <c r="AX52" s="1"/>
+      <c r="AY52" s="1"/>
+      <c r="AZ52" s="1"/>
+      <c r="BA52" s="1"/>
+      <c r="BB52" s="1"/>
+      <c r="BC52" s="1"/>
+      <c r="BD52" s="1"/>
+      <c r="BE52" s="1"/>
+      <c r="BF52" s="1"/>
+      <c r="BG52" s="1"/>
+      <c r="BH52" s="1"/>
+      <c r="BI52" s="1"/>
+      <c r="BJ52" s="1"/>
+      <c r="BK52" s="1"/>
+      <c r="BL52" s="238" t="str">
+        <v>L</v>
+      </c>
+      <c r="BM52" s="238" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN52" s="239" t="str">
+        <v>ㄥ</v>
+      </c>
+      <c r="BO52" s="238"/>
+      <c r="BP52" s="238"/>
+    </row>
+    <row r="53" spans="1:68" s="237" customFormat="1">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1"/>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="1"/>
+      <c r="R53" s="1"/>
+      <c r="S53" s="1"/>
+      <c r="T53" s="1"/>
+      <c r="U53" s="1"/>
+      <c r="V53" s="1"/>
+      <c r="W53" s="1"/>
+      <c r="X53" s="1"/>
+      <c r="Y53" s="1"/>
+      <c r="Z53" s="1"/>
+      <c r="AA53" s="1"/>
+      <c r="AB53" s="1"/>
+      <c r="AC53" s="1"/>
+      <c r="AD53" s="1"/>
+      <c r="AE53" s="1"/>
+      <c r="AF53" s="1"/>
+      <c r="AG53" s="1"/>
+      <c r="AH53" s="1"/>
+      <c r="AI53" s="1"/>
+      <c r="AJ53" s="1"/>
+      <c r="AK53" s="1"/>
+      <c r="AL53" s="1"/>
+      <c r="AM53" s="1"/>
+      <c r="AN53" s="1"/>
+      <c r="AO53" s="1"/>
+      <c r="AP53" s="1"/>
+      <c r="AQ53" s="1"/>
+      <c r="AR53" s="1"/>
+      <c r="AS53" s="1"/>
+      <c r="AT53" s="1"/>
+      <c r="AU53" s="1"/>
+      <c r="AV53" s="1"/>
+      <c r="AW53" s="1"/>
+      <c r="AX53" s="1"/>
+      <c r="AY53" s="1"/>
+      <c r="AZ53" s="1"/>
+      <c r="BA53" s="1"/>
+      <c r="BB53" s="1"/>
+      <c r="BC53" s="1"/>
+      <c r="BD53" s="1"/>
+      <c r="BE53" s="1"/>
+      <c r="BF53" s="1"/>
+      <c r="BG53" s="1"/>
+      <c r="BH53" s="1"/>
+      <c r="BI53" s="1"/>
+      <c r="BJ53" s="1"/>
+      <c r="BK53" s="1"/>
+      <c r="BL53" s="238" t="str">
+        <v>&amp;</v>
+      </c>
+      <c r="BM53" s="238" t="str">
+        <v>.</v>
+      </c>
+      <c r="BN53" s="239" t="str">
+        <v>入</v>
+      </c>
+      <c r="BO53" s="238"/>
+      <c r="BP53" s="238"/>
+    </row>
+    <row r="54" spans="1:68">
+      <c r="BL54" s="237" t="str">
+        <v>1</v>
+      </c>
+      <c r="BM54" s="237" t="str">
+        <v>"</v>
+      </c>
+      <c r="BN54" s="237" t="str">
+        <v>一</v>
+      </c>
+    </row>
+    <row r="55" spans="1:68">
+      <c r="BL55" s="237" t="str">
+        <v>7</v>
+      </c>
+      <c r="BM55" s="237" t="str">
+        <v>5</v>
+      </c>
+      <c r="BN55" s="237" t="str">
+        <v>˫</v>
+      </c>
+    </row>
+    <row r="56" spans="1:68">
+      <c r="BL56" s="237" t="str">
+        <v>3</v>
+      </c>
+      <c r="BM56" s="237" t="str">
+        <v>3</v>
+      </c>
+      <c r="BN56" s="237" t="str">
+        <v>˪</v>
+      </c>
+    </row>
+    <row r="57" spans="1:68">
+      <c r="BL57" s="237" t="str">
+        <v>2</v>
+      </c>
+      <c r="BM57" s="237" t="str">
+        <v>4</v>
+      </c>
+      <c r="BN57" s="237" t="str">
+        <v>ˋ</v>
+      </c>
+    </row>
+    <row r="58" spans="1:68">
+      <c r="BL58" s="237" t="str">
+        <v>5</v>
+      </c>
+      <c r="BM58" s="237" t="str">
+        <v>6</v>
+      </c>
+      <c r="BN58" s="237" t="str">
+        <v>ˊ</v>
+      </c>
+    </row>
+    <row r="59" spans="1:68">
+      <c r="BL59" s="237" t="str">
+        <v>8</v>
+      </c>
+      <c r="BM59" s="237" t="str">
+        <v>]</v>
+      </c>
+      <c r="BN59" s="237" t="str">
+        <v>八</v>
+      </c>
+    </row>
+    <row r="60" spans="1:68" s="237" customFormat="1">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
+      <c r="M60" s="1"/>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1"/>
+      <c r="P60" s="1"/>
+      <c r="Q60" s="1"/>
+      <c r="R60" s="1"/>
+      <c r="S60" s="1"/>
+      <c r="T60" s="1"/>
+      <c r="U60" s="1"/>
+      <c r="V60" s="1"/>
+      <c r="W60" s="1"/>
+      <c r="X60" s="1"/>
+      <c r="Y60" s="1"/>
+      <c r="Z60" s="1"/>
+      <c r="AA60" s="1"/>
+      <c r="AB60" s="1"/>
+      <c r="AC60" s="1"/>
+      <c r="AD60" s="1"/>
+      <c r="AE60" s="1"/>
+      <c r="AF60" s="1"/>
+      <c r="AG60" s="1"/>
+      <c r="AH60" s="1"/>
+      <c r="AI60" s="1"/>
+      <c r="AJ60" s="1"/>
+      <c r="AK60" s="1"/>
+      <c r="AL60" s="1"/>
+      <c r="AM60" s="1"/>
+      <c r="AN60" s="1"/>
+      <c r="AO60" s="1"/>
+      <c r="AP60" s="1"/>
+      <c r="AQ60" s="1"/>
+      <c r="AR60" s="1"/>
+      <c r="AS60" s="1"/>
+      <c r="AT60" s="1"/>
+      <c r="AU60" s="1"/>
+      <c r="AV60" s="1"/>
+      <c r="AW60" s="1"/>
+      <c r="AX60" s="1"/>
+      <c r="AY60" s="1"/>
+      <c r="AZ60" s="1"/>
+      <c r="BA60" s="1"/>
+      <c r="BB60" s="1"/>
+      <c r="BC60" s="1"/>
+      <c r="BD60" s="1"/>
+      <c r="BE60" s="1"/>
+      <c r="BF60" s="1"/>
+      <c r="BG60" s="1"/>
+      <c r="BH60" s="1"/>
+      <c r="BI60" s="1"/>
+      <c r="BJ60" s="1"/>
+      <c r="BK60" s="1"/>
+      <c r="BL60" s="238" t="str">
+        <v>4</v>
+      </c>
+      <c r="BM60" s="238" t="str">
+        <v>[</v>
+      </c>
+      <c r="BN60" s="238" t="str">
+        <v>四</v>
+      </c>
+      <c r="BO60" s="238"/>
+      <c r="BP60" s="238"/>
+    </row>
+    <row r="61" spans="1:68" s="237" customFormat="1">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
+      <c r="M61" s="1"/>
+      <c r="N61" s="1"/>
+      <c r="O61" s="1"/>
+      <c r="P61" s="1"/>
+      <c r="Q61" s="1"/>
+      <c r="R61" s="1"/>
+      <c r="S61" s="1"/>
+      <c r="T61" s="1"/>
+      <c r="U61" s="1"/>
+      <c r="V61" s="1"/>
+      <c r="W61" s="1"/>
+      <c r="X61" s="1"/>
+      <c r="Y61" s="1"/>
+      <c r="Z61" s="1"/>
+      <c r="AA61" s="1"/>
+      <c r="AB61" s="1"/>
+      <c r="AC61" s="1"/>
+      <c r="AD61" s="1"/>
+      <c r="AE61" s="1"/>
+      <c r="AF61" s="1"/>
+      <c r="AG61" s="1"/>
+      <c r="AH61" s="1"/>
+      <c r="AI61" s="1"/>
+      <c r="AJ61" s="1"/>
+      <c r="AK61" s="1"/>
+      <c r="AL61" s="1"/>
+      <c r="AM61" s="1"/>
+      <c r="AN61" s="1"/>
+      <c r="AO61" s="1"/>
+      <c r="AP61" s="1"/>
+      <c r="AQ61" s="1"/>
+      <c r="AR61" s="1"/>
+      <c r="AS61" s="1"/>
+      <c r="AT61" s="1"/>
+      <c r="AU61" s="1"/>
+      <c r="AV61" s="1"/>
+      <c r="AW61" s="1"/>
+      <c r="AX61" s="1"/>
+      <c r="AY61" s="1"/>
+      <c r="AZ61" s="1"/>
+      <c r="BA61" s="1"/>
+      <c r="BB61" s="1"/>
+      <c r="BC61" s="1"/>
+      <c r="BD61" s="1"/>
+      <c r="BE61" s="1"/>
+      <c r="BF61" s="1"/>
+      <c r="BG61" s="1"/>
+      <c r="BH61" s="1"/>
+      <c r="BI61" s="1"/>
+      <c r="BJ61" s="1"/>
+      <c r="BK61" s="1"/>
+      <c r="BL61" s="238">
+        <v>0</v>
+      </c>
+      <c r="BM61" s="238">
+        <v>0</v>
+      </c>
+      <c r="BN61" s="238">
+        <v>0</v>
+      </c>
+      <c r="BO61" s="238"/>
+      <c r="BP61" s="238"/>
+    </row>
+    <row r="62" spans="1:68" s="237" customFormat="1">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1"/>
+      <c r="N62" s="1"/>
+      <c r="O62" s="1"/>
+      <c r="P62" s="1"/>
+      <c r="Q62" s="1"/>
+      <c r="R62" s="1"/>
+      <c r="S62" s="1"/>
+      <c r="T62" s="1"/>
+      <c r="U62" s="1"/>
+      <c r="V62" s="1"/>
+      <c r="W62" s="1"/>
+      <c r="X62" s="1"/>
+      <c r="Y62" s="1"/>
+      <c r="Z62" s="1"/>
+      <c r="AA62" s="1"/>
+      <c r="AB62" s="1"/>
+      <c r="AC62" s="1"/>
+      <c r="AD62" s="1"/>
+      <c r="AE62" s="1"/>
+      <c r="AF62" s="1"/>
+      <c r="AG62" s="1"/>
+      <c r="AH62" s="1"/>
+      <c r="AI62" s="1"/>
+      <c r="AJ62" s="1"/>
+      <c r="AK62" s="1"/>
+      <c r="AL62" s="1"/>
+      <c r="AM62" s="1"/>
+      <c r="AN62" s="1"/>
+      <c r="AO62" s="1"/>
+      <c r="AP62" s="1"/>
+      <c r="AQ62" s="1"/>
+      <c r="AR62" s="1"/>
+      <c r="AS62" s="1"/>
+      <c r="AT62" s="1"/>
+      <c r="AU62" s="1"/>
+      <c r="AV62" s="1"/>
+      <c r="AW62" s="1"/>
+      <c r="AX62" s="1"/>
+      <c r="AY62" s="1"/>
+      <c r="AZ62" s="1"/>
+      <c r="BA62" s="1"/>
+      <c r="BB62" s="1"/>
+      <c r="BC62" s="1"/>
+      <c r="BD62" s="1"/>
+      <c r="BE62" s="1"/>
+      <c r="BF62" s="1"/>
+      <c r="BG62" s="1"/>
+      <c r="BH62" s="1"/>
+      <c r="BI62" s="1"/>
+      <c r="BJ62" s="1"/>
+      <c r="BK62" s="1"/>
+      <c r="BL62" s="238" t="str">
+        <v/>
+      </c>
+      <c r="BM62" s="238" t="str">
+        <v/>
+      </c>
+      <c r="BN62" s="238" t="str">
+        <v/>
+      </c>
+      <c r="BO62" s="238"/>
+      <c r="BP62" s="238"/>
+    </row>
+    <row r="63" spans="1:68" s="237" customFormat="1">
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+      <c r="M63" s="1"/>
+      <c r="N63" s="1"/>
+      <c r="O63" s="1"/>
+      <c r="P63" s="1"/>
+      <c r="Q63" s="1"/>
+      <c r="R63" s="1"/>
+      <c r="S63" s="1"/>
+      <c r="T63" s="1"/>
+      <c r="U63" s="1"/>
+      <c r="V63" s="1"/>
+      <c r="W63" s="1"/>
+      <c r="X63" s="1"/>
+      <c r="Y63" s="1"/>
+      <c r="Z63" s="1"/>
+      <c r="AA63" s="1"/>
+      <c r="AB63" s="1"/>
+      <c r="AC63" s="1"/>
+      <c r="AD63" s="1"/>
+      <c r="AE63" s="1"/>
+      <c r="AF63" s="1"/>
+      <c r="AG63" s="1"/>
+      <c r="AH63" s="1"/>
+      <c r="AI63" s="1"/>
+      <c r="AJ63" s="1"/>
+      <c r="AK63" s="1"/>
+      <c r="AL63" s="1"/>
+      <c r="AM63" s="1"/>
+      <c r="AN63" s="1"/>
+      <c r="AO63" s="1"/>
+      <c r="AP63" s="1"/>
+      <c r="AQ63" s="1"/>
+      <c r="AR63" s="1"/>
+      <c r="AS63" s="1"/>
+      <c r="AT63" s="1"/>
+      <c r="AU63" s="1"/>
+      <c r="AV63" s="1"/>
+      <c r="AW63" s="1"/>
+      <c r="AX63" s="1"/>
+      <c r="AY63" s="1"/>
+      <c r="AZ63" s="1"/>
+      <c r="BA63" s="1"/>
+      <c r="BB63" s="1"/>
+      <c r="BC63" s="1"/>
+      <c r="BD63" s="1"/>
+      <c r="BE63" s="1"/>
+      <c r="BF63" s="1"/>
+      <c r="BG63" s="1"/>
+      <c r="BH63" s="1"/>
+      <c r="BI63" s="1"/>
+      <c r="BJ63" s="1"/>
+      <c r="BK63" s="1"/>
+      <c r="BL63" s="238"/>
+      <c r="BM63" s="238"/>
+      <c r="BN63" s="239"/>
+      <c r="BO63" s="238"/>
+      <c r="BP63" s="238"/>
+    </row>
+    <row r="64" spans="1:68" s="237" customFormat="1">
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1"/>
+      <c r="M64" s="1"/>
+      <c r="N64" s="1"/>
+      <c r="O64" s="1"/>
+      <c r="P64" s="1"/>
+      <c r="Q64" s="1"/>
+      <c r="R64" s="1"/>
+      <c r="S64" s="1"/>
+      <c r="T64" s="1"/>
+      <c r="U64" s="1"/>
+      <c r="V64" s="1"/>
+      <c r="W64" s="1"/>
+      <c r="X64" s="1"/>
+      <c r="Y64" s="1"/>
+      <c r="Z64" s="1"/>
+      <c r="AA64" s="1"/>
+      <c r="AB64" s="1"/>
+      <c r="AC64" s="1"/>
+      <c r="AD64" s="1"/>
+      <c r="AE64" s="1"/>
+      <c r="AF64" s="1"/>
+      <c r="AG64" s="1"/>
+      <c r="AH64" s="1"/>
+      <c r="AI64" s="1"/>
+      <c r="AJ64" s="1"/>
+      <c r="AK64" s="1"/>
+      <c r="AL64" s="1"/>
+      <c r="AM64" s="1"/>
+      <c r="AN64" s="1"/>
+      <c r="AO64" s="1"/>
+      <c r="AP64" s="1"/>
+      <c r="AQ64" s="1"/>
+      <c r="AR64" s="1"/>
+      <c r="AS64" s="1"/>
+      <c r="AT64" s="1"/>
+      <c r="AU64" s="1"/>
+      <c r="AV64" s="1"/>
+      <c r="AW64" s="1"/>
+      <c r="AX64" s="1"/>
+      <c r="AY64" s="1"/>
+      <c r="AZ64" s="1"/>
+      <c r="BA64" s="1"/>
+      <c r="BB64" s="1"/>
+      <c r="BC64" s="1"/>
+      <c r="BD64" s="1"/>
+      <c r="BE64" s="1"/>
+      <c r="BF64" s="1"/>
+      <c r="BG64" s="1"/>
+      <c r="BH64" s="1"/>
+      <c r="BI64" s="1"/>
+      <c r="BJ64" s="1"/>
+      <c r="BK64" s="1"/>
+      <c r="BL64" s="238"/>
+      <c r="BM64" s="238"/>
+      <c r="BN64" s="239"/>
+      <c r="BO64" s="238"/>
+      <c r="BP64" s="238"/>
+    </row>
+    <row r="65" spans="1:68" s="237" customFormat="1">
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
+      <c r="N65" s="1"/>
+      <c r="O65" s="1"/>
+      <c r="P65" s="1"/>
+      <c r="Q65" s="1"/>
+      <c r="R65" s="1"/>
+      <c r="S65" s="1"/>
+      <c r="T65" s="1"/>
+      <c r="U65" s="1"/>
+      <c r="V65" s="1"/>
+      <c r="W65" s="1"/>
+      <c r="X65" s="1"/>
+      <c r="Y65" s="1"/>
+      <c r="Z65" s="1"/>
+      <c r="AA65" s="1"/>
+      <c r="AB65" s="1"/>
+      <c r="AC65" s="1"/>
+      <c r="AD65" s="1"/>
+      <c r="AE65" s="1"/>
+      <c r="AF65" s="1"/>
+      <c r="AG65" s="1"/>
+      <c r="AH65" s="1"/>
+      <c r="AI65" s="1"/>
+      <c r="AJ65" s="1"/>
+      <c r="AK65" s="1"/>
+      <c r="AL65" s="1"/>
+      <c r="AM65" s="1"/>
+      <c r="AN65" s="1"/>
+      <c r="AO65" s="1"/>
+      <c r="AP65" s="1"/>
+      <c r="AQ65" s="1"/>
+      <c r="AR65" s="1"/>
+      <c r="AS65" s="1"/>
+      <c r="AT65" s="1"/>
+      <c r="AU65" s="1"/>
+      <c r="AV65" s="1"/>
+      <c r="AW65" s="1"/>
+      <c r="AX65" s="1"/>
+      <c r="AY65" s="1"/>
+      <c r="AZ65" s="1"/>
+      <c r="BA65" s="1"/>
+      <c r="BB65" s="1"/>
+      <c r="BC65" s="1"/>
+      <c r="BD65" s="1"/>
+      <c r="BE65" s="1"/>
+      <c r="BF65" s="1"/>
+      <c r="BG65" s="1"/>
+      <c r="BH65" s="1"/>
+      <c r="BI65" s="1"/>
+      <c r="BJ65" s="1"/>
+      <c r="BK65" s="1"/>
+      <c r="BL65" s="238"/>
+      <c r="BM65" s="238"/>
+      <c r="BN65" s="239"/>
+      <c r="BO65" s="238"/>
+      <c r="BP65" s="238"/>
+    </row>
+    <row r="66" spans="1:68" s="237" customFormat="1">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1"/>
+      <c r="N66" s="1"/>
+      <c r="O66" s="1"/>
+      <c r="P66" s="1"/>
+      <c r="Q66" s="1"/>
+      <c r="R66" s="1"/>
+      <c r="S66" s="1"/>
+      <c r="T66" s="1"/>
+      <c r="U66" s="1"/>
+      <c r="V66" s="1"/>
+      <c r="W66" s="1"/>
+      <c r="X66" s="1"/>
+      <c r="Y66" s="1"/>
+      <c r="Z66" s="1"/>
+      <c r="AA66" s="1"/>
+      <c r="AB66" s="1"/>
+      <c r="AC66" s="1"/>
+      <c r="AD66" s="1"/>
+      <c r="AE66" s="1"/>
+      <c r="AF66" s="1"/>
+      <c r="AG66" s="1"/>
+      <c r="AH66" s="1"/>
+      <c r="AI66" s="1"/>
+      <c r="AJ66" s="1"/>
+      <c r="AK66" s="1"/>
+      <c r="AL66" s="1"/>
+      <c r="AM66" s="1"/>
+      <c r="AN66" s="1"/>
+      <c r="AO66" s="1"/>
+      <c r="AP66" s="1"/>
+      <c r="AQ66" s="1"/>
+      <c r="AR66" s="1"/>
+      <c r="AS66" s="1"/>
+      <c r="AT66" s="1"/>
+      <c r="AU66" s="1"/>
+      <c r="AV66" s="1"/>
+      <c r="AW66" s="1"/>
+      <c r="AX66" s="1"/>
+      <c r="AY66" s="1"/>
+      <c r="AZ66" s="1"/>
+      <c r="BA66" s="1"/>
+      <c r="BB66" s="1"/>
+      <c r="BC66" s="1"/>
+      <c r="BD66" s="1"/>
+      <c r="BE66" s="1"/>
+      <c r="BF66" s="1"/>
+      <c r="BG66" s="1"/>
+      <c r="BH66" s="1"/>
+      <c r="BI66" s="1"/>
+      <c r="BJ66" s="1"/>
+      <c r="BK66" s="1"/>
+      <c r="BL66" s="238"/>
+      <c r="BM66" s="238"/>
+      <c r="BN66" s="239"/>
+      <c r="BO66" s="238"/>
+      <c r="BP66" s="238"/>
+    </row>
+    <row r="67" spans="1:68" s="237" customFormat="1">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1"/>
+      <c r="N67" s="1"/>
+      <c r="O67" s="1"/>
+      <c r="P67" s="1"/>
+      <c r="Q67" s="1"/>
+      <c r="R67" s="1"/>
+      <c r="S67" s="1"/>
+      <c r="T67" s="1"/>
+      <c r="U67" s="1"/>
+      <c r="V67" s="1"/>
+      <c r="W67" s="1"/>
+      <c r="X67" s="1"/>
+      <c r="Y67" s="1"/>
+      <c r="Z67" s="1"/>
+      <c r="AA67" s="1"/>
+      <c r="AB67" s="1"/>
+      <c r="AC67" s="1"/>
+      <c r="AD67" s="1"/>
+      <c r="AE67" s="1"/>
+      <c r="AF67" s="1"/>
+      <c r="AG67" s="1"/>
+      <c r="AH67" s="1"/>
+      <c r="AI67" s="1"/>
+      <c r="AJ67" s="1"/>
+      <c r="AK67" s="1"/>
+      <c r="AL67" s="1"/>
+      <c r="AM67" s="1"/>
+      <c r="AN67" s="1"/>
+      <c r="AO67" s="1"/>
+      <c r="AP67" s="1"/>
+      <c r="AQ67" s="1"/>
+      <c r="AR67" s="1"/>
+      <c r="AS67" s="1"/>
+      <c r="AT67" s="1"/>
+      <c r="AU67" s="1"/>
+      <c r="AV67" s="1"/>
+      <c r="AW67" s="1"/>
+      <c r="AX67" s="1"/>
+      <c r="AY67" s="1"/>
+      <c r="AZ67" s="1"/>
+      <c r="BA67" s="1"/>
+      <c r="BB67" s="1"/>
+      <c r="BC67" s="1"/>
+      <c r="BD67" s="1"/>
+      <c r="BE67" s="1"/>
+      <c r="BF67" s="1"/>
+      <c r="BG67" s="1"/>
+      <c r="BH67" s="1"/>
+      <c r="BI67" s="1"/>
+      <c r="BJ67" s="1"/>
+      <c r="BK67" s="1"/>
+      <c r="BL67" s="238"/>
+      <c r="BM67" s="238"/>
+      <c r="BN67" s="239"/>
+      <c r="BO67" s="238"/>
+      <c r="BP67" s="238"/>
+    </row>
+    <row r="68" spans="1:68" s="237" customFormat="1">
+      <c r="A68" s="1"/>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+      <c r="M68" s="1"/>
+      <c r="N68" s="1"/>
+      <c r="O68" s="1"/>
+      <c r="P68" s="1"/>
+      <c r="Q68" s="1"/>
+      <c r="R68" s="1"/>
+      <c r="S68" s="1"/>
+      <c r="T68" s="1"/>
+      <c r="U68" s="1"/>
+      <c r="V68" s="1"/>
+      <c r="W68" s="1"/>
+      <c r="X68" s="1"/>
+      <c r="Y68" s="1"/>
+      <c r="Z68" s="1"/>
+      <c r="AA68" s="1"/>
+      <c r="AB68" s="1"/>
+      <c r="AC68" s="1"/>
+      <c r="AD68" s="1"/>
+      <c r="AE68" s="1"/>
+      <c r="AF68" s="1"/>
+      <c r="AG68" s="1"/>
+      <c r="AH68" s="1"/>
+      <c r="AI68" s="1"/>
+      <c r="AJ68" s="1"/>
+      <c r="AK68" s="1"/>
+      <c r="AL68" s="1"/>
+      <c r="AM68" s="1"/>
+      <c r="AN68" s="1"/>
+      <c r="AO68" s="1"/>
+      <c r="AP68" s="1"/>
+      <c r="AQ68" s="1"/>
+      <c r="AR68" s="1"/>
+      <c r="AS68" s="1"/>
+      <c r="AT68" s="1"/>
+      <c r="AU68" s="1"/>
+      <c r="AV68" s="1"/>
+      <c r="AW68" s="1"/>
+      <c r="AX68" s="1"/>
+      <c r="AY68" s="1"/>
+      <c r="AZ68" s="1"/>
+      <c r="BA68" s="1"/>
+      <c r="BB68" s="1"/>
+      <c r="BC68" s="1"/>
+      <c r="BD68" s="1"/>
+      <c r="BE68" s="1"/>
+      <c r="BF68" s="1"/>
+      <c r="BG68" s="1"/>
+      <c r="BH68" s="1"/>
+      <c r="BI68" s="1"/>
+      <c r="BJ68" s="1"/>
+      <c r="BK68" s="1"/>
+      <c r="BL68" s="238"/>
+      <c r="BM68" s="238"/>
+      <c r="BN68" s="239"/>
+      <c r="BO68" s="238"/>
+      <c r="BP68" s="238"/>
+    </row>
+    <row r="75" spans="1:68" s="237" customFormat="1">
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+      <c r="M75" s="1"/>
+      <c r="N75" s="1"/>
+      <c r="O75" s="1"/>
+      <c r="P75" s="1"/>
+      <c r="Q75" s="1"/>
+      <c r="R75" s="1"/>
+      <c r="S75" s="1"/>
+      <c r="T75" s="1"/>
+      <c r="U75" s="1"/>
+      <c r="V75" s="1"/>
+      <c r="W75" s="1"/>
+      <c r="X75" s="1"/>
+      <c r="Y75" s="1"/>
+      <c r="Z75" s="1"/>
+      <c r="AA75" s="1"/>
+      <c r="AB75" s="1"/>
+      <c r="AC75" s="1"/>
+      <c r="AD75" s="1"/>
+      <c r="AE75" s="1"/>
+      <c r="AF75" s="1"/>
+      <c r="AG75" s="1"/>
+      <c r="AH75" s="1"/>
+      <c r="AI75" s="1"/>
+      <c r="AJ75" s="1"/>
+      <c r="AK75" s="1"/>
+      <c r="AL75" s="1"/>
+      <c r="AM75" s="1"/>
+      <c r="AN75" s="1"/>
+      <c r="AO75" s="1"/>
+      <c r="AP75" s="1"/>
+      <c r="AQ75" s="1"/>
+      <c r="AR75" s="1"/>
+      <c r="AS75" s="1"/>
+      <c r="AT75" s="1"/>
+      <c r="AU75" s="1"/>
+      <c r="AV75" s="1"/>
+      <c r="AW75" s="1"/>
+      <c r="AX75" s="1"/>
+      <c r="AY75" s="1"/>
+      <c r="AZ75" s="1"/>
+      <c r="BA75" s="1"/>
+      <c r="BB75" s="1"/>
+      <c r="BC75" s="1"/>
+      <c r="BD75" s="1"/>
+      <c r="BE75" s="1"/>
+      <c r="BF75" s="1"/>
+      <c r="BG75" s="1"/>
+      <c r="BH75" s="1"/>
+      <c r="BI75" s="1"/>
+      <c r="BJ75" s="1"/>
+      <c r="BK75" s="1"/>
+      <c r="BL75" s="238"/>
+      <c r="BM75" s="238"/>
+      <c r="BN75" s="238"/>
+      <c r="BO75" s="238"/>
+      <c r="BP75" s="238"/>
+    </row>
+    <row r="76" spans="1:68" s="237" customFormat="1">
+      <c r="A76" s="1"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+      <c r="K76" s="1"/>
+      <c r="L76" s="1"/>
+      <c r="M76" s="1"/>
+      <c r="N76" s="1"/>
+      <c r="O76" s="1"/>
+      <c r="P76" s="1"/>
+      <c r="Q76" s="1"/>
+      <c r="R76" s="1"/>
+      <c r="S76" s="1"/>
+      <c r="T76" s="1"/>
+      <c r="U76" s="1"/>
+      <c r="V76" s="1"/>
+      <c r="W76" s="1"/>
+      <c r="X76" s="1"/>
+      <c r="Y76" s="1"/>
+      <c r="Z76" s="1"/>
+      <c r="AA76" s="1"/>
+      <c r="AB76" s="1"/>
+      <c r="AC76" s="1"/>
+      <c r="AD76" s="1"/>
+      <c r="AE76" s="1"/>
+      <c r="AF76" s="1"/>
+      <c r="AG76" s="1"/>
+      <c r="AH76" s="1"/>
+      <c r="AI76" s="1"/>
+      <c r="AJ76" s="1"/>
+      <c r="AK76" s="1"/>
+      <c r="AL76" s="1"/>
+      <c r="AM76" s="1"/>
+      <c r="AN76" s="1"/>
+      <c r="AO76" s="1"/>
+      <c r="AP76" s="1"/>
+      <c r="AQ76" s="1"/>
+      <c r="AR76" s="1"/>
+      <c r="AS76" s="1"/>
+      <c r="AT76" s="1"/>
+      <c r="AU76" s="1"/>
+      <c r="AV76" s="1"/>
+      <c r="AW76" s="1"/>
+      <c r="AX76" s="1"/>
+      <c r="AY76" s="1"/>
+      <c r="AZ76" s="1"/>
+      <c r="BA76" s="1"/>
+      <c r="BB76" s="1"/>
+      <c r="BC76" s="1"/>
+      <c r="BD76" s="1"/>
+      <c r="BE76" s="1"/>
+      <c r="BF76" s="1"/>
+      <c r="BG76" s="1"/>
+      <c r="BH76" s="1"/>
+      <c r="BI76" s="1"/>
+      <c r="BJ76" s="1"/>
+      <c r="BK76" s="1"/>
+      <c r="BL76" s="238"/>
+      <c r="BM76" s="238"/>
+      <c r="BN76" s="238"/>
+      <c r="BO76" s="238"/>
+      <c r="BP76" s="238"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BF81F2E-F753-443A-9338-E9183376337C}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -26695,7 +34010,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14158527-94DC-4FED-8C0E-3D91F976F89A}">
   <dimension ref="A1:CH62"/>
   <sheetFormatPr defaultRowHeight="25.5" outlineLevelRow="1"/>
@@ -31795,7 +39110,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50EA2289-9B8A-4614-ACA7-AA3E199A79B3}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -46688,7 +54003,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92A2CFCB-5854-4835-8802-8D34ADF19BD0}">
   <dimension ref="B1:Y28"/>
   <sheetFormatPr defaultRowHeight="21"/>
@@ -46701,25 +54016,25 @@
   <sheetData>
     <row r="1" spans="2:19" ht="21.75" thickBot="1"/>
     <row r="2" spans="2:19" ht="24" thickBot="1">
-      <c r="B2" s="277" t="s">
+      <c r="B2" s="280" t="s">
         <v>328</v>
       </c>
-      <c r="C2" s="279" t="s">
+      <c r="C2" s="282" t="s">
         <v>329</v>
       </c>
-      <c r="D2" s="280"/>
-      <c r="E2" s="283" t="s">
+      <c r="D2" s="283"/>
+      <c r="E2" s="286" t="s">
         <v>330</v>
       </c>
-      <c r="F2" s="284"/>
-      <c r="G2" s="285"/>
-      <c r="H2" s="283" t="s">
+      <c r="F2" s="287"/>
+      <c r="G2" s="288"/>
+      <c r="H2" s="286" t="s">
         <v>331</v>
       </c>
-      <c r="I2" s="284"/>
-      <c r="J2" s="284"/>
-      <c r="K2" s="284"/>
-      <c r="L2" s="285"/>
+      <c r="I2" s="287"/>
+      <c r="J2" s="287"/>
+      <c r="K2" s="287"/>
+      <c r="L2" s="288"/>
       <c r="O2" s="228" t="s">
         <v>480</v>
       </c>
@@ -46734,9 +54049,9 @@
       </c>
     </row>
     <row r="3" spans="2:19" ht="24" thickBot="1">
-      <c r="B3" s="278"/>
-      <c r="C3" s="281"/>
-      <c r="D3" s="282"/>
+      <c r="B3" s="281"/>
+      <c r="C3" s="284"/>
+      <c r="D3" s="285"/>
       <c r="E3" s="226" t="s">
         <v>332</v>
       </c>
@@ -46755,10 +54070,10 @@
       <c r="J3" s="226" t="s">
         <v>337</v>
       </c>
-      <c r="K3" s="283" t="s">
+      <c r="K3" s="286" t="s">
         <v>338</v>
       </c>
-      <c r="L3" s="285"/>
+      <c r="L3" s="288"/>
       <c r="O3" s="228" t="s">
         <v>274</v>
       </c>
@@ -47650,64 +54965,64 @@
       <c r="B27" s="226" t="s">
         <v>443</v>
       </c>
-      <c r="C27" s="286" t="s">
+      <c r="C27" s="277" t="s">
         <v>188</v>
       </c>
-      <c r="D27" s="287"/>
-      <c r="E27" s="286" t="s">
+      <c r="D27" s="278"/>
+      <c r="E27" s="277" t="s">
         <v>444</v>
       </c>
-      <c r="F27" s="288"/>
-      <c r="G27" s="288"/>
-      <c r="H27" s="288"/>
-      <c r="I27" s="288"/>
-      <c r="J27" s="287"/>
-      <c r="K27" s="286" t="s">
+      <c r="F27" s="279"/>
+      <c r="G27" s="279"/>
+      <c r="H27" s="279"/>
+      <c r="I27" s="279"/>
+      <c r="J27" s="278"/>
+      <c r="K27" s="277" t="s">
         <v>445</v>
       </c>
-      <c r="L27" s="287"/>
+      <c r="L27" s="278"/>
     </row>
     <row r="28" spans="2:20" ht="24" thickBot="1">
       <c r="B28" s="226" t="s">
         <v>446</v>
       </c>
-      <c r="C28" s="286" t="s">
+      <c r="C28" s="277" t="s">
         <v>447</v>
       </c>
-      <c r="D28" s="287"/>
-      <c r="E28" s="286" t="s">
+      <c r="D28" s="278"/>
+      <c r="E28" s="277" t="s">
         <v>444</v>
       </c>
-      <c r="F28" s="288"/>
-      <c r="G28" s="288"/>
-      <c r="H28" s="288"/>
-      <c r="I28" s="288"/>
-      <c r="J28" s="287"/>
-      <c r="K28" s="286" t="s">
+      <c r="F28" s="279"/>
+      <c r="G28" s="279"/>
+      <c r="H28" s="279"/>
+      <c r="I28" s="279"/>
+      <c r="J28" s="278"/>
+      <c r="K28" s="277" t="s">
         <v>448</v>
       </c>
-      <c r="L28" s="287"/>
+      <c r="L28" s="278"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:D3"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="K3:L3"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="E27:J27"/>
     <mergeCell ref="K27:L27"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:J28"/>
     <mergeCell ref="K28:L28"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:D3"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A576E6A5-6E98-4E7F-8993-972F5CA6ECFB}">
   <dimension ref="B1:Z28"/>
   <sheetFormatPr defaultRowHeight="21"/>
@@ -47722,30 +55037,30 @@
   <sheetData>
     <row r="1" spans="2:20" ht="21.75" thickBot="1"/>
     <row r="2" spans="2:20" ht="24" thickBot="1">
-      <c r="B2" s="277" t="s">
+      <c r="B2" s="280" t="s">
         <v>328</v>
       </c>
-      <c r="C2" s="279" t="s">
+      <c r="C2" s="282" t="s">
         <v>329</v>
       </c>
-      <c r="D2" s="280"/>
-      <c r="E2" s="283" t="s">
+      <c r="D2" s="283"/>
+      <c r="E2" s="286" t="s">
         <v>330</v>
       </c>
-      <c r="F2" s="284"/>
-      <c r="G2" s="285"/>
-      <c r="H2" s="283" t="s">
+      <c r="F2" s="287"/>
+      <c r="G2" s="288"/>
+      <c r="H2" s="286" t="s">
         <v>331</v>
       </c>
-      <c r="I2" s="284"/>
-      <c r="J2" s="284"/>
-      <c r="K2" s="284"/>
-      <c r="L2" s="285"/>
+      <c r="I2" s="287"/>
+      <c r="J2" s="287"/>
+      <c r="K2" s="287"/>
+      <c r="L2" s="288"/>
     </row>
     <row r="3" spans="2:20" ht="24" thickBot="1">
-      <c r="B3" s="278"/>
-      <c r="C3" s="281"/>
-      <c r="D3" s="282"/>
+      <c r="B3" s="281"/>
+      <c r="C3" s="284"/>
+      <c r="D3" s="285"/>
       <c r="E3" s="226" t="s">
         <v>332</v>
       </c>
@@ -47764,10 +55079,10 @@
       <c r="J3" s="226" t="s">
         <v>337</v>
       </c>
-      <c r="K3" s="283" t="s">
+      <c r="K3" s="286" t="s">
         <v>338</v>
       </c>
-      <c r="L3" s="285"/>
+      <c r="L3" s="288"/>
       <c r="N3" s="232" t="s">
         <v>505</v>
       </c>
@@ -48800,43 +56115,43 @@
       <c r="B27" s="226" t="s">
         <v>443</v>
       </c>
-      <c r="C27" s="286" t="s">
+      <c r="C27" s="277" t="s">
         <v>188</v>
       </c>
-      <c r="D27" s="287"/>
-      <c r="E27" s="286" t="s">
+      <c r="D27" s="278"/>
+      <c r="E27" s="277" t="s">
         <v>444</v>
       </c>
-      <c r="F27" s="288"/>
-      <c r="G27" s="288"/>
-      <c r="H27" s="288"/>
-      <c r="I27" s="288"/>
-      <c r="J27" s="287"/>
-      <c r="K27" s="286" t="s">
+      <c r="F27" s="279"/>
+      <c r="G27" s="279"/>
+      <c r="H27" s="279"/>
+      <c r="I27" s="279"/>
+      <c r="J27" s="278"/>
+      <c r="K27" s="277" t="s">
         <v>445</v>
       </c>
-      <c r="L27" s="287"/>
+      <c r="L27" s="278"/>
     </row>
     <row r="28" spans="2:21" ht="24" thickBot="1">
       <c r="B28" s="226" t="s">
         <v>446</v>
       </c>
-      <c r="C28" s="286" t="s">
+      <c r="C28" s="277" t="s">
         <v>447</v>
       </c>
-      <c r="D28" s="287"/>
-      <c r="E28" s="286" t="s">
+      <c r="D28" s="278"/>
+      <c r="E28" s="277" t="s">
         <v>444</v>
       </c>
-      <c r="F28" s="288"/>
-      <c r="G28" s="288"/>
-      <c r="H28" s="288"/>
-      <c r="I28" s="288"/>
-      <c r="J28" s="287"/>
-      <c r="K28" s="286" t="s">
+      <c r="F28" s="279"/>
+      <c r="G28" s="279"/>
+      <c r="H28" s="279"/>
+      <c r="I28" s="279"/>
+      <c r="J28" s="278"/>
+      <c r="K28" s="277" t="s">
         <v>448</v>
       </c>
-      <c r="L28" s="287"/>
+      <c r="L28" s="278"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N4:T20">
@@ -48861,7 +56176,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ED0EFA4-32E9-4AEC-A6ED-2DBF7A08ED31}">
   <dimension ref="B1:X28"/>
   <sheetFormatPr defaultRowHeight="21"/>
@@ -48875,25 +56190,25 @@
   <sheetData>
     <row r="1" spans="2:18" ht="21.75" thickBot="1"/>
     <row r="2" spans="2:18" ht="24" thickBot="1">
-      <c r="B2" s="277" t="s">
+      <c r="B2" s="280" t="s">
         <v>328</v>
       </c>
-      <c r="C2" s="279" t="s">
+      <c r="C2" s="282" t="s">
         <v>329</v>
       </c>
-      <c r="D2" s="280"/>
-      <c r="E2" s="283" t="s">
+      <c r="D2" s="283"/>
+      <c r="E2" s="286" t="s">
         <v>330</v>
       </c>
-      <c r="F2" s="284"/>
-      <c r="G2" s="285"/>
-      <c r="H2" s="283" t="s">
+      <c r="F2" s="287"/>
+      <c r="G2" s="288"/>
+      <c r="H2" s="286" t="s">
         <v>331</v>
       </c>
-      <c r="I2" s="284"/>
-      <c r="J2" s="284"/>
-      <c r="K2" s="284"/>
-      <c r="L2" s="285"/>
+      <c r="I2" s="287"/>
+      <c r="J2" s="287"/>
+      <c r="K2" s="287"/>
+      <c r="L2" s="288"/>
       <c r="P2" s="228" t="str">
         <f xml:space="preserve"> "([48])"</f>
         <v>([48])</v>
@@ -48903,9 +56218,9 @@
       </c>
     </row>
     <row r="3" spans="2:18" ht="24" thickBot="1">
-      <c r="B3" s="278"/>
-      <c r="C3" s="281"/>
-      <c r="D3" s="282"/>
+      <c r="B3" s="281"/>
+      <c r="C3" s="284"/>
+      <c r="D3" s="285"/>
       <c r="E3" s="226" t="s">
         <v>332</v>
       </c>
@@ -48924,10 +56239,10 @@
       <c r="J3" s="226" t="s">
         <v>337</v>
       </c>
-      <c r="K3" s="283" t="s">
+      <c r="K3" s="286" t="s">
         <v>338</v>
       </c>
-      <c r="L3" s="285"/>
+      <c r="L3" s="288"/>
       <c r="N3" s="228" t="s">
         <v>450</v>
       </c>
@@ -49819,43 +57134,43 @@
       <c r="B27" s="226" t="s">
         <v>443</v>
       </c>
-      <c r="C27" s="286" t="s">
+      <c r="C27" s="277" t="s">
         <v>188</v>
       </c>
-      <c r="D27" s="287"/>
-      <c r="E27" s="286" t="s">
+      <c r="D27" s="278"/>
+      <c r="E27" s="277" t="s">
         <v>444</v>
       </c>
-      <c r="F27" s="288"/>
-      <c r="G27" s="288"/>
-      <c r="H27" s="288"/>
-      <c r="I27" s="288"/>
-      <c r="J27" s="287"/>
-      <c r="K27" s="286" t="s">
+      <c r="F27" s="279"/>
+      <c r="G27" s="279"/>
+      <c r="H27" s="279"/>
+      <c r="I27" s="279"/>
+      <c r="J27" s="278"/>
+      <c r="K27" s="277" t="s">
         <v>445</v>
       </c>
-      <c r="L27" s="287"/>
+      <c r="L27" s="278"/>
     </row>
     <row r="28" spans="2:19" ht="24" thickBot="1">
       <c r="B28" s="226" t="s">
         <v>446</v>
       </c>
-      <c r="C28" s="286" t="s">
+      <c r="C28" s="277" t="s">
         <v>447</v>
       </c>
-      <c r="D28" s="287"/>
-      <c r="E28" s="286" t="s">
+      <c r="D28" s="278"/>
+      <c r="E28" s="277" t="s">
         <v>444</v>
       </c>
-      <c r="F28" s="288"/>
-      <c r="G28" s="288"/>
-      <c r="H28" s="288"/>
-      <c r="I28" s="288"/>
-      <c r="J28" s="287"/>
-      <c r="K28" s="286" t="s">
+      <c r="F28" s="279"/>
+      <c r="G28" s="279"/>
+      <c r="H28" s="279"/>
+      <c r="I28" s="279"/>
+      <c r="J28" s="278"/>
+      <c r="K28" s="277" t="s">
         <v>448</v>
       </c>
-      <c r="L28" s="287"/>
+      <c r="L28" s="278"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -49876,7 +57191,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE696064-E7AA-4532-A325-42E320CBBB3B}">
   <dimension ref="B2:Z11"/>
   <sheetFormatPr defaultRowHeight="21"/>
@@ -50387,5 +57702,6 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
 </file>